--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,57 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Goiás</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
+    <t>['4']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['33', '72']</t>
+  </si>
+  <si>
+    <t>['36', '58']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +321,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +830,624 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7841033</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45751.79166666666</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2">
+        <v>2.25</v>
+      </c>
+      <c r="R2">
+        <v>2.1</v>
+      </c>
+      <c r="S2">
+        <v>6</v>
+      </c>
+      <c r="T2">
+        <v>1.44</v>
+      </c>
+      <c r="U2">
+        <v>2.63</v>
+      </c>
+      <c r="V2">
+        <v>3.25</v>
+      </c>
+      <c r="W2">
+        <v>1.33</v>
+      </c>
+      <c r="X2">
+        <v>9</v>
+      </c>
+      <c r="Y2">
+        <v>1.07</v>
+      </c>
+      <c r="Z2">
+        <v>1.63</v>
+      </c>
+      <c r="AA2">
+        <v>3.65</v>
+      </c>
+      <c r="AB2">
+        <v>5.5</v>
+      </c>
+      <c r="AC2">
+        <v>1.06</v>
+      </c>
+      <c r="AD2">
+        <v>8.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.35</v>
+      </c>
+      <c r="AF2">
+        <v>3.1</v>
+      </c>
+      <c r="AG2">
+        <v>2</v>
+      </c>
+      <c r="AH2">
+        <v>1.67</v>
+      </c>
+      <c r="AI2">
+        <v>2.1</v>
+      </c>
+      <c r="AJ2">
+        <v>1.67</v>
+      </c>
+      <c r="AK2">
+        <v>1.15</v>
+      </c>
+      <c r="AL2">
+        <v>1.26</v>
+      </c>
+      <c r="AM2">
+        <v>2.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>3</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>3</v>
+      </c>
+      <c r="AV2">
+        <v>5</v>
+      </c>
+      <c r="AW2">
+        <v>12</v>
+      </c>
+      <c r="AX2">
+        <v>7</v>
+      </c>
+      <c r="AY2">
+        <v>18</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
+        <v>8</v>
+      </c>
+      <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>10</v>
+      </c>
+      <c r="BD2">
+        <v>1.44</v>
+      </c>
+      <c r="BE2">
+        <v>6.75</v>
+      </c>
+      <c r="BF2">
+        <v>3.15</v>
+      </c>
+      <c r="BG2">
+        <v>1.38</v>
+      </c>
+      <c r="BH2">
+        <v>2.8</v>
+      </c>
+      <c r="BI2">
+        <v>1.65</v>
+      </c>
+      <c r="BJ2">
+        <v>2.08</v>
+      </c>
+      <c r="BK2">
+        <v>2.02</v>
+      </c>
+      <c r="BL2">
+        <v>1.7</v>
+      </c>
+      <c r="BM2">
+        <v>2.55</v>
+      </c>
+      <c r="BN2">
+        <v>1.44</v>
+      </c>
+      <c r="BO2">
+        <v>3.4</v>
+      </c>
+      <c r="BP2">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7841035</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45751.875</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3">
+        <v>3.5</v>
+      </c>
+      <c r="R3">
+        <v>2.05</v>
+      </c>
+      <c r="S3">
+        <v>3.25</v>
+      </c>
+      <c r="T3">
+        <v>1.44</v>
+      </c>
+      <c r="U3">
+        <v>2.63</v>
+      </c>
+      <c r="V3">
+        <v>3.4</v>
+      </c>
+      <c r="W3">
+        <v>1.3</v>
+      </c>
+      <c r="X3">
+        <v>10</v>
+      </c>
+      <c r="Y3">
+        <v>1.06</v>
+      </c>
+      <c r="Z3">
+        <v>2.81</v>
+      </c>
+      <c r="AA3">
+        <v>3.13</v>
+      </c>
+      <c r="AB3">
+        <v>2.53</v>
+      </c>
+      <c r="AC3">
+        <v>1.07</v>
+      </c>
+      <c r="AD3">
+        <v>8</v>
+      </c>
+      <c r="AE3">
+        <v>1.38</v>
+      </c>
+      <c r="AF3">
+        <v>3</v>
+      </c>
+      <c r="AG3">
+        <v>2.1</v>
+      </c>
+      <c r="AH3">
+        <v>1.67</v>
+      </c>
+      <c r="AI3">
+        <v>1.83</v>
+      </c>
+      <c r="AJ3">
+        <v>1.83</v>
+      </c>
+      <c r="AK3">
+        <v>1.51</v>
+      </c>
+      <c r="AL3">
+        <v>1.32</v>
+      </c>
+      <c r="AM3">
+        <v>1.42</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>3</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>3</v>
+      </c>
+      <c r="AV3">
+        <v>3</v>
+      </c>
+      <c r="AW3">
+        <v>10</v>
+      </c>
+      <c r="AX3">
+        <v>7</v>
+      </c>
+      <c r="AY3">
+        <v>16</v>
+      </c>
+      <c r="AZ3">
+        <v>12</v>
+      </c>
+      <c r="BA3">
+        <v>5</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>5</v>
+      </c>
+      <c r="BD3">
+        <v>2.15</v>
+      </c>
+      <c r="BE3">
+        <v>6.25</v>
+      </c>
+      <c r="BF3">
+        <v>1.88</v>
+      </c>
+      <c r="BG3">
+        <v>1.4</v>
+      </c>
+      <c r="BH3">
+        <v>2.7</v>
+      </c>
+      <c r="BI3">
+        <v>1.68</v>
+      </c>
+      <c r="BJ3">
+        <v>2.05</v>
+      </c>
+      <c r="BK3">
+        <v>2.07</v>
+      </c>
+      <c r="BL3">
+        <v>1.67</v>
+      </c>
+      <c r="BM3">
+        <v>2.65</v>
+      </c>
+      <c r="BN3">
+        <v>1.41</v>
+      </c>
+      <c r="BO3">
+        <v>3.45</v>
+      </c>
+      <c r="BP3">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7841037</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45751.875</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q4">
+        <v>2.5</v>
+      </c>
+      <c r="R4">
+        <v>2.05</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <v>1.5</v>
+      </c>
+      <c r="U4">
+        <v>2.5</v>
+      </c>
+      <c r="V4">
+        <v>3.4</v>
+      </c>
+      <c r="W4">
+        <v>1.3</v>
+      </c>
+      <c r="X4">
+        <v>10</v>
+      </c>
+      <c r="Y4">
+        <v>1.06</v>
+      </c>
+      <c r="Z4">
+        <v>1.79</v>
+      </c>
+      <c r="AA4">
+        <v>3.34</v>
+      </c>
+      <c r="AB4">
+        <v>4.75</v>
+      </c>
+      <c r="AC4">
+        <v>1.08</v>
+      </c>
+      <c r="AD4">
+        <v>7.5</v>
+      </c>
+      <c r="AE4">
+        <v>1.4</v>
+      </c>
+      <c r="AF4">
+        <v>2.88</v>
+      </c>
+      <c r="AG4">
+        <v>2.09</v>
+      </c>
+      <c r="AH4">
+        <v>1.71</v>
+      </c>
+      <c r="AI4">
+        <v>2</v>
+      </c>
+      <c r="AJ4">
+        <v>1.73</v>
+      </c>
+      <c r="AK4">
+        <v>1.21</v>
+      </c>
+      <c r="AL4">
+        <v>1.3</v>
+      </c>
+      <c r="AM4">
+        <v>1.9</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>3</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>8</v>
+      </c>
+      <c r="AW4">
+        <v>11</v>
+      </c>
+      <c r="AX4">
+        <v>6</v>
+      </c>
+      <c r="AY4">
+        <v>18</v>
+      </c>
+      <c r="AZ4">
+        <v>16</v>
+      </c>
+      <c r="BA4">
+        <v>6</v>
+      </c>
+      <c r="BB4">
+        <v>6</v>
+      </c>
+      <c r="BC4">
+        <v>12</v>
+      </c>
+      <c r="BD4">
+        <v>1.54</v>
+      </c>
+      <c r="BE4">
+        <v>6.75</v>
+      </c>
+      <c r="BF4">
+        <v>2.7</v>
+      </c>
+      <c r="BG4">
+        <v>1.38</v>
+      </c>
+      <c r="BH4">
+        <v>2.8</v>
+      </c>
+      <c r="BI4">
+        <v>1.64</v>
+      </c>
+      <c r="BJ4">
+        <v>2.12</v>
+      </c>
+      <c r="BK4">
+        <v>2</v>
+      </c>
+      <c r="BL4">
+        <v>1.71</v>
+      </c>
+      <c r="BM4">
+        <v>2.55</v>
+      </c>
+      <c r="BN4">
+        <v>1.44</v>
+      </c>
+      <c r="BO4">
+        <v>3.4</v>
+      </c>
+      <c r="BP4">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -235,6 +235,15 @@
     <t>Criciúma</t>
   </si>
   <si>
+    <t>Coritiba</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
     <t>Amazonas</t>
   </si>
   <si>
@@ -244,6 +253,15 @@
     <t>Operário PR</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>['4']</t>
   </si>
   <si>
@@ -251,6 +269,15 @@
   </si>
   <si>
     <t>['11']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
+    <t>['10']</t>
+  </si>
+  <si>
+    <t>['82']</t>
   </si>
   <si>
     <t>[]</t>
@@ -621,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP4"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -853,7 +880,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -874,10 +901,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1059,7 +1086,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1080,10 +1107,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1188,7 +1215,7 @@
         <v>7</v>
       </c>
       <c r="AY3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ3">
         <v>12</v>
@@ -1265,7 +1292,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1286,10 +1313,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1446,6 +1473,624 @@
       </c>
       <c r="BP4">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7841032</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45752.66666666666</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q5">
+        <v>2.3</v>
+      </c>
+      <c r="R5">
+        <v>2.1</v>
+      </c>
+      <c r="S5">
+        <v>5.5</v>
+      </c>
+      <c r="T5">
+        <v>1.44</v>
+      </c>
+      <c r="U5">
+        <v>2.63</v>
+      </c>
+      <c r="V5">
+        <v>3.25</v>
+      </c>
+      <c r="W5">
+        <v>1.33</v>
+      </c>
+      <c r="X5">
+        <v>9</v>
+      </c>
+      <c r="Y5">
+        <v>1.07</v>
+      </c>
+      <c r="Z5">
+        <v>1.61</v>
+      </c>
+      <c r="AA5">
+        <v>3.7</v>
+      </c>
+      <c r="AB5">
+        <v>5.6</v>
+      </c>
+      <c r="AC5">
+        <v>1.06</v>
+      </c>
+      <c r="AD5">
+        <v>8.5</v>
+      </c>
+      <c r="AE5">
+        <v>1.35</v>
+      </c>
+      <c r="AF5">
+        <v>3.1</v>
+      </c>
+      <c r="AG5">
+        <v>1.85</v>
+      </c>
+      <c r="AH5">
+        <v>1.8</v>
+      </c>
+      <c r="AI5">
+        <v>2</v>
+      </c>
+      <c r="AJ5">
+        <v>1.73</v>
+      </c>
+      <c r="AK5">
+        <v>1.17</v>
+      </c>
+      <c r="AL5">
+        <v>1.26</v>
+      </c>
+      <c r="AM5">
+        <v>2.15</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>3</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>10</v>
+      </c>
+      <c r="AX5">
+        <v>5</v>
+      </c>
+      <c r="AY5">
+        <v>15</v>
+      </c>
+      <c r="AZ5">
+        <v>5</v>
+      </c>
+      <c r="BA5">
+        <v>11</v>
+      </c>
+      <c r="BB5">
+        <v>1</v>
+      </c>
+      <c r="BC5">
+        <v>12</v>
+      </c>
+      <c r="BD5">
+        <v>1.37</v>
+      </c>
+      <c r="BE5">
+        <v>7.5</v>
+      </c>
+      <c r="BF5">
+        <v>3.8</v>
+      </c>
+      <c r="BG5">
+        <v>1.22</v>
+      </c>
+      <c r="BH5">
+        <v>3.7</v>
+      </c>
+      <c r="BI5">
+        <v>1.33</v>
+      </c>
+      <c r="BJ5">
+        <v>2.9</v>
+      </c>
+      <c r="BK5">
+        <v>1.6</v>
+      </c>
+      <c r="BL5">
+        <v>2.1</v>
+      </c>
+      <c r="BM5">
+        <v>2.05</v>
+      </c>
+      <c r="BN5">
+        <v>1.65</v>
+      </c>
+      <c r="BO5">
+        <v>2.7</v>
+      </c>
+      <c r="BP5">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7841038</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45752.66666666666</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q6">
+        <v>2.5</v>
+      </c>
+      <c r="R6">
+        <v>2.05</v>
+      </c>
+      <c r="S6">
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <v>1.5</v>
+      </c>
+      <c r="U6">
+        <v>2.5</v>
+      </c>
+      <c r="V6">
+        <v>3.4</v>
+      </c>
+      <c r="W6">
+        <v>1.3</v>
+      </c>
+      <c r="X6">
+        <v>10</v>
+      </c>
+      <c r="Y6">
+        <v>1.06</v>
+      </c>
+      <c r="Z6">
+        <v>1.76</v>
+      </c>
+      <c r="AA6">
+        <v>3.47</v>
+      </c>
+      <c r="AB6">
+        <v>4.7</v>
+      </c>
+      <c r="AC6">
+        <v>1.08</v>
+      </c>
+      <c r="AD6">
+        <v>7.5</v>
+      </c>
+      <c r="AE6">
+        <v>1.42</v>
+      </c>
+      <c r="AF6">
+        <v>2.8</v>
+      </c>
+      <c r="AG6">
+        <v>2.2</v>
+      </c>
+      <c r="AH6">
+        <v>1.55</v>
+      </c>
+      <c r="AI6">
+        <v>2</v>
+      </c>
+      <c r="AJ6">
+        <v>1.73</v>
+      </c>
+      <c r="AK6">
+        <v>1.21</v>
+      </c>
+      <c r="AL6">
+        <v>1.3</v>
+      </c>
+      <c r="AM6">
+        <v>1.9</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>10</v>
+      </c>
+      <c r="AV6">
+        <v>12</v>
+      </c>
+      <c r="AW6">
+        <v>5</v>
+      </c>
+      <c r="AX6">
+        <v>13</v>
+      </c>
+      <c r="AY6">
+        <v>19</v>
+      </c>
+      <c r="AZ6">
+        <v>26</v>
+      </c>
+      <c r="BA6">
+        <v>3</v>
+      </c>
+      <c r="BB6">
+        <v>6</v>
+      </c>
+      <c r="BC6">
+        <v>9</v>
+      </c>
+      <c r="BD6">
+        <v>1.49</v>
+      </c>
+      <c r="BE6">
+        <v>7</v>
+      </c>
+      <c r="BF6">
+        <v>3.2</v>
+      </c>
+      <c r="BG6">
+        <v>1.22</v>
+      </c>
+      <c r="BH6">
+        <v>3.7</v>
+      </c>
+      <c r="BI6">
+        <v>1.32</v>
+      </c>
+      <c r="BJ6">
+        <v>3</v>
+      </c>
+      <c r="BK6">
+        <v>1.57</v>
+      </c>
+      <c r="BL6">
+        <v>2.15</v>
+      </c>
+      <c r="BM6">
+        <v>1.98</v>
+      </c>
+      <c r="BN6">
+        <v>1.68</v>
+      </c>
+      <c r="BO6">
+        <v>2.6</v>
+      </c>
+      <c r="BP6">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7841039</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45752.77083333334</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7">
+        <v>2.25</v>
+      </c>
+      <c r="R7">
+        <v>2.2</v>
+      </c>
+      <c r="S7">
+        <v>6</v>
+      </c>
+      <c r="T7">
+        <v>1.44</v>
+      </c>
+      <c r="U7">
+        <v>2.63</v>
+      </c>
+      <c r="V7">
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <v>1.36</v>
+      </c>
+      <c r="X7">
+        <v>9</v>
+      </c>
+      <c r="Y7">
+        <v>1.07</v>
+      </c>
+      <c r="Z7">
+        <v>1.61</v>
+      </c>
+      <c r="AA7">
+        <v>3.77</v>
+      </c>
+      <c r="AB7">
+        <v>5.5</v>
+      </c>
+      <c r="AC7">
+        <v>1.06</v>
+      </c>
+      <c r="AD7">
+        <v>8.5</v>
+      </c>
+      <c r="AE7">
+        <v>1.35</v>
+      </c>
+      <c r="AF7">
+        <v>3.1</v>
+      </c>
+      <c r="AG7">
+        <v>1.98</v>
+      </c>
+      <c r="AH7">
+        <v>1.77</v>
+      </c>
+      <c r="AI7">
+        <v>2</v>
+      </c>
+      <c r="AJ7">
+        <v>1.73</v>
+      </c>
+      <c r="AK7">
+        <v>1.15</v>
+      </c>
+      <c r="AL7">
+        <v>1.26</v>
+      </c>
+      <c r="AM7">
+        <v>2.2</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>7</v>
+      </c>
+      <c r="AV7">
+        <v>2</v>
+      </c>
+      <c r="AW7">
+        <v>11</v>
+      </c>
+      <c r="AX7">
+        <v>10</v>
+      </c>
+      <c r="AY7">
+        <v>18</v>
+      </c>
+      <c r="AZ7">
+        <v>14</v>
+      </c>
+      <c r="BA7">
+        <v>2</v>
+      </c>
+      <c r="BB7">
+        <v>8</v>
+      </c>
+      <c r="BC7">
+        <v>10</v>
+      </c>
+      <c r="BD7">
+        <v>1.51</v>
+      </c>
+      <c r="BE7">
+        <v>6.75</v>
+      </c>
+      <c r="BF7">
+        <v>3.1</v>
+      </c>
+      <c r="BG7">
+        <v>1.2</v>
+      </c>
+      <c r="BH7">
+        <v>3.9</v>
+      </c>
+      <c r="BI7">
+        <v>1.39</v>
+      </c>
+      <c r="BJ7">
+        <v>2.65</v>
+      </c>
+      <c r="BK7">
+        <v>1.68</v>
+      </c>
+      <c r="BL7">
+        <v>1.98</v>
+      </c>
+      <c r="BM7">
+        <v>2.15</v>
+      </c>
+      <c r="BN7">
+        <v>1.57</v>
+      </c>
+      <c r="BO7">
+        <v>2.95</v>
+      </c>
+      <c r="BP7">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -244,6 +244,15 @@
     <t>América Mineiro</t>
   </si>
   <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
+    <t>Volta Redonda</t>
+  </si>
+  <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Amazonas</t>
   </si>
   <si>
@@ -262,6 +271,15 @@
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
     <t>['4']</t>
   </si>
   <si>
@@ -280,13 +298,25 @@
     <t>['82']</t>
   </si>
   <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
     <t>['36', '58']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['13']</t>
   </si>
 </sst>
 </file>
@@ -648,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -880,7 +910,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -901,10 +931,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1086,7 +1116,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1107,10 +1137,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1292,7 +1322,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1313,10 +1343,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1498,7 +1528,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1519,10 +1549,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1636,10 +1666,10 @@
         <v>11</v>
       </c>
       <c r="BB5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD5">
         <v>1.37</v>
@@ -1704,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1725,10 +1755,10 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>2.5</v>
@@ -1910,7 +1940,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1931,10 +1961,10 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="Q7">
         <v>2.25</v>
@@ -2039,10 +2069,10 @@
         <v>10</v>
       </c>
       <c r="AY7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA7">
         <v>2</v>
@@ -2091,6 +2121,624 @@
       </c>
       <c r="BP7">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7841040</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45753.79166666666</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+      <c r="O8" t="s">
+        <v>94</v>
+      </c>
+      <c r="P8" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q8">
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <v>1.95</v>
+      </c>
+      <c r="S8">
+        <v>4</v>
+      </c>
+      <c r="T8">
+        <v>1.53</v>
+      </c>
+      <c r="U8">
+        <v>2.38</v>
+      </c>
+      <c r="V8">
+        <v>3.5</v>
+      </c>
+      <c r="W8">
+        <v>1.29</v>
+      </c>
+      <c r="X8">
+        <v>11</v>
+      </c>
+      <c r="Y8">
+        <v>1.05</v>
+      </c>
+      <c r="Z8">
+        <v>2.24</v>
+      </c>
+      <c r="AA8">
+        <v>3.01</v>
+      </c>
+      <c r="AB8">
+        <v>3.45</v>
+      </c>
+      <c r="AC8">
+        <v>1.09</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8">
+        <v>1.45</v>
+      </c>
+      <c r="AF8">
+        <v>2.7</v>
+      </c>
+      <c r="AG8">
+        <v>2.44</v>
+      </c>
+      <c r="AH8">
+        <v>1.49</v>
+      </c>
+      <c r="AI8">
+        <v>2.1</v>
+      </c>
+      <c r="AJ8">
+        <v>1.67</v>
+      </c>
+      <c r="AK8">
+        <v>1.31</v>
+      </c>
+      <c r="AL8">
+        <v>1.33</v>
+      </c>
+      <c r="AM8">
+        <v>1.63</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>11</v>
+      </c>
+      <c r="AV8">
+        <v>4</v>
+      </c>
+      <c r="AW8">
+        <v>18</v>
+      </c>
+      <c r="AX8">
+        <v>6</v>
+      </c>
+      <c r="AY8">
+        <v>37</v>
+      </c>
+      <c r="AZ8">
+        <v>13</v>
+      </c>
+      <c r="BA8">
+        <v>11</v>
+      </c>
+      <c r="BB8">
+        <v>7</v>
+      </c>
+      <c r="BC8">
+        <v>18</v>
+      </c>
+      <c r="BD8">
+        <v>1.76</v>
+      </c>
+      <c r="BE8">
+        <v>6.75</v>
+      </c>
+      <c r="BF8">
+        <v>2.3</v>
+      </c>
+      <c r="BG8">
+        <v>1.24</v>
+      </c>
+      <c r="BH8">
+        <v>3.55</v>
+      </c>
+      <c r="BI8">
+        <v>1.41</v>
+      </c>
+      <c r="BJ8">
+        <v>2.65</v>
+      </c>
+      <c r="BK8">
+        <v>1.67</v>
+      </c>
+      <c r="BL8">
+        <v>2.07</v>
+      </c>
+      <c r="BM8">
+        <v>2.02</v>
+      </c>
+      <c r="BN8">
+        <v>1.7</v>
+      </c>
+      <c r="BO8">
+        <v>2.5</v>
+      </c>
+      <c r="BP8">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7841041</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45753.79166666666</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>95</v>
+      </c>
+      <c r="P9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q9">
+        <v>3</v>
+      </c>
+      <c r="R9">
+        <v>2.05</v>
+      </c>
+      <c r="S9">
+        <v>4</v>
+      </c>
+      <c r="T9">
+        <v>1.5</v>
+      </c>
+      <c r="U9">
+        <v>2.5</v>
+      </c>
+      <c r="V9">
+        <v>3.4</v>
+      </c>
+      <c r="W9">
+        <v>1.3</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>1.06</v>
+      </c>
+      <c r="Z9">
+        <v>2.2</v>
+      </c>
+      <c r="AA9">
+        <v>3.13</v>
+      </c>
+      <c r="AB9">
+        <v>3.39</v>
+      </c>
+      <c r="AC9">
+        <v>1.07</v>
+      </c>
+      <c r="AD9">
+        <v>8</v>
+      </c>
+      <c r="AE9">
+        <v>1.4</v>
+      </c>
+      <c r="AF9">
+        <v>2.9</v>
+      </c>
+      <c r="AG9">
+        <v>1.94</v>
+      </c>
+      <c r="AH9">
+        <v>1.83</v>
+      </c>
+      <c r="AI9">
+        <v>1.91</v>
+      </c>
+      <c r="AJ9">
+        <v>1.8</v>
+      </c>
+      <c r="AK9">
+        <v>1.34</v>
+      </c>
+      <c r="AL9">
+        <v>1.32</v>
+      </c>
+      <c r="AM9">
+        <v>1.62</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>3</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>6</v>
+      </c>
+      <c r="AW9">
+        <v>14</v>
+      </c>
+      <c r="AX9">
+        <v>10</v>
+      </c>
+      <c r="AY9">
+        <v>20</v>
+      </c>
+      <c r="AZ9">
+        <v>17</v>
+      </c>
+      <c r="BA9">
+        <v>4</v>
+      </c>
+      <c r="BB9">
+        <v>6</v>
+      </c>
+      <c r="BC9">
+        <v>10</v>
+      </c>
+      <c r="BD9">
+        <v>1.77</v>
+      </c>
+      <c r="BE9">
+        <v>6.5</v>
+      </c>
+      <c r="BF9">
+        <v>2.25</v>
+      </c>
+      <c r="BG9">
+        <v>1.3</v>
+      </c>
+      <c r="BH9">
+        <v>3.15</v>
+      </c>
+      <c r="BI9">
+        <v>1.5</v>
+      </c>
+      <c r="BJ9">
+        <v>2.33</v>
+      </c>
+      <c r="BK9">
+        <v>1.84</v>
+      </c>
+      <c r="BL9">
+        <v>1.84</v>
+      </c>
+      <c r="BM9">
+        <v>2.32</v>
+      </c>
+      <c r="BN9">
+        <v>1.53</v>
+      </c>
+      <c r="BO9">
+        <v>2.95</v>
+      </c>
+      <c r="BP9">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7841036</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45753.83333333334</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10" t="s">
+        <v>96</v>
+      </c>
+      <c r="P10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>3.1</v>
+      </c>
+      <c r="R10">
+        <v>1.95</v>
+      </c>
+      <c r="S10">
+        <v>4</v>
+      </c>
+      <c r="T10">
+        <v>1.53</v>
+      </c>
+      <c r="U10">
+        <v>2.38</v>
+      </c>
+      <c r="V10">
+        <v>3.5</v>
+      </c>
+      <c r="W10">
+        <v>1.29</v>
+      </c>
+      <c r="X10">
+        <v>11</v>
+      </c>
+      <c r="Y10">
+        <v>1.05</v>
+      </c>
+      <c r="Z10">
+        <v>2.42</v>
+      </c>
+      <c r="AA10">
+        <v>2.99</v>
+      </c>
+      <c r="AB10">
+        <v>3.11</v>
+      </c>
+      <c r="AC10">
+        <v>1.09</v>
+      </c>
+      <c r="AD10">
+        <v>7</v>
+      </c>
+      <c r="AE10">
+        <v>1.45</v>
+      </c>
+      <c r="AF10">
+        <v>2.7</v>
+      </c>
+      <c r="AG10">
+        <v>2.2</v>
+      </c>
+      <c r="AH10">
+        <v>1.57</v>
+      </c>
+      <c r="AI10">
+        <v>2</v>
+      </c>
+      <c r="AJ10">
+        <v>1.73</v>
+      </c>
+      <c r="AK10">
+        <v>1.37</v>
+      </c>
+      <c r="AL10">
+        <v>1.33</v>
+      </c>
+      <c r="AM10">
+        <v>1.55</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>1</v>
+      </c>
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>5</v>
+      </c>
+      <c r="AV10">
+        <v>4</v>
+      </c>
+      <c r="AW10">
+        <v>7</v>
+      </c>
+      <c r="AX10">
+        <v>11</v>
+      </c>
+      <c r="AY10">
+        <v>16</v>
+      </c>
+      <c r="AZ10">
+        <v>20</v>
+      </c>
+      <c r="BA10">
+        <v>4</v>
+      </c>
+      <c r="BB10">
+        <v>6</v>
+      </c>
+      <c r="BC10">
+        <v>10</v>
+      </c>
+      <c r="BD10">
+        <v>1.96</v>
+      </c>
+      <c r="BE10">
+        <v>6.5</v>
+      </c>
+      <c r="BF10">
+        <v>2</v>
+      </c>
+      <c r="BG10">
+        <v>1.28</v>
+      </c>
+      <c r="BH10">
+        <v>3.2</v>
+      </c>
+      <c r="BI10">
+        <v>1.49</v>
+      </c>
+      <c r="BJ10">
+        <v>2.4</v>
+      </c>
+      <c r="BK10">
+        <v>1.79</v>
+      </c>
+      <c r="BL10">
+        <v>1.9</v>
+      </c>
+      <c r="BM10">
+        <v>2.23</v>
+      </c>
+      <c r="BN10">
+        <v>1.56</v>
+      </c>
+      <c r="BO10">
+        <v>2.85</v>
+      </c>
+      <c r="BP10">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="105">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -253,6 +253,9 @@
     <t>Avaí</t>
   </si>
   <si>
+    <t>Atlético GO</t>
+  </si>
+  <si>
     <t>Amazonas</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t>Novorizontino</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>['4']</t>
   </si>
   <si>
@@ -307,6 +313,9 @@
     <t>['25']</t>
   </si>
   <si>
+    <t>['43', '69', '79', '90+3']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -317,6 +326,9 @@
   </si>
   <si>
     <t>['13']</t>
+  </si>
+  <si>
+    <t>['9', '88']</t>
   </si>
 </sst>
 </file>
@@ -678,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -910,7 +922,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -931,10 +943,10 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q2">
         <v>2.25</v>
@@ -1116,7 +1128,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1137,10 +1149,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1322,7 +1334,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1343,10 +1355,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1528,7 +1540,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1549,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>2.3</v>
@@ -1734,7 +1746,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1755,10 +1767,10 @@
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q6">
         <v>2.5</v>
@@ -1940,7 +1952,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1961,10 +1973,10 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>2.25</v>
@@ -2146,7 +2158,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2167,10 +2179,10 @@
         <v>2</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2352,7 +2364,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2373,10 +2385,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2558,7 +2570,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2579,10 +2591,10 @@
         <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q10">
         <v>3.1</v>
@@ -2739,6 +2751,212 @@
       </c>
       <c r="BP10">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7841034</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45754.79166666666</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>4</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11">
+        <v>6</v>
+      </c>
+      <c r="O11" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11">
+        <v>2.38</v>
+      </c>
+      <c r="R11">
+        <v>2.2</v>
+      </c>
+      <c r="S11">
+        <v>5</v>
+      </c>
+      <c r="T11">
+        <v>1.4</v>
+      </c>
+      <c r="U11">
+        <v>2.75</v>
+      </c>
+      <c r="V11">
+        <v>2.75</v>
+      </c>
+      <c r="W11">
+        <v>1.4</v>
+      </c>
+      <c r="X11">
+        <v>8</v>
+      </c>
+      <c r="Y11">
+        <v>1.08</v>
+      </c>
+      <c r="Z11">
+        <v>1.72</v>
+      </c>
+      <c r="AA11">
+        <v>3.66</v>
+      </c>
+      <c r="AB11">
+        <v>4.6</v>
+      </c>
+      <c r="AC11">
+        <v>1.01</v>
+      </c>
+      <c r="AD11">
+        <v>8.9</v>
+      </c>
+      <c r="AE11">
+        <v>1.28</v>
+      </c>
+      <c r="AF11">
+        <v>3.08</v>
+      </c>
+      <c r="AG11">
+        <v>1.89</v>
+      </c>
+      <c r="AH11">
+        <v>1.85</v>
+      </c>
+      <c r="AI11">
+        <v>1.83</v>
+      </c>
+      <c r="AJ11">
+        <v>1.83</v>
+      </c>
+      <c r="AK11">
+        <v>1.21</v>
+      </c>
+      <c r="AL11">
+        <v>1.28</v>
+      </c>
+      <c r="AM11">
+        <v>1.93</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>3</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>8</v>
+      </c>
+      <c r="AV11">
+        <v>3</v>
+      </c>
+      <c r="AW11">
+        <v>6</v>
+      </c>
+      <c r="AX11">
+        <v>8</v>
+      </c>
+      <c r="AY11">
+        <v>16</v>
+      </c>
+      <c r="AZ11">
+        <v>12</v>
+      </c>
+      <c r="BA11">
+        <v>7</v>
+      </c>
+      <c r="BB11">
+        <v>4</v>
+      </c>
+      <c r="BC11">
+        <v>11</v>
+      </c>
+      <c r="BD11">
+        <v>1.4</v>
+      </c>
+      <c r="BE11">
+        <v>7.5</v>
+      </c>
+      <c r="BF11">
+        <v>3.6</v>
+      </c>
+      <c r="BG11">
+        <v>1.18</v>
+      </c>
+      <c r="BH11">
+        <v>4.1</v>
+      </c>
+      <c r="BI11">
+        <v>1.26</v>
+      </c>
+      <c r="BJ11">
+        <v>3.4</v>
+      </c>
+      <c r="BK11">
+        <v>1.47</v>
+      </c>
+      <c r="BL11">
+        <v>2.37</v>
+      </c>
+      <c r="BM11">
+        <v>1.82</v>
+      </c>
+      <c r="BN11">
+        <v>1.83</v>
+      </c>
+      <c r="BO11">
+        <v>2.35</v>
+      </c>
+      <c r="BP11">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="109">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -256,12 +256,15 @@
     <t>Atlético GO</t>
   </si>
   <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Amazonas</t>
   </si>
   <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -277,9 +280,6 @@
     <t>Remo</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Novorizontino</t>
   </si>
   <si>
@@ -316,6 +316,12 @@
     <t>['43', '69', '79', '90+3']</t>
   </si>
   <si>
+    <t>['22', '84']</t>
+  </si>
+  <si>
+    <t>['7', '70']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -329,6 +335,12 @@
   </si>
   <si>
     <t>['9', '88']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['66', '81']</t>
   </si>
 </sst>
 </file>
@@ -690,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -922,7 +934,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -1128,7 +1140,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1152,7 +1164,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1334,7 +1346,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1358,7 +1370,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1540,7 +1552,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1746,7 +1758,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1952,7 +1964,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2158,7 +2170,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2182,7 +2194,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2364,7 +2376,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2594,7 +2606,7 @@
         <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q10">
         <v>3.1</v>
@@ -2800,7 +2812,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -2957,6 +2969,418 @@
       </c>
       <c r="BP11">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7841042</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45757.79166666666</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="s">
+        <v>100</v>
+      </c>
+      <c r="P12" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q12">
+        <v>2.51</v>
+      </c>
+      <c r="R12">
+        <v>1.95</v>
+      </c>
+      <c r="S12">
+        <v>4.85</v>
+      </c>
+      <c r="T12">
+        <v>1.53</v>
+      </c>
+      <c r="U12">
+        <v>2.35</v>
+      </c>
+      <c r="V12">
+        <v>3.5</v>
+      </c>
+      <c r="W12">
+        <v>1.25</v>
+      </c>
+      <c r="X12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y12">
+        <v>1.01</v>
+      </c>
+      <c r="Z12">
+        <v>1.81</v>
+      </c>
+      <c r="AA12">
+        <v>3.25</v>
+      </c>
+      <c r="AB12">
+        <v>5.15</v>
+      </c>
+      <c r="AC12">
+        <v>1.1</v>
+      </c>
+      <c r="AD12">
+        <v>7</v>
+      </c>
+      <c r="AE12">
+        <v>1.5</v>
+      </c>
+      <c r="AF12">
+        <v>2.43</v>
+      </c>
+      <c r="AG12">
+        <v>2.5</v>
+      </c>
+      <c r="AH12">
+        <v>1.5</v>
+      </c>
+      <c r="AI12">
+        <v>2.25</v>
+      </c>
+      <c r="AJ12">
+        <v>1.57</v>
+      </c>
+      <c r="AK12">
+        <v>1.33</v>
+      </c>
+      <c r="AL12">
+        <v>1.2</v>
+      </c>
+      <c r="AM12">
+        <v>1.91</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>7</v>
+      </c>
+      <c r="AV12">
+        <v>3</v>
+      </c>
+      <c r="AW12">
+        <v>9</v>
+      </c>
+      <c r="AX12">
+        <v>7</v>
+      </c>
+      <c r="AY12">
+        <v>16</v>
+      </c>
+      <c r="AZ12">
+        <v>12</v>
+      </c>
+      <c r="BA12">
+        <v>7</v>
+      </c>
+      <c r="BB12">
+        <v>2</v>
+      </c>
+      <c r="BC12">
+        <v>9</v>
+      </c>
+      <c r="BD12">
+        <v>1.45</v>
+      </c>
+      <c r="BE12">
+        <v>7.5</v>
+      </c>
+      <c r="BF12">
+        <v>3.4</v>
+      </c>
+      <c r="BG12">
+        <v>1.17</v>
+      </c>
+      <c r="BH12">
+        <v>4.35</v>
+      </c>
+      <c r="BI12">
+        <v>1.29</v>
+      </c>
+      <c r="BJ12">
+        <v>3.15</v>
+      </c>
+      <c r="BK12">
+        <v>1.66</v>
+      </c>
+      <c r="BL12">
+        <v>2.35</v>
+      </c>
+      <c r="BM12">
+        <v>1.77</v>
+      </c>
+      <c r="BN12">
+        <v>1.86</v>
+      </c>
+      <c r="BO12">
+        <v>2.34</v>
+      </c>
+      <c r="BP12">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7841044</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45757.89583333334</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13" t="s">
+        <v>101</v>
+      </c>
+      <c r="P13" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q13">
+        <v>2.8</v>
+      </c>
+      <c r="R13">
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <v>3.7</v>
+      </c>
+      <c r="T13">
+        <v>1.58</v>
+      </c>
+      <c r="U13">
+        <v>2.42</v>
+      </c>
+      <c r="V13">
+        <v>3.34</v>
+      </c>
+      <c r="W13">
+        <v>1.22</v>
+      </c>
+      <c r="X13">
+        <v>10.5</v>
+      </c>
+      <c r="Y13">
+        <v>1.01</v>
+      </c>
+      <c r="Z13">
+        <v>2.19</v>
+      </c>
+      <c r="AA13">
+        <v>2.81</v>
+      </c>
+      <c r="AB13">
+        <v>4.04</v>
+      </c>
+      <c r="AC13">
+        <v>1.11</v>
+      </c>
+      <c r="AD13">
+        <v>6.25</v>
+      </c>
+      <c r="AE13">
+        <v>1.42</v>
+      </c>
+      <c r="AF13">
+        <v>2.53</v>
+      </c>
+      <c r="AG13">
+        <v>2.4</v>
+      </c>
+      <c r="AH13">
+        <v>1.5</v>
+      </c>
+      <c r="AI13">
+        <v>2</v>
+      </c>
+      <c r="AJ13">
+        <v>1.7</v>
+      </c>
+      <c r="AK13">
+        <v>1.42</v>
+      </c>
+      <c r="AL13">
+        <v>1.33</v>
+      </c>
+      <c r="AM13">
+        <v>1.72</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1</v>
+      </c>
+      <c r="AQ13">
+        <v>1</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>5</v>
+      </c>
+      <c r="AV13">
+        <v>3</v>
+      </c>
+      <c r="AW13">
+        <v>13</v>
+      </c>
+      <c r="AX13">
+        <v>7</v>
+      </c>
+      <c r="AY13">
+        <v>24</v>
+      </c>
+      <c r="AZ13">
+        <v>13</v>
+      </c>
+      <c r="BA13">
+        <v>7</v>
+      </c>
+      <c r="BB13">
+        <v>5</v>
+      </c>
+      <c r="BC13">
+        <v>12</v>
+      </c>
+      <c r="BD13">
+        <v>1.66</v>
+      </c>
+      <c r="BE13">
+        <v>8.1</v>
+      </c>
+      <c r="BF13">
+        <v>2.88</v>
+      </c>
+      <c r="BG13">
+        <v>1.24</v>
+      </c>
+      <c r="BH13">
+        <v>3.52</v>
+      </c>
+      <c r="BI13">
+        <v>1.41</v>
+      </c>
+      <c r="BJ13">
+        <v>2.61</v>
+      </c>
+      <c r="BK13">
+        <v>1.73</v>
+      </c>
+      <c r="BL13">
+        <v>2</v>
+      </c>
+      <c r="BM13">
+        <v>2.23</v>
+      </c>
+      <c r="BN13">
+        <v>1.58</v>
+      </c>
+      <c r="BO13">
+        <v>2.83</v>
+      </c>
+      <c r="BP13">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="208">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -514,6 +514,18 @@
     <t>['90+1']</t>
   </si>
   <si>
+    <t>['21', '90+4']</t>
+  </si>
+  <si>
+    <t>['67', '90']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -598,9 +610,6 @@
     <t>['58', '70']</t>
   </si>
   <si>
-    <t>['77']</t>
-  </si>
-  <si>
     <t>['55', '67']</t>
   </si>
   <si>
@@ -613,9 +622,6 @@
     <t>['60']</t>
   </si>
   <si>
-    <t>['63']</t>
-  </si>
-  <si>
     <t>['86']</t>
   </si>
   <si>
@@ -626,6 +632,12 @@
   </si>
   <si>
     <t>['71', '80']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
+  </si>
+  <si>
+    <t>['49']</t>
   </si>
 </sst>
 </file>
@@ -987,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP106"/>
+  <dimension ref="A1:BP111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1321,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ2">
         <v>0.2</v>
@@ -1449,7 +1461,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1655,7 +1667,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1733,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1942,7 +1954,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ5">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2479,7 +2491,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3097,7 +3109,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3178,7 +3190,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ11">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3303,7 +3315,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3381,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12">
         <v>0.8</v>
@@ -3509,7 +3521,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3715,7 +3727,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4205,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16">
         <v>1</v>
@@ -4414,7 +4426,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ17">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4539,7 +4551,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4745,7 +4757,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5029,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ20">
         <v>0</v>
@@ -5157,7 +5169,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5238,7 +5250,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5363,7 +5375,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5569,7 +5581,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5856,7 +5868,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ24">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -6187,7 +6199,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6265,10 +6277,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ26">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6471,10 +6483,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR27">
         <v>1.99</v>
@@ -6680,7 +6692,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ28">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR28">
         <v>1.84</v>
@@ -6805,7 +6817,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7092,7 +7104,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ30">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>2.86</v>
@@ -7217,7 +7229,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7916,7 +7928,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ34">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR34">
         <v>2.24</v>
@@ -8119,7 +8131,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ35">
         <v>0.83</v>
@@ -8453,7 +8465,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8531,7 +8543,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -8659,7 +8671,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -8943,7 +8955,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ39">
         <v>1.17</v>
@@ -9483,7 +9495,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9767,7 +9779,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ43">
         <v>0.8</v>
@@ -10182,7 +10194,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ45">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR45">
         <v>1.46</v>
@@ -10594,7 +10606,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ47">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR47">
         <v>2.22</v>
@@ -10719,7 +10731,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10797,10 +10809,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>2.04</v>
@@ -10925,7 +10937,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11337,7 +11349,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11543,7 +11555,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11827,7 +11839,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ53">
         <v>0.2</v>
@@ -12573,7 +12585,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12651,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57">
         <v>0.8</v>
@@ -12985,7 +12997,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13063,7 +13075,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13397,7 +13409,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13478,7 +13490,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ61">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -13603,7 +13615,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q62">
         <v>2.13</v>
@@ -13681,7 +13693,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ62">
         <v>0.67</v>
@@ -13890,7 +13902,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ63">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14093,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ64">
         <v>1.17</v>
@@ -14299,10 +14311,10 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ65">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR65">
         <v>2.13</v>
@@ -14427,7 +14439,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14508,7 +14520,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.58</v>
@@ -14633,7 +14645,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14839,7 +14851,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -14920,7 +14932,7 @@
         <v>1</v>
       </c>
       <c r="AQ68">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -15045,7 +15057,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15123,7 +15135,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69">
         <v>0.83</v>
@@ -15329,10 +15341,10 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ70">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR70">
         <v>1.26</v>
@@ -15457,7 +15469,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16281,7 +16293,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="Q75">
         <v>3.6</v>
@@ -16487,7 +16499,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16693,7 +16705,7 @@
         <v>148</v>
       </c>
       <c r="P77" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17801,7 +17813,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ82">
         <v>1</v>
@@ -18007,10 +18019,10 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ83">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR83">
         <v>1.64</v>
@@ -18213,10 +18225,10 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ84">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AR84">
         <v>1.23</v>
@@ -18341,7 +18353,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18831,10 +18843,10 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR87">
         <v>1.81</v>
@@ -18959,7 +18971,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19037,7 +19049,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ88">
         <v>1.17</v>
@@ -19165,7 +19177,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="Q89">
         <v>2.8</v>
@@ -19452,7 +19464,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ90">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR90">
         <v>1.68</v>
@@ -19577,7 +19589,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19658,7 +19670,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ91">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR91">
         <v>1.96</v>
@@ -19783,7 +19795,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -19989,7 +20001,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20401,7 +20413,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20607,7 +20619,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21637,7 +21649,7 @@
         <v>97</v>
       </c>
       <c r="P101" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q101">
         <v>3.12</v>
@@ -22461,7 +22473,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22824,6 +22836,1036 @@
       </c>
       <c r="BP106">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7841133</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45816.66666666666</v>
+      </c>
+      <c r="F107">
+        <v>11</v>
+      </c>
+      <c r="G107" t="s">
+        <v>70</v>
+      </c>
+      <c r="H107" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>2</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>2</v>
+      </c>
+      <c r="O107" t="s">
+        <v>166</v>
+      </c>
+      <c r="P107" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q107">
+        <v>2.2</v>
+      </c>
+      <c r="R107">
+        <v>1.91</v>
+      </c>
+      <c r="S107">
+        <v>4.65</v>
+      </c>
+      <c r="T107">
+        <v>1.59</v>
+      </c>
+      <c r="U107">
+        <v>2.4</v>
+      </c>
+      <c r="V107">
+        <v>3.5</v>
+      </c>
+      <c r="W107">
+        <v>1.24</v>
+      </c>
+      <c r="X107">
+        <v>10</v>
+      </c>
+      <c r="Y107">
+        <v>1.01</v>
+      </c>
+      <c r="Z107">
+        <v>1.72</v>
+      </c>
+      <c r="AA107">
+        <v>3.15</v>
+      </c>
+      <c r="AB107">
+        <v>4.5</v>
+      </c>
+      <c r="AC107">
+        <v>1.06</v>
+      </c>
+      <c r="AD107">
+        <v>6.5</v>
+      </c>
+      <c r="AE107">
+        <v>1.45</v>
+      </c>
+      <c r="AF107">
+        <v>2.4</v>
+      </c>
+      <c r="AG107">
+        <v>2.25</v>
+      </c>
+      <c r="AH107">
+        <v>1.53</v>
+      </c>
+      <c r="AI107">
+        <v>2.2</v>
+      </c>
+      <c r="AJ107">
+        <v>1.62</v>
+      </c>
+      <c r="AK107">
+        <v>1.22</v>
+      </c>
+      <c r="AL107">
+        <v>1.32</v>
+      </c>
+      <c r="AM107">
+        <v>1.95</v>
+      </c>
+      <c r="AN107">
+        <v>2.6</v>
+      </c>
+      <c r="AO107">
+        <v>0.4</v>
+      </c>
+      <c r="AP107">
+        <v>2.67</v>
+      </c>
+      <c r="AQ107">
+        <v>0.33</v>
+      </c>
+      <c r="AR107">
+        <v>1.73</v>
+      </c>
+      <c r="AS107">
+        <v>1.45</v>
+      </c>
+      <c r="AT107">
+        <v>3.18</v>
+      </c>
+      <c r="AU107">
+        <v>3</v>
+      </c>
+      <c r="AV107">
+        <v>2</v>
+      </c>
+      <c r="AW107">
+        <v>3</v>
+      </c>
+      <c r="AX107">
+        <v>6</v>
+      </c>
+      <c r="AY107">
+        <v>6</v>
+      </c>
+      <c r="AZ107">
+        <v>8</v>
+      </c>
+      <c r="BA107">
+        <v>2</v>
+      </c>
+      <c r="BB107">
+        <v>6</v>
+      </c>
+      <c r="BC107">
+        <v>8</v>
+      </c>
+      <c r="BD107">
+        <v>1.6</v>
+      </c>
+      <c r="BE107">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF107">
+        <v>3.36</v>
+      </c>
+      <c r="BG107">
+        <v>1.18</v>
+      </c>
+      <c r="BH107">
+        <v>4.33</v>
+      </c>
+      <c r="BI107">
+        <v>1.25</v>
+      </c>
+      <c r="BJ107">
+        <v>3.5</v>
+      </c>
+      <c r="BK107">
+        <v>1.7</v>
+      </c>
+      <c r="BL107">
+        <v>2.45</v>
+      </c>
+      <c r="BM107">
+        <v>1.85</v>
+      </c>
+      <c r="BN107">
+        <v>1.9</v>
+      </c>
+      <c r="BO107">
+        <v>2.3</v>
+      </c>
+      <c r="BP107">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7841132</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45816.75</v>
+      </c>
+      <c r="F108">
+        <v>11</v>
+      </c>
+      <c r="G108" t="s">
+        <v>80</v>
+      </c>
+      <c r="H108" t="s">
+        <v>79</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108" t="s">
+        <v>97</v>
+      </c>
+      <c r="P108" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q108">
+        <v>2.47</v>
+      </c>
+      <c r="R108">
+        <v>1.99</v>
+      </c>
+      <c r="S108">
+        <v>4.7</v>
+      </c>
+      <c r="T108">
+        <v>1.45</v>
+      </c>
+      <c r="U108">
+        <v>2.69</v>
+      </c>
+      <c r="V108">
+        <v>3.45</v>
+      </c>
+      <c r="W108">
+        <v>1.32</v>
+      </c>
+      <c r="X108">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y108">
+        <v>1.05</v>
+      </c>
+      <c r="Z108">
+        <v>1.8</v>
+      </c>
+      <c r="AA108">
+        <v>3.2</v>
+      </c>
+      <c r="AB108">
+        <v>4.2</v>
+      </c>
+      <c r="AC108">
+        <v>1.03</v>
+      </c>
+      <c r="AD108">
+        <v>6.5</v>
+      </c>
+      <c r="AE108">
+        <v>1.4</v>
+      </c>
+      <c r="AF108">
+        <v>2.67</v>
+      </c>
+      <c r="AG108">
+        <v>2.25</v>
+      </c>
+      <c r="AH108">
+        <v>1.61</v>
+      </c>
+      <c r="AI108">
+        <v>2.25</v>
+      </c>
+      <c r="AJ108">
+        <v>1.62</v>
+      </c>
+      <c r="AK108">
+        <v>1.18</v>
+      </c>
+      <c r="AL108">
+        <v>1.3</v>
+      </c>
+      <c r="AM108">
+        <v>1.95</v>
+      </c>
+      <c r="AN108">
+        <v>2</v>
+      </c>
+      <c r="AO108">
+        <v>0.6</v>
+      </c>
+      <c r="AP108">
+        <v>1.67</v>
+      </c>
+      <c r="AQ108">
+        <v>1</v>
+      </c>
+      <c r="AR108">
+        <v>1.63</v>
+      </c>
+      <c r="AS108">
+        <v>1.54</v>
+      </c>
+      <c r="AT108">
+        <v>3.17</v>
+      </c>
+      <c r="AU108">
+        <v>-1</v>
+      </c>
+      <c r="AV108">
+        <v>-1</v>
+      </c>
+      <c r="AW108">
+        <v>-1</v>
+      </c>
+      <c r="AX108">
+        <v>-1</v>
+      </c>
+      <c r="AY108">
+        <v>-1</v>
+      </c>
+      <c r="AZ108">
+        <v>-1</v>
+      </c>
+      <c r="BA108">
+        <v>-1</v>
+      </c>
+      <c r="BB108">
+        <v>-1</v>
+      </c>
+      <c r="BC108">
+        <v>-1</v>
+      </c>
+      <c r="BD108">
+        <v>1.5</v>
+      </c>
+      <c r="BE108">
+        <v>7</v>
+      </c>
+      <c r="BF108">
+        <v>3.24</v>
+      </c>
+      <c r="BG108">
+        <v>1.2</v>
+      </c>
+      <c r="BH108">
+        <v>3.9</v>
+      </c>
+      <c r="BI108">
+        <v>1.41</v>
+      </c>
+      <c r="BJ108">
+        <v>2.78</v>
+      </c>
+      <c r="BK108">
+        <v>1.64</v>
+      </c>
+      <c r="BL108">
+        <v>2.17</v>
+      </c>
+      <c r="BM108">
+        <v>2.02</v>
+      </c>
+      <c r="BN108">
+        <v>1.74</v>
+      </c>
+      <c r="BO108">
+        <v>2.52</v>
+      </c>
+      <c r="BP108">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7841135</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45816.85416666666</v>
+      </c>
+      <c r="F109">
+        <v>11</v>
+      </c>
+      <c r="G109" t="s">
+        <v>88</v>
+      </c>
+      <c r="H109" t="s">
+        <v>86</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>2</v>
+      </c>
+      <c r="M109">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>3</v>
+      </c>
+      <c r="O109" t="s">
+        <v>167</v>
+      </c>
+      <c r="P109" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q109">
+        <v>3.19</v>
+      </c>
+      <c r="R109">
+        <v>1.85</v>
+      </c>
+      <c r="S109">
+        <v>4.2</v>
+      </c>
+      <c r="T109">
+        <v>1.56</v>
+      </c>
+      <c r="U109">
+        <v>2.28</v>
+      </c>
+      <c r="V109">
+        <v>3.7</v>
+      </c>
+      <c r="W109">
+        <v>1.25</v>
+      </c>
+      <c r="X109">
+        <v>12</v>
+      </c>
+      <c r="Y109">
+        <v>1.05</v>
+      </c>
+      <c r="Z109">
+        <v>2.32</v>
+      </c>
+      <c r="AA109">
+        <v>2.91</v>
+      </c>
+      <c r="AB109">
+        <v>3.4</v>
+      </c>
+      <c r="AC109">
+        <v>1.1</v>
+      </c>
+      <c r="AD109">
+        <v>7</v>
+      </c>
+      <c r="AE109">
+        <v>1.57</v>
+      </c>
+      <c r="AF109">
+        <v>2.43</v>
+      </c>
+      <c r="AG109">
+        <v>2.6</v>
+      </c>
+      <c r="AH109">
+        <v>1.41</v>
+      </c>
+      <c r="AI109">
+        <v>2.16</v>
+      </c>
+      <c r="AJ109">
+        <v>1.68</v>
+      </c>
+      <c r="AK109">
+        <v>1.41</v>
+      </c>
+      <c r="AL109">
+        <v>1.37</v>
+      </c>
+      <c r="AM109">
+        <v>1.62</v>
+      </c>
+      <c r="AN109">
+        <v>2.6</v>
+      </c>
+      <c r="AO109">
+        <v>1.2</v>
+      </c>
+      <c r="AP109">
+        <v>2.67</v>
+      </c>
+      <c r="AQ109">
+        <v>1</v>
+      </c>
+      <c r="AR109">
+        <v>1.3</v>
+      </c>
+      <c r="AS109">
+        <v>1.45</v>
+      </c>
+      <c r="AT109">
+        <v>2.75</v>
+      </c>
+      <c r="AU109">
+        <v>4</v>
+      </c>
+      <c r="AV109">
+        <v>4</v>
+      </c>
+      <c r="AW109">
+        <v>8</v>
+      </c>
+      <c r="AX109">
+        <v>6</v>
+      </c>
+      <c r="AY109">
+        <v>12</v>
+      </c>
+      <c r="AZ109">
+        <v>10</v>
+      </c>
+      <c r="BA109">
+        <v>6</v>
+      </c>
+      <c r="BB109">
+        <v>0</v>
+      </c>
+      <c r="BC109">
+        <v>6</v>
+      </c>
+      <c r="BD109">
+        <v>2.1</v>
+      </c>
+      <c r="BE109">
+        <v>7.4</v>
+      </c>
+      <c r="BF109">
+        <v>2.05</v>
+      </c>
+      <c r="BG109">
+        <v>1.22</v>
+      </c>
+      <c r="BH109">
+        <v>3.65</v>
+      </c>
+      <c r="BI109">
+        <v>1.4</v>
+      </c>
+      <c r="BJ109">
+        <v>2.87</v>
+      </c>
+      <c r="BK109">
+        <v>1.61</v>
+      </c>
+      <c r="BL109">
+        <v>2.23</v>
+      </c>
+      <c r="BM109">
+        <v>1.97</v>
+      </c>
+      <c r="BN109">
+        <v>1.78</v>
+      </c>
+      <c r="BO109">
+        <v>2.45</v>
+      </c>
+      <c r="BP109">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7841137</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45817.79166666666</v>
+      </c>
+      <c r="F110">
+        <v>11</v>
+      </c>
+      <c r="G110" t="s">
+        <v>72</v>
+      </c>
+      <c r="H110" t="s">
+        <v>83</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="s">
+        <v>168</v>
+      </c>
+      <c r="P110" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q110">
+        <v>3</v>
+      </c>
+      <c r="R110">
+        <v>1.83</v>
+      </c>
+      <c r="S110">
+        <v>4.3</v>
+      </c>
+      <c r="T110">
+        <v>1.64</v>
+      </c>
+      <c r="U110">
+        <v>2.1</v>
+      </c>
+      <c r="V110">
+        <v>4.25</v>
+      </c>
+      <c r="W110">
+        <v>1.2</v>
+      </c>
+      <c r="X110">
+        <v>7.8</v>
+      </c>
+      <c r="Y110">
+        <v>1.02</v>
+      </c>
+      <c r="Z110">
+        <v>2.2</v>
+      </c>
+      <c r="AA110">
+        <v>2.88</v>
+      </c>
+      <c r="AB110">
+        <v>3.25</v>
+      </c>
+      <c r="AC110">
+        <v>1.07</v>
+      </c>
+      <c r="AD110">
+        <v>5.25</v>
+      </c>
+      <c r="AE110">
+        <v>1.66</v>
+      </c>
+      <c r="AF110">
+        <v>2.1</v>
+      </c>
+      <c r="AG110">
+        <v>2.98</v>
+      </c>
+      <c r="AH110">
+        <v>1.4</v>
+      </c>
+      <c r="AI110">
+        <v>2.45</v>
+      </c>
+      <c r="AJ110">
+        <v>1.53</v>
+      </c>
+      <c r="AK110">
+        <v>1.28</v>
+      </c>
+      <c r="AL110">
+        <v>1.35</v>
+      </c>
+      <c r="AM110">
+        <v>1.57</v>
+      </c>
+      <c r="AN110">
+        <v>1</v>
+      </c>
+      <c r="AO110">
+        <v>0.8</v>
+      </c>
+      <c r="AP110">
+        <v>1.33</v>
+      </c>
+      <c r="AQ110">
+        <v>0.67</v>
+      </c>
+      <c r="AR110">
+        <v>2.01</v>
+      </c>
+      <c r="AS110">
+        <v>1.25</v>
+      </c>
+      <c r="AT110">
+        <v>3.26</v>
+      </c>
+      <c r="AU110">
+        <v>6</v>
+      </c>
+      <c r="AV110">
+        <v>0</v>
+      </c>
+      <c r="AW110">
+        <v>13</v>
+      </c>
+      <c r="AX110">
+        <v>14</v>
+      </c>
+      <c r="AY110">
+        <v>19</v>
+      </c>
+      <c r="AZ110">
+        <v>14</v>
+      </c>
+      <c r="BA110">
+        <v>16</v>
+      </c>
+      <c r="BB110">
+        <v>3</v>
+      </c>
+      <c r="BC110">
+        <v>19</v>
+      </c>
+      <c r="BD110">
+        <v>1.54</v>
+      </c>
+      <c r="BE110">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF110">
+        <v>3</v>
+      </c>
+      <c r="BG110">
+        <v>1.24</v>
+      </c>
+      <c r="BH110">
+        <v>4.15</v>
+      </c>
+      <c r="BI110">
+        <v>1.3</v>
+      </c>
+      <c r="BJ110">
+        <v>3.08</v>
+      </c>
+      <c r="BK110">
+        <v>1.77</v>
+      </c>
+      <c r="BL110">
+        <v>2.25</v>
+      </c>
+      <c r="BM110">
+        <v>1.88</v>
+      </c>
+      <c r="BN110">
+        <v>1.82</v>
+      </c>
+      <c r="BO110">
+        <v>2.55</v>
+      </c>
+      <c r="BP110">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7841138</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45817.8125</v>
+      </c>
+      <c r="F111">
+        <v>11</v>
+      </c>
+      <c r="G111" t="s">
+        <v>84</v>
+      </c>
+      <c r="H111" t="s">
+        <v>87</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>169</v>
+      </c>
+      <c r="P111" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q111">
+        <v>2.86</v>
+      </c>
+      <c r="R111">
+        <v>1.95</v>
+      </c>
+      <c r="S111">
+        <v>4</v>
+      </c>
+      <c r="T111">
+        <v>1.57</v>
+      </c>
+      <c r="U111">
+        <v>2.35</v>
+      </c>
+      <c r="V111">
+        <v>3.6</v>
+      </c>
+      <c r="W111">
+        <v>1.25</v>
+      </c>
+      <c r="X111">
+        <v>9</v>
+      </c>
+      <c r="Y111">
+        <v>1.02</v>
+      </c>
+      <c r="Z111">
+        <v>2.3</v>
+      </c>
+      <c r="AA111">
+        <v>2.85</v>
+      </c>
+      <c r="AB111">
+        <v>3.4</v>
+      </c>
+      <c r="AC111">
+        <v>1.06</v>
+      </c>
+      <c r="AD111">
+        <v>5.75</v>
+      </c>
+      <c r="AE111">
+        <v>1.5</v>
+      </c>
+      <c r="AF111">
+        <v>2.4</v>
+      </c>
+      <c r="AG111">
+        <v>2.7</v>
+      </c>
+      <c r="AH111">
+        <v>1.45</v>
+      </c>
+      <c r="AI111">
+        <v>2.2</v>
+      </c>
+      <c r="AJ111">
+        <v>1.62</v>
+      </c>
+      <c r="AK111">
+        <v>1.4</v>
+      </c>
+      <c r="AL111">
+        <v>1.34</v>
+      </c>
+      <c r="AM111">
+        <v>1.6</v>
+      </c>
+      <c r="AN111">
+        <v>1.2</v>
+      </c>
+      <c r="AO111">
+        <v>0.6</v>
+      </c>
+      <c r="AP111">
+        <v>1.5</v>
+      </c>
+      <c r="AQ111">
+        <v>0.5</v>
+      </c>
+      <c r="AR111">
+        <v>1.71</v>
+      </c>
+      <c r="AS111">
+        <v>1.22</v>
+      </c>
+      <c r="AT111">
+        <v>2.93</v>
+      </c>
+      <c r="AU111">
+        <v>5</v>
+      </c>
+      <c r="AV111">
+        <v>4</v>
+      </c>
+      <c r="AW111">
+        <v>3</v>
+      </c>
+      <c r="AX111">
+        <v>10</v>
+      </c>
+      <c r="AY111">
+        <v>8</v>
+      </c>
+      <c r="AZ111">
+        <v>14</v>
+      </c>
+      <c r="BA111">
+        <v>2</v>
+      </c>
+      <c r="BB111">
+        <v>8</v>
+      </c>
+      <c r="BC111">
+        <v>10</v>
+      </c>
+      <c r="BD111">
+        <v>1.65</v>
+      </c>
+      <c r="BE111">
+        <v>7.8</v>
+      </c>
+      <c r="BF111">
+        <v>2.46</v>
+      </c>
+      <c r="BG111">
+        <v>1.26</v>
+      </c>
+      <c r="BH111">
+        <v>3.85</v>
+      </c>
+      <c r="BI111">
+        <v>1.31</v>
+      </c>
+      <c r="BJ111">
+        <v>2.92</v>
+      </c>
+      <c r="BK111">
+        <v>1.58</v>
+      </c>
+      <c r="BL111">
+        <v>2.18</v>
+      </c>
+      <c r="BM111">
+        <v>1.99</v>
+      </c>
+      <c r="BN111">
+        <v>1.78</v>
+      </c>
+      <c r="BO111">
+        <v>2.53</v>
+      </c>
+      <c r="BP111">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -23614,13 +23614,13 @@
         <v>14</v>
       </c>
       <c r="BA110">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BB110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC110">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BD110">
         <v>1.54</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="209">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,9 @@
     <t>['63']</t>
   </si>
   <si>
+    <t>['90']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -551,9 +554,6 @@
   </si>
   <si>
     <t>['52', '90+1']</t>
-  </si>
-  <si>
-    <t>['90']</t>
   </si>
   <si>
     <t>['15']</t>
@@ -638,6 +638,9 @@
   </si>
   <si>
     <t>['49']</t>
+  </si>
+  <si>
+    <t>['81', '90+4', '60']</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1461,7 +1464,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1539,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ3">
         <v>0.8</v>
@@ -1667,7 +1670,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2366,7 +2369,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ7">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2491,7 +2494,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3109,7 +3112,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3315,7 +3318,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3521,7 +3524,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3727,7 +3730,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4011,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>0.33</v>
@@ -4551,7 +4554,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4757,7 +4760,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5044,7 +5047,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5169,7 +5172,7 @@
         <v>92</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="Q21">
         <v>3.5</v>
@@ -5659,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ23">
         <v>0.67</v>
@@ -7719,10 +7722,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR33">
         <v>1.59</v>
@@ -9985,7 +9988,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>0.67</v>
@@ -10400,7 +10403,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR46">
         <v>1.53</v>
@@ -11015,7 +11018,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ49">
         <v>0.83</v>
@@ -12666,7 +12669,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ57">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -12872,7 +12875,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR58">
         <v>1.48</v>
@@ -13615,7 +13618,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="Q62">
         <v>2.13</v>
@@ -16168,7 +16171,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ74">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR74">
         <v>1.6</v>
@@ -16371,7 +16374,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>0.8</v>
@@ -17195,7 +17198,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ79">
         <v>2</v>
@@ -17610,7 +17613,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ81">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR81">
         <v>1.39</v>
@@ -19876,7 +19879,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ92">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20079,7 +20082,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ93">
         <v>1.6</v>
@@ -21318,7 +21321,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ99">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR99">
         <v>2.28</v>
@@ -21727,7 +21730,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AQ101">
         <v>0.8</v>
@@ -23866,6 +23869,418 @@
       </c>
       <c r="BP111">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7841143</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45821.79166666666</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
+        <v>83</v>
+      </c>
+      <c r="H112" t="s">
+        <v>75</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>3</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
+      <c r="O112" t="s">
+        <v>97</v>
+      </c>
+      <c r="P112" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q112">
+        <v>2.62</v>
+      </c>
+      <c r="R112">
+        <v>1.92</v>
+      </c>
+      <c r="S112">
+        <v>5.3</v>
+      </c>
+      <c r="T112">
+        <v>1.58</v>
+      </c>
+      <c r="U112">
+        <v>2.25</v>
+      </c>
+      <c r="V112">
+        <v>3.66</v>
+      </c>
+      <c r="W112">
+        <v>1.22</v>
+      </c>
+      <c r="X112">
+        <v>10</v>
+      </c>
+      <c r="Y112">
+        <v>1</v>
+      </c>
+      <c r="Z112">
+        <v>1.91</v>
+      </c>
+      <c r="AA112">
+        <v>3</v>
+      </c>
+      <c r="AB112">
+        <v>4.25</v>
+      </c>
+      <c r="AC112">
+        <v>1.07</v>
+      </c>
+      <c r="AD112">
+        <v>5.75</v>
+      </c>
+      <c r="AE112">
+        <v>1.6</v>
+      </c>
+      <c r="AF112">
+        <v>2.45</v>
+      </c>
+      <c r="AG112">
+        <v>2.7</v>
+      </c>
+      <c r="AH112">
+        <v>1.43</v>
+      </c>
+      <c r="AI112">
+        <v>2.25</v>
+      </c>
+      <c r="AJ112">
+        <v>1.59</v>
+      </c>
+      <c r="AK112">
+        <v>1.28</v>
+      </c>
+      <c r="AL112">
+        <v>1.33</v>
+      </c>
+      <c r="AM112">
+        <v>1.86</v>
+      </c>
+      <c r="AN112">
+        <v>2.4</v>
+      </c>
+      <c r="AO112">
+        <v>0</v>
+      </c>
+      <c r="AP112">
+        <v>2</v>
+      </c>
+      <c r="AQ112">
+        <v>0.5</v>
+      </c>
+      <c r="AR112">
+        <v>1.8</v>
+      </c>
+      <c r="AS112">
+        <v>1.71</v>
+      </c>
+      <c r="AT112">
+        <v>3.51</v>
+      </c>
+      <c r="AU112">
+        <v>2</v>
+      </c>
+      <c r="AV112">
+        <v>7</v>
+      </c>
+      <c r="AW112">
+        <v>6</v>
+      </c>
+      <c r="AX112">
+        <v>4</v>
+      </c>
+      <c r="AY112">
+        <v>8</v>
+      </c>
+      <c r="AZ112">
+        <v>11</v>
+      </c>
+      <c r="BA112">
+        <v>4</v>
+      </c>
+      <c r="BB112">
+        <v>2</v>
+      </c>
+      <c r="BC112">
+        <v>6</v>
+      </c>
+      <c r="BD112">
+        <v>1.95</v>
+      </c>
+      <c r="BE112">
+        <v>7</v>
+      </c>
+      <c r="BF112">
+        <v>2.25</v>
+      </c>
+      <c r="BG112">
+        <v>1.15</v>
+      </c>
+      <c r="BH112">
+        <v>4.75</v>
+      </c>
+      <c r="BI112">
+        <v>1.32</v>
+      </c>
+      <c r="BJ112">
+        <v>3.05</v>
+      </c>
+      <c r="BK112">
+        <v>1.58</v>
+      </c>
+      <c r="BL112">
+        <v>2.32</v>
+      </c>
+      <c r="BM112">
+        <v>1.78</v>
+      </c>
+      <c r="BN112">
+        <v>1.95</v>
+      </c>
+      <c r="BO112">
+        <v>2.2</v>
+      </c>
+      <c r="BP112">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7841145</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45821.89930555555</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s">
+        <v>71</v>
+      </c>
+      <c r="H113" t="s">
+        <v>89</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="s">
+        <v>170</v>
+      </c>
+      <c r="P113" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q113">
+        <v>2.62</v>
+      </c>
+      <c r="R113">
+        <v>2.01</v>
+      </c>
+      <c r="S113">
+        <v>4.7</v>
+      </c>
+      <c r="T113">
+        <v>1.5</v>
+      </c>
+      <c r="U113">
+        <v>2.4</v>
+      </c>
+      <c r="V113">
+        <v>3.56</v>
+      </c>
+      <c r="W113">
+        <v>1.29</v>
+      </c>
+      <c r="X113">
+        <v>11</v>
+      </c>
+      <c r="Y113">
+        <v>1.02</v>
+      </c>
+      <c r="Z113">
+        <v>2.04</v>
+      </c>
+      <c r="AA113">
+        <v>2.95</v>
+      </c>
+      <c r="AB113">
+        <v>3.85</v>
+      </c>
+      <c r="AC113">
+        <v>1.04</v>
+      </c>
+      <c r="AD113">
+        <v>6.5</v>
+      </c>
+      <c r="AE113">
+        <v>1.5</v>
+      </c>
+      <c r="AF113">
+        <v>2.53</v>
+      </c>
+      <c r="AG113">
+        <v>2.61</v>
+      </c>
+      <c r="AH113">
+        <v>1.48</v>
+      </c>
+      <c r="AI113">
+        <v>2.1</v>
+      </c>
+      <c r="AJ113">
+        <v>1.6</v>
+      </c>
+      <c r="AK113">
+        <v>1.25</v>
+      </c>
+      <c r="AL113">
+        <v>1.32</v>
+      </c>
+      <c r="AM113">
+        <v>1.81</v>
+      </c>
+      <c r="AN113">
+        <v>0.4</v>
+      </c>
+      <c r="AO113">
+        <v>0.8</v>
+      </c>
+      <c r="AP113">
+        <v>0.83</v>
+      </c>
+      <c r="AQ113">
+        <v>0.67</v>
+      </c>
+      <c r="AR113">
+        <v>1.9</v>
+      </c>
+      <c r="AS113">
+        <v>1.16</v>
+      </c>
+      <c r="AT113">
+        <v>3.06</v>
+      </c>
+      <c r="AU113">
+        <v>4</v>
+      </c>
+      <c r="AV113">
+        <v>7</v>
+      </c>
+      <c r="AW113">
+        <v>14</v>
+      </c>
+      <c r="AX113">
+        <v>5</v>
+      </c>
+      <c r="AY113">
+        <v>18</v>
+      </c>
+      <c r="AZ113">
+        <v>12</v>
+      </c>
+      <c r="BA113">
+        <v>8</v>
+      </c>
+      <c r="BB113">
+        <v>5</v>
+      </c>
+      <c r="BC113">
+        <v>13</v>
+      </c>
+      <c r="BD113">
+        <v>1.43</v>
+      </c>
+      <c r="BE113">
+        <v>7.25</v>
+      </c>
+      <c r="BF113">
+        <v>3.44</v>
+      </c>
+      <c r="BG113">
+        <v>1.22</v>
+      </c>
+      <c r="BH113">
+        <v>3.9</v>
+      </c>
+      <c r="BI113">
+        <v>1.32</v>
+      </c>
+      <c r="BJ113">
+        <v>2.88</v>
+      </c>
+      <c r="BK113">
+        <v>1.57</v>
+      </c>
+      <c r="BL113">
+        <v>2.2</v>
+      </c>
+      <c r="BM113">
+        <v>1.95</v>
+      </c>
+      <c r="BN113">
+        <v>1.73</v>
+      </c>
+      <c r="BO113">
+        <v>2.4</v>
+      </c>
+      <c r="BP113">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -529,6 +529,15 @@
     <t>['90']</t>
   </si>
   <si>
+    <t>['34', '76']</t>
+  </si>
+  <si>
+    <t>['54', '90']</t>
+  </si>
+  <si>
+    <t>['29', '90+5']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -640,7 +649,10 @@
     <t>['49']</t>
   </si>
   <si>
-    <t>['81', '90+4', '60']</t>
+    <t>['90+4', '81', '60']</t>
+  </si>
+  <si>
+    <t>['1']</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1464,7 +1476,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1670,7 +1682,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1751,7 +1763,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2160,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ6">
         <v>0.67</v>
@@ -2494,7 +2506,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2575,7 +2587,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ8">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3112,7 +3124,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3318,7 +3330,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3396,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ12">
         <v>0.8</v>
@@ -3524,7 +3536,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3730,7 +3742,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4554,7 +4566,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4635,7 +4647,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4760,7 +4772,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -4838,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>0.83</v>
@@ -5378,7 +5390,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5584,7 +5596,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5871,7 +5883,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -6202,7 +6214,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6692,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ28">
         <v>0.33</v>
@@ -6820,7 +6832,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -6901,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR29">
         <v>1.52</v>
@@ -7232,7 +7244,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8134,7 +8146,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ35">
         <v>0.83</v>
@@ -8343,7 +8355,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR36">
         <v>1.95</v>
@@ -8468,7 +8480,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8674,7 +8686,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9498,7 +9510,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9785,7 +9797,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ43">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR43">
         <v>2.25</v>
@@ -10197,7 +10209,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ45">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR45">
         <v>1.46</v>
@@ -10606,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
         <v>0.33</v>
@@ -10734,7 +10746,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10940,7 +10952,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11352,7 +11364,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11433,7 +11445,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR51">
         <v>1.16</v>
@@ -11558,7 +11570,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12588,7 +12600,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12666,7 +12678,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ57">
         <v>0.67</v>
@@ -13000,7 +13012,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13284,7 +13296,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ60">
         <v>1.6</v>
@@ -13412,7 +13424,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13490,7 +13502,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ61">
         <v>0.67</v>
@@ -13696,7 +13708,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ62">
         <v>0.67</v>
@@ -14442,7 +14454,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14523,7 +14535,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR66">
         <v>1.58</v>
@@ -14648,7 +14660,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14854,7 +14866,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15060,7 +15072,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15472,7 +15484,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16502,7 +16514,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16580,7 +16592,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.6</v>
@@ -16708,7 +16720,7 @@
         <v>148</v>
       </c>
       <c r="P77" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16789,7 +16801,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ77">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR77">
         <v>1.59</v>
@@ -16992,7 +17004,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ78">
         <v>0.8</v>
@@ -17201,7 +17213,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ79">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR79">
         <v>1.67</v>
@@ -18022,7 +18034,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ83">
         <v>0.5</v>
@@ -18356,7 +18368,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18849,7 +18861,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ87">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR87">
         <v>1.81</v>
@@ -18974,7 +18986,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19592,7 +19604,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19798,7 +19810,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20004,7 +20016,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20416,7 +20428,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20497,7 +20509,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ95">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR95">
         <v>1.93</v>
@@ -20622,7 +20634,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20700,7 +20712,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
         <v>1.6</v>
@@ -21112,10 +21124,10 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ98">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR98">
         <v>1.74</v>
@@ -21652,7 +21664,7 @@
         <v>97</v>
       </c>
       <c r="P101" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q101">
         <v>3.12</v>
@@ -22476,7 +22488,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23094,7 +23106,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23172,7 +23184,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ108">
         <v>1</v>
@@ -23300,7 +23312,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23381,7 +23393,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR109">
         <v>1.3</v>
@@ -23918,7 +23930,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24281,6 +24293,624 @@
       </c>
       <c r="BP113">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7841148</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45822.66666666666</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
+        <v>74</v>
+      </c>
+      <c r="H114" t="s">
+        <v>70</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>171</v>
+      </c>
+      <c r="P114" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q114">
+        <v>2.95</v>
+      </c>
+      <c r="R114">
+        <v>1.84</v>
+      </c>
+      <c r="S114">
+        <v>4.34</v>
+      </c>
+      <c r="T114">
+        <v>1.56</v>
+      </c>
+      <c r="U114">
+        <v>2.47</v>
+      </c>
+      <c r="V114">
+        <v>3.4</v>
+      </c>
+      <c r="W114">
+        <v>1.25</v>
+      </c>
+      <c r="X114">
+        <v>7.8</v>
+      </c>
+      <c r="Y114">
+        <v>1.03</v>
+      </c>
+      <c r="Z114">
+        <v>2.98</v>
+      </c>
+      <c r="AA114">
+        <v>2.88</v>
+      </c>
+      <c r="AB114">
+        <v>2.29</v>
+      </c>
+      <c r="AC114">
+        <v>1.12</v>
+      </c>
+      <c r="AD114">
+        <v>6.2</v>
+      </c>
+      <c r="AE114">
+        <v>1.48</v>
+      </c>
+      <c r="AF114">
+        <v>2.37</v>
+      </c>
+      <c r="AG114">
+        <v>2.56</v>
+      </c>
+      <c r="AH114">
+        <v>1.45</v>
+      </c>
+      <c r="AI114">
+        <v>1.95</v>
+      </c>
+      <c r="AJ114">
+        <v>1.8</v>
+      </c>
+      <c r="AK114">
+        <v>1.4</v>
+      </c>
+      <c r="AL114">
+        <v>1.37</v>
+      </c>
+      <c r="AM114">
+        <v>1.53</v>
+      </c>
+      <c r="AN114">
+        <v>2.6</v>
+      </c>
+      <c r="AO114">
+        <v>2</v>
+      </c>
+      <c r="AP114">
+        <v>2.67</v>
+      </c>
+      <c r="AQ114">
+        <v>1.67</v>
+      </c>
+      <c r="AR114">
+        <v>1.72</v>
+      </c>
+      <c r="AS114">
+        <v>1.19</v>
+      </c>
+      <c r="AT114">
+        <v>2.91</v>
+      </c>
+      <c r="AU114">
+        <v>5</v>
+      </c>
+      <c r="AV114">
+        <v>8</v>
+      </c>
+      <c r="AW114">
+        <v>11</v>
+      </c>
+      <c r="AX114">
+        <v>10</v>
+      </c>
+      <c r="AY114">
+        <v>16</v>
+      </c>
+      <c r="AZ114">
+        <v>18</v>
+      </c>
+      <c r="BA114">
+        <v>1</v>
+      </c>
+      <c r="BB114">
+        <v>8</v>
+      </c>
+      <c r="BC114">
+        <v>9</v>
+      </c>
+      <c r="BD114">
+        <v>1.75</v>
+      </c>
+      <c r="BE114">
+        <v>7.5</v>
+      </c>
+      <c r="BF114">
+        <v>2.5</v>
+      </c>
+      <c r="BG114">
+        <v>1.16</v>
+      </c>
+      <c r="BH114">
+        <v>4.33</v>
+      </c>
+      <c r="BI114">
+        <v>1.31</v>
+      </c>
+      <c r="BJ114">
+        <v>3.05</v>
+      </c>
+      <c r="BK114">
+        <v>1.69</v>
+      </c>
+      <c r="BL114">
+        <v>2.3</v>
+      </c>
+      <c r="BM114">
+        <v>1.85</v>
+      </c>
+      <c r="BN114">
+        <v>1.85</v>
+      </c>
+      <c r="BO114">
+        <v>2.3</v>
+      </c>
+      <c r="BP114">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7841142</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45822.77083333334</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115" t="s">
+        <v>80</v>
+      </c>
+      <c r="H115" t="s">
+        <v>88</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>2</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>3</v>
+      </c>
+      <c r="O115" t="s">
+        <v>172</v>
+      </c>
+      <c r="P115" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q115">
+        <v>2.2</v>
+      </c>
+      <c r="R115">
+        <v>2.15</v>
+      </c>
+      <c r="S115">
+        <v>5</v>
+      </c>
+      <c r="T115">
+        <v>1.44</v>
+      </c>
+      <c r="U115">
+        <v>2.59</v>
+      </c>
+      <c r="V115">
+        <v>3.2</v>
+      </c>
+      <c r="W115">
+        <v>1.32</v>
+      </c>
+      <c r="X115">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y115">
+        <v>1</v>
+      </c>
+      <c r="Z115">
+        <v>1.62</v>
+      </c>
+      <c r="AA115">
+        <v>3.6</v>
+      </c>
+      <c r="AB115">
+        <v>5.5</v>
+      </c>
+      <c r="AC115">
+        <v>1.06</v>
+      </c>
+      <c r="AD115">
+        <v>7.5</v>
+      </c>
+      <c r="AE115">
+        <v>1.4</v>
+      </c>
+      <c r="AF115">
+        <v>2.79</v>
+      </c>
+      <c r="AG115">
+        <v>2.24</v>
+      </c>
+      <c r="AH115">
+        <v>1.62</v>
+      </c>
+      <c r="AI115">
+        <v>2</v>
+      </c>
+      <c r="AJ115">
+        <v>1.67</v>
+      </c>
+      <c r="AK115">
+        <v>1.29</v>
+      </c>
+      <c r="AL115">
+        <v>1.28</v>
+      </c>
+      <c r="AM115">
+        <v>2.15</v>
+      </c>
+      <c r="AN115">
+        <v>1.67</v>
+      </c>
+      <c r="AO115">
+        <v>0.8</v>
+      </c>
+      <c r="AP115">
+        <v>1.86</v>
+      </c>
+      <c r="AQ115">
+        <v>0.67</v>
+      </c>
+      <c r="AR115">
+        <v>1.63</v>
+      </c>
+      <c r="AS115">
+        <v>1.49</v>
+      </c>
+      <c r="AT115">
+        <v>3.12</v>
+      </c>
+      <c r="AU115">
+        <v>13</v>
+      </c>
+      <c r="AV115">
+        <v>4</v>
+      </c>
+      <c r="AW115">
+        <v>15</v>
+      </c>
+      <c r="AX115">
+        <v>5</v>
+      </c>
+      <c r="AY115">
+        <v>28</v>
+      </c>
+      <c r="AZ115">
+        <v>9</v>
+      </c>
+      <c r="BA115">
+        <v>13</v>
+      </c>
+      <c r="BB115">
+        <v>3</v>
+      </c>
+      <c r="BC115">
+        <v>16</v>
+      </c>
+      <c r="BD115">
+        <v>1.3</v>
+      </c>
+      <c r="BE115">
+        <v>7.5</v>
+      </c>
+      <c r="BF115">
+        <v>4.66</v>
+      </c>
+      <c r="BG115">
+        <v>1.21</v>
+      </c>
+      <c r="BH115">
+        <v>4.1</v>
+      </c>
+      <c r="BI115">
+        <v>1.35</v>
+      </c>
+      <c r="BJ115">
+        <v>2.9</v>
+      </c>
+      <c r="BK115">
+        <v>1.58</v>
+      </c>
+      <c r="BL115">
+        <v>2.23</v>
+      </c>
+      <c r="BM115">
+        <v>1.94</v>
+      </c>
+      <c r="BN115">
+        <v>1.8</v>
+      </c>
+      <c r="BO115">
+        <v>2.41</v>
+      </c>
+      <c r="BP115">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7841149</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45822.85416666666</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116" t="s">
+        <v>87</v>
+      </c>
+      <c r="H116" t="s">
+        <v>86</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116">
+        <v>2</v>
+      </c>
+      <c r="L116">
+        <v>2</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116">
+        <v>3</v>
+      </c>
+      <c r="O116" t="s">
+        <v>173</v>
+      </c>
+      <c r="P116" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q116">
+        <v>3.15</v>
+      </c>
+      <c r="R116">
+        <v>1.83</v>
+      </c>
+      <c r="S116">
+        <v>4.35</v>
+      </c>
+      <c r="T116">
+        <v>1.64</v>
+      </c>
+      <c r="U116">
+        <v>2.2</v>
+      </c>
+      <c r="V116">
+        <v>3.55</v>
+      </c>
+      <c r="W116">
+        <v>1.22</v>
+      </c>
+      <c r="X116">
+        <v>12</v>
+      </c>
+      <c r="Y116">
+        <v>1.03</v>
+      </c>
+      <c r="Z116">
+        <v>2.45</v>
+      </c>
+      <c r="AA116">
+        <v>2.8</v>
+      </c>
+      <c r="AB116">
+        <v>3.1</v>
+      </c>
+      <c r="AC116">
+        <v>1.14</v>
+      </c>
+      <c r="AD116">
+        <v>5.75</v>
+      </c>
+      <c r="AE116">
+        <v>1.49</v>
+      </c>
+      <c r="AF116">
+        <v>2.3</v>
+      </c>
+      <c r="AG116">
+        <v>2.55</v>
+      </c>
+      <c r="AH116">
+        <v>1.44</v>
+      </c>
+      <c r="AI116">
+        <v>2.2</v>
+      </c>
+      <c r="AJ116">
+        <v>1.62</v>
+      </c>
+      <c r="AK116">
+        <v>1.33</v>
+      </c>
+      <c r="AL116">
+        <v>1.35</v>
+      </c>
+      <c r="AM116">
+        <v>1.51</v>
+      </c>
+      <c r="AN116">
+        <v>0.6</v>
+      </c>
+      <c r="AO116">
+        <v>1</v>
+      </c>
+      <c r="AP116">
+        <v>1</v>
+      </c>
+      <c r="AQ116">
+        <v>0.86</v>
+      </c>
+      <c r="AR116">
+        <v>1.63</v>
+      </c>
+      <c r="AS116">
+        <v>1.41</v>
+      </c>
+      <c r="AT116">
+        <v>3.04</v>
+      </c>
+      <c r="AU116">
+        <v>6</v>
+      </c>
+      <c r="AV116">
+        <v>4</v>
+      </c>
+      <c r="AW116">
+        <v>7</v>
+      </c>
+      <c r="AX116">
+        <v>9</v>
+      </c>
+      <c r="AY116">
+        <v>13</v>
+      </c>
+      <c r="AZ116">
+        <v>13</v>
+      </c>
+      <c r="BA116">
+        <v>5</v>
+      </c>
+      <c r="BB116">
+        <v>3</v>
+      </c>
+      <c r="BC116">
+        <v>8</v>
+      </c>
+      <c r="BD116">
+        <v>1.74</v>
+      </c>
+      <c r="BE116">
+        <v>8.4</v>
+      </c>
+      <c r="BF116">
+        <v>2.5</v>
+      </c>
+      <c r="BG116">
+        <v>1.21</v>
+      </c>
+      <c r="BH116">
+        <v>3.8</v>
+      </c>
+      <c r="BI116">
+        <v>1.45</v>
+      </c>
+      <c r="BJ116">
+        <v>2.5</v>
+      </c>
+      <c r="BK116">
+        <v>1.73</v>
+      </c>
+      <c r="BL116">
+        <v>2</v>
+      </c>
+      <c r="BM116">
+        <v>2.2</v>
+      </c>
+      <c r="BN116">
+        <v>1.55</v>
+      </c>
+      <c r="BO116">
+        <v>3</v>
+      </c>
+      <c r="BP116">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,6 +538,12 @@
     <t>['29', '90+5']</t>
   </si>
   <si>
+    <t>['82', '90+7', '21']</t>
+  </si>
+  <si>
+    <t>['19', '47', '90+2']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -653,6 +659,9 @@
   </si>
   <si>
     <t>['1']</t>
+  </si>
+  <si>
+    <t>['30', '59']</t>
   </si>
 </sst>
 </file>
@@ -1014,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1351,7 +1360,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ2">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1476,7 +1485,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1682,7 +1691,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1760,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ4">
         <v>0.86</v>
@@ -2506,7 +2515,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2793,7 +2802,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ9">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3124,7 +3133,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3202,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3330,7 +3339,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3536,7 +3545,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3742,7 +3751,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -3823,7 +3832,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ14">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4438,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ17">
         <v>0.33</v>
@@ -4566,7 +4575,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4772,7 +4781,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5390,7 +5399,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5596,7 +5605,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6214,7 +6223,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6498,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ27">
         <v>0.5</v>
@@ -6832,7 +6841,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7244,7 +7253,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7325,7 +7334,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ31">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR31">
         <v>2.07</v>
@@ -8480,7 +8489,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8686,7 +8695,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -8764,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ38">
         <v>0.8</v>
@@ -8973,7 +8982,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ39">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR39">
         <v>1.19</v>
@@ -9176,10 +9185,10 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ40">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR40">
         <v>1.82</v>
@@ -9510,7 +9519,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9588,7 +9597,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ42">
         <v>0.8</v>
@@ -9794,7 +9803,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ43">
         <v>0.67</v>
@@ -10746,7 +10755,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10952,7 +10961,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11364,7 +11373,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11570,7 +11579,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11651,7 +11660,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ52">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR52">
         <v>2.26</v>
@@ -11857,7 +11866,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ53">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR53">
         <v>1.06</v>
@@ -12266,7 +12275,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ55">
         <v>1.6</v>
@@ -12600,7 +12609,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13012,7 +13021,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13299,7 +13308,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ60">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
         <v>1.78</v>
@@ -13424,7 +13433,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14123,7 +14132,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ64">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR64">
         <v>1.84</v>
@@ -14326,7 +14335,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ65">
         <v>0.33</v>
@@ -14454,7 +14463,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14660,7 +14669,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14738,7 +14747,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -14866,7 +14875,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15072,7 +15081,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15484,7 +15493,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15977,7 +15986,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ73">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR73">
         <v>1.75</v>
@@ -16514,7 +16523,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16720,7 +16729,7 @@
         <v>148</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16798,7 +16807,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ77">
         <v>0.67</v>
@@ -17419,7 +17428,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ80">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR80">
         <v>1.86</v>
@@ -18368,7 +18377,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18652,7 +18661,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ86">
         <v>0.33</v>
@@ -18986,7 +18995,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19064,10 +19073,10 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ88">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR88">
         <v>2.01</v>
@@ -19604,7 +19613,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19810,7 +19819,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20016,7 +20025,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20428,7 +20437,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20506,7 +20515,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ95">
         <v>1.67</v>
@@ -20634,7 +20643,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20715,7 +20724,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR96">
         <v>1.76</v>
@@ -21539,7 +21548,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ100">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AR100">
         <v>1.63</v>
@@ -21664,7 +21673,7 @@
         <v>97</v>
       </c>
       <c r="P101" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q101">
         <v>3.12</v>
@@ -21951,7 +21960,7 @@
         <v>1</v>
       </c>
       <c r="AQ102">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -22154,7 +22163,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ103">
         <v>0.67</v>
@@ -22488,7 +22497,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23106,7 +23115,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23312,7 +23321,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23596,7 +23605,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ110">
         <v>0.67</v>
@@ -23930,7 +23939,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24548,7 +24557,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24754,7 +24763,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -24911,6 +24920,624 @@
       </c>
       <c r="BP116">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7841150</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45823.66666666666</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117" t="s">
+        <v>85</v>
+      </c>
+      <c r="H117" t="s">
+        <v>81</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117">
+        <v>3</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>3</v>
+      </c>
+      <c r="O117" t="s">
+        <v>174</v>
+      </c>
+      <c r="P117" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q117">
+        <v>2.35</v>
+      </c>
+      <c r="R117">
+        <v>1.85</v>
+      </c>
+      <c r="S117">
+        <v>5.2</v>
+      </c>
+      <c r="T117">
+        <v>1.6</v>
+      </c>
+      <c r="U117">
+        <v>2.35</v>
+      </c>
+      <c r="V117">
+        <v>3.75</v>
+      </c>
+      <c r="W117">
+        <v>1.22</v>
+      </c>
+      <c r="X117">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y117">
+        <v>1</v>
+      </c>
+      <c r="Z117">
+        <v>1.97</v>
+      </c>
+      <c r="AA117">
+        <v>2.59</v>
+      </c>
+      <c r="AB117">
+        <v>4.4</v>
+      </c>
+      <c r="AC117">
+        <v>1.14</v>
+      </c>
+      <c r="AD117">
+        <v>5</v>
+      </c>
+      <c r="AE117">
+        <v>1.48</v>
+      </c>
+      <c r="AF117">
+        <v>2.37</v>
+      </c>
+      <c r="AG117">
+        <v>2.55</v>
+      </c>
+      <c r="AH117">
+        <v>1.45</v>
+      </c>
+      <c r="AI117">
+        <v>2.3</v>
+      </c>
+      <c r="AJ117">
+        <v>1.55</v>
+      </c>
+      <c r="AK117">
+        <v>1.4</v>
+      </c>
+      <c r="AL117">
+        <v>1.37</v>
+      </c>
+      <c r="AM117">
+        <v>1.79</v>
+      </c>
+      <c r="AN117">
+        <v>2.33</v>
+      </c>
+      <c r="AO117">
+        <v>1.6</v>
+      </c>
+      <c r="AP117">
+        <v>2.43</v>
+      </c>
+      <c r="AQ117">
+        <v>1.33</v>
+      </c>
+      <c r="AR117">
+        <v>2</v>
+      </c>
+      <c r="AS117">
+        <v>1.66</v>
+      </c>
+      <c r="AT117">
+        <v>3.66</v>
+      </c>
+      <c r="AU117">
+        <v>3</v>
+      </c>
+      <c r="AV117">
+        <v>10</v>
+      </c>
+      <c r="AW117">
+        <v>4</v>
+      </c>
+      <c r="AX117">
+        <v>5</v>
+      </c>
+      <c r="AY117">
+        <v>7</v>
+      </c>
+      <c r="AZ117">
+        <v>15</v>
+      </c>
+      <c r="BA117">
+        <v>2</v>
+      </c>
+      <c r="BB117">
+        <v>4</v>
+      </c>
+      <c r="BC117">
+        <v>6</v>
+      </c>
+      <c r="BD117">
+        <v>1.53</v>
+      </c>
+      <c r="BE117">
+        <v>7</v>
+      </c>
+      <c r="BF117">
+        <v>2.9</v>
+      </c>
+      <c r="BG117">
+        <v>1.22</v>
+      </c>
+      <c r="BH117">
+        <v>3.6</v>
+      </c>
+      <c r="BI117">
+        <v>1.45</v>
+      </c>
+      <c r="BJ117">
+        <v>2.55</v>
+      </c>
+      <c r="BK117">
+        <v>1.63</v>
+      </c>
+      <c r="BL117">
+        <v>2.01</v>
+      </c>
+      <c r="BM117">
+        <v>2.1</v>
+      </c>
+      <c r="BN117">
+        <v>1.67</v>
+      </c>
+      <c r="BO117">
+        <v>2.55</v>
+      </c>
+      <c r="BP117">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7841144</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45823.66666666666</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s">
+        <v>79</v>
+      </c>
+      <c r="H118" t="s">
+        <v>73</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118" t="s">
+        <v>97</v>
+      </c>
+      <c r="P118" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q118">
+        <v>3.12</v>
+      </c>
+      <c r="R118">
+        <v>1.8</v>
+      </c>
+      <c r="S118">
+        <v>4.2</v>
+      </c>
+      <c r="T118">
+        <v>1.61</v>
+      </c>
+      <c r="U118">
+        <v>2.2</v>
+      </c>
+      <c r="V118">
+        <v>3.88</v>
+      </c>
+      <c r="W118">
+        <v>1.22</v>
+      </c>
+      <c r="X118">
+        <v>12.5</v>
+      </c>
+      <c r="Y118">
+        <v>1.02</v>
+      </c>
+      <c r="Z118">
+        <v>2.28</v>
+      </c>
+      <c r="AA118">
+        <v>2.85</v>
+      </c>
+      <c r="AB118">
+        <v>3.02</v>
+      </c>
+      <c r="AC118">
+        <v>1.09</v>
+      </c>
+      <c r="AD118">
+        <v>5.5</v>
+      </c>
+      <c r="AE118">
+        <v>1.5</v>
+      </c>
+      <c r="AF118">
+        <v>2.3</v>
+      </c>
+      <c r="AG118">
+        <v>2.59</v>
+      </c>
+      <c r="AH118">
+        <v>1.44</v>
+      </c>
+      <c r="AI118">
+        <v>2.25</v>
+      </c>
+      <c r="AJ118">
+        <v>1.6</v>
+      </c>
+      <c r="AK118">
+        <v>1.3</v>
+      </c>
+      <c r="AL118">
+        <v>1.37</v>
+      </c>
+      <c r="AM118">
+        <v>1.57</v>
+      </c>
+      <c r="AN118">
+        <v>1.6</v>
+      </c>
+      <c r="AO118">
+        <v>1.17</v>
+      </c>
+      <c r="AP118">
+        <v>1.5</v>
+      </c>
+      <c r="AQ118">
+        <v>1.14</v>
+      </c>
+      <c r="AR118">
+        <v>1.9</v>
+      </c>
+      <c r="AS118">
+        <v>1.24</v>
+      </c>
+      <c r="AT118">
+        <v>3.14</v>
+      </c>
+      <c r="AU118">
+        <v>5</v>
+      </c>
+      <c r="AV118">
+        <v>2</v>
+      </c>
+      <c r="AW118">
+        <v>9</v>
+      </c>
+      <c r="AX118">
+        <v>7</v>
+      </c>
+      <c r="AY118">
+        <v>14</v>
+      </c>
+      <c r="AZ118">
+        <v>9</v>
+      </c>
+      <c r="BA118">
+        <v>4</v>
+      </c>
+      <c r="BB118">
+        <v>5</v>
+      </c>
+      <c r="BC118">
+        <v>9</v>
+      </c>
+      <c r="BD118">
+        <v>1.67</v>
+      </c>
+      <c r="BE118">
+        <v>8.6</v>
+      </c>
+      <c r="BF118">
+        <v>2.8</v>
+      </c>
+      <c r="BG118">
+        <v>1.18</v>
+      </c>
+      <c r="BH118">
+        <v>4.1</v>
+      </c>
+      <c r="BI118">
+        <v>1.36</v>
+      </c>
+      <c r="BJ118">
+        <v>2.98</v>
+      </c>
+      <c r="BK118">
+        <v>1.73</v>
+      </c>
+      <c r="BL118">
+        <v>2.27</v>
+      </c>
+      <c r="BM118">
+        <v>1.93</v>
+      </c>
+      <c r="BN118">
+        <v>1.86</v>
+      </c>
+      <c r="BO118">
+        <v>2.4</v>
+      </c>
+      <c r="BP118">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7841147</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45823.85416666666</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119" t="s">
+        <v>72</v>
+      </c>
+      <c r="H119" t="s">
+        <v>84</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>1</v>
+      </c>
+      <c r="K119">
+        <v>2</v>
+      </c>
+      <c r="L119">
+        <v>3</v>
+      </c>
+      <c r="M119">
+        <v>2</v>
+      </c>
+      <c r="N119">
+        <v>5</v>
+      </c>
+      <c r="O119" t="s">
+        <v>175</v>
+      </c>
+      <c r="P119" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q119">
+        <v>2.38</v>
+      </c>
+      <c r="R119">
+        <v>2.05</v>
+      </c>
+      <c r="S119">
+        <v>4.6</v>
+      </c>
+      <c r="T119">
+        <v>1.46</v>
+      </c>
+      <c r="U119">
+        <v>2.4</v>
+      </c>
+      <c r="V119">
+        <v>3.44</v>
+      </c>
+      <c r="W119">
+        <v>1.33</v>
+      </c>
+      <c r="X119">
+        <v>9.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.04</v>
+      </c>
+      <c r="Z119">
+        <v>1.65</v>
+      </c>
+      <c r="AA119">
+        <v>3.58</v>
+      </c>
+      <c r="AB119">
+        <v>5.3</v>
+      </c>
+      <c r="AC119">
+        <v>1.04</v>
+      </c>
+      <c r="AD119">
+        <v>7.5</v>
+      </c>
+      <c r="AE119">
+        <v>1.42</v>
+      </c>
+      <c r="AF119">
+        <v>2.75</v>
+      </c>
+      <c r="AG119">
+        <v>2.2</v>
+      </c>
+      <c r="AH119">
+        <v>1.57</v>
+      </c>
+      <c r="AI119">
+        <v>2.14</v>
+      </c>
+      <c r="AJ119">
+        <v>1.65</v>
+      </c>
+      <c r="AK119">
+        <v>1.3</v>
+      </c>
+      <c r="AL119">
+        <v>1.3</v>
+      </c>
+      <c r="AM119">
+        <v>2.1</v>
+      </c>
+      <c r="AN119">
+        <v>1.33</v>
+      </c>
+      <c r="AO119">
+        <v>0.2</v>
+      </c>
+      <c r="AP119">
+        <v>1.57</v>
+      </c>
+      <c r="AQ119">
+        <v>0.17</v>
+      </c>
+      <c r="AR119">
+        <v>1.99</v>
+      </c>
+      <c r="AS119">
+        <v>1.12</v>
+      </c>
+      <c r="AT119">
+        <v>3.11</v>
+      </c>
+      <c r="AU119">
+        <v>12</v>
+      </c>
+      <c r="AV119">
+        <v>5</v>
+      </c>
+      <c r="AW119">
+        <v>8</v>
+      </c>
+      <c r="AX119">
+        <v>7</v>
+      </c>
+      <c r="AY119">
+        <v>20</v>
+      </c>
+      <c r="AZ119">
+        <v>12</v>
+      </c>
+      <c r="BA119">
+        <v>5</v>
+      </c>
+      <c r="BB119">
+        <v>3</v>
+      </c>
+      <c r="BC119">
+        <v>8</v>
+      </c>
+      <c r="BD119">
+        <v>1.42</v>
+      </c>
+      <c r="BE119">
+        <v>8.4</v>
+      </c>
+      <c r="BF119">
+        <v>3.75</v>
+      </c>
+      <c r="BG119">
+        <v>1.16</v>
+      </c>
+      <c r="BH119">
+        <v>4</v>
+      </c>
+      <c r="BI119">
+        <v>1.38</v>
+      </c>
+      <c r="BJ119">
+        <v>3.14</v>
+      </c>
+      <c r="BK119">
+        <v>1.69</v>
+      </c>
+      <c r="BL119">
+        <v>2.35</v>
+      </c>
+      <c r="BM119">
+        <v>1.86</v>
+      </c>
+      <c r="BN119">
+        <v>1.84</v>
+      </c>
+      <c r="BO119">
+        <v>2.38</v>
+      </c>
+      <c r="BP119">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="217">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -544,6 +544,9 @@
     <t>['19', '47', '90+2']</t>
   </si>
   <si>
+    <t>['29', '52']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1023,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP119"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1485,7 +1488,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1691,7 +1694,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2515,7 +2518,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3133,7 +3136,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3339,7 +3342,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3545,7 +3548,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3751,7 +3754,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -3829,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ14">
         <v>1.14</v>
@@ -4244,7 +4247,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4575,7 +4578,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4781,7 +4784,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5399,7 +5402,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5605,7 +5608,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6223,7 +6226,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6841,7 +6844,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7253,7 +7256,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7949,7 +7952,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ34">
         <v>0.5</v>
@@ -8489,7 +8492,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8695,7 +8698,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9394,7 +9397,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR41">
         <v>1.74</v>
@@ -9519,7 +9522,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10755,7 +10758,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10961,7 +10964,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11248,7 +11251,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR50">
         <v>1.55</v>
@@ -11373,7 +11376,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11579,7 +11582,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12481,7 +12484,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ56">
         <v>0.8</v>
@@ -12609,7 +12612,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13021,7 +13024,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13433,7 +13436,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14463,7 +14466,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14669,7 +14672,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14750,7 +14753,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR67">
         <v>2.23</v>
@@ -14875,7 +14878,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15081,7 +15084,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15493,7 +15496,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15983,7 +15986,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ73">
         <v>1.33</v>
@@ -16523,7 +16526,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16729,7 +16732,7 @@
         <v>148</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17840,7 +17843,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ82">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR82">
         <v>1.86</v>
@@ -18377,7 +18380,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18995,7 +18998,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19613,7 +19616,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19819,7 +19822,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20025,7 +20028,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20437,7 +20440,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20643,7 +20646,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21545,7 +21548,7 @@
         <v>0.25</v>
       </c>
       <c r="AP100">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ100">
         <v>0.17</v>
@@ -21673,7 +21676,7 @@
         <v>97</v>
       </c>
       <c r="P101" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q101">
         <v>3.12</v>
@@ -22497,7 +22500,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22578,7 +22581,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ105">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR105">
         <v>1.85</v>
@@ -23115,7 +23118,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23321,7 +23324,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23939,7 +23942,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24557,7 +24560,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24763,7 +24766,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25062,7 +25065,7 @@
         <v>3.66</v>
       </c>
       <c r="AU117">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV117">
         <v>10</v>
@@ -25071,13 +25074,13 @@
         <v>4</v>
       </c>
       <c r="AX117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY117">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ117">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA117">
         <v>2</v>
@@ -25274,25 +25277,25 @@
         <v>2</v>
       </c>
       <c r="AW118">
+        <v>4</v>
+      </c>
+      <c r="AX118">
+        <v>4</v>
+      </c>
+      <c r="AY118">
         <v>9</v>
       </c>
-      <c r="AX118">
-        <v>7</v>
-      </c>
-      <c r="AY118">
-        <v>14</v>
-      </c>
       <c r="AZ118">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA118">
         <v>4</v>
       </c>
       <c r="BB118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC118">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD118">
         <v>1.67</v>
@@ -25381,7 +25384,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25474,22 +25477,22 @@
         <v>3.11</v>
       </c>
       <c r="AU119">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV119">
+        <v>4</v>
+      </c>
+      <c r="AW119">
+        <v>6</v>
+      </c>
+      <c r="AX119">
         <v>5</v>
       </c>
-      <c r="AW119">
-        <v>8</v>
-      </c>
-      <c r="AX119">
-        <v>7</v>
-      </c>
       <c r="AY119">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ119">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA119">
         <v>5</v>
@@ -25538,6 +25541,212 @@
       </c>
       <c r="BP119">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7841146</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45824.79166666666</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120" t="s">
+        <v>82</v>
+      </c>
+      <c r="H120" t="s">
+        <v>76</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+      <c r="L120">
+        <v>2</v>
+      </c>
+      <c r="M120">
+        <v>1</v>
+      </c>
+      <c r="N120">
+        <v>3</v>
+      </c>
+      <c r="O120" t="s">
+        <v>176</v>
+      </c>
+      <c r="P120" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q120">
+        <v>3.12</v>
+      </c>
+      <c r="R120">
+        <v>1.76</v>
+      </c>
+      <c r="S120">
+        <v>4.8</v>
+      </c>
+      <c r="T120">
+        <v>1.55</v>
+      </c>
+      <c r="U120">
+        <v>2.25</v>
+      </c>
+      <c r="V120">
+        <v>3.6</v>
+      </c>
+      <c r="W120">
+        <v>1.22</v>
+      </c>
+      <c r="X120">
+        <v>11.5</v>
+      </c>
+      <c r="Y120">
+        <v>1.01</v>
+      </c>
+      <c r="Z120">
+        <v>2.15</v>
+      </c>
+      <c r="AA120">
+        <v>2.7</v>
+      </c>
+      <c r="AB120">
+        <v>3.78</v>
+      </c>
+      <c r="AC120">
+        <v>1.1</v>
+      </c>
+      <c r="AD120">
+        <v>5.69</v>
+      </c>
+      <c r="AE120">
+        <v>1.63</v>
+      </c>
+      <c r="AF120">
+        <v>2.25</v>
+      </c>
+      <c r="AG120">
+        <v>2.84</v>
+      </c>
+      <c r="AH120">
+        <v>1.36</v>
+      </c>
+      <c r="AI120">
+        <v>2.3</v>
+      </c>
+      <c r="AJ120">
+        <v>1.55</v>
+      </c>
+      <c r="AK120">
+        <v>1.29</v>
+      </c>
+      <c r="AL120">
+        <v>1.36</v>
+      </c>
+      <c r="AM120">
+        <v>1.62</v>
+      </c>
+      <c r="AN120">
+        <v>2.4</v>
+      </c>
+      <c r="AO120">
+        <v>1</v>
+      </c>
+      <c r="AP120">
+        <v>2.5</v>
+      </c>
+      <c r="AQ120">
+        <v>0.86</v>
+      </c>
+      <c r="AR120">
+        <v>1.66</v>
+      </c>
+      <c r="AS120">
+        <v>1.47</v>
+      </c>
+      <c r="AT120">
+        <v>3.13</v>
+      </c>
+      <c r="AU120">
+        <v>4</v>
+      </c>
+      <c r="AV120">
+        <v>8</v>
+      </c>
+      <c r="AW120">
+        <v>3</v>
+      </c>
+      <c r="AX120">
+        <v>7</v>
+      </c>
+      <c r="AY120">
+        <v>7</v>
+      </c>
+      <c r="AZ120">
+        <v>15</v>
+      </c>
+      <c r="BA120">
+        <v>1</v>
+      </c>
+      <c r="BB120">
+        <v>6</v>
+      </c>
+      <c r="BC120">
+        <v>7</v>
+      </c>
+      <c r="BD120">
+        <v>1.62</v>
+      </c>
+      <c r="BE120">
+        <v>8.1</v>
+      </c>
+      <c r="BF120">
+        <v>2.86</v>
+      </c>
+      <c r="BG120">
+        <v>1.19</v>
+      </c>
+      <c r="BH120">
+        <v>3.3</v>
+      </c>
+      <c r="BI120">
+        <v>1.5</v>
+      </c>
+      <c r="BJ120">
+        <v>2.4</v>
+      </c>
+      <c r="BK120">
+        <v>1.64</v>
+      </c>
+      <c r="BL120">
+        <v>2.05</v>
+      </c>
+      <c r="BM120">
+        <v>2.25</v>
+      </c>
+      <c r="BN120">
+        <v>1.57</v>
+      </c>
+      <c r="BO120">
+        <v>2.67</v>
+      </c>
+      <c r="BP120">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -25065,7 +25065,7 @@
         <v>3.66</v>
       </c>
       <c r="AU117">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV117">
         <v>10</v>
@@ -25074,13 +25074,13 @@
         <v>4</v>
       </c>
       <c r="AX117">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY117">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ117">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA117">
         <v>2</v>
@@ -25277,25 +25277,25 @@
         <v>2</v>
       </c>
       <c r="AW118">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AX118">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY118">
+        <v>14</v>
+      </c>
+      <c r="AZ118">
         <v>9</v>
-      </c>
-      <c r="AZ118">
-        <v>6</v>
       </c>
       <c r="BA118">
         <v>4</v>
       </c>
       <c r="BB118">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC118">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD118">
         <v>1.67</v>
@@ -25477,22 +25477,22 @@
         <v>3.11</v>
       </c>
       <c r="AU119">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV119">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW119">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX119">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY119">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ119">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA119">
         <v>5</v>
@@ -25683,22 +25683,22 @@
         <v>3.13</v>
       </c>
       <c r="AU120">
+        <v>5</v>
+      </c>
+      <c r="AV120">
+        <v>7</v>
+      </c>
+      <c r="AW120">
         <v>4</v>
       </c>
-      <c r="AV120">
-        <v>8</v>
-      </c>
-      <c r="AW120">
-        <v>3</v>
-      </c>
       <c r="AX120">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY120">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ120">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA120">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="218">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,9 @@
     <t>['29', '52']</t>
   </si>
   <si>
+    <t>['52']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -631,9 +634,6 @@
     <t>['55', '67']</t>
   </si>
   <si>
-    <t>['52']</t>
-  </si>
-  <si>
     <t>['74']</t>
   </si>
   <si>
@@ -665,6 +665,9 @@
   </si>
   <si>
     <t>['30', '59']</t>
+  </si>
+  <si>
+    <t>['28']</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1488,7 +1491,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1694,7 +1697,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2518,7 +2521,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2802,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
         <v>1.33</v>
@@ -3136,7 +3139,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3342,7 +3345,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3548,7 +3551,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3754,7 +3757,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4578,7 +4581,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4784,7 +4787,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5402,7 +5405,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5608,7 +5611,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6226,7 +6229,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6844,7 +6847,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7256,7 +7259,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8492,7 +8495,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8698,7 +8701,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9394,7 +9397,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
         <v>0.86</v>
@@ -9522,7 +9525,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10758,7 +10761,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10964,7 +10967,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11376,7 +11379,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11582,7 +11585,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12072,7 +12075,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ54">
         <v>0.33</v>
@@ -12612,7 +12615,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13024,7 +13027,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13436,7 +13439,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14466,7 +14469,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14672,7 +14675,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14878,7 +14881,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15084,7 +15087,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15496,7 +15499,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16526,7 +16529,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16732,7 +16735,7 @@
         <v>148</v>
       </c>
       <c r="P77" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17428,7 +17431,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ80">
         <v>0.17</v>
@@ -19616,7 +19619,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -20028,7 +20031,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -21342,7 +21345,7 @@
         <v>0</v>
       </c>
       <c r="AP99">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99">
         <v>0.5</v>
@@ -21676,7 +21679,7 @@
         <v>97</v>
       </c>
       <c r="P101" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="Q101">
         <v>3.12</v>
@@ -24766,7 +24769,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25747,6 +25750,212 @@
       </c>
       <c r="BP120">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7841151</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45825.8125</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>77</v>
+      </c>
+      <c r="H121" t="s">
+        <v>78</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>2</v>
+      </c>
+      <c r="O121" t="s">
+        <v>177</v>
+      </c>
+      <c r="P121" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q121">
+        <v>3.22</v>
+      </c>
+      <c r="R121">
+        <v>1.87</v>
+      </c>
+      <c r="S121">
+        <v>4.11</v>
+      </c>
+      <c r="T121">
+        <v>1.5</v>
+      </c>
+      <c r="U121">
+        <v>2.35</v>
+      </c>
+      <c r="V121">
+        <v>3.58</v>
+      </c>
+      <c r="W121">
+        <v>1.23</v>
+      </c>
+      <c r="X121">
+        <v>10</v>
+      </c>
+      <c r="Y121">
+        <v>1.04</v>
+      </c>
+      <c r="Z121">
+        <v>2.31</v>
+      </c>
+      <c r="AA121">
+        <v>2.8</v>
+      </c>
+      <c r="AB121">
+        <v>2.9</v>
+      </c>
+      <c r="AC121">
+        <v>1.11</v>
+      </c>
+      <c r="AD121">
+        <v>6.25</v>
+      </c>
+      <c r="AE121">
+        <v>1.5</v>
+      </c>
+      <c r="AF121">
+        <v>2.5</v>
+      </c>
+      <c r="AG121">
+        <v>2.47</v>
+      </c>
+      <c r="AH121">
+        <v>1.43</v>
+      </c>
+      <c r="AI121">
+        <v>2.19</v>
+      </c>
+      <c r="AJ121">
+        <v>1.7</v>
+      </c>
+      <c r="AK121">
+        <v>1.4</v>
+      </c>
+      <c r="AL121">
+        <v>1.37</v>
+      </c>
+      <c r="AM121">
+        <v>1.53</v>
+      </c>
+      <c r="AN121">
+        <v>1.6</v>
+      </c>
+      <c r="AO121">
+        <v>1</v>
+      </c>
+      <c r="AP121">
+        <v>1.5</v>
+      </c>
+      <c r="AQ121">
+        <v>1</v>
+      </c>
+      <c r="AR121">
+        <v>2.18</v>
+      </c>
+      <c r="AS121">
+        <v>1.39</v>
+      </c>
+      <c r="AT121">
+        <v>3.57</v>
+      </c>
+      <c r="AU121">
+        <v>11</v>
+      </c>
+      <c r="AV121">
+        <v>4</v>
+      </c>
+      <c r="AW121">
+        <v>3</v>
+      </c>
+      <c r="AX121">
+        <v>4</v>
+      </c>
+      <c r="AY121">
+        <v>14</v>
+      </c>
+      <c r="AZ121">
+        <v>8</v>
+      </c>
+      <c r="BA121">
+        <v>12</v>
+      </c>
+      <c r="BB121">
+        <v>1</v>
+      </c>
+      <c r="BC121">
+        <v>13</v>
+      </c>
+      <c r="BD121">
+        <v>1.67</v>
+      </c>
+      <c r="BE121">
+        <v>7</v>
+      </c>
+      <c r="BF121">
+        <v>2.66</v>
+      </c>
+      <c r="BG121">
+        <v>1.18</v>
+      </c>
+      <c r="BH121">
+        <v>4.05</v>
+      </c>
+      <c r="BI121">
+        <v>1.3</v>
+      </c>
+      <c r="BJ121">
+        <v>2.95</v>
+      </c>
+      <c r="BK121">
+        <v>1.77</v>
+      </c>
+      <c r="BL121">
+        <v>2.24</v>
+      </c>
+      <c r="BM121">
+        <v>1.96</v>
+      </c>
+      <c r="BN121">
+        <v>1.79</v>
+      </c>
+      <c r="BO121">
+        <v>2.43</v>
+      </c>
+      <c r="BP121">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -25892,19 +25892,19 @@
         <v>3.57</v>
       </c>
       <c r="AU121">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV121">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW121">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX121">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY121">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AZ121">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="219">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -550,6 +550,9 @@
     <t>['52']</t>
   </si>
   <si>
+    <t>['39']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1029,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1491,7 +1494,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1697,7 +1700,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2190,7 +2193,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ6">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2393,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>0.67</v>
@@ -2521,7 +2524,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3139,7 +3142,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3345,7 +3348,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3426,7 +3429,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ12">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3551,7 +3554,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3757,7 +3760,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4581,7 +4584,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4787,7 +4790,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5277,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ21">
         <v>1</v>
@@ -5405,7 +5408,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5611,7 +5614,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5692,7 +5695,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ23">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR23">
         <v>1.37</v>
@@ -6229,7 +6232,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6847,7 +6850,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -6925,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ29">
         <v>0.67</v>
@@ -7259,7 +7262,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7337,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>0.17</v>
@@ -8367,7 +8370,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
         <v>1.67</v>
@@ -8495,7 +8498,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8701,7 +8704,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -8782,7 +8785,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ38">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -9525,7 +9528,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10018,7 +10021,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR44">
         <v>1.73</v>
@@ -10761,7 +10764,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10967,7 +10970,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11379,7 +11382,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11457,7 +11460,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51">
         <v>1.67</v>
@@ -11585,7 +11588,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12490,7 +12493,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ56">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR56">
         <v>1.78</v>
@@ -12615,7 +12618,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13027,7 +13030,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13439,7 +13442,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13726,7 +13729,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ62">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -14469,7 +14472,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14675,7 +14678,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14881,7 +14884,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -14959,7 +14962,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ68">
         <v>0.5</v>
@@ -15087,7 +15090,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15499,7 +15502,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15577,7 +15580,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ71">
         <v>0.33</v>
@@ -16529,7 +16532,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17022,7 +17025,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ78">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR78">
         <v>1.76</v>
@@ -18383,7 +18386,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18464,7 +18467,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ85">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR85">
         <v>1.73</v>
@@ -19001,7 +19004,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19285,7 +19288,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ89">
         <v>0.83</v>
@@ -19619,7 +19622,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19697,7 +19700,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -19825,7 +19828,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20031,7 +20034,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20443,7 +20446,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20649,7 +20652,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21760,7 +21763,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ101">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR101">
         <v>1.81</v>
@@ -21963,7 +21966,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ102">
         <v>1.14</v>
@@ -22172,7 +22175,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ103">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR103">
         <v>2.14</v>
@@ -22503,7 +22506,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22581,7 +22584,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ105">
         <v>0.86</v>
@@ -23121,7 +23124,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23327,7 +23330,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23945,7 +23948,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24563,7 +24566,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24769,7 +24772,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25387,7 +25390,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25799,7 +25802,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -25956,6 +25959,418 @@
       </c>
       <c r="BP121">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7841161</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45828.79166666666</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122" t="s">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s">
+        <v>82</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+      <c r="O122" t="s">
+        <v>96</v>
+      </c>
+      <c r="P122" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q122">
+        <v>3.15</v>
+      </c>
+      <c r="R122">
+        <v>1.8</v>
+      </c>
+      <c r="S122">
+        <v>3.4</v>
+      </c>
+      <c r="T122">
+        <v>1.64</v>
+      </c>
+      <c r="U122">
+        <v>2.28</v>
+      </c>
+      <c r="V122">
+        <v>3.66</v>
+      </c>
+      <c r="W122">
+        <v>1.25</v>
+      </c>
+      <c r="X122">
+        <v>7.5</v>
+      </c>
+      <c r="Y122">
+        <v>1.04</v>
+      </c>
+      <c r="Z122">
+        <v>2.5</v>
+      </c>
+      <c r="AA122">
+        <v>2.89</v>
+      </c>
+      <c r="AB122">
+        <v>3.2</v>
+      </c>
+      <c r="AC122">
+        <v>1.08</v>
+      </c>
+      <c r="AD122">
+        <v>5.75</v>
+      </c>
+      <c r="AE122">
+        <v>1.59</v>
+      </c>
+      <c r="AF122">
+        <v>2.4</v>
+      </c>
+      <c r="AG122">
+        <v>2.6</v>
+      </c>
+      <c r="AH122">
+        <v>1.4</v>
+      </c>
+      <c r="AI122">
+        <v>2.2</v>
+      </c>
+      <c r="AJ122">
+        <v>1.62</v>
+      </c>
+      <c r="AK122">
+        <v>1.42</v>
+      </c>
+      <c r="AL122">
+        <v>1.36</v>
+      </c>
+      <c r="AM122">
+        <v>1.51</v>
+      </c>
+      <c r="AN122">
+        <v>1</v>
+      </c>
+      <c r="AO122">
+        <v>0.67</v>
+      </c>
+      <c r="AP122">
+        <v>1.29</v>
+      </c>
+      <c r="AQ122">
+        <v>0.57</v>
+      </c>
+      <c r="AR122">
+        <v>1.2</v>
+      </c>
+      <c r="AS122">
+        <v>1.52</v>
+      </c>
+      <c r="AT122">
+        <v>2.72</v>
+      </c>
+      <c r="AU122">
+        <v>6</v>
+      </c>
+      <c r="AV122">
+        <v>3</v>
+      </c>
+      <c r="AW122">
+        <v>11</v>
+      </c>
+      <c r="AX122">
+        <v>3</v>
+      </c>
+      <c r="AY122">
+        <v>17</v>
+      </c>
+      <c r="AZ122">
+        <v>6</v>
+      </c>
+      <c r="BA122">
+        <v>13</v>
+      </c>
+      <c r="BB122">
+        <v>4</v>
+      </c>
+      <c r="BC122">
+        <v>17</v>
+      </c>
+      <c r="BD122">
+        <v>1.8</v>
+      </c>
+      <c r="BE122">
+        <v>7</v>
+      </c>
+      <c r="BF122">
+        <v>2.5</v>
+      </c>
+      <c r="BG122">
+        <v>1.22</v>
+      </c>
+      <c r="BH122">
+        <v>3.92</v>
+      </c>
+      <c r="BI122">
+        <v>1.38</v>
+      </c>
+      <c r="BJ122">
+        <v>2.8</v>
+      </c>
+      <c r="BK122">
+        <v>1.63</v>
+      </c>
+      <c r="BL122">
+        <v>2.19</v>
+      </c>
+      <c r="BM122">
+        <v>2</v>
+      </c>
+      <c r="BN122">
+        <v>1.75</v>
+      </c>
+      <c r="BO122">
+        <v>2.7</v>
+      </c>
+      <c r="BP122">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7841159</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45828.89930555555</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123" t="s">
+        <v>75</v>
+      </c>
+      <c r="H123" t="s">
+        <v>72</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>2</v>
+      </c>
+      <c r="O123" t="s">
+        <v>178</v>
+      </c>
+      <c r="P123" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q123">
+        <v>2.51</v>
+      </c>
+      <c r="R123">
+        <v>2.05</v>
+      </c>
+      <c r="S123">
+        <v>3.8</v>
+      </c>
+      <c r="T123">
+        <v>1.48</v>
+      </c>
+      <c r="U123">
+        <v>2.55</v>
+      </c>
+      <c r="V123">
+        <v>3.2</v>
+      </c>
+      <c r="W123">
+        <v>1.31</v>
+      </c>
+      <c r="X123">
+        <v>6.8</v>
+      </c>
+      <c r="Y123">
+        <v>1.05</v>
+      </c>
+      <c r="Z123">
+        <v>1.85</v>
+      </c>
+      <c r="AA123">
+        <v>3.2</v>
+      </c>
+      <c r="AB123">
+        <v>4.55</v>
+      </c>
+      <c r="AC123">
+        <v>1.04</v>
+      </c>
+      <c r="AD123">
+        <v>7.8</v>
+      </c>
+      <c r="AE123">
+        <v>1.36</v>
+      </c>
+      <c r="AF123">
+        <v>2.71</v>
+      </c>
+      <c r="AG123">
+        <v>2.25</v>
+      </c>
+      <c r="AH123">
+        <v>1.62</v>
+      </c>
+      <c r="AI123">
+        <v>2</v>
+      </c>
+      <c r="AJ123">
+        <v>1.68</v>
+      </c>
+      <c r="AK123">
+        <v>1.33</v>
+      </c>
+      <c r="AL123">
+        <v>1.31</v>
+      </c>
+      <c r="AM123">
+        <v>1.91</v>
+      </c>
+      <c r="AN123">
+        <v>2.17</v>
+      </c>
+      <c r="AO123">
+        <v>0.8</v>
+      </c>
+      <c r="AP123">
+        <v>2</v>
+      </c>
+      <c r="AQ123">
+        <v>0.83</v>
+      </c>
+      <c r="AR123">
+        <v>1.83</v>
+      </c>
+      <c r="AS123">
+        <v>1.29</v>
+      </c>
+      <c r="AT123">
+        <v>3.12</v>
+      </c>
+      <c r="AU123">
+        <v>3</v>
+      </c>
+      <c r="AV123">
+        <v>4</v>
+      </c>
+      <c r="AW123">
+        <v>8</v>
+      </c>
+      <c r="AX123">
+        <v>6</v>
+      </c>
+      <c r="AY123">
+        <v>11</v>
+      </c>
+      <c r="AZ123">
+        <v>10</v>
+      </c>
+      <c r="BA123">
+        <v>7</v>
+      </c>
+      <c r="BB123">
+        <v>5</v>
+      </c>
+      <c r="BC123">
+        <v>12</v>
+      </c>
+      <c r="BD123">
+        <v>1.64</v>
+      </c>
+      <c r="BE123">
+        <v>8.6</v>
+      </c>
+      <c r="BF123">
+        <v>2.81</v>
+      </c>
+      <c r="BG123">
+        <v>1.16</v>
+      </c>
+      <c r="BH123">
+        <v>4.3</v>
+      </c>
+      <c r="BI123">
+        <v>1.31</v>
+      </c>
+      <c r="BJ123">
+        <v>3.05</v>
+      </c>
+      <c r="BK123">
+        <v>1.68</v>
+      </c>
+      <c r="BL123">
+        <v>2.34</v>
+      </c>
+      <c r="BM123">
+        <v>1.88</v>
+      </c>
+      <c r="BN123">
+        <v>1.86</v>
+      </c>
+      <c r="BO123">
+        <v>2.32</v>
+      </c>
+      <c r="BP123">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="222">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,9 @@
     <t>['39']</t>
   </si>
   <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -671,6 +674,12 @@
   </si>
   <si>
     <t>['28']</t>
+  </si>
+  <si>
+    <t>['26', '76']</t>
+  </si>
+  <si>
+    <t>['72']</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP123"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1494,7 +1503,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1575,7 +1584,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ3">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1700,7 +1709,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2524,7 +2533,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2602,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>0.67</v>
@@ -3014,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
         <v>1.6</v>
@@ -3142,7 +3151,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3348,7 +3357,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3554,7 +3563,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3760,7 +3769,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4047,7 +4056,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4584,7 +4593,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4790,7 +4799,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -4871,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="AQ19">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5074,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ20">
         <v>0.5</v>
@@ -5408,7 +5417,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5489,7 +5498,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ22">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR22">
         <v>1.69</v>
@@ -5614,7 +5623,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5898,7 +5907,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ24">
         <v>0.86</v>
@@ -6232,7 +6241,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6850,7 +6859,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7134,7 +7143,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>1</v>
@@ -7262,7 +7271,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7549,7 +7558,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ32">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR32">
         <v>1.17</v>
@@ -8167,7 +8176,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ35">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR35">
         <v>1.66</v>
@@ -8498,7 +8507,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8704,7 +8713,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -8988,7 +8997,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ39">
         <v>1.14</v>
@@ -9528,7 +9537,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9609,7 +9618,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ42">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
         <v>2.49</v>
@@ -10430,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.5</v>
@@ -10764,7 +10773,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10970,7 +10979,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11051,7 +11060,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ49">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR49">
         <v>1.47</v>
@@ -11382,7 +11391,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11588,7 +11597,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11666,7 +11675,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>1.14</v>
@@ -11872,7 +11881,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ53">
         <v>0.17</v>
@@ -12081,7 +12090,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ54">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR54">
         <v>1.72</v>
@@ -12618,7 +12627,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13030,7 +13039,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13442,7 +13451,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13932,7 +13941,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ63">
         <v>1</v>
@@ -14472,7 +14481,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14678,7 +14687,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14884,7 +14893,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15090,7 +15099,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15171,7 +15180,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR69">
         <v>1.87</v>
@@ -15374,7 +15383,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ70">
         <v>0.67</v>
@@ -15502,7 +15511,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15583,7 +15592,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR71">
         <v>2.01</v>
@@ -15786,7 +15795,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ72">
         <v>1</v>
@@ -16407,7 +16416,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR75">
         <v>1.88</v>
@@ -16532,7 +16541,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -18258,7 +18267,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ84">
         <v>0.33</v>
@@ -18386,7 +18395,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18464,7 +18473,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ85">
         <v>0.57</v>
@@ -18673,7 +18682,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ86">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR86">
         <v>2.07</v>
@@ -19004,7 +19013,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19291,7 +19300,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ89">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR89">
         <v>1.31</v>
@@ -19622,7 +19631,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19828,7 +19837,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -19906,7 +19915,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>0.67</v>
@@ -20034,7 +20043,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20446,7 +20455,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20652,7 +20661,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20939,7 +20948,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ97">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR97">
         <v>1.76</v>
@@ -22381,7 +22390,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ104">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AR104">
         <v>1.67</v>
@@ -22506,7 +22515,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22790,10 +22799,10 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR106">
         <v>1.79</v>
@@ -23124,7 +23133,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23330,7 +23339,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23408,7 +23417,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ109">
         <v>0.86</v>
@@ -23948,7 +23957,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24566,7 +24575,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24772,7 +24781,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25390,7 +25399,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25802,7 +25811,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26101,22 +26110,22 @@
         <v>2.72</v>
       </c>
       <c r="AU122">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV122">
         <v>3</v>
       </c>
       <c r="AW122">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AX122">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY122">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AZ122">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA122">
         <v>13</v>
@@ -26313,16 +26322,16 @@
         <v>4</v>
       </c>
       <c r="AW123">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX123">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY123">
+        <v>17</v>
+      </c>
+      <c r="AZ123">
         <v>11</v>
-      </c>
-      <c r="AZ123">
-        <v>10</v>
       </c>
       <c r="BA123">
         <v>7</v>
@@ -26371,6 +26380,624 @@
       </c>
       <c r="BP123">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7841156</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45829.66666666666</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124" t="s">
+        <v>78</v>
+      </c>
+      <c r="H124" t="s">
+        <v>80</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>1</v>
+      </c>
+      <c r="K124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>2</v>
+      </c>
+      <c r="N124">
+        <v>3</v>
+      </c>
+      <c r="O124" t="s">
+        <v>102</v>
+      </c>
+      <c r="P124" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q124">
+        <v>3.6</v>
+      </c>
+      <c r="R124">
+        <v>1.7</v>
+      </c>
+      <c r="S124">
+        <v>3.9</v>
+      </c>
+      <c r="T124">
+        <v>1.55</v>
+      </c>
+      <c r="U124">
+        <v>2.45</v>
+      </c>
+      <c r="V124">
+        <v>3.2</v>
+      </c>
+      <c r="W124">
+        <v>1.26</v>
+      </c>
+      <c r="X124">
+        <v>9.9</v>
+      </c>
+      <c r="Y124">
+        <v>1</v>
+      </c>
+      <c r="Z124">
+        <v>2.32</v>
+      </c>
+      <c r="AA124">
+        <v>2.95</v>
+      </c>
+      <c r="AB124">
+        <v>2.86</v>
+      </c>
+      <c r="AC124">
+        <v>1.1</v>
+      </c>
+      <c r="AD124">
+        <v>7</v>
+      </c>
+      <c r="AE124">
+        <v>1.57</v>
+      </c>
+      <c r="AF124">
+        <v>2.25</v>
+      </c>
+      <c r="AG124">
+        <v>2.2</v>
+      </c>
+      <c r="AH124">
+        <v>1.55</v>
+      </c>
+      <c r="AI124">
+        <v>2</v>
+      </c>
+      <c r="AJ124">
+        <v>1.75</v>
+      </c>
+      <c r="AK124">
+        <v>1.36</v>
+      </c>
+      <c r="AL124">
+        <v>1.36</v>
+      </c>
+      <c r="AM124">
+        <v>1.53</v>
+      </c>
+      <c r="AN124">
+        <v>2.33</v>
+      </c>
+      <c r="AO124">
+        <v>0.8</v>
+      </c>
+      <c r="AP124">
+        <v>2</v>
+      </c>
+      <c r="AQ124">
+        <v>1.17</v>
+      </c>
+      <c r="AR124">
+        <v>1.84</v>
+      </c>
+      <c r="AS124">
+        <v>1.31</v>
+      </c>
+      <c r="AT124">
+        <v>3.15</v>
+      </c>
+      <c r="AU124">
+        <v>6</v>
+      </c>
+      <c r="AV124">
+        <v>5</v>
+      </c>
+      <c r="AW124">
+        <v>10</v>
+      </c>
+      <c r="AX124">
+        <v>6</v>
+      </c>
+      <c r="AY124">
+        <v>16</v>
+      </c>
+      <c r="AZ124">
+        <v>11</v>
+      </c>
+      <c r="BA124">
+        <v>4</v>
+      </c>
+      <c r="BB124">
+        <v>2</v>
+      </c>
+      <c r="BC124">
+        <v>6</v>
+      </c>
+      <c r="BD124">
+        <v>2.2</v>
+      </c>
+      <c r="BE124">
+        <v>6.55</v>
+      </c>
+      <c r="BF124">
+        <v>2</v>
+      </c>
+      <c r="BG124">
+        <v>1.17</v>
+      </c>
+      <c r="BH124">
+        <v>4.2</v>
+      </c>
+      <c r="BI124">
+        <v>1.28</v>
+      </c>
+      <c r="BJ124">
+        <v>3.08</v>
+      </c>
+      <c r="BK124">
+        <v>1.57</v>
+      </c>
+      <c r="BL124">
+        <v>2.31</v>
+      </c>
+      <c r="BM124">
+        <v>2.02</v>
+      </c>
+      <c r="BN124">
+        <v>1.81</v>
+      </c>
+      <c r="BO124">
+        <v>2.36</v>
+      </c>
+      <c r="BP124">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7841155</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45829.77083333334</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125" t="s">
+        <v>88</v>
+      </c>
+      <c r="H125" t="s">
+        <v>71</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>1</v>
+      </c>
+      <c r="O125" t="s">
+        <v>97</v>
+      </c>
+      <c r="P125" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q125">
+        <v>2.8</v>
+      </c>
+      <c r="R125">
+        <v>1.96</v>
+      </c>
+      <c r="S125">
+        <v>3.6</v>
+      </c>
+      <c r="T125">
+        <v>1.4</v>
+      </c>
+      <c r="U125">
+        <v>2.6</v>
+      </c>
+      <c r="V125">
+        <v>3.1</v>
+      </c>
+      <c r="W125">
+        <v>1.35</v>
+      </c>
+      <c r="X125">
+        <v>8.6</v>
+      </c>
+      <c r="Y125">
+        <v>1.05</v>
+      </c>
+      <c r="Z125">
+        <v>2.2</v>
+      </c>
+      <c r="AA125">
+        <v>3.15</v>
+      </c>
+      <c r="AB125">
+        <v>3.65</v>
+      </c>
+      <c r="AC125">
+        <v>1.04</v>
+      </c>
+      <c r="AD125">
+        <v>6.81</v>
+      </c>
+      <c r="AE125">
+        <v>1.36</v>
+      </c>
+      <c r="AF125">
+        <v>3.1</v>
+      </c>
+      <c r="AG125">
+        <v>2.1</v>
+      </c>
+      <c r="AH125">
+        <v>1.65</v>
+      </c>
+      <c r="AI125">
+        <v>1.72</v>
+      </c>
+      <c r="AJ125">
+        <v>1.85</v>
+      </c>
+      <c r="AK125">
+        <v>1.36</v>
+      </c>
+      <c r="AL125">
+        <v>1.35</v>
+      </c>
+      <c r="AM125">
+        <v>1.62</v>
+      </c>
+      <c r="AN125">
+        <v>2.67</v>
+      </c>
+      <c r="AO125">
+        <v>0.33</v>
+      </c>
+      <c r="AP125">
+        <v>2.29</v>
+      </c>
+      <c r="AQ125">
+        <v>0.71</v>
+      </c>
+      <c r="AR125">
+        <v>1.3</v>
+      </c>
+      <c r="AS125">
+        <v>1.1</v>
+      </c>
+      <c r="AT125">
+        <v>2.4</v>
+      </c>
+      <c r="AU125">
+        <v>3</v>
+      </c>
+      <c r="AV125">
+        <v>8</v>
+      </c>
+      <c r="AW125">
+        <v>15</v>
+      </c>
+      <c r="AX125">
+        <v>14</v>
+      </c>
+      <c r="AY125">
+        <v>18</v>
+      </c>
+      <c r="AZ125">
+        <v>22</v>
+      </c>
+      <c r="BA125">
+        <v>7</v>
+      </c>
+      <c r="BB125">
+        <v>9</v>
+      </c>
+      <c r="BC125">
+        <v>16</v>
+      </c>
+      <c r="BD125">
+        <v>1.9</v>
+      </c>
+      <c r="BE125">
+        <v>7.7</v>
+      </c>
+      <c r="BF125">
+        <v>1.9</v>
+      </c>
+      <c r="BG125">
+        <v>1.2</v>
+      </c>
+      <c r="BH125">
+        <v>4.25</v>
+      </c>
+      <c r="BI125">
+        <v>1.31</v>
+      </c>
+      <c r="BJ125">
+        <v>3.02</v>
+      </c>
+      <c r="BK125">
+        <v>1.56</v>
+      </c>
+      <c r="BL125">
+        <v>2.25</v>
+      </c>
+      <c r="BM125">
+        <v>2</v>
+      </c>
+      <c r="BN125">
+        <v>1.78</v>
+      </c>
+      <c r="BO125">
+        <v>2.38</v>
+      </c>
+      <c r="BP125">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7841160</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45829.85416666666</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126" t="s">
+        <v>76</v>
+      </c>
+      <c r="H126" t="s">
+        <v>74</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>179</v>
+      </c>
+      <c r="P126" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q126">
+        <v>2.6</v>
+      </c>
+      <c r="R126">
+        <v>1.91</v>
+      </c>
+      <c r="S126">
+        <v>5.1</v>
+      </c>
+      <c r="T126">
+        <v>1.5</v>
+      </c>
+      <c r="U126">
+        <v>2.35</v>
+      </c>
+      <c r="V126">
+        <v>3.4</v>
+      </c>
+      <c r="W126">
+        <v>1.27</v>
+      </c>
+      <c r="X126">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y126">
+        <v>1.05</v>
+      </c>
+      <c r="Z126">
+        <v>1.91</v>
+      </c>
+      <c r="AA126">
+        <v>3.12</v>
+      </c>
+      <c r="AB126">
+        <v>3.5</v>
+      </c>
+      <c r="AC126">
+        <v>1.04</v>
+      </c>
+      <c r="AD126">
+        <v>6.85</v>
+      </c>
+      <c r="AE126">
+        <v>1.47</v>
+      </c>
+      <c r="AF126">
+        <v>2.6</v>
+      </c>
+      <c r="AG126">
+        <v>2.5</v>
+      </c>
+      <c r="AH126">
+        <v>1.57</v>
+      </c>
+      <c r="AI126">
+        <v>2.15</v>
+      </c>
+      <c r="AJ126">
+        <v>1.64</v>
+      </c>
+      <c r="AK126">
+        <v>1.36</v>
+      </c>
+      <c r="AL126">
+        <v>1.37</v>
+      </c>
+      <c r="AM126">
+        <v>1.85</v>
+      </c>
+      <c r="AN126">
+        <v>1.8</v>
+      </c>
+      <c r="AO126">
+        <v>0.83</v>
+      </c>
+      <c r="AP126">
+        <v>2</v>
+      </c>
+      <c r="AQ126">
+        <v>0.71</v>
+      </c>
+      <c r="AR126">
+        <v>1.99</v>
+      </c>
+      <c r="AS126">
+        <v>1.71</v>
+      </c>
+      <c r="AT126">
+        <v>3.7</v>
+      </c>
+      <c r="AU126">
+        <v>3</v>
+      </c>
+      <c r="AV126">
+        <v>6</v>
+      </c>
+      <c r="AW126">
+        <v>8</v>
+      </c>
+      <c r="AX126">
+        <v>16</v>
+      </c>
+      <c r="AY126">
+        <v>11</v>
+      </c>
+      <c r="AZ126">
+        <v>22</v>
+      </c>
+      <c r="BA126">
+        <v>2</v>
+      </c>
+      <c r="BB126">
+        <v>9</v>
+      </c>
+      <c r="BC126">
+        <v>11</v>
+      </c>
+      <c r="BD126">
+        <v>1.75</v>
+      </c>
+      <c r="BE126">
+        <v>6.75</v>
+      </c>
+      <c r="BF126">
+        <v>2.52</v>
+      </c>
+      <c r="BG126">
+        <v>1.22</v>
+      </c>
+      <c r="BH126">
+        <v>3.45</v>
+      </c>
+      <c r="BI126">
+        <v>1.31</v>
+      </c>
+      <c r="BJ126">
+        <v>2.92</v>
+      </c>
+      <c r="BK126">
+        <v>1.65</v>
+      </c>
+      <c r="BL126">
+        <v>2.25</v>
+      </c>
+      <c r="BM126">
+        <v>2</v>
+      </c>
+      <c r="BN126">
+        <v>1.75</v>
+      </c>
+      <c r="BO126">
+        <v>2.5</v>
+      </c>
+      <c r="BP126">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -556,6 +556,15 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['61', '77']</t>
+  </si>
+  <si>
+    <t>['88', '90+8']</t>
+  </si>
+  <si>
+    <t>['32', '71']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -680,6 +689,9 @@
   </si>
   <si>
     <t>['72']</t>
+  </si>
+  <si>
+    <t>['19']</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1503,7 +1515,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1709,7 +1721,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1993,10 +2005,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ5">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2533,7 +2545,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2820,7 +2832,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3151,7 +3163,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3229,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ11">
         <v>0.5</v>
@@ -3357,7 +3369,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3563,7 +3575,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3769,7 +3781,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4259,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ16">
         <v>0.86</v>
@@ -4468,7 +4480,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ17">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4593,7 +4605,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4799,7 +4811,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5417,7 +5429,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5623,7 +5635,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6113,7 +6125,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ25">
         <v>1.6</v>
@@ -6241,7 +6253,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6322,7 +6334,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ26">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6734,7 +6746,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ28">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR28">
         <v>1.84</v>
@@ -6859,7 +6871,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7271,7 +7283,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8507,7 +8519,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8585,7 +8597,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ37">
         <v>1</v>
@@ -8713,7 +8725,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9203,10 +9215,10 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ40">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR40">
         <v>1.82</v>
@@ -9537,7 +9549,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10233,7 +10245,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ45">
         <v>0.86</v>
@@ -10648,7 +10660,7 @@
         <v>1</v>
       </c>
       <c r="AQ47">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR47">
         <v>2.22</v>
@@ -10773,7 +10785,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10851,7 +10863,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -10979,7 +10991,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11391,7 +11403,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11597,7 +11609,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12293,7 +12305,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ55">
         <v>1.6</v>
@@ -12627,7 +12639,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13039,7 +13051,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13326,7 +13338,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ60">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR60">
         <v>1.78</v>
@@ -13451,7 +13463,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13532,7 +13544,7 @@
         <v>1</v>
       </c>
       <c r="AQ61">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -14356,7 +14368,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ65">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR65">
         <v>2.13</v>
@@ -14481,7 +14493,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14687,7 +14699,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14893,7 +14905,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15099,7 +15111,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15177,7 +15189,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ69">
         <v>0.71</v>
@@ -15386,7 +15398,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ70">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR70">
         <v>1.26</v>
@@ -15511,7 +15523,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16004,7 +16016,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR73">
         <v>1.75</v>
@@ -16541,7 +16553,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16825,7 +16837,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ77">
         <v>0.67</v>
@@ -17649,7 +17661,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ81">
         <v>0.5</v>
@@ -18270,7 +18282,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ84">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR84">
         <v>1.23</v>
@@ -18395,7 +18407,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18885,7 +18897,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ87">
         <v>0.86</v>
@@ -19013,7 +19025,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19506,7 +19518,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ90">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR90">
         <v>1.68</v>
@@ -19631,7 +19643,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19837,7 +19849,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20043,7 +20055,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20327,7 +20339,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20455,7 +20467,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20533,7 +20545,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ95">
         <v>1.67</v>
@@ -20661,7 +20673,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20742,7 +20754,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR96">
         <v>1.76</v>
@@ -22515,7 +22527,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23008,7 +23020,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ107">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -23133,7 +23145,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23339,7 +23351,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23626,7 +23638,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ110">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR110">
         <v>2.01</v>
@@ -23829,7 +23841,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ111">
         <v>0.5</v>
@@ -23957,7 +23969,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24575,7 +24587,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24781,7 +24793,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -24945,7 +24957,7 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>7841150</v>
+        <v>7841144</v>
       </c>
       <c r="C117" t="s">
         <v>68</v>
@@ -24960,190 +24972,190 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M117">
         <v>0</v>
       </c>
       <c r="N117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O117" t="s">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="P117" t="s">
         <v>97</v>
       </c>
       <c r="Q117">
-        <v>2.35</v>
+        <v>3.12</v>
       </c>
       <c r="R117">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S117">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="T117">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U117">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="V117">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="W117">
         <v>1.22</v>
       </c>
       <c r="X117">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="Y117">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Z117">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="AA117">
+        <v>2.85</v>
+      </c>
+      <c r="AB117">
+        <v>3.02</v>
+      </c>
+      <c r="AC117">
+        <v>1.09</v>
+      </c>
+      <c r="AD117">
+        <v>5.5</v>
+      </c>
+      <c r="AE117">
+        <v>1.5</v>
+      </c>
+      <c r="AF117">
+        <v>2.3</v>
+      </c>
+      <c r="AG117">
         <v>2.59</v>
       </c>
-      <c r="AB117">
-        <v>4.4</v>
-      </c>
-      <c r="AC117">
-        <v>1.14</v>
-      </c>
-      <c r="AD117">
-        <v>5</v>
-      </c>
-      <c r="AE117">
-        <v>1.48</v>
-      </c>
-      <c r="AF117">
-        <v>2.37</v>
-      </c>
-      <c r="AG117">
-        <v>2.55</v>
-      </c>
       <c r="AH117">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI117">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AJ117">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AK117">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL117">
         <v>1.37</v>
       </c>
       <c r="AM117">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AN117">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="AO117">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="AP117">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="AQ117">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR117">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AS117">
-        <v>1.66</v>
+        <v>1.24</v>
       </c>
       <c r="AT117">
-        <v>3.66</v>
+        <v>3.14</v>
       </c>
       <c r="AU117">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV117">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AW117">
+        <v>9</v>
+      </c>
+      <c r="AX117">
+        <v>7</v>
+      </c>
+      <c r="AY117">
+        <v>14</v>
+      </c>
+      <c r="AZ117">
+        <v>9</v>
+      </c>
+      <c r="BA117">
         <v>4</v>
       </c>
-      <c r="AX117">
+      <c r="BB117">
         <v>5</v>
       </c>
-      <c r="AY117">
-        <v>7</v>
-      </c>
-      <c r="AZ117">
-        <v>15</v>
-      </c>
-      <c r="BA117">
-        <v>2</v>
-      </c>
-      <c r="BB117">
-        <v>4</v>
-      </c>
       <c r="BC117">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD117">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="BE117">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BF117">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BG117">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BH117">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BI117">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="BJ117">
-        <v>2.55</v>
+        <v>2.98</v>
       </c>
       <c r="BK117">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="BL117">
-        <v>2.01</v>
+        <v>2.27</v>
       </c>
       <c r="BM117">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="BN117">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="BO117">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="BP117">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="118" spans="1:68">
@@ -25151,7 +25163,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7841144</v>
+        <v>7841150</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25166,190 +25178,190 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H118" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M118">
         <v>0</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O118" t="s">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="P118" t="s">
         <v>97</v>
       </c>
       <c r="Q118">
-        <v>3.12</v>
+        <v>2.35</v>
       </c>
       <c r="R118">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S118">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="T118">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U118">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="V118">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="W118">
         <v>1.22</v>
       </c>
       <c r="X118">
-        <v>12.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y118">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Z118">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AA118">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AB118">
-        <v>3.02</v>
+        <v>4.4</v>
       </c>
       <c r="AC118">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AD118">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AE118">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF118">
+        <v>2.37</v>
+      </c>
+      <c r="AG118">
+        <v>2.55</v>
+      </c>
+      <c r="AH118">
+        <v>1.45</v>
+      </c>
+      <c r="AI118">
         <v>2.3</v>
       </c>
-      <c r="AG118">
-        <v>2.59</v>
-      </c>
-      <c r="AH118">
-        <v>1.44</v>
-      </c>
-      <c r="AI118">
-        <v>2.25</v>
-      </c>
       <c r="AJ118">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AK118">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL118">
         <v>1.37</v>
       </c>
       <c r="AM118">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AN118">
+        <v>2.33</v>
+      </c>
+      <c r="AO118">
         <v>1.6</v>
       </c>
-      <c r="AO118">
-        <v>1.17</v>
-      </c>
       <c r="AP118">
-        <v>1.5</v>
+        <v>2.43</v>
       </c>
       <c r="AQ118">
         <v>1.14</v>
       </c>
       <c r="AR118">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AS118">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="AT118">
-        <v>3.14</v>
+        <v>3.66</v>
       </c>
       <c r="AU118">
+        <v>3</v>
+      </c>
+      <c r="AV118">
+        <v>10</v>
+      </c>
+      <c r="AW118">
+        <v>4</v>
+      </c>
+      <c r="AX118">
         <v>5</v>
       </c>
-      <c r="AV118">
-        <v>2</v>
-      </c>
-      <c r="AW118">
-        <v>9</v>
-      </c>
-      <c r="AX118">
+      <c r="AY118">
         <v>7</v>
       </c>
-      <c r="AY118">
-        <v>14</v>
-      </c>
       <c r="AZ118">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BA118">
+        <v>2</v>
+      </c>
+      <c r="BB118">
         <v>4</v>
       </c>
-      <c r="BB118">
-        <v>5</v>
-      </c>
       <c r="BC118">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD118">
+        <v>1.53</v>
+      </c>
+      <c r="BE118">
+        <v>7</v>
+      </c>
+      <c r="BF118">
+        <v>2.9</v>
+      </c>
+      <c r="BG118">
+        <v>1.22</v>
+      </c>
+      <c r="BH118">
+        <v>3.6</v>
+      </c>
+      <c r="BI118">
+        <v>1.45</v>
+      </c>
+      <c r="BJ118">
+        <v>2.55</v>
+      </c>
+      <c r="BK118">
+        <v>1.63</v>
+      </c>
+      <c r="BL118">
+        <v>2.01</v>
+      </c>
+      <c r="BM118">
+        <v>2.1</v>
+      </c>
+      <c r="BN118">
         <v>1.67</v>
       </c>
-      <c r="BE118">
-        <v>8.6</v>
-      </c>
-      <c r="BF118">
-        <v>2.8</v>
-      </c>
-      <c r="BG118">
-        <v>1.18</v>
-      </c>
-      <c r="BH118">
-        <v>4.1</v>
-      </c>
-      <c r="BI118">
-        <v>1.36</v>
-      </c>
-      <c r="BJ118">
-        <v>2.98</v>
-      </c>
-      <c r="BK118">
-        <v>1.73</v>
-      </c>
-      <c r="BL118">
-        <v>2.27</v>
-      </c>
-      <c r="BM118">
-        <v>1.93</v>
-      </c>
-      <c r="BN118">
-        <v>1.86</v>
-      </c>
       <c r="BO118">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BP118">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="119" spans="1:68">
@@ -25399,7 +25411,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25811,7 +25823,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26429,7 +26441,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26635,7 +26647,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -26998,6 +27010,624 @@
       </c>
       <c r="BP126">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7841152</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45830.66666666666</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
+        <v>73</v>
+      </c>
+      <c r="H127" t="s">
+        <v>81</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>2</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>2</v>
+      </c>
+      <c r="O127" t="s">
+        <v>180</v>
+      </c>
+      <c r="P127" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q127">
+        <v>2.62</v>
+      </c>
+      <c r="R127">
+        <v>1.91</v>
+      </c>
+      <c r="S127">
+        <v>5</v>
+      </c>
+      <c r="T127">
+        <v>1.55</v>
+      </c>
+      <c r="U127">
+        <v>2.26</v>
+      </c>
+      <c r="V127">
+        <v>3.66</v>
+      </c>
+      <c r="W127">
+        <v>1.22</v>
+      </c>
+      <c r="X127">
+        <v>7.8</v>
+      </c>
+      <c r="Y127">
+        <v>1.01</v>
+      </c>
+      <c r="Z127">
+        <v>1.91</v>
+      </c>
+      <c r="AA127">
+        <v>2.82</v>
+      </c>
+      <c r="AB127">
+        <v>4.1</v>
+      </c>
+      <c r="AC127">
+        <v>1.07</v>
+      </c>
+      <c r="AD127">
+        <v>5.87</v>
+      </c>
+      <c r="AE127">
+        <v>1.53</v>
+      </c>
+      <c r="AF127">
+        <v>2.25</v>
+      </c>
+      <c r="AG127">
+        <v>2.85</v>
+      </c>
+      <c r="AH127">
+        <v>1.37</v>
+      </c>
+      <c r="AI127">
+        <v>2.27</v>
+      </c>
+      <c r="AJ127">
+        <v>1.56</v>
+      </c>
+      <c r="AK127">
+        <v>1.36</v>
+      </c>
+      <c r="AL127">
+        <v>1.35</v>
+      </c>
+      <c r="AM127">
+        <v>1.86</v>
+      </c>
+      <c r="AN127">
+        <v>2.6</v>
+      </c>
+      <c r="AO127">
+        <v>1.33</v>
+      </c>
+      <c r="AP127">
+        <v>2.67</v>
+      </c>
+      <c r="AQ127">
+        <v>1.14</v>
+      </c>
+      <c r="AR127">
+        <v>1.46</v>
+      </c>
+      <c r="AS127">
+        <v>1.71</v>
+      </c>
+      <c r="AT127">
+        <v>3.17</v>
+      </c>
+      <c r="AU127">
+        <v>4</v>
+      </c>
+      <c r="AV127">
+        <v>3</v>
+      </c>
+      <c r="AW127">
+        <v>8</v>
+      </c>
+      <c r="AX127">
+        <v>6</v>
+      </c>
+      <c r="AY127">
+        <v>12</v>
+      </c>
+      <c r="AZ127">
+        <v>9</v>
+      </c>
+      <c r="BA127">
+        <v>5</v>
+      </c>
+      <c r="BB127">
+        <v>7</v>
+      </c>
+      <c r="BC127">
+        <v>12</v>
+      </c>
+      <c r="BD127">
+        <v>1.67</v>
+      </c>
+      <c r="BE127">
+        <v>7</v>
+      </c>
+      <c r="BF127">
+        <v>2.99</v>
+      </c>
+      <c r="BG127">
+        <v>1.19</v>
+      </c>
+      <c r="BH127">
+        <v>4.1</v>
+      </c>
+      <c r="BI127">
+        <v>1.38</v>
+      </c>
+      <c r="BJ127">
+        <v>2.95</v>
+      </c>
+      <c r="BK127">
+        <v>1.55</v>
+      </c>
+      <c r="BL127">
+        <v>2.28</v>
+      </c>
+      <c r="BM127">
+        <v>1.86</v>
+      </c>
+      <c r="BN127">
+        <v>1.73</v>
+      </c>
+      <c r="BO127">
+        <v>2.55</v>
+      </c>
+      <c r="BP127">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7841154</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45830.66666666666</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128" t="s">
+        <v>79</v>
+      </c>
+      <c r="H128" t="s">
+        <v>77</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>2</v>
+      </c>
+      <c r="O128" t="s">
+        <v>181</v>
+      </c>
+      <c r="P128" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q128">
+        <v>2.58</v>
+      </c>
+      <c r="R128">
+        <v>1.95</v>
+      </c>
+      <c r="S128">
+        <v>4.55</v>
+      </c>
+      <c r="T128">
+        <v>1.56</v>
+      </c>
+      <c r="U128">
+        <v>2.5</v>
+      </c>
+      <c r="V128">
+        <v>3.25</v>
+      </c>
+      <c r="W128">
+        <v>1.28</v>
+      </c>
+      <c r="X128">
+        <v>8.5</v>
+      </c>
+      <c r="Y128">
+        <v>1</v>
+      </c>
+      <c r="Z128">
+        <v>1.77</v>
+      </c>
+      <c r="AA128">
+        <v>2.94</v>
+      </c>
+      <c r="AB128">
+        <v>4.6</v>
+      </c>
+      <c r="AC128">
+        <v>1.04</v>
+      </c>
+      <c r="AD128">
+        <v>7</v>
+      </c>
+      <c r="AE128">
+        <v>1.53</v>
+      </c>
+      <c r="AF128">
+        <v>2.25</v>
+      </c>
+      <c r="AG128">
+        <v>2.46</v>
+      </c>
+      <c r="AH128">
+        <v>1.48</v>
+      </c>
+      <c r="AI128">
+        <v>2.1</v>
+      </c>
+      <c r="AJ128">
+        <v>1.63</v>
+      </c>
+      <c r="AK128">
+        <v>1.35</v>
+      </c>
+      <c r="AL128">
+        <v>1.35</v>
+      </c>
+      <c r="AM128">
+        <v>1.91</v>
+      </c>
+      <c r="AN128">
+        <v>1.5</v>
+      </c>
+      <c r="AO128">
+        <v>0.33</v>
+      </c>
+      <c r="AP128">
+        <v>1.71</v>
+      </c>
+      <c r="AQ128">
+        <v>0.29</v>
+      </c>
+      <c r="AR128">
+        <v>1.85</v>
+      </c>
+      <c r="AS128">
+        <v>1.33</v>
+      </c>
+      <c r="AT128">
+        <v>3.18</v>
+      </c>
+      <c r="AU128">
+        <v>7</v>
+      </c>
+      <c r="AV128">
+        <v>0</v>
+      </c>
+      <c r="AW128">
+        <v>15</v>
+      </c>
+      <c r="AX128">
+        <v>7</v>
+      </c>
+      <c r="AY128">
+        <v>22</v>
+      </c>
+      <c r="AZ128">
+        <v>7</v>
+      </c>
+      <c r="BA128">
+        <v>8</v>
+      </c>
+      <c r="BB128">
+        <v>1</v>
+      </c>
+      <c r="BC128">
+        <v>9</v>
+      </c>
+      <c r="BD128">
+        <v>1.59</v>
+      </c>
+      <c r="BE128">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF128">
+        <v>2.76</v>
+      </c>
+      <c r="BG128">
+        <v>1.22</v>
+      </c>
+      <c r="BH128">
+        <v>3.8</v>
+      </c>
+      <c r="BI128">
+        <v>1.38</v>
+      </c>
+      <c r="BJ128">
+        <v>2.8</v>
+      </c>
+      <c r="BK128">
+        <v>1.64</v>
+      </c>
+      <c r="BL128">
+        <v>2.23</v>
+      </c>
+      <c r="BM128">
+        <v>2.03</v>
+      </c>
+      <c r="BN128">
+        <v>1.77</v>
+      </c>
+      <c r="BO128">
+        <v>2.4</v>
+      </c>
+      <c r="BP128">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7841158</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45830.75</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
+        <v>84</v>
+      </c>
+      <c r="H129" t="s">
+        <v>83</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>2</v>
+      </c>
+      <c r="M129">
+        <v>1</v>
+      </c>
+      <c r="N129">
+        <v>3</v>
+      </c>
+      <c r="O129" t="s">
+        <v>182</v>
+      </c>
+      <c r="P129" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q129">
+        <v>3.8</v>
+      </c>
+      <c r="R129">
+        <v>1.75</v>
+      </c>
+      <c r="S129">
+        <v>3.5</v>
+      </c>
+      <c r="T129">
+        <v>1.65</v>
+      </c>
+      <c r="U129">
+        <v>2.1</v>
+      </c>
+      <c r="V129">
+        <v>3.8</v>
+      </c>
+      <c r="W129">
+        <v>1.22</v>
+      </c>
+      <c r="X129">
+        <v>10.5</v>
+      </c>
+      <c r="Y129">
+        <v>1.01</v>
+      </c>
+      <c r="Z129">
+        <v>3.04</v>
+      </c>
+      <c r="AA129">
+        <v>2.91</v>
+      </c>
+      <c r="AB129">
+        <v>2.6</v>
+      </c>
+      <c r="AC129">
+        <v>1.12</v>
+      </c>
+      <c r="AD129">
+        <v>5.5</v>
+      </c>
+      <c r="AE129">
+        <v>1.55</v>
+      </c>
+      <c r="AF129">
+        <v>2.2</v>
+      </c>
+      <c r="AG129">
+        <v>2.87</v>
+      </c>
+      <c r="AH129">
+        <v>1.34</v>
+      </c>
+      <c r="AI129">
+        <v>2.27</v>
+      </c>
+      <c r="AJ129">
+        <v>1.62</v>
+      </c>
+      <c r="AK129">
+        <v>1.42</v>
+      </c>
+      <c r="AL129">
+        <v>1.39</v>
+      </c>
+      <c r="AM129">
+        <v>1.37</v>
+      </c>
+      <c r="AN129">
+        <v>1.5</v>
+      </c>
+      <c r="AO129">
+        <v>0.67</v>
+      </c>
+      <c r="AP129">
+        <v>1.71</v>
+      </c>
+      <c r="AQ129">
+        <v>0.57</v>
+      </c>
+      <c r="AR129">
+        <v>1.61</v>
+      </c>
+      <c r="AS129">
+        <v>1.22</v>
+      </c>
+      <c r="AT129">
+        <v>2.83</v>
+      </c>
+      <c r="AU129">
+        <v>3</v>
+      </c>
+      <c r="AV129">
+        <v>3</v>
+      </c>
+      <c r="AW129">
+        <v>8</v>
+      </c>
+      <c r="AX129">
+        <v>11</v>
+      </c>
+      <c r="AY129">
+        <v>11</v>
+      </c>
+      <c r="AZ129">
+        <v>14</v>
+      </c>
+      <c r="BA129">
+        <v>8</v>
+      </c>
+      <c r="BB129">
+        <v>6</v>
+      </c>
+      <c r="BC129">
+        <v>14</v>
+      </c>
+      <c r="BD129">
+        <v>1.78</v>
+      </c>
+      <c r="BE129">
+        <v>6.7</v>
+      </c>
+      <c r="BF129">
+        <v>2.52</v>
+      </c>
+      <c r="BG129">
+        <v>1.22</v>
+      </c>
+      <c r="BH129">
+        <v>3.8</v>
+      </c>
+      <c r="BI129">
+        <v>1.42</v>
+      </c>
+      <c r="BJ129">
+        <v>2.65</v>
+      </c>
+      <c r="BK129">
+        <v>1.63</v>
+      </c>
+      <c r="BL129">
+        <v>2.05</v>
+      </c>
+      <c r="BM129">
+        <v>2.07</v>
+      </c>
+      <c r="BN129">
+        <v>1.69</v>
+      </c>
+      <c r="BO129">
+        <v>2.63</v>
+      </c>
+      <c r="BP129">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -27158,16 +27158,16 @@
         <v>3</v>
       </c>
       <c r="AW127">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX127">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY127">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ127">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BA127">
         <v>5</v>
@@ -27364,13 +27364,13 @@
         <v>0</v>
       </c>
       <c r="AW128">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AX128">
         <v>7</v>
       </c>
       <c r="AY128">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ128">
         <v>7</v>
@@ -27567,19 +27567,19 @@
         <v>3</v>
       </c>
       <c r="AV129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW129">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX129">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AY129">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ129">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA129">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="227">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -565,6 +565,9 @@
     <t>['32', '71']</t>
   </si>
   <si>
+    <t>['62', '31']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1053,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP129"/>
+  <dimension ref="A1:BP130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1515,7 +1518,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1721,7 +1724,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2545,7 +2548,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3038,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="AQ10">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3163,7 +3166,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3369,7 +3372,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3575,7 +3578,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3781,7 +3784,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4605,7 +4608,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4683,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ18">
         <v>1.67</v>
@@ -4811,7 +4814,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5429,7 +5432,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5635,7 +5638,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6128,7 +6131,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ25">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR25">
         <v>1.41</v>
@@ -6253,7 +6256,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6871,7 +6874,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7283,7 +7286,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7567,7 +7570,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ32">
         <v>0.71</v>
@@ -8519,7 +8522,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8725,7 +8728,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9549,7 +9552,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10785,7 +10788,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10991,7 +10994,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11403,7 +11406,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11609,7 +11612,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12308,7 +12311,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ55">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR55">
         <v>1.76</v>
@@ -12639,7 +12642,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12923,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ58">
         <v>0.5</v>
@@ -13051,7 +13054,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13463,7 +13466,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14493,7 +14496,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14699,7 +14702,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14905,7 +14908,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15111,7 +15114,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15523,7 +15526,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16219,7 +16222,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ74">
         <v>0.67</v>
@@ -16553,7 +16556,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16634,7 +16637,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR76">
         <v>1.64</v>
@@ -18407,7 +18410,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19025,7 +19028,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19643,7 +19646,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19849,7 +19852,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20055,7 +20058,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20136,7 +20139,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
         <v>1.7</v>
@@ -20467,7 +20470,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20673,7 +20676,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20957,7 +20960,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AQ97">
         <v>1.17</v>
@@ -22527,7 +22530,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23145,7 +23148,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23351,7 +23354,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23969,7 +23972,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24587,7 +24590,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24793,7 +24796,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25411,7 +25414,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25823,7 +25826,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26441,7 +26444,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26647,7 +26650,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27471,7 +27474,7 @@
         <v>182</v>
       </c>
       <c r="P129" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q129">
         <v>3.8</v>
@@ -27628,6 +27631,212 @@
       </c>
       <c r="BP129">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7841157</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45831.79166666666</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130" t="s">
+        <v>86</v>
+      </c>
+      <c r="H130" t="s">
+        <v>85</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>2</v>
+      </c>
+      <c r="O130" t="s">
+        <v>183</v>
+      </c>
+      <c r="P130" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q130">
+        <v>3.7</v>
+      </c>
+      <c r="R130">
+        <v>1.67</v>
+      </c>
+      <c r="S130">
+        <v>3.9</v>
+      </c>
+      <c r="T130">
+        <v>1.71</v>
+      </c>
+      <c r="U130">
+        <v>2.07</v>
+      </c>
+      <c r="V130">
+        <v>4.7</v>
+      </c>
+      <c r="W130">
+        <v>1.14</v>
+      </c>
+      <c r="X130">
+        <v>8.5</v>
+      </c>
+      <c r="Y130">
+        <v>1.02</v>
+      </c>
+      <c r="Z130">
+        <v>2.95</v>
+      </c>
+      <c r="AA130">
+        <v>2.6</v>
+      </c>
+      <c r="AB130">
+        <v>2.8</v>
+      </c>
+      <c r="AC130">
+        <v>1.17</v>
+      </c>
+      <c r="AD130">
+        <v>4.8</v>
+      </c>
+      <c r="AE130">
+        <v>1.75</v>
+      </c>
+      <c r="AF130">
+        <v>2</v>
+      </c>
+      <c r="AG130">
+        <v>3.05</v>
+      </c>
+      <c r="AH130">
+        <v>1.3</v>
+      </c>
+      <c r="AI130">
+        <v>2.57</v>
+      </c>
+      <c r="AJ130">
+        <v>1.5</v>
+      </c>
+      <c r="AK130">
+        <v>1.36</v>
+      </c>
+      <c r="AL130">
+        <v>1.41</v>
+      </c>
+      <c r="AM130">
+        <v>1.44</v>
+      </c>
+      <c r="AN130">
+        <v>1.6</v>
+      </c>
+      <c r="AO130">
+        <v>1.6</v>
+      </c>
+      <c r="AP130">
+        <v>1.83</v>
+      </c>
+      <c r="AQ130">
+        <v>1.33</v>
+      </c>
+      <c r="AR130">
+        <v>1.68</v>
+      </c>
+      <c r="AS130">
+        <v>1.2</v>
+      </c>
+      <c r="AT130">
+        <v>2.88</v>
+      </c>
+      <c r="AU130">
+        <v>6</v>
+      </c>
+      <c r="AV130">
+        <v>2</v>
+      </c>
+      <c r="AW130">
+        <v>11</v>
+      </c>
+      <c r="AX130">
+        <v>9</v>
+      </c>
+      <c r="AY130">
+        <v>17</v>
+      </c>
+      <c r="AZ130">
+        <v>11</v>
+      </c>
+      <c r="BA130">
+        <v>2</v>
+      </c>
+      <c r="BB130">
+        <v>1</v>
+      </c>
+      <c r="BC130">
+        <v>3</v>
+      </c>
+      <c r="BD130">
+        <v>1.6</v>
+      </c>
+      <c r="BE130">
+        <v>6.75</v>
+      </c>
+      <c r="BF130">
+        <v>2.46</v>
+      </c>
+      <c r="BG130">
+        <v>1.22</v>
+      </c>
+      <c r="BH130">
+        <v>3.2</v>
+      </c>
+      <c r="BI130">
+        <v>1.48</v>
+      </c>
+      <c r="BJ130">
+        <v>2.2</v>
+      </c>
+      <c r="BK130">
+        <v>2.03</v>
+      </c>
+      <c r="BL130">
+        <v>1.94</v>
+      </c>
+      <c r="BM130">
+        <v>2.26</v>
+      </c>
+      <c r="BN130">
+        <v>1.59</v>
+      </c>
+      <c r="BO130">
+        <v>3</v>
+      </c>
+      <c r="BP130">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -696,6 +696,9 @@
   <si>
     <t>['19']</t>
   </si>
+  <si>
+    <t>['40', '90+5']</t>
+  </si>
 </sst>
 </file>
 
@@ -1056,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP130"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1390,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ2">
         <v>0.17</v>
@@ -3247,7 +3250,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ11">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -6334,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ26">
         <v>0.57</v>
@@ -6543,7 +6546,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ27">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR27">
         <v>1.99</v>
@@ -7985,7 +7988,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ34">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR34">
         <v>2.24</v>
@@ -13132,7 +13135,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -14162,7 +14165,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ64">
         <v>1.14</v>
@@ -14989,7 +14992,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ68">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -17870,7 +17873,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ82">
         <v>0.86</v>
@@ -18079,7 +18082,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ83">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR83">
         <v>1.64</v>
@@ -23020,7 +23023,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ107">
         <v>0.29</v>
@@ -23847,7 +23850,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ111">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -27161,16 +27164,16 @@
         <v>3</v>
       </c>
       <c r="AW127">
+        <v>8</v>
+      </c>
+      <c r="AX127">
         <v>6</v>
       </c>
-      <c r="AX127">
-        <v>2</v>
-      </c>
       <c r="AY127">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ127">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA127">
         <v>5</v>
@@ -27367,13 +27370,13 @@
         <v>0</v>
       </c>
       <c r="AW128">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AX128">
         <v>7</v>
       </c>
       <c r="AY128">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AZ128">
         <v>7</v>
@@ -27570,19 +27573,19 @@
         <v>3</v>
       </c>
       <c r="AV129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW129">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX129">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY129">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ129">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA129">
         <v>8</v>
@@ -27776,19 +27779,19 @@
         <v>6</v>
       </c>
       <c r="AV130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW130">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX130">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY130">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ130">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA130">
         <v>2</v>
@@ -27837,6 +27840,212 @@
       </c>
       <c r="BP130">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7841153</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45831.875</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>70</v>
+      </c>
+      <c r="H131" t="s">
+        <v>87</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
+      <c r="N131">
+        <v>3</v>
+      </c>
+      <c r="O131" t="s">
+        <v>177</v>
+      </c>
+      <c r="P131" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q131">
+        <v>2.38</v>
+      </c>
+      <c r="R131">
+        <v>2.1</v>
+      </c>
+      <c r="S131">
+        <v>5.5</v>
+      </c>
+      <c r="T131">
+        <v>1.4</v>
+      </c>
+      <c r="U131">
+        <v>2.6</v>
+      </c>
+      <c r="V131">
+        <v>3.45</v>
+      </c>
+      <c r="W131">
+        <v>1.33</v>
+      </c>
+      <c r="X131">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y131">
+        <v>1.06</v>
+      </c>
+      <c r="Z131">
+        <v>1.52</v>
+      </c>
+      <c r="AA131">
+        <v>3.51</v>
+      </c>
+      <c r="AB131">
+        <v>5.7</v>
+      </c>
+      <c r="AC131">
+        <v>1.01</v>
+      </c>
+      <c r="AD131">
+        <v>8</v>
+      </c>
+      <c r="AE131">
+        <v>1.4</v>
+      </c>
+      <c r="AF131">
+        <v>2.75</v>
+      </c>
+      <c r="AG131">
+        <v>2.38</v>
+      </c>
+      <c r="AH131">
+        <v>1.54</v>
+      </c>
+      <c r="AI131">
+        <v>2.05</v>
+      </c>
+      <c r="AJ131">
+        <v>1.73</v>
+      </c>
+      <c r="AK131">
+        <v>1.14</v>
+      </c>
+      <c r="AL131">
+        <v>1.25</v>
+      </c>
+      <c r="AM131">
+        <v>2.12</v>
+      </c>
+      <c r="AN131">
+        <v>2.67</v>
+      </c>
+      <c r="AO131">
+        <v>0.5</v>
+      </c>
+      <c r="AP131">
+        <v>2.29</v>
+      </c>
+      <c r="AQ131">
+        <v>0.86</v>
+      </c>
+      <c r="AR131">
+        <v>1.55</v>
+      </c>
+      <c r="AS131">
+        <v>1.26</v>
+      </c>
+      <c r="AT131">
+        <v>2.81</v>
+      </c>
+      <c r="AU131">
+        <v>3</v>
+      </c>
+      <c r="AV131">
+        <v>5</v>
+      </c>
+      <c r="AW131">
+        <v>10</v>
+      </c>
+      <c r="AX131">
+        <v>12</v>
+      </c>
+      <c r="AY131">
+        <v>13</v>
+      </c>
+      <c r="AZ131">
+        <v>17</v>
+      </c>
+      <c r="BA131">
+        <v>4</v>
+      </c>
+      <c r="BB131">
+        <v>4</v>
+      </c>
+      <c r="BC131">
+        <v>8</v>
+      </c>
+      <c r="BD131">
+        <v>1.42</v>
+      </c>
+      <c r="BE131">
+        <v>8</v>
+      </c>
+      <c r="BF131">
+        <v>3.8</v>
+      </c>
+      <c r="BG131">
+        <v>1.18</v>
+      </c>
+      <c r="BH131">
+        <v>4.33</v>
+      </c>
+      <c r="BI131">
+        <v>1.28</v>
+      </c>
+      <c r="BJ131">
+        <v>3.22</v>
+      </c>
+      <c r="BK131">
+        <v>1.5</v>
+      </c>
+      <c r="BL131">
+        <v>2.41</v>
+      </c>
+      <c r="BM131">
+        <v>1.81</v>
+      </c>
+      <c r="BN131">
+        <v>1.93</v>
+      </c>
+      <c r="BO131">
+        <v>2.25</v>
+      </c>
+      <c r="BP131">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -699,6 +699,9 @@
   <si>
     <t>['40', '90+5']</t>
   </si>
+  <si>
+    <t>['25', '47']</t>
+  </si>
 </sst>
 </file>
 
@@ -1059,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2217,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ6">
         <v>0.57</v>
@@ -5104,7 +5107,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -6749,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ28">
         <v>0.29</v>
@@ -10460,7 +10463,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR46">
         <v>1.53</v>
@@ -12932,7 +12935,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ58">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR58">
         <v>1.48</v>
@@ -13341,7 +13344,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ60">
         <v>1.14</v>
@@ -17049,7 +17052,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ78">
         <v>0.83</v>
@@ -17670,7 +17673,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ81">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR81">
         <v>1.39</v>
@@ -21169,7 +21172,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ98">
         <v>0.67</v>
@@ -21378,7 +21381,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR99">
         <v>2.28</v>
@@ -24056,7 +24059,7 @@
         <v>2</v>
       </c>
       <c r="AQ112">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR112">
         <v>1.8</v>
@@ -24465,7 +24468,7 @@
         <v>2</v>
       </c>
       <c r="AP114">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ114">
         <v>1.67</v>
@@ -28046,6 +28049,212 @@
       </c>
       <c r="BP131">
         <v>1.6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7841168</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45834.89930555555</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
+        <v>74</v>
+      </c>
+      <c r="H132" t="s">
+        <v>75</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>2</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>2</v>
+      </c>
+      <c r="N132">
+        <v>3</v>
+      </c>
+      <c r="O132" t="s">
+        <v>134</v>
+      </c>
+      <c r="P132" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q132">
+        <v>2.88</v>
+      </c>
+      <c r="R132">
+        <v>1.95</v>
+      </c>
+      <c r="S132">
+        <v>3.75</v>
+      </c>
+      <c r="T132">
+        <v>1.47</v>
+      </c>
+      <c r="U132">
+        <v>2.4</v>
+      </c>
+      <c r="V132">
+        <v>3.2</v>
+      </c>
+      <c r="W132">
+        <v>1.3</v>
+      </c>
+      <c r="X132">
+        <v>8.75</v>
+      </c>
+      <c r="Y132">
+        <v>1</v>
+      </c>
+      <c r="Z132">
+        <v>2.04</v>
+      </c>
+      <c r="AA132">
+        <v>3</v>
+      </c>
+      <c r="AB132">
+        <v>3.2</v>
+      </c>
+      <c r="AC132">
+        <v>1.03</v>
+      </c>
+      <c r="AD132">
+        <v>6.5</v>
+      </c>
+      <c r="AE132">
+        <v>1.38</v>
+      </c>
+      <c r="AF132">
+        <v>2.6</v>
+      </c>
+      <c r="AG132">
+        <v>2.35</v>
+      </c>
+      <c r="AH132">
+        <v>1.53</v>
+      </c>
+      <c r="AI132">
+        <v>2</v>
+      </c>
+      <c r="AJ132">
+        <v>1.8</v>
+      </c>
+      <c r="AK132">
+        <v>1.33</v>
+      </c>
+      <c r="AL132">
+        <v>1.33</v>
+      </c>
+      <c r="AM132">
+        <v>1.62</v>
+      </c>
+      <c r="AN132">
+        <v>2.67</v>
+      </c>
+      <c r="AO132">
+        <v>0.5</v>
+      </c>
+      <c r="AP132">
+        <v>2.29</v>
+      </c>
+      <c r="AQ132">
+        <v>0.86</v>
+      </c>
+      <c r="AR132">
+        <v>1.69</v>
+      </c>
+      <c r="AS132">
+        <v>1.67</v>
+      </c>
+      <c r="AT132">
+        <v>3.36</v>
+      </c>
+      <c r="AU132">
+        <v>7</v>
+      </c>
+      <c r="AV132">
+        <v>5</v>
+      </c>
+      <c r="AW132">
+        <v>19</v>
+      </c>
+      <c r="AX132">
+        <v>6</v>
+      </c>
+      <c r="AY132">
+        <v>26</v>
+      </c>
+      <c r="AZ132">
+        <v>11</v>
+      </c>
+      <c r="BA132">
+        <v>14</v>
+      </c>
+      <c r="BB132">
+        <v>1</v>
+      </c>
+      <c r="BC132">
+        <v>15</v>
+      </c>
+      <c r="BD132">
+        <v>1.74</v>
+      </c>
+      <c r="BE132">
+        <v>8</v>
+      </c>
+      <c r="BF132">
+        <v>2.55</v>
+      </c>
+      <c r="BG132">
+        <v>1.25</v>
+      </c>
+      <c r="BH132">
+        <v>3.6</v>
+      </c>
+      <c r="BI132">
+        <v>1.31</v>
+      </c>
+      <c r="BJ132">
+        <v>3.1</v>
+      </c>
+      <c r="BK132">
+        <v>1.55</v>
+      </c>
+      <c r="BL132">
+        <v>2.2</v>
+      </c>
+      <c r="BM132">
+        <v>2.05</v>
+      </c>
+      <c r="BN132">
+        <v>1.71</v>
+      </c>
+      <c r="BO132">
+        <v>2.6</v>
+      </c>
+      <c r="BP132">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="230">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -568,6 +568,9 @@
     <t>['62', '31']</t>
   </si>
   <si>
+    <t>['19']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -694,13 +697,13 @@
     <t>['72']</t>
   </si>
   <si>
-    <t>['19']</t>
-  </si>
-  <si>
     <t>['40', '90+5']</t>
   </si>
   <si>
     <t>['25', '47']</t>
+  </si>
+  <si>
+    <t>['12', '88']</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1524,7 +1527,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1730,7 +1733,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1808,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4">
         <v>0.86</v>
@@ -2554,7 +2557,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3172,7 +3175,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3378,7 +3381,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3584,7 +3587,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3665,7 +3668,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3790,7 +3793,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4614,7 +4617,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4820,7 +4823,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5438,7 +5441,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5644,7 +5647,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6262,7 +6265,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6546,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27">
         <v>0.86</v>
@@ -6880,7 +6883,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7292,7 +7295,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8528,7 +8531,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8609,7 +8612,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ37">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR37">
         <v>2.41</v>
@@ -8734,7 +8737,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9558,7 +9561,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9842,7 +9845,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43">
         <v>0.67</v>
@@ -10794,7 +10797,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11000,7 +11003,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11412,7 +11415,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11618,7 +11621,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12648,7 +12651,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13060,7 +13063,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13141,7 +13144,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR59">
         <v>1.57</v>
@@ -13472,7 +13475,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14374,7 +14377,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ65">
         <v>0.29</v>
@@ -14502,7 +14505,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14708,7 +14711,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14914,7 +14917,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15120,7 +15123,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15532,7 +15535,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15819,7 +15822,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR72">
         <v>2.1</v>
@@ -16562,7 +16565,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -18416,7 +18419,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19034,7 +19037,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19112,7 +19115,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ88">
         <v>1.14</v>
@@ -19652,7 +19655,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19858,7 +19861,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20064,7 +20067,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20351,7 +20354,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR94">
         <v>1.37</v>
@@ -20476,7 +20479,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20682,7 +20685,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -22536,7 +22539,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23154,7 +23157,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23360,7 +23363,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23644,7 +23647,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ110">
         <v>0.57</v>
@@ -23978,7 +23981,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24596,7 +24599,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24802,7 +24805,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25420,7 +25423,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25498,7 +25501,7 @@
         <v>0.2</v>
       </c>
       <c r="AP119">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ119">
         <v>0.17</v>
@@ -25832,7 +25835,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -25913,7 +25916,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AR121">
         <v>2.18</v>
@@ -26450,7 +26453,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26656,7 +26659,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27480,7 +27483,7 @@
         <v>182</v>
       </c>
       <c r="P129" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="Q129">
         <v>3.8</v>
@@ -28255,6 +28258,212 @@
       </c>
       <c r="BP132">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7841167</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45835.85416666666</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
+        <v>72</v>
+      </c>
+      <c r="H133" t="s">
+        <v>78</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>2</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>2</v>
+      </c>
+      <c r="N133">
+        <v>3</v>
+      </c>
+      <c r="O133" t="s">
+        <v>184</v>
+      </c>
+      <c r="P133" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q133">
+        <v>3.01</v>
+      </c>
+      <c r="R133">
+        <v>1.79</v>
+      </c>
+      <c r="S133">
+        <v>4.29</v>
+      </c>
+      <c r="T133">
+        <v>1.65</v>
+      </c>
+      <c r="U133">
+        <v>2.16</v>
+      </c>
+      <c r="V133">
+        <v>4.15</v>
+      </c>
+      <c r="W133">
+        <v>1.18</v>
+      </c>
+      <c r="X133">
+        <v>10</v>
+      </c>
+      <c r="Y133">
+        <v>1.02</v>
+      </c>
+      <c r="Z133">
+        <v>2.2</v>
+      </c>
+      <c r="AA133">
+        <v>2.92</v>
+      </c>
+      <c r="AB133">
+        <v>3.8</v>
+      </c>
+      <c r="AC133">
+        <v>1.09</v>
+      </c>
+      <c r="AD133">
+        <v>5.8</v>
+      </c>
+      <c r="AE133">
+        <v>1.65</v>
+      </c>
+      <c r="AF133">
+        <v>2.25</v>
+      </c>
+      <c r="AG133">
+        <v>3.04</v>
+      </c>
+      <c r="AH133">
+        <v>1.37</v>
+      </c>
+      <c r="AI133">
+        <v>2.4</v>
+      </c>
+      <c r="AJ133">
+        <v>1.53</v>
+      </c>
+      <c r="AK133">
+        <v>1.25</v>
+      </c>
+      <c r="AL133">
+        <v>1.34</v>
+      </c>
+      <c r="AM133">
+        <v>1.7</v>
+      </c>
+      <c r="AN133">
+        <v>1.57</v>
+      </c>
+      <c r="AO133">
+        <v>1</v>
+      </c>
+      <c r="AP133">
+        <v>1.38</v>
+      </c>
+      <c r="AQ133">
+        <v>1.29</v>
+      </c>
+      <c r="AR133">
+        <v>2.05</v>
+      </c>
+      <c r="AS133">
+        <v>1.3</v>
+      </c>
+      <c r="AT133">
+        <v>3.35</v>
+      </c>
+      <c r="AU133">
+        <v>5</v>
+      </c>
+      <c r="AV133">
+        <v>7</v>
+      </c>
+      <c r="AW133">
+        <v>14</v>
+      </c>
+      <c r="AX133">
+        <v>4</v>
+      </c>
+      <c r="AY133">
+        <v>19</v>
+      </c>
+      <c r="AZ133">
+        <v>11</v>
+      </c>
+      <c r="BA133">
+        <v>6</v>
+      </c>
+      <c r="BB133">
+        <v>3</v>
+      </c>
+      <c r="BC133">
+        <v>9</v>
+      </c>
+      <c r="BD133">
+        <v>1.5</v>
+      </c>
+      <c r="BE133">
+        <v>7.5</v>
+      </c>
+      <c r="BF133">
+        <v>2.65</v>
+      </c>
+      <c r="BG133">
+        <v>1.18</v>
+      </c>
+      <c r="BH133">
+        <v>4.33</v>
+      </c>
+      <c r="BI133">
+        <v>1.36</v>
+      </c>
+      <c r="BJ133">
+        <v>3.4</v>
+      </c>
+      <c r="BK133">
+        <v>1.47</v>
+      </c>
+      <c r="BL133">
+        <v>2.3</v>
+      </c>
+      <c r="BM133">
+        <v>1.8</v>
+      </c>
+      <c r="BN133">
+        <v>1.83</v>
+      </c>
+      <c r="BO133">
+        <v>2.3</v>
+      </c>
+      <c r="BP133">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="231">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -571,6 +571,9 @@
     <t>['19']</t>
   </si>
   <si>
+    <t>['84']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1065,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1527,7 +1530,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1733,7 +1736,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2557,7 +2560,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3175,7 +3178,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3381,7 +3384,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3459,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ12">
         <v>0.83</v>
@@ -3587,7 +3590,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3793,7 +3796,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -3874,7 +3877,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ14">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4077,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ15">
         <v>0.71</v>
@@ -4617,7 +4620,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4823,7 +4826,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5316,7 +5319,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5441,7 +5444,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5647,7 +5650,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6265,7 +6268,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6883,7 +6886,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7170,7 +7173,7 @@
         <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR30">
         <v>2.86</v>
@@ -7295,7 +7298,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7785,7 +7788,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ33">
         <v>0.67</v>
@@ -8197,7 +8200,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ35">
         <v>0.71</v>
@@ -8531,7 +8534,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8737,7 +8740,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9024,7 +9027,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ39">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR39">
         <v>1.19</v>
@@ -9561,7 +9564,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10051,7 +10054,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ44">
         <v>0.57</v>
@@ -10797,7 +10800,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10878,7 +10881,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR48">
         <v>2.04</v>
@@ -11003,7 +11006,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11415,7 +11418,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11621,7 +11624,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11702,7 +11705,7 @@
         <v>2</v>
       </c>
       <c r="AQ52">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR52">
         <v>2.26</v>
@@ -12651,7 +12654,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12729,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ57">
         <v>0.67</v>
@@ -13063,7 +13066,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13475,7 +13478,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13759,7 +13762,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ62">
         <v>0.57</v>
@@ -13968,7 +13971,7 @@
         <v>2</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14174,7 +14177,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ64">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR64">
         <v>1.84</v>
@@ -14505,7 +14508,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14711,7 +14714,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14917,7 +14920,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15123,7 +15126,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15535,7 +15538,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16437,7 +16440,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ75">
         <v>1.17</v>
@@ -16565,7 +16568,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -18085,7 +18088,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ83">
         <v>0.86</v>
@@ -18419,7 +18422,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19037,7 +19040,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19118,7 +19121,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ88">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR88">
         <v>2.01</v>
@@ -19655,7 +19658,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19736,7 +19739,7 @@
         <v>2</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR91">
         <v>1.96</v>
@@ -19861,7 +19864,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20067,7 +20070,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20145,7 +20148,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20479,7 +20482,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20685,7 +20688,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -22002,7 +22005,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ102">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -22539,7 +22542,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23157,7 +23160,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23235,10 +23238,10 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ108">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR108">
         <v>1.63</v>
@@ -23363,7 +23366,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23981,7 +23984,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24059,7 +24062,7 @@
         <v>0</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ112">
         <v>0.86</v>
@@ -24599,7 +24602,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24677,7 +24680,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ115">
         <v>0.67</v>
@@ -24805,7 +24808,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25092,7 +25095,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ117">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR117">
         <v>1.9</v>
@@ -25423,7 +25426,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25835,7 +25838,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26453,7 +26456,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26659,7 +26662,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27895,7 +27898,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28101,7 +28104,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28307,7 +28310,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28400,22 +28403,22 @@
         <v>3.35</v>
       </c>
       <c r="AU133">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV133">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW133">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AX133">
         <v>4</v>
       </c>
       <c r="AY133">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ133">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA133">
         <v>6</v>
@@ -28464,6 +28467,418 @@
       </c>
       <c r="BP133">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7841163</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45836.66666666666</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s">
+        <v>83</v>
+      </c>
+      <c r="H134" t="s">
+        <v>79</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134" t="s">
+        <v>185</v>
+      </c>
+      <c r="P134" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q134">
+        <v>2.94</v>
+      </c>
+      <c r="R134">
+        <v>1.83</v>
+      </c>
+      <c r="S134">
+        <v>3.84</v>
+      </c>
+      <c r="T134">
+        <v>1.67</v>
+      </c>
+      <c r="U134">
+        <v>2.26</v>
+      </c>
+      <c r="V134">
+        <v>4.1</v>
+      </c>
+      <c r="W134">
+        <v>1.22</v>
+      </c>
+      <c r="X134">
+        <v>10</v>
+      </c>
+      <c r="Y134">
+        <v>1</v>
+      </c>
+      <c r="Z134">
+        <v>2.05</v>
+      </c>
+      <c r="AA134">
+        <v>2.88</v>
+      </c>
+      <c r="AB134">
+        <v>3.51</v>
+      </c>
+      <c r="AC134">
+        <v>1.06</v>
+      </c>
+      <c r="AD134">
+        <v>5.75</v>
+      </c>
+      <c r="AE134">
+        <v>1.53</v>
+      </c>
+      <c r="AF134">
+        <v>2.2</v>
+      </c>
+      <c r="AG134">
+        <v>2.73</v>
+      </c>
+      <c r="AH134">
+        <v>1.4</v>
+      </c>
+      <c r="AI134">
+        <v>2.15</v>
+      </c>
+      <c r="AJ134">
+        <v>1.65</v>
+      </c>
+      <c r="AK134">
+        <v>1.36</v>
+      </c>
+      <c r="AL134">
+        <v>1.35</v>
+      </c>
+      <c r="AM134">
+        <v>1.5</v>
+      </c>
+      <c r="AN134">
+        <v>2</v>
+      </c>
+      <c r="AO134">
+        <v>1</v>
+      </c>
+      <c r="AP134">
+        <v>2.14</v>
+      </c>
+      <c r="AQ134">
+        <v>0.86</v>
+      </c>
+      <c r="AR134">
+        <v>1.64</v>
+      </c>
+      <c r="AS134">
+        <v>1.54</v>
+      </c>
+      <c r="AT134">
+        <v>3.18</v>
+      </c>
+      <c r="AU134">
+        <v>2</v>
+      </c>
+      <c r="AV134">
+        <v>4</v>
+      </c>
+      <c r="AW134">
+        <v>3</v>
+      </c>
+      <c r="AX134">
+        <v>5</v>
+      </c>
+      <c r="AY134">
+        <v>5</v>
+      </c>
+      <c r="AZ134">
+        <v>9</v>
+      </c>
+      <c r="BA134">
+        <v>5</v>
+      </c>
+      <c r="BB134">
+        <v>6</v>
+      </c>
+      <c r="BC134">
+        <v>11</v>
+      </c>
+      <c r="BD134">
+        <v>1.85</v>
+      </c>
+      <c r="BE134">
+        <v>6.5</v>
+      </c>
+      <c r="BF134">
+        <v>2.27</v>
+      </c>
+      <c r="BG134">
+        <v>1.17</v>
+      </c>
+      <c r="BH134">
+        <v>4.3</v>
+      </c>
+      <c r="BI134">
+        <v>1.33</v>
+      </c>
+      <c r="BJ134">
+        <v>3.22</v>
+      </c>
+      <c r="BK134">
+        <v>1.49</v>
+      </c>
+      <c r="BL134">
+        <v>2.35</v>
+      </c>
+      <c r="BM134">
+        <v>1.92</v>
+      </c>
+      <c r="BN134">
+        <v>1.88</v>
+      </c>
+      <c r="BO134">
+        <v>2.3</v>
+      </c>
+      <c r="BP134">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7841162</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45836.77083333334</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>80</v>
+      </c>
+      <c r="H135" t="s">
+        <v>73</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>97</v>
+      </c>
+      <c r="P135" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q135">
+        <v>3.1</v>
+      </c>
+      <c r="R135">
+        <v>1.8</v>
+      </c>
+      <c r="S135">
+        <v>4.5</v>
+      </c>
+      <c r="T135">
+        <v>1.65</v>
+      </c>
+      <c r="U135">
+        <v>2.26</v>
+      </c>
+      <c r="V135">
+        <v>3.7</v>
+      </c>
+      <c r="W135">
+        <v>1.22</v>
+      </c>
+      <c r="X135">
+        <v>13</v>
+      </c>
+      <c r="Y135">
+        <v>1.03</v>
+      </c>
+      <c r="Z135">
+        <v>2.18</v>
+      </c>
+      <c r="AA135">
+        <v>2.78</v>
+      </c>
+      <c r="AB135">
+        <v>3.75</v>
+      </c>
+      <c r="AC135">
+        <v>1.12</v>
+      </c>
+      <c r="AD135">
+        <v>5.3</v>
+      </c>
+      <c r="AE135">
+        <v>1.67</v>
+      </c>
+      <c r="AF135">
+        <v>2.23</v>
+      </c>
+      <c r="AG135">
+        <v>2.93</v>
+      </c>
+      <c r="AH135">
+        <v>1.36</v>
+      </c>
+      <c r="AI135">
+        <v>2.38</v>
+      </c>
+      <c r="AJ135">
+        <v>1.53</v>
+      </c>
+      <c r="AK135">
+        <v>1.44</v>
+      </c>
+      <c r="AL135">
+        <v>1.36</v>
+      </c>
+      <c r="AM135">
+        <v>1.57</v>
+      </c>
+      <c r="AN135">
+        <v>1.86</v>
+      </c>
+      <c r="AO135">
+        <v>1.14</v>
+      </c>
+      <c r="AP135">
+        <v>1.63</v>
+      </c>
+      <c r="AQ135">
+        <v>1.38</v>
+      </c>
+      <c r="AR135">
+        <v>1.89</v>
+      </c>
+      <c r="AS135">
+        <v>1.19</v>
+      </c>
+      <c r="AT135">
+        <v>3.08</v>
+      </c>
+      <c r="AU135">
+        <v>4</v>
+      </c>
+      <c r="AV135">
+        <v>5</v>
+      </c>
+      <c r="AW135">
+        <v>13</v>
+      </c>
+      <c r="AX135">
+        <v>3</v>
+      </c>
+      <c r="AY135">
+        <v>17</v>
+      </c>
+      <c r="AZ135">
+        <v>8</v>
+      </c>
+      <c r="BA135">
+        <v>7</v>
+      </c>
+      <c r="BB135">
+        <v>4</v>
+      </c>
+      <c r="BC135">
+        <v>11</v>
+      </c>
+      <c r="BD135">
+        <v>1.6</v>
+      </c>
+      <c r="BE135">
+        <v>9</v>
+      </c>
+      <c r="BF135">
+        <v>2.91</v>
+      </c>
+      <c r="BG135">
+        <v>1.18</v>
+      </c>
+      <c r="BH135">
+        <v>3.8</v>
+      </c>
+      <c r="BI135">
+        <v>1.36</v>
+      </c>
+      <c r="BJ135">
+        <v>3.05</v>
+      </c>
+      <c r="BK135">
+        <v>1.62</v>
+      </c>
+      <c r="BL135">
+        <v>2.2</v>
+      </c>
+      <c r="BM135">
+        <v>1.96</v>
+      </c>
+      <c r="BN135">
+        <v>1.75</v>
+      </c>
+      <c r="BO135">
+        <v>2.4</v>
+      </c>
+      <c r="BP135">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -28403,22 +28403,22 @@
         <v>3.35</v>
       </c>
       <c r="AU133">
+        <v>5</v>
+      </c>
+      <c r="AV133">
         <v>7</v>
       </c>
-      <c r="AV133">
-        <v>6</v>
-      </c>
       <c r="AW133">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AX133">
         <v>4</v>
       </c>
       <c r="AY133">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AZ133">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA133">
         <v>6</v>
@@ -28615,16 +28615,16 @@
         <v>4</v>
       </c>
       <c r="AW134">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX134">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY134">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ134">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA134">
         <v>5</v>
@@ -28815,22 +28815,22 @@
         <v>3.08</v>
       </c>
       <c r="AU135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV135">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW135">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX135">
         <v>3</v>
       </c>
       <c r="AY135">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ135">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA135">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="234">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -574,6 +574,12 @@
     <t>['84']</t>
   </si>
   <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -707,6 +713,9 @@
   </si>
   <si>
     <t>['12', '88']</t>
+  </si>
+  <si>
+    <t>['78', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP135"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1530,7 +1539,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1736,7 +1745,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1817,7 +1826,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ4">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2560,7 +2569,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2641,7 +2650,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2844,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ9">
         <v>1.14</v>
@@ -3178,7 +3187,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3384,7 +3393,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3590,7 +3599,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3796,7 +3805,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4620,7 +4629,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4826,7 +4835,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -4904,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ19">
         <v>0.71</v>
@@ -5444,7 +5453,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -5650,7 +5659,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5937,7 +5946,7 @@
         <v>2</v>
       </c>
       <c r="AQ24">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -6268,7 +6277,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6886,7 +6895,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -6967,7 +6976,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ29">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR29">
         <v>1.52</v>
@@ -7298,7 +7307,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8534,7 +8543,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8740,7 +8749,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9436,7 +9445,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ41">
         <v>0.86</v>
@@ -9564,7 +9573,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9851,7 +9860,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ43">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>2.25</v>
@@ -10263,7 +10272,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ45">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR45">
         <v>1.46</v>
@@ -10672,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ47">
         <v>0.29</v>
@@ -10800,7 +10809,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11006,7 +11015,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11418,7 +11427,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11624,7 +11633,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12114,7 +12123,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ54">
         <v>0.71</v>
@@ -12654,7 +12663,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13066,7 +13075,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13478,7 +13487,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13556,7 +13565,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ61">
         <v>0.57</v>
@@ -14508,7 +14517,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14589,7 +14598,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ66">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR66">
         <v>1.58</v>
@@ -14714,7 +14723,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14920,7 +14929,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15126,7 +15135,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15538,7 +15547,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16568,7 +16577,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16646,7 +16655,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ76">
         <v>1.33</v>
@@ -16855,7 +16864,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ77">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.59</v>
@@ -17470,7 +17479,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ80">
         <v>0.17</v>
@@ -18422,7 +18431,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18915,7 +18924,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ87">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR87">
         <v>1.81</v>
@@ -19040,7 +19049,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19658,7 +19667,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19864,7 +19873,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20070,7 +20079,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20482,7 +20491,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20688,7 +20697,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20766,7 +20775,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ96">
         <v>1.14</v>
@@ -21181,7 +21190,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ98">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.74</v>
@@ -21384,7 +21393,7 @@
         <v>0</v>
       </c>
       <c r="AP99">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99">
         <v>0.86</v>
@@ -22542,7 +22551,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23160,7 +23169,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23366,7 +23375,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23447,7 +23456,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ109">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR109">
         <v>1.3</v>
@@ -23984,7 +23993,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24602,7 +24611,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24683,7 +24692,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ115">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.63</v>
@@ -24808,7 +24817,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -24886,10 +24895,10 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ116">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR116">
         <v>1.63</v>
@@ -25426,7 +25435,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25838,7 +25847,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -25916,7 +25925,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ121">
         <v>1.29</v>
@@ -26456,7 +26465,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26662,7 +26671,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27898,7 +27907,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28104,7 +28113,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28310,7 +28319,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28615,16 +28624,16 @@
         <v>4</v>
       </c>
       <c r="AW134">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX134">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY134">
+        <v>5</v>
+      </c>
+      <c r="AZ134">
         <v>9</v>
-      </c>
-      <c r="AZ134">
-        <v>12</v>
       </c>
       <c r="BA134">
         <v>5</v>
@@ -28722,7 +28731,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -28815,22 +28824,22 @@
         <v>3.08</v>
       </c>
       <c r="AU135">
+        <v>4</v>
+      </c>
+      <c r="AV135">
         <v>5</v>
       </c>
-      <c r="AV135">
-        <v>6</v>
-      </c>
       <c r="AW135">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX135">
         <v>3</v>
       </c>
       <c r="AY135">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ135">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA135">
         <v>7</v>
@@ -28879,6 +28888,418 @@
       </c>
       <c r="BP135">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7841171</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45837.66666666666</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136" t="s">
+        <v>77</v>
+      </c>
+      <c r="H136" t="s">
+        <v>86</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>1</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>186</v>
+      </c>
+      <c r="P136" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q136">
+        <v>3</v>
+      </c>
+      <c r="R136">
+        <v>1.8</v>
+      </c>
+      <c r="S136">
+        <v>4.3</v>
+      </c>
+      <c r="T136">
+        <v>1.63</v>
+      </c>
+      <c r="U136">
+        <v>2.2</v>
+      </c>
+      <c r="V136">
+        <v>3.6</v>
+      </c>
+      <c r="W136">
+        <v>1.22</v>
+      </c>
+      <c r="X136">
+        <v>12</v>
+      </c>
+      <c r="Y136">
+        <v>1.01</v>
+      </c>
+      <c r="Z136">
+        <v>2.19</v>
+      </c>
+      <c r="AA136">
+        <v>2.9</v>
+      </c>
+      <c r="AB136">
+        <v>3.14</v>
+      </c>
+      <c r="AC136">
+        <v>1.11</v>
+      </c>
+      <c r="AD136">
+        <v>6.5</v>
+      </c>
+      <c r="AE136">
+        <v>1.57</v>
+      </c>
+      <c r="AF136">
+        <v>2.25</v>
+      </c>
+      <c r="AG136">
+        <v>2.3</v>
+      </c>
+      <c r="AH136">
+        <v>1.5</v>
+      </c>
+      <c r="AI136">
+        <v>2.2</v>
+      </c>
+      <c r="AJ136">
+        <v>1.6</v>
+      </c>
+      <c r="AK136">
+        <v>1.29</v>
+      </c>
+      <c r="AL136">
+        <v>1.37</v>
+      </c>
+      <c r="AM136">
+        <v>1.57</v>
+      </c>
+      <c r="AN136">
+        <v>1.5</v>
+      </c>
+      <c r="AO136">
+        <v>0.86</v>
+      </c>
+      <c r="AP136">
+        <v>1.71</v>
+      </c>
+      <c r="AQ136">
+        <v>0.75</v>
+      </c>
+      <c r="AR136">
+        <v>2.25</v>
+      </c>
+      <c r="AS136">
+        <v>1.39</v>
+      </c>
+      <c r="AT136">
+        <v>3.64</v>
+      </c>
+      <c r="AU136">
+        <v>3</v>
+      </c>
+      <c r="AV136">
+        <v>2</v>
+      </c>
+      <c r="AW136">
+        <v>10</v>
+      </c>
+      <c r="AX136">
+        <v>5</v>
+      </c>
+      <c r="AY136">
+        <v>13</v>
+      </c>
+      <c r="AZ136">
+        <v>7</v>
+      </c>
+      <c r="BA136">
+        <v>5</v>
+      </c>
+      <c r="BB136">
+        <v>4</v>
+      </c>
+      <c r="BC136">
+        <v>9</v>
+      </c>
+      <c r="BD136">
+        <v>1.67</v>
+      </c>
+      <c r="BE136">
+        <v>6.75</v>
+      </c>
+      <c r="BF136">
+        <v>2.66</v>
+      </c>
+      <c r="BG136">
+        <v>1.21</v>
+      </c>
+      <c r="BH136">
+        <v>3.8</v>
+      </c>
+      <c r="BI136">
+        <v>1.5</v>
+      </c>
+      <c r="BJ136">
+        <v>2.43</v>
+      </c>
+      <c r="BK136">
+        <v>1.73</v>
+      </c>
+      <c r="BL136">
+        <v>1.92</v>
+      </c>
+      <c r="BM136">
+        <v>2.26</v>
+      </c>
+      <c r="BN136">
+        <v>1.6</v>
+      </c>
+      <c r="BO136">
+        <v>3.1</v>
+      </c>
+      <c r="BP136">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7841169</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45837.66666666666</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>87</v>
+      </c>
+      <c r="H137" t="s">
+        <v>88</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>2</v>
+      </c>
+      <c r="N137">
+        <v>3</v>
+      </c>
+      <c r="O137" t="s">
+        <v>187</v>
+      </c>
+      <c r="P137" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q137">
+        <v>2.62</v>
+      </c>
+      <c r="R137">
+        <v>1.97</v>
+      </c>
+      <c r="S137">
+        <v>4.05</v>
+      </c>
+      <c r="T137">
+        <v>1.49</v>
+      </c>
+      <c r="U137">
+        <v>2.4</v>
+      </c>
+      <c r="V137">
+        <v>3.25</v>
+      </c>
+      <c r="W137">
+        <v>1.29</v>
+      </c>
+      <c r="X137">
+        <v>6.8</v>
+      </c>
+      <c r="Y137">
+        <v>1.05</v>
+      </c>
+      <c r="Z137">
+        <v>2.36</v>
+      </c>
+      <c r="AA137">
+        <v>3.07</v>
+      </c>
+      <c r="AB137">
+        <v>2.69</v>
+      </c>
+      <c r="AC137">
+        <v>1.08</v>
+      </c>
+      <c r="AD137">
+        <v>8.5</v>
+      </c>
+      <c r="AE137">
+        <v>1.37</v>
+      </c>
+      <c r="AF137">
+        <v>2.65</v>
+      </c>
+      <c r="AG137">
+        <v>2.25</v>
+      </c>
+      <c r="AH137">
+        <v>1.53</v>
+      </c>
+      <c r="AI137">
+        <v>2</v>
+      </c>
+      <c r="AJ137">
+        <v>1.77</v>
+      </c>
+      <c r="AK137">
+        <v>1.25</v>
+      </c>
+      <c r="AL137">
+        <v>1.32</v>
+      </c>
+      <c r="AM137">
+        <v>1.79</v>
+      </c>
+      <c r="AN137">
+        <v>1</v>
+      </c>
+      <c r="AO137">
+        <v>0.67</v>
+      </c>
+      <c r="AP137">
+        <v>0.86</v>
+      </c>
+      <c r="AQ137">
+        <v>1</v>
+      </c>
+      <c r="AR137">
+        <v>1.61</v>
+      </c>
+      <c r="AS137">
+        <v>1.4</v>
+      </c>
+      <c r="AT137">
+        <v>3.01</v>
+      </c>
+      <c r="AU137">
+        <v>10</v>
+      </c>
+      <c r="AV137">
+        <v>4</v>
+      </c>
+      <c r="AW137">
+        <v>3</v>
+      </c>
+      <c r="AX137">
+        <v>3</v>
+      </c>
+      <c r="AY137">
+        <v>13</v>
+      </c>
+      <c r="AZ137">
+        <v>7</v>
+      </c>
+      <c r="BA137">
+        <v>10</v>
+      </c>
+      <c r="BB137">
+        <v>2</v>
+      </c>
+      <c r="BC137">
+        <v>12</v>
+      </c>
+      <c r="BD137">
+        <v>1.48</v>
+      </c>
+      <c r="BE137">
+        <v>7</v>
+      </c>
+      <c r="BF137">
+        <v>2.8</v>
+      </c>
+      <c r="BG137">
+        <v>1.16</v>
+      </c>
+      <c r="BH137">
+        <v>4.6</v>
+      </c>
+      <c r="BI137">
+        <v>1.25</v>
+      </c>
+      <c r="BJ137">
+        <v>3.5</v>
+      </c>
+      <c r="BK137">
+        <v>1.47</v>
+      </c>
+      <c r="BL137">
+        <v>2.45</v>
+      </c>
+      <c r="BM137">
+        <v>1.8</v>
+      </c>
+      <c r="BN137">
+        <v>1.85</v>
+      </c>
+      <c r="BO137">
+        <v>2.3</v>
+      </c>
+      <c r="BP137">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -580,6 +580,9 @@
     <t>['70']</t>
   </si>
   <si>
+    <t>['15']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -605,9 +608,6 @@
   </si>
   <si>
     <t>['52', '90+1']</t>
-  </si>
-  <si>
-    <t>['15']</t>
   </si>
   <si>
     <t>['26', '35']</t>
@@ -716,6 +716,9 @@
   </si>
   <si>
     <t>['78', '90+4']</t>
+  </si>
+  <si>
+    <t>['89', '90+7']</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1414,7 +1417,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ2">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1539,7 +1542,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1745,7 +1748,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2569,7 +2572,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3187,7 +3190,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3393,7 +3396,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3599,7 +3602,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3805,7 +3808,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -3883,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ14">
         <v>1.38</v>
@@ -4501,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ17">
         <v>0.29</v>
@@ -4629,7 +4632,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4710,7 +4713,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ18">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4835,7 +4838,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5453,7 +5456,7 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="Q22">
         <v>3.5</v>
@@ -7388,7 +7391,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR31">
         <v>2.07</v>
@@ -8003,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ34">
         <v>0.86</v>
@@ -8418,7 +8421,7 @@
         <v>2</v>
       </c>
       <c r="AQ36">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR36">
         <v>1.95</v>
@@ -8827,7 +8830,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ38">
         <v>0.83</v>
@@ -9651,7 +9654,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ42">
         <v>1.17</v>
@@ -11508,7 +11511,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ51">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR51">
         <v>1.16</v>
@@ -11920,7 +11923,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ53">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR53">
         <v>1.06</v>
@@ -12535,7 +12538,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ56">
         <v>0.83</v>
@@ -14801,7 +14804,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ67">
         <v>0.86</v>
@@ -16037,7 +16040,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ73">
         <v>1.14</v>
@@ -17276,7 +17279,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ79">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR79">
         <v>1.67</v>
@@ -17482,7 +17485,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ80">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR80">
         <v>1.86</v>
@@ -18715,7 +18718,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ86">
         <v>0.71</v>
@@ -20572,7 +20575,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ95">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR95">
         <v>1.93</v>
@@ -21599,10 +21602,10 @@
         <v>0.25</v>
       </c>
       <c r="AP100">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ100">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR100">
         <v>1.63</v>
@@ -22217,7 +22220,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ103">
         <v>0.57</v>
@@ -24486,7 +24489,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ114">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AR114">
         <v>1.72</v>
@@ -24817,7 +24820,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25307,7 +25310,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ118">
         <v>1.14</v>
@@ -25516,7 +25519,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ119">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AR119">
         <v>1.99</v>
@@ -25719,7 +25722,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ120">
         <v>0.86</v>
@@ -29300,6 +29303,418 @@
       </c>
       <c r="BP137">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7841166</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45837.79166666666</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138" t="s">
+        <v>82</v>
+      </c>
+      <c r="H138" t="s">
+        <v>70</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>1</v>
+      </c>
+      <c r="M138">
+        <v>2</v>
+      </c>
+      <c r="N138">
+        <v>3</v>
+      </c>
+      <c r="O138" t="s">
+        <v>188</v>
+      </c>
+      <c r="P138" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q138">
+        <v>3.02</v>
+      </c>
+      <c r="R138">
+        <v>1.88</v>
+      </c>
+      <c r="S138">
+        <v>3.9</v>
+      </c>
+      <c r="T138">
+        <v>1.47</v>
+      </c>
+      <c r="U138">
+        <v>2.35</v>
+      </c>
+      <c r="V138">
+        <v>3.4</v>
+      </c>
+      <c r="W138">
+        <v>1.27</v>
+      </c>
+      <c r="X138">
+        <v>9.6</v>
+      </c>
+      <c r="Y138">
+        <v>1</v>
+      </c>
+      <c r="Z138">
+        <v>2.25</v>
+      </c>
+      <c r="AA138">
+        <v>2.95</v>
+      </c>
+      <c r="AB138">
+        <v>3.43</v>
+      </c>
+      <c r="AC138">
+        <v>1.07</v>
+      </c>
+      <c r="AD138">
+        <v>6</v>
+      </c>
+      <c r="AE138">
+        <v>1.46</v>
+      </c>
+      <c r="AF138">
+        <v>2.39</v>
+      </c>
+      <c r="AG138">
+        <v>2.55</v>
+      </c>
+      <c r="AH138">
+        <v>1.51</v>
+      </c>
+      <c r="AI138">
+        <v>2.11</v>
+      </c>
+      <c r="AJ138">
+        <v>1.69</v>
+      </c>
+      <c r="AK138">
+        <v>1.26</v>
+      </c>
+      <c r="AL138">
+        <v>1.37</v>
+      </c>
+      <c r="AM138">
+        <v>1.59</v>
+      </c>
+      <c r="AN138">
+        <v>2.5</v>
+      </c>
+      <c r="AO138">
+        <v>1.67</v>
+      </c>
+      <c r="AP138">
+        <v>2.14</v>
+      </c>
+      <c r="AQ138">
+        <v>1.86</v>
+      </c>
+      <c r="AR138">
+        <v>1.57</v>
+      </c>
+      <c r="AS138">
+        <v>1.35</v>
+      </c>
+      <c r="AT138">
+        <v>2.92</v>
+      </c>
+      <c r="AU138">
+        <v>4</v>
+      </c>
+      <c r="AV138">
+        <v>6</v>
+      </c>
+      <c r="AW138">
+        <v>4</v>
+      </c>
+      <c r="AX138">
+        <v>10</v>
+      </c>
+      <c r="AY138">
+        <v>8</v>
+      </c>
+      <c r="AZ138">
+        <v>16</v>
+      </c>
+      <c r="BA138">
+        <v>5</v>
+      </c>
+      <c r="BB138">
+        <v>4</v>
+      </c>
+      <c r="BC138">
+        <v>9</v>
+      </c>
+      <c r="BD138">
+        <v>1.95</v>
+      </c>
+      <c r="BE138">
+        <v>6.75</v>
+      </c>
+      <c r="BF138">
+        <v>2.07</v>
+      </c>
+      <c r="BG138">
+        <v>1.2</v>
+      </c>
+      <c r="BH138">
+        <v>4.2</v>
+      </c>
+      <c r="BI138">
+        <v>1.28</v>
+      </c>
+      <c r="BJ138">
+        <v>3.05</v>
+      </c>
+      <c r="BK138">
+        <v>1.49</v>
+      </c>
+      <c r="BL138">
+        <v>2.31</v>
+      </c>
+      <c r="BM138">
+        <v>2.05</v>
+      </c>
+      <c r="BN138">
+        <v>1.85</v>
+      </c>
+      <c r="BO138">
+        <v>2.45</v>
+      </c>
+      <c r="BP138">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7841170</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45837.79166666666</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139" t="s">
+        <v>85</v>
+      </c>
+      <c r="H139" t="s">
+        <v>84</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>2</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>2</v>
+      </c>
+      <c r="O139" t="s">
+        <v>120</v>
+      </c>
+      <c r="P139" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q139">
+        <v>1.87</v>
+      </c>
+      <c r="R139">
+        <v>2.02</v>
+      </c>
+      <c r="S139">
+        <v>7.58</v>
+      </c>
+      <c r="T139">
+        <v>1.52</v>
+      </c>
+      <c r="U139">
+        <v>2.39</v>
+      </c>
+      <c r="V139">
+        <v>3.2</v>
+      </c>
+      <c r="W139">
+        <v>1.27</v>
+      </c>
+      <c r="X139">
+        <v>8.4</v>
+      </c>
+      <c r="Y139">
+        <v>1.04</v>
+      </c>
+      <c r="Z139">
+        <v>1.53</v>
+      </c>
+      <c r="AA139">
+        <v>3.68</v>
+      </c>
+      <c r="AB139">
+        <v>6.97</v>
+      </c>
+      <c r="AC139">
+        <v>1.05</v>
+      </c>
+      <c r="AD139">
+        <v>6.5</v>
+      </c>
+      <c r="AE139">
+        <v>1.4</v>
+      </c>
+      <c r="AF139">
+        <v>2.6</v>
+      </c>
+      <c r="AG139">
+        <v>2.47</v>
+      </c>
+      <c r="AH139">
+        <v>1.54</v>
+      </c>
+      <c r="AI139">
+        <v>2.5</v>
+      </c>
+      <c r="AJ139">
+        <v>1.5</v>
+      </c>
+      <c r="AK139">
+        <v>1.22</v>
+      </c>
+      <c r="AL139">
+        <v>1.28</v>
+      </c>
+      <c r="AM139">
+        <v>2.44</v>
+      </c>
+      <c r="AN139">
+        <v>2.43</v>
+      </c>
+      <c r="AO139">
+        <v>0.17</v>
+      </c>
+      <c r="AP139">
+        <v>2.25</v>
+      </c>
+      <c r="AQ139">
+        <v>0.29</v>
+      </c>
+      <c r="AR139">
+        <v>1.83</v>
+      </c>
+      <c r="AS139">
+        <v>1.16</v>
+      </c>
+      <c r="AT139">
+        <v>2.99</v>
+      </c>
+      <c r="AU139">
+        <v>4</v>
+      </c>
+      <c r="AV139">
+        <v>4</v>
+      </c>
+      <c r="AW139">
+        <v>7</v>
+      </c>
+      <c r="AX139">
+        <v>4</v>
+      </c>
+      <c r="AY139">
+        <v>11</v>
+      </c>
+      <c r="AZ139">
+        <v>8</v>
+      </c>
+      <c r="BA139">
+        <v>6</v>
+      </c>
+      <c r="BB139">
+        <v>4</v>
+      </c>
+      <c r="BC139">
+        <v>10</v>
+      </c>
+      <c r="BD139">
+        <v>1.46</v>
+      </c>
+      <c r="BE139">
+        <v>7.5</v>
+      </c>
+      <c r="BF139">
+        <v>5.25</v>
+      </c>
+      <c r="BG139">
+        <v>1.25</v>
+      </c>
+      <c r="BH139">
+        <v>3.6</v>
+      </c>
+      <c r="BI139">
+        <v>1.37</v>
+      </c>
+      <c r="BJ139">
+        <v>2.62</v>
+      </c>
+      <c r="BK139">
+        <v>1.88</v>
+      </c>
+      <c r="BL139">
+        <v>1.95</v>
+      </c>
+      <c r="BM139">
+        <v>2.07</v>
+      </c>
+      <c r="BN139">
+        <v>1.68</v>
+      </c>
+      <c r="BO139">
+        <v>2.87</v>
+      </c>
+      <c r="BP139">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -28627,16 +28627,16 @@
         <v>4</v>
       </c>
       <c r="AW134">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX134">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY134">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ134">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA134">
         <v>5</v>
@@ -28827,22 +28827,22 @@
         <v>3.08</v>
       </c>
       <c r="AU135">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV135">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW135">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX135">
         <v>3</v>
       </c>
       <c r="AY135">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ135">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA135">
         <v>7</v>
@@ -29033,22 +29033,22 @@
         <v>3.64</v>
       </c>
       <c r="AU136">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV136">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW136">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX136">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY136">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ136">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA136">
         <v>5</v>
@@ -29245,13 +29245,13 @@
         <v>4</v>
       </c>
       <c r="AW137">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AX137">
         <v>3</v>
       </c>
       <c r="AY137">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AZ137">
         <v>7</v>
@@ -29445,22 +29445,22 @@
         <v>2.92</v>
       </c>
       <c r="AU138">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV138">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW138">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX138">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY138">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ138">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA138">
         <v>5</v>
@@ -29651,22 +29651,22 @@
         <v>2.99</v>
       </c>
       <c r="AU139">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV139">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW139">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX139">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY139">
+        <v>17</v>
+      </c>
+      <c r="AZ139">
         <v>11</v>
-      </c>
-      <c r="AZ139">
-        <v>8</v>
       </c>
       <c r="BA139">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -718,7 +718,7 @@
     <t>['78', '90+4']</t>
   </si>
   <si>
-    <t>['89', '90+7']</t>
+    <t>['90+7', '89']</t>
   </si>
 </sst>
 </file>
@@ -29033,22 +29033,22 @@
         <v>3.64</v>
       </c>
       <c r="AU136">
+        <v>3</v>
+      </c>
+      <c r="AV136">
+        <v>2</v>
+      </c>
+      <c r="AW136">
+        <v>10</v>
+      </c>
+      <c r="AX136">
         <v>5</v>
       </c>
-      <c r="AV136">
-        <v>0</v>
-      </c>
-      <c r="AW136">
-        <v>12</v>
-      </c>
-      <c r="AX136">
-        <v>12</v>
-      </c>
       <c r="AY136">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ136">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA136">
         <v>5</v>
@@ -29245,13 +29245,13 @@
         <v>4</v>
       </c>
       <c r="AW137">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AX137">
         <v>3</v>
       </c>
       <c r="AY137">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AZ137">
         <v>7</v>
@@ -29445,22 +29445,22 @@
         <v>2.92</v>
       </c>
       <c r="AU138">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV138">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW138">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX138">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY138">
         <v>9</v>
       </c>
       <c r="AZ138">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA138">
         <v>5</v>
@@ -29651,22 +29651,22 @@
         <v>2.99</v>
       </c>
       <c r="AU139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW139">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX139">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY139">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ139">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA139">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="236">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -583,6 +583,9 @@
     <t>['15']</t>
   </si>
   <si>
+    <t>['65', '68']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1080,7 +1083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1542,7 +1545,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1620,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3">
         <v>1.17</v>
@@ -1748,7 +1751,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2447,7 +2450,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2572,7 +2575,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3190,7 +3193,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3396,7 +3399,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3602,7 +3605,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3680,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ13">
         <v>1.29</v>
@@ -3808,7 +3811,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4301,7 +4304,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ16">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4632,7 +4635,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4838,7 +4841,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5534,7 +5537,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ22">
         <v>1.17</v>
@@ -5662,7 +5665,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5740,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ23">
         <v>0.57</v>
@@ -6280,7 +6283,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6898,7 +6901,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7310,7 +7313,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7803,7 +7806,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ33">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.59</v>
@@ -8546,7 +8549,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8752,7 +8755,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9451,7 +9454,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ41">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR41">
         <v>1.74</v>
@@ -9576,7 +9579,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10812,7 +10815,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11018,7 +11021,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11096,7 +11099,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ49">
         <v>0.71</v>
@@ -11302,10 +11305,10 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ50">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR50">
         <v>1.55</v>
@@ -11430,7 +11433,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11636,7 +11639,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12666,7 +12669,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12747,7 +12750,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ57">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13078,7 +13081,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13490,7 +13493,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14520,7 +14523,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14598,7 +14601,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ66">
         <v>0.75</v>
@@ -14726,7 +14729,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14807,7 +14810,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ67">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR67">
         <v>2.23</v>
@@ -14932,7 +14935,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15138,7 +15141,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15550,7 +15553,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16249,7 +16252,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ74">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR74">
         <v>1.6</v>
@@ -16580,7 +16583,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17276,7 +17279,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ79">
         <v>1.86</v>
@@ -17897,7 +17900,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ82">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR82">
         <v>1.86</v>
@@ -18434,7 +18437,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19052,7 +19055,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19542,7 +19545,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ90">
         <v>0.57</v>
@@ -19670,7 +19673,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19876,7 +19879,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -19957,7 +19960,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20082,7 +20085,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20494,7 +20497,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20700,7 +20703,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21808,7 +21811,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ101">
         <v>0.83</v>
@@ -22426,7 +22429,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ104">
         <v>0.71</v>
@@ -22554,7 +22557,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22635,7 +22638,7 @@
         <v>2</v>
       </c>
       <c r="AQ105">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR105">
         <v>1.85</v>
@@ -23172,7 +23175,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23378,7 +23381,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23996,7 +23999,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24280,10 +24283,10 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ113">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AR113">
         <v>1.9</v>
@@ -24614,7 +24617,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24820,7 +24823,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25438,7 +25441,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25725,7 +25728,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ120">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR120">
         <v>1.66</v>
@@ -25850,7 +25853,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26468,7 +26471,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26674,7 +26677,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27910,7 +27913,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28116,7 +28119,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28322,7 +28325,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28734,7 +28737,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29146,7 +29149,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29352,7 +29355,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -29715,6 +29718,418 @@
       </c>
       <c r="BP139">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7841165</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45838.79166666666</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140" t="s">
+        <v>71</v>
+      </c>
+      <c r="H140" t="s">
+        <v>76</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>3</v>
+      </c>
+      <c r="O140" t="s">
+        <v>189</v>
+      </c>
+      <c r="P140" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q140">
+        <v>2.76</v>
+      </c>
+      <c r="R140">
+        <v>1.87</v>
+      </c>
+      <c r="S140">
+        <v>4.8</v>
+      </c>
+      <c r="T140">
+        <v>1.55</v>
+      </c>
+      <c r="U140">
+        <v>2.38</v>
+      </c>
+      <c r="V140">
+        <v>3.8</v>
+      </c>
+      <c r="W140">
+        <v>1.27</v>
+      </c>
+      <c r="X140">
+        <v>10</v>
+      </c>
+      <c r="Y140">
+        <v>1</v>
+      </c>
+      <c r="Z140">
+        <v>1.92</v>
+      </c>
+      <c r="AA140">
+        <v>3.24</v>
+      </c>
+      <c r="AB140">
+        <v>4.25</v>
+      </c>
+      <c r="AC140">
+        <v>1.07</v>
+      </c>
+      <c r="AD140">
+        <v>6.5</v>
+      </c>
+      <c r="AE140">
+        <v>1.44</v>
+      </c>
+      <c r="AF140">
+        <v>2.5</v>
+      </c>
+      <c r="AG140">
+        <v>2.69</v>
+      </c>
+      <c r="AH140">
+        <v>1.47</v>
+      </c>
+      <c r="AI140">
+        <v>2.2</v>
+      </c>
+      <c r="AJ140">
+        <v>1.62</v>
+      </c>
+      <c r="AK140">
+        <v>1.36</v>
+      </c>
+      <c r="AL140">
+        <v>1.3</v>
+      </c>
+      <c r="AM140">
+        <v>1.8</v>
+      </c>
+      <c r="AN140">
+        <v>0.83</v>
+      </c>
+      <c r="AO140">
+        <v>0.86</v>
+      </c>
+      <c r="AP140">
+        <v>1.14</v>
+      </c>
+      <c r="AQ140">
+        <v>0.75</v>
+      </c>
+      <c r="AR140">
+        <v>1.87</v>
+      </c>
+      <c r="AS140">
+        <v>1.53</v>
+      </c>
+      <c r="AT140">
+        <v>3.4</v>
+      </c>
+      <c r="AU140">
+        <v>6</v>
+      </c>
+      <c r="AV140">
+        <v>3</v>
+      </c>
+      <c r="AW140">
+        <v>5</v>
+      </c>
+      <c r="AX140">
+        <v>5</v>
+      </c>
+      <c r="AY140">
+        <v>11</v>
+      </c>
+      <c r="AZ140">
+        <v>8</v>
+      </c>
+      <c r="BA140">
+        <v>5</v>
+      </c>
+      <c r="BB140">
+        <v>5</v>
+      </c>
+      <c r="BC140">
+        <v>10</v>
+      </c>
+      <c r="BD140">
+        <v>1.45</v>
+      </c>
+      <c r="BE140">
+        <v>9.6</v>
+      </c>
+      <c r="BF140">
+        <v>4.69</v>
+      </c>
+      <c r="BG140">
+        <v>1.08</v>
+      </c>
+      <c r="BH140">
+        <v>5.07</v>
+      </c>
+      <c r="BI140">
+        <v>1.26</v>
+      </c>
+      <c r="BJ140">
+        <v>3.3</v>
+      </c>
+      <c r="BK140">
+        <v>1.61</v>
+      </c>
+      <c r="BL140">
+        <v>2.38</v>
+      </c>
+      <c r="BM140">
+        <v>1.81</v>
+      </c>
+      <c r="BN140">
+        <v>1.89</v>
+      </c>
+      <c r="BO140">
+        <v>2.25</v>
+      </c>
+      <c r="BP140">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7841164</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45838.875</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141" t="s">
+        <v>81</v>
+      </c>
+      <c r="H141" t="s">
+        <v>89</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141" t="s">
+        <v>97</v>
+      </c>
+      <c r="P141" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q141">
+        <v>2.27</v>
+      </c>
+      <c r="R141">
+        <v>2.05</v>
+      </c>
+      <c r="S141">
+        <v>6.5</v>
+      </c>
+      <c r="T141">
+        <v>1.5</v>
+      </c>
+      <c r="U141">
+        <v>2.42</v>
+      </c>
+      <c r="V141">
+        <v>3.34</v>
+      </c>
+      <c r="W141">
+        <v>1.29</v>
+      </c>
+      <c r="X141">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y141">
+        <v>1.04</v>
+      </c>
+      <c r="Z141">
+        <v>1.62</v>
+      </c>
+      <c r="AA141">
+        <v>3.48</v>
+      </c>
+      <c r="AB141">
+        <v>5.7</v>
+      </c>
+      <c r="AC141">
+        <v>1.1</v>
+      </c>
+      <c r="AD141">
+        <v>7.38</v>
+      </c>
+      <c r="AE141">
+        <v>1.48</v>
+      </c>
+      <c r="AF141">
+        <v>2.63</v>
+      </c>
+      <c r="AG141">
+        <v>2.3</v>
+      </c>
+      <c r="AH141">
+        <v>1.5</v>
+      </c>
+      <c r="AI141">
+        <v>2.3</v>
+      </c>
+      <c r="AJ141">
+        <v>1.64</v>
+      </c>
+      <c r="AK141">
+        <v>1.3</v>
+      </c>
+      <c r="AL141">
+        <v>1.27</v>
+      </c>
+      <c r="AM141">
+        <v>2.2</v>
+      </c>
+      <c r="AN141">
+        <v>2.17</v>
+      </c>
+      <c r="AO141">
+        <v>0.67</v>
+      </c>
+      <c r="AP141">
+        <v>1.86</v>
+      </c>
+      <c r="AQ141">
+        <v>1</v>
+      </c>
+      <c r="AR141">
+        <v>1.78</v>
+      </c>
+      <c r="AS141">
+        <v>1.21</v>
+      </c>
+      <c r="AT141">
+        <v>2.99</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>4</v>
+      </c>
+      <c r="AW141">
+        <v>9</v>
+      </c>
+      <c r="AX141">
+        <v>7</v>
+      </c>
+      <c r="AY141">
+        <v>13</v>
+      </c>
+      <c r="AZ141">
+        <v>11</v>
+      </c>
+      <c r="BA141">
+        <v>5</v>
+      </c>
+      <c r="BB141">
+        <v>3</v>
+      </c>
+      <c r="BC141">
+        <v>8</v>
+      </c>
+      <c r="BD141">
+        <v>1.33</v>
+      </c>
+      <c r="BE141">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF141">
+        <v>3.8</v>
+      </c>
+      <c r="BG141">
+        <v>1.26</v>
+      </c>
+      <c r="BH141">
+        <v>4.2</v>
+      </c>
+      <c r="BI141">
+        <v>1.47</v>
+      </c>
+      <c r="BJ141">
+        <v>2.9</v>
+      </c>
+      <c r="BK141">
+        <v>1.73</v>
+      </c>
+      <c r="BL141">
+        <v>2</v>
+      </c>
+      <c r="BM141">
+        <v>2.15</v>
+      </c>
+      <c r="BN141">
+        <v>1.61</v>
+      </c>
+      <c r="BO141">
+        <v>2.7</v>
+      </c>
+      <c r="BP141">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -29036,22 +29036,22 @@
         <v>3.64</v>
       </c>
       <c r="AU136">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV136">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW136">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX136">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY136">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ136">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA136">
         <v>5</v>
@@ -29248,13 +29248,13 @@
         <v>4</v>
       </c>
       <c r="AW137">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AX137">
         <v>3</v>
       </c>
       <c r="AY137">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AZ137">
         <v>7</v>
@@ -29448,22 +29448,22 @@
         <v>2.92</v>
       </c>
       <c r="AU138">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV138">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW138">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX138">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY138">
         <v>9</v>
       </c>
       <c r="AZ138">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA138">
         <v>5</v>
@@ -29654,22 +29654,22 @@
         <v>2.99</v>
       </c>
       <c r="AU139">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV139">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW139">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX139">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY139">
+        <v>17</v>
+      </c>
+      <c r="AZ139">
         <v>11</v>
-      </c>
-      <c r="AZ139">
-        <v>8</v>
       </c>
       <c r="BA139">
         <v>6</v>
@@ -29866,16 +29866,16 @@
         <v>3</v>
       </c>
       <c r="AW140">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX140">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY140">
+        <v>14</v>
+      </c>
+      <c r="AZ140">
         <v>11</v>
-      </c>
-      <c r="AZ140">
-        <v>8</v>
       </c>
       <c r="BA140">
         <v>5</v>
@@ -30066,22 +30066,22 @@
         <v>2.99</v>
       </c>
       <c r="AU141">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV141">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW141">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX141">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY141">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ141">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA141">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -29866,16 +29866,16 @@
         <v>3</v>
       </c>
       <c r="AW140">
+        <v>5</v>
+      </c>
+      <c r="AX140">
+        <v>5</v>
+      </c>
+      <c r="AY140">
+        <v>11</v>
+      </c>
+      <c r="AZ140">
         <v>8</v>
-      </c>
-      <c r="AX140">
-        <v>8</v>
-      </c>
-      <c r="AY140">
-        <v>14</v>
-      </c>
-      <c r="AZ140">
-        <v>11</v>
       </c>
       <c r="BA140">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -29866,16 +29866,16 @@
         <v>3</v>
       </c>
       <c r="AW140">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX140">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY140">
+        <v>14</v>
+      </c>
+      <c r="AZ140">
         <v>11</v>
-      </c>
-      <c r="AZ140">
-        <v>8</v>
       </c>
       <c r="BA140">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="237">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -586,6 +586,9 @@
     <t>['65', '68']</t>
   </si>
   <si>
+    <t>['14', '61']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1083,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1545,7 +1548,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1751,7 +1754,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2575,7 +2578,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3193,7 +3196,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3271,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ11">
         <v>0.86</v>
@@ -3399,7 +3402,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3605,7 +3608,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3811,7 +3814,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4635,7 +4638,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4841,7 +4844,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -4922,7 +4925,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ19">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5665,7 +5668,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6283,7 +6286,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6901,7 +6904,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7313,7 +7316,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8218,7 +8221,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ35">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR35">
         <v>1.66</v>
@@ -8549,7 +8552,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8755,7 +8758,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9245,7 +9248,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ40">
         <v>1.14</v>
@@ -9579,7 +9582,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10815,7 +10818,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11021,7 +11024,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11102,7 +11105,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ49">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR49">
         <v>1.47</v>
@@ -11433,7 +11436,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11639,7 +11642,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12335,7 +12338,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ55">
         <v>1.33</v>
@@ -12669,7 +12672,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13081,7 +13084,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13493,7 +13496,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14523,7 +14526,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14729,7 +14732,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14935,7 +14938,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15141,7 +15144,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15222,7 +15225,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ69">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR69">
         <v>1.87</v>
@@ -15553,7 +15556,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16583,7 +16586,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16867,7 +16870,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -18437,7 +18440,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19055,7 +19058,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19342,7 +19345,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ89">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR89">
         <v>1.31</v>
@@ -19673,7 +19676,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19879,7 +19882,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20085,7 +20088,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20497,7 +20500,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20575,7 +20578,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ95">
         <v>1.86</v>
@@ -20703,7 +20706,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -22557,7 +22560,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22844,7 +22847,7 @@
         <v>2</v>
       </c>
       <c r="AQ106">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR106">
         <v>1.79</v>
@@ -23175,7 +23178,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23381,7 +23384,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -23999,7 +24002,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24617,7 +24620,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24823,7 +24826,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25107,7 +25110,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ117">
         <v>1.38</v>
@@ -25441,7 +25444,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25853,7 +25856,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26471,7 +26474,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26677,7 +26680,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -26964,7 +26967,7 @@
         <v>2</v>
       </c>
       <c r="AQ126">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AR126">
         <v>1.99</v>
@@ -27373,7 +27376,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ128">
         <v>0.29</v>
@@ -27913,7 +27916,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28119,7 +28122,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28325,7 +28328,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28737,7 +28740,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29149,7 +29152,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29355,7 +29358,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -30130,6 +30133,212 @@
       </c>
       <c r="BP141">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7841174</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45841.89930555555</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142" t="s">
+        <v>79</v>
+      </c>
+      <c r="H142" t="s">
+        <v>74</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>2</v>
+      </c>
+      <c r="L142">
+        <v>2</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>3</v>
+      </c>
+      <c r="O142" t="s">
+        <v>190</v>
+      </c>
+      <c r="P142" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q142">
+        <v>2.4</v>
+      </c>
+      <c r="R142">
+        <v>2</v>
+      </c>
+      <c r="S142">
+        <v>5.2</v>
+      </c>
+      <c r="T142">
+        <v>1.54</v>
+      </c>
+      <c r="U142">
+        <v>2.47</v>
+      </c>
+      <c r="V142">
+        <v>3.22</v>
+      </c>
+      <c r="W142">
+        <v>1.3</v>
+      </c>
+      <c r="X142">
+        <v>8.5</v>
+      </c>
+      <c r="Y142">
+        <v>1.05</v>
+      </c>
+      <c r="Z142">
+        <v>1.75</v>
+      </c>
+      <c r="AA142">
+        <v>3.4</v>
+      </c>
+      <c r="AB142">
+        <v>4.25</v>
+      </c>
+      <c r="AC142">
+        <v>1.07</v>
+      </c>
+      <c r="AD142">
+        <v>7</v>
+      </c>
+      <c r="AE142">
+        <v>1.35</v>
+      </c>
+      <c r="AF142">
+        <v>2.9</v>
+      </c>
+      <c r="AG142">
+        <v>2.2</v>
+      </c>
+      <c r="AH142">
+        <v>1.58</v>
+      </c>
+      <c r="AI142">
+        <v>1.93</v>
+      </c>
+      <c r="AJ142">
+        <v>1.72</v>
+      </c>
+      <c r="AK142">
+        <v>1.3</v>
+      </c>
+      <c r="AL142">
+        <v>1.25</v>
+      </c>
+      <c r="AM142">
+        <v>2.05</v>
+      </c>
+      <c r="AN142">
+        <v>1.71</v>
+      </c>
+      <c r="AO142">
+        <v>0.71</v>
+      </c>
+      <c r="AP142">
+        <v>1.88</v>
+      </c>
+      <c r="AQ142">
+        <v>0.63</v>
+      </c>
+      <c r="AR142">
+        <v>1.94</v>
+      </c>
+      <c r="AS142">
+        <v>1.79</v>
+      </c>
+      <c r="AT142">
+        <v>3.73</v>
+      </c>
+      <c r="AU142">
+        <v>7</v>
+      </c>
+      <c r="AV142">
+        <v>7</v>
+      </c>
+      <c r="AW142">
+        <v>8</v>
+      </c>
+      <c r="AX142">
+        <v>15</v>
+      </c>
+      <c r="AY142">
+        <v>15</v>
+      </c>
+      <c r="AZ142">
+        <v>22</v>
+      </c>
+      <c r="BA142">
+        <v>2</v>
+      </c>
+      <c r="BB142">
+        <v>5</v>
+      </c>
+      <c r="BC142">
+        <v>7</v>
+      </c>
+      <c r="BD142">
+        <v>1.55</v>
+      </c>
+      <c r="BE142">
+        <v>7.5</v>
+      </c>
+      <c r="BF142">
+        <v>3.1</v>
+      </c>
+      <c r="BG142">
+        <v>1.23</v>
+      </c>
+      <c r="BH142">
+        <v>5.1</v>
+      </c>
+      <c r="BI142">
+        <v>1.4</v>
+      </c>
+      <c r="BJ142">
+        <v>3.2</v>
+      </c>
+      <c r="BK142">
+        <v>1.61</v>
+      </c>
+      <c r="BL142">
+        <v>2.38</v>
+      </c>
+      <c r="BM142">
+        <v>1.8</v>
+      </c>
+      <c r="BN142">
+        <v>1.91</v>
+      </c>
+      <c r="BO142">
+        <v>2.25</v>
+      </c>
+      <c r="BP142">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="238">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -589,6 +589,9 @@
     <t>['14', '61']</t>
   </si>
   <si>
+    <t>['18', '23']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1086,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP142"/>
+  <dimension ref="A1:BP143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1548,7 +1551,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1754,7 +1757,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2038,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ5">
         <v>0.57</v>
@@ -2578,7 +2581,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3196,7 +3199,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3402,7 +3405,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3608,7 +3611,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3814,7 +3817,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4513,7 +4516,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ17">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4638,7 +4641,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4844,7 +4847,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5668,7 +5671,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6158,7 +6161,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ25">
         <v>1.33</v>
@@ -6286,7 +6289,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6779,7 +6782,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ28">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR28">
         <v>1.84</v>
@@ -6904,7 +6907,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7316,7 +7319,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8552,7 +8555,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8758,7 +8761,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9582,7 +9585,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10278,7 +10281,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ45">
         <v>0.75</v>
@@ -10693,7 +10696,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ47">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR47">
         <v>2.22</v>
@@ -10818,7 +10821,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11024,7 +11027,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11436,7 +11439,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11642,7 +11645,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12672,7 +12675,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13084,7 +13087,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13496,7 +13499,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14401,7 +14404,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ65">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR65">
         <v>2.13</v>
@@ -14526,7 +14529,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14732,7 +14735,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14938,7 +14941,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15144,7 +15147,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15556,7 +15559,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16586,7 +16589,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17694,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ81">
         <v>0.86</v>
@@ -18315,7 +18318,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ84">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR84">
         <v>1.23</v>
@@ -18440,7 +18443,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19058,7 +19061,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19676,7 +19679,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19882,7 +19885,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20088,7 +20091,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20372,7 +20375,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ94">
         <v>1.29</v>
@@ -20500,7 +20503,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20706,7 +20709,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -22560,7 +22563,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23053,7 +23056,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ107">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -23178,7 +23181,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23384,7 +23387,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -24002,7 +24005,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24620,7 +24623,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24826,7 +24829,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25444,7 +25447,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25856,7 +25859,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26474,7 +26477,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26680,7 +26683,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27170,7 +27173,7 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ127">
         <v>1.14</v>
@@ -27379,7 +27382,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ128">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR128">
         <v>1.85</v>
@@ -27916,7 +27919,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28122,7 +28125,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28328,7 +28331,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28740,7 +28743,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29152,7 +29155,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29358,7 +29361,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -30275,22 +30278,22 @@
         <v>3.73</v>
       </c>
       <c r="AU142">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV142">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW142">
         <v>8</v>
       </c>
       <c r="AX142">
+        <v>10</v>
+      </c>
+      <c r="AY142">
+        <v>13</v>
+      </c>
+      <c r="AZ142">
         <v>15</v>
-      </c>
-      <c r="AY142">
-        <v>15</v>
-      </c>
-      <c r="AZ142">
-        <v>22</v>
       </c>
       <c r="BA142">
         <v>2</v>
@@ -30339,6 +30342,212 @@
       </c>
       <c r="BP142">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7841172</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45842.79166666666</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143" t="s">
+        <v>73</v>
+      </c>
+      <c r="H143" t="s">
+        <v>77</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="L143">
+        <v>2</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>2</v>
+      </c>
+      <c r="O143" t="s">
+        <v>191</v>
+      </c>
+      <c r="P143" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q143">
+        <v>2.1</v>
+      </c>
+      <c r="R143">
+        <v>1.83</v>
+      </c>
+      <c r="S143">
+        <v>5.5</v>
+      </c>
+      <c r="T143">
+        <v>1.61</v>
+      </c>
+      <c r="U143">
+        <v>2.25</v>
+      </c>
+      <c r="V143">
+        <v>3.8</v>
+      </c>
+      <c r="W143">
+        <v>1.21</v>
+      </c>
+      <c r="X143">
+        <v>12.5</v>
+      </c>
+      <c r="Y143">
+        <v>1.03</v>
+      </c>
+      <c r="Z143">
+        <v>1.65</v>
+      </c>
+      <c r="AA143">
+        <v>3.32</v>
+      </c>
+      <c r="AB143">
+        <v>5.7</v>
+      </c>
+      <c r="AC143">
+        <v>1.08</v>
+      </c>
+      <c r="AD143">
+        <v>6.5</v>
+      </c>
+      <c r="AE143">
+        <v>1.55</v>
+      </c>
+      <c r="AF143">
+        <v>2.25</v>
+      </c>
+      <c r="AG143">
+        <v>2.87</v>
+      </c>
+      <c r="AH143">
+        <v>1.39</v>
+      </c>
+      <c r="AI143">
+        <v>2.45</v>
+      </c>
+      <c r="AJ143">
+        <v>1.55</v>
+      </c>
+      <c r="AK143">
+        <v>1.33</v>
+      </c>
+      <c r="AL143">
+        <v>1.35</v>
+      </c>
+      <c r="AM143">
+        <v>2.05</v>
+      </c>
+      <c r="AN143">
+        <v>2.67</v>
+      </c>
+      <c r="AO143">
+        <v>0.29</v>
+      </c>
+      <c r="AP143">
+        <v>2.71</v>
+      </c>
+      <c r="AQ143">
+        <v>0.25</v>
+      </c>
+      <c r="AR143">
+        <v>1.44</v>
+      </c>
+      <c r="AS143">
+        <v>1.22</v>
+      </c>
+      <c r="AT143">
+        <v>2.66</v>
+      </c>
+      <c r="AU143">
+        <v>6</v>
+      </c>
+      <c r="AV143">
+        <v>8</v>
+      </c>
+      <c r="AW143">
+        <v>3</v>
+      </c>
+      <c r="AX143">
+        <v>7</v>
+      </c>
+      <c r="AY143">
+        <v>9</v>
+      </c>
+      <c r="AZ143">
+        <v>15</v>
+      </c>
+      <c r="BA143">
+        <v>2</v>
+      </c>
+      <c r="BB143">
+        <v>5</v>
+      </c>
+      <c r="BC143">
+        <v>7</v>
+      </c>
+      <c r="BD143">
+        <v>1.49</v>
+      </c>
+      <c r="BE143">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF143">
+        <v>4.03</v>
+      </c>
+      <c r="BG143">
+        <v>1.23</v>
+      </c>
+      <c r="BH143">
+        <v>3.8</v>
+      </c>
+      <c r="BI143">
+        <v>1.28</v>
+      </c>
+      <c r="BJ143">
+        <v>3.12</v>
+      </c>
+      <c r="BK143">
+        <v>1.57</v>
+      </c>
+      <c r="BL143">
+        <v>2.3</v>
+      </c>
+      <c r="BM143">
+        <v>1.96</v>
+      </c>
+      <c r="BN143">
+        <v>1.75</v>
+      </c>
+      <c r="BO143">
+        <v>2.54</v>
+      </c>
+      <c r="BP143">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -30278,22 +30278,22 @@
         <v>3.73</v>
       </c>
       <c r="AU142">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV142">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW142">
         <v>8</v>
       </c>
       <c r="AX142">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AY142">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ142">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BA142">
         <v>2</v>
@@ -30484,22 +30484,22 @@
         <v>2.66</v>
       </c>
       <c r="AU143">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV143">
         <v>8</v>
       </c>
       <c r="AW143">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX143">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY143">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ143">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA143">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="238">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1089,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP143"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2868,7 +2868,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -5131,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ20">
         <v>0.86</v>
@@ -9045,7 +9045,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ39">
         <v>1.38</v>
@@ -9254,7 +9254,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR40">
         <v>1.82</v>
@@ -11929,7 +11929,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ53">
         <v>0.29</v>
@@ -13374,7 +13374,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ60">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR60">
         <v>1.78</v>
@@ -15431,7 +15431,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ70">
         <v>0.57</v>
@@ -16052,7 +16052,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ73">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR73">
         <v>1.75</v>
@@ -18315,7 +18315,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ84">
         <v>0.25</v>
@@ -20790,7 +20790,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ96">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR96">
         <v>1.76</v>
@@ -23465,7 +23465,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ109">
         <v>0.75</v>
@@ -25322,7 +25322,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ118">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR118">
         <v>2</v>
@@ -26761,7 +26761,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ125">
         <v>0.71</v>
@@ -27176,7 +27176,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ127">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -30502,13 +30502,13 @@
         <v>18</v>
       </c>
       <c r="BA143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB143">
         <v>5</v>
       </c>
       <c r="BC143">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD143">
         <v>1.49</v>
@@ -30548,6 +30548,212 @@
       </c>
       <c r="BP143">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7841175</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45843.66666666666</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144" t="s">
+        <v>88</v>
+      </c>
+      <c r="H144" t="s">
+        <v>81</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144" t="s">
+        <v>97</v>
+      </c>
+      <c r="P144" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q144">
+        <v>3</v>
+      </c>
+      <c r="R144">
+        <v>1.89</v>
+      </c>
+      <c r="S144">
+        <v>3.95</v>
+      </c>
+      <c r="T144">
+        <v>1.57</v>
+      </c>
+      <c r="U144">
+        <v>2.4</v>
+      </c>
+      <c r="V144">
+        <v>3.4</v>
+      </c>
+      <c r="W144">
+        <v>1.3</v>
+      </c>
+      <c r="X144">
+        <v>10.25</v>
+      </c>
+      <c r="Y144">
+        <v>1.05</v>
+      </c>
+      <c r="Z144">
+        <v>2.44</v>
+      </c>
+      <c r="AA144">
+        <v>2.9</v>
+      </c>
+      <c r="AB144">
+        <v>2.9</v>
+      </c>
+      <c r="AC144">
+        <v>1.07</v>
+      </c>
+      <c r="AD144">
+        <v>6.75</v>
+      </c>
+      <c r="AE144">
+        <v>1.39</v>
+      </c>
+      <c r="AF144">
+        <v>2.6</v>
+      </c>
+      <c r="AG144">
+        <v>2.55</v>
+      </c>
+      <c r="AH144">
+        <v>1.55</v>
+      </c>
+      <c r="AI144">
+        <v>1.85</v>
+      </c>
+      <c r="AJ144">
+        <v>1.8</v>
+      </c>
+      <c r="AK144">
+        <v>1.3</v>
+      </c>
+      <c r="AL144">
+        <v>1.38</v>
+      </c>
+      <c r="AM144">
+        <v>1.6</v>
+      </c>
+      <c r="AN144">
+        <v>2.29</v>
+      </c>
+      <c r="AO144">
+        <v>1.14</v>
+      </c>
+      <c r="AP144">
+        <v>2.13</v>
+      </c>
+      <c r="AQ144">
+        <v>1.13</v>
+      </c>
+      <c r="AR144">
+        <v>1.33</v>
+      </c>
+      <c r="AS144">
+        <v>1.62</v>
+      </c>
+      <c r="AT144">
+        <v>2.95</v>
+      </c>
+      <c r="AU144">
+        <v>6</v>
+      </c>
+      <c r="AV144">
+        <v>4</v>
+      </c>
+      <c r="AW144">
+        <v>3</v>
+      </c>
+      <c r="AX144">
+        <v>3</v>
+      </c>
+      <c r="AY144">
+        <v>9</v>
+      </c>
+      <c r="AZ144">
+        <v>7</v>
+      </c>
+      <c r="BA144">
+        <v>7</v>
+      </c>
+      <c r="BB144">
+        <v>5</v>
+      </c>
+      <c r="BC144">
+        <v>12</v>
+      </c>
+      <c r="BD144">
+        <v>2.33</v>
+      </c>
+      <c r="BE144">
+        <v>6.65</v>
+      </c>
+      <c r="BF144">
+        <v>1.81</v>
+      </c>
+      <c r="BG144">
+        <v>1.16</v>
+      </c>
+      <c r="BH144">
+        <v>4</v>
+      </c>
+      <c r="BI144">
+        <v>1.3</v>
+      </c>
+      <c r="BJ144">
+        <v>3.5</v>
+      </c>
+      <c r="BK144">
+        <v>1.56</v>
+      </c>
+      <c r="BL144">
+        <v>2.25</v>
+      </c>
+      <c r="BM144">
+        <v>1.91</v>
+      </c>
+      <c r="BN144">
+        <v>1.8</v>
+      </c>
+      <c r="BO144">
+        <v>2.38</v>
+      </c>
+      <c r="BP144">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="238">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1089,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -4104,7 +4104,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ15">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ24">
         <v>0.75</v>
@@ -7606,7 +7606,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ32">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR32">
         <v>1.17</v>
@@ -10487,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ46">
         <v>0.86</v>
@@ -12138,7 +12138,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ54">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR54">
         <v>1.72</v>
@@ -13989,7 +13989,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ63">
         <v>0.86</v>
@@ -15640,7 +15640,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR71">
         <v>2.01</v>
@@ -18521,7 +18521,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ85">
         <v>0.57</v>
@@ -18730,7 +18730,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ86">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR86">
         <v>2.07</v>
@@ -22438,7 +22438,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ104">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR104">
         <v>1.67</v>
@@ -22847,7 +22847,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ106">
         <v>0.63</v>
@@ -26555,7 +26555,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ124">
         <v>1.17</v>
@@ -26764,7 +26764,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ125">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR125">
         <v>1.3</v>
@@ -30484,31 +30484,31 @@
         <v>2.66</v>
       </c>
       <c r="AU143">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV143">
         <v>8</v>
       </c>
       <c r="AW143">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX143">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY143">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ143">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB143">
         <v>5</v>
       </c>
       <c r="BC143">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD143">
         <v>1.49</v>
@@ -30754,6 +30754,212 @@
       </c>
       <c r="BP144">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7841176</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45843.8125</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145" t="s">
+        <v>78</v>
+      </c>
+      <c r="H145" t="s">
+        <v>71</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145" t="s">
+        <v>97</v>
+      </c>
+      <c r="P145" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q145">
+        <v>2.3</v>
+      </c>
+      <c r="R145">
+        <v>2.05</v>
+      </c>
+      <c r="S145">
+        <v>5.03</v>
+      </c>
+      <c r="T145">
+        <v>1.49</v>
+      </c>
+      <c r="U145">
+        <v>2.58</v>
+      </c>
+      <c r="V145">
+        <v>3.1</v>
+      </c>
+      <c r="W145">
+        <v>1.33</v>
+      </c>
+      <c r="X145">
+        <v>6.8</v>
+      </c>
+      <c r="Y145">
+        <v>1.06</v>
+      </c>
+      <c r="Z145">
+        <v>1.71</v>
+      </c>
+      <c r="AA145">
+        <v>3.3</v>
+      </c>
+      <c r="AB145">
+        <v>4.98</v>
+      </c>
+      <c r="AC145">
+        <v>1.08</v>
+      </c>
+      <c r="AD145">
+        <v>7.6</v>
+      </c>
+      <c r="AE145">
+        <v>1.36</v>
+      </c>
+      <c r="AF145">
+        <v>2.71</v>
+      </c>
+      <c r="AG145">
+        <v>2.25</v>
+      </c>
+      <c r="AH145">
+        <v>1.62</v>
+      </c>
+      <c r="AI145">
+        <v>2.1</v>
+      </c>
+      <c r="AJ145">
+        <v>1.61</v>
+      </c>
+      <c r="AK145">
+        <v>1.15</v>
+      </c>
+      <c r="AL145">
+        <v>1.29</v>
+      </c>
+      <c r="AM145">
+        <v>2.05</v>
+      </c>
+      <c r="AN145">
+        <v>2</v>
+      </c>
+      <c r="AO145">
+        <v>0.71</v>
+      </c>
+      <c r="AP145">
+        <v>1.88</v>
+      </c>
+      <c r="AQ145">
+        <v>0.75</v>
+      </c>
+      <c r="AR145">
+        <v>1.83</v>
+      </c>
+      <c r="AS145">
+        <v>1.26</v>
+      </c>
+      <c r="AT145">
+        <v>3.09</v>
+      </c>
+      <c r="AU145">
+        <v>6</v>
+      </c>
+      <c r="AV145">
+        <v>2</v>
+      </c>
+      <c r="AW145">
+        <v>9</v>
+      </c>
+      <c r="AX145">
+        <v>1</v>
+      </c>
+      <c r="AY145">
+        <v>15</v>
+      </c>
+      <c r="AZ145">
+        <v>3</v>
+      </c>
+      <c r="BA145">
+        <v>2</v>
+      </c>
+      <c r="BB145">
+        <v>1</v>
+      </c>
+      <c r="BC145">
+        <v>3</v>
+      </c>
+      <c r="BD145">
+        <v>1.7</v>
+      </c>
+      <c r="BE145">
+        <v>6.9</v>
+      </c>
+      <c r="BF145">
+        <v>2.79</v>
+      </c>
+      <c r="BG145">
+        <v>1.11</v>
+      </c>
+      <c r="BH145">
+        <v>4.33</v>
+      </c>
+      <c r="BI145">
+        <v>1.33</v>
+      </c>
+      <c r="BJ145">
+        <v>3.25</v>
+      </c>
+      <c r="BK145">
+        <v>1.49</v>
+      </c>
+      <c r="BL145">
+        <v>2.38</v>
+      </c>
+      <c r="BM145">
+        <v>1.85</v>
+      </c>
+      <c r="BN145">
+        <v>1.85</v>
+      </c>
+      <c r="BO145">
+        <v>2.45</v>
+      </c>
+      <c r="BP145">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="238">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1089,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1632,7 +1632,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ3">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -4307,7 +4307,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16">
         <v>0.75</v>
@@ -5546,7 +5546,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ22">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR22">
         <v>1.69</v>
@@ -8633,7 +8633,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ37">
         <v>1.29</v>
@@ -9666,7 +9666,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ42">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR42">
         <v>2.49</v>
@@ -10899,7 +10899,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48">
         <v>0.86</v>
@@ -15225,7 +15225,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69">
         <v>0.63</v>
@@ -16464,7 +16464,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ75">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR75">
         <v>1.88</v>
@@ -18933,7 +18933,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87">
         <v>0.75</v>
@@ -20996,7 +20996,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR97">
         <v>1.76</v>
@@ -23877,7 +23877,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
         <v>0.86</v>
@@ -26558,7 +26558,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ124">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR124">
         <v>1.84</v>
@@ -27585,7 +27585,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ129">
         <v>0.57</v>
@@ -30484,22 +30484,22 @@
         <v>2.66</v>
       </c>
       <c r="AU143">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV143">
         <v>8</v>
       </c>
       <c r="AW143">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX143">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY143">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ143">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA143">
         <v>2</v>
@@ -30693,19 +30693,19 @@
         <v>6</v>
       </c>
       <c r="AV144">
+        <v>5</v>
+      </c>
+      <c r="AW144">
+        <v>5</v>
+      </c>
+      <c r="AX144">
         <v>4</v>
       </c>
-      <c r="AW144">
-        <v>3</v>
-      </c>
-      <c r="AX144">
-        <v>3</v>
-      </c>
       <c r="AY144">
+        <v>11</v>
+      </c>
+      <c r="AZ144">
         <v>9</v>
-      </c>
-      <c r="AZ144">
-        <v>7</v>
       </c>
       <c r="BA144">
         <v>7</v>
@@ -30896,7 +30896,7 @@
         <v>3.09</v>
       </c>
       <c r="AU145">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AV145">
         <v>2</v>
@@ -30905,13 +30905,13 @@
         <v>9</v>
       </c>
       <c r="AX145">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY145">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ145">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA145">
         <v>2</v>
@@ -30960,6 +30960,212 @@
       </c>
       <c r="BP145">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7841178</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45843.85416666666</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146" t="s">
+        <v>84</v>
+      </c>
+      <c r="H146" t="s">
+        <v>80</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>1</v>
+      </c>
+      <c r="N146">
+        <v>1</v>
+      </c>
+      <c r="O146" t="s">
+        <v>97</v>
+      </c>
+      <c r="P146" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q146">
+        <v>4.7</v>
+      </c>
+      <c r="R146">
+        <v>1.91</v>
+      </c>
+      <c r="S146">
+        <v>2.8</v>
+      </c>
+      <c r="T146">
+        <v>1.57</v>
+      </c>
+      <c r="U146">
+        <v>2.25</v>
+      </c>
+      <c r="V146">
+        <v>3.65</v>
+      </c>
+      <c r="W146">
+        <v>1.25</v>
+      </c>
+      <c r="X146">
+        <v>11</v>
+      </c>
+      <c r="Y146">
+        <v>1.02</v>
+      </c>
+      <c r="Z146">
+        <v>3.45</v>
+      </c>
+      <c r="AA146">
+        <v>2.75</v>
+      </c>
+      <c r="AB146">
+        <v>2.09</v>
+      </c>
+      <c r="AC146">
+        <v>1.11</v>
+      </c>
+      <c r="AD146">
+        <v>5.75</v>
+      </c>
+      <c r="AE146">
+        <v>1.57</v>
+      </c>
+      <c r="AF146">
+        <v>2.3</v>
+      </c>
+      <c r="AG146">
+        <v>2.6</v>
+      </c>
+      <c r="AH146">
+        <v>1.42</v>
+      </c>
+      <c r="AI146">
+        <v>2.25</v>
+      </c>
+      <c r="AJ146">
+        <v>1.57</v>
+      </c>
+      <c r="AK146">
+        <v>1.57</v>
+      </c>
+      <c r="AL146">
+        <v>1.3</v>
+      </c>
+      <c r="AM146">
+        <v>1.25</v>
+      </c>
+      <c r="AN146">
+        <v>1.71</v>
+      </c>
+      <c r="AO146">
+        <v>1.17</v>
+      </c>
+      <c r="AP146">
+        <v>1.5</v>
+      </c>
+      <c r="AQ146">
+        <v>1.43</v>
+      </c>
+      <c r="AR146">
+        <v>1.55</v>
+      </c>
+      <c r="AS146">
+        <v>1.31</v>
+      </c>
+      <c r="AT146">
+        <v>2.86</v>
+      </c>
+      <c r="AU146">
+        <v>2</v>
+      </c>
+      <c r="AV146">
+        <v>8</v>
+      </c>
+      <c r="AW146">
+        <v>8</v>
+      </c>
+      <c r="AX146">
+        <v>8</v>
+      </c>
+      <c r="AY146">
+        <v>10</v>
+      </c>
+      <c r="AZ146">
+        <v>16</v>
+      </c>
+      <c r="BA146">
+        <v>3</v>
+      </c>
+      <c r="BB146">
+        <v>5</v>
+      </c>
+      <c r="BC146">
+        <v>8</v>
+      </c>
+      <c r="BD146">
+        <v>2.18</v>
+      </c>
+      <c r="BE146">
+        <v>6.75</v>
+      </c>
+      <c r="BF146">
+        <v>1.82</v>
+      </c>
+      <c r="BG146">
+        <v>1.17</v>
+      </c>
+      <c r="BH146">
+        <v>3.8</v>
+      </c>
+      <c r="BI146">
+        <v>1.4</v>
+      </c>
+      <c r="BJ146">
+        <v>2.7</v>
+      </c>
+      <c r="BK146">
+        <v>1.67</v>
+      </c>
+      <c r="BL146">
+        <v>2.16</v>
+      </c>
+      <c r="BM146">
+        <v>1.85</v>
+      </c>
+      <c r="BN146">
+        <v>1.85</v>
+      </c>
+      <c r="BO146">
+        <v>2.6</v>
+      </c>
+      <c r="BP146">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -729,6 +729,9 @@
   <si>
     <t>['90+7', '89']</t>
   </si>
+  <si>
+    <t>['3', '61', '90+9']</t>
+  </si>
 </sst>
 </file>
 
@@ -1089,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP146"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2044,7 +2047,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ5">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2659,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -3074,7 +3077,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -5337,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ21">
         <v>0.86</v>
@@ -6164,7 +6167,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR25">
         <v>1.41</v>
@@ -6370,7 +6373,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ26">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6985,7 +6988,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -7191,7 +7194,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ30">
         <v>0.86</v>
@@ -11517,7 +11520,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51">
         <v>1.86</v>
@@ -11723,7 +11726,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ52">
         <v>1.38</v>
@@ -12344,7 +12347,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR55">
         <v>1.76</v>
@@ -13580,7 +13583,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ61">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -15019,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ68">
         <v>0.86</v>
@@ -15434,7 +15437,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ70">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR70">
         <v>1.26</v>
@@ -15843,7 +15846,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ72">
         <v>1.29</v>
@@ -16670,7 +16673,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR76">
         <v>1.64</v>
@@ -19345,7 +19348,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ89">
         <v>0.63</v>
@@ -19554,7 +19557,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ90">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR90">
         <v>1.68</v>
@@ -19963,7 +19966,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20172,7 +20175,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR93">
         <v>1.7</v>
@@ -22023,7 +22026,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ102">
         <v>1.38</v>
@@ -23674,7 +23677,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ110">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR110">
         <v>2.01</v>
@@ -26143,7 +26146,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ122">
         <v>0.57</v>
@@ -26967,7 +26970,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ126">
         <v>0.63</v>
@@ -27588,7 +27591,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR129">
         <v>1.61</v>
@@ -27794,7 +27797,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ130">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AR130">
         <v>1.68</v>
@@ -30693,19 +30696,19 @@
         <v>6</v>
       </c>
       <c r="AV144">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW144">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX144">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY144">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ144">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA144">
         <v>7</v>
@@ -30896,7 +30899,7 @@
         <v>3.09</v>
       </c>
       <c r="AU145">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AV145">
         <v>2</v>
@@ -30905,13 +30908,13 @@
         <v>9</v>
       </c>
       <c r="AX145">
+        <v>1</v>
+      </c>
+      <c r="AY145">
+        <v>15</v>
+      </c>
+      <c r="AZ145">
         <v>3</v>
-      </c>
-      <c r="AY145">
-        <v>21</v>
-      </c>
-      <c r="AZ145">
-        <v>5</v>
       </c>
       <c r="BA145">
         <v>2</v>
@@ -31105,19 +31108,19 @@
         <v>2</v>
       </c>
       <c r="AV146">
+        <v>5</v>
+      </c>
+      <c r="AW146">
+        <v>6</v>
+      </c>
+      <c r="AX146">
+        <v>3</v>
+      </c>
+      <c r="AY146">
         <v>8</v>
       </c>
-      <c r="AW146">
+      <c r="AZ146">
         <v>8</v>
-      </c>
-      <c r="AX146">
-        <v>8</v>
-      </c>
-      <c r="AY146">
-        <v>10</v>
-      </c>
-      <c r="AZ146">
-        <v>16</v>
       </c>
       <c r="BA146">
         <v>3</v>
@@ -31166,6 +31169,418 @@
       </c>
       <c r="BP146">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7841180</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45844.66666666666</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147" t="s">
+        <v>76</v>
+      </c>
+      <c r="H147" t="s">
+        <v>83</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>1</v>
+      </c>
+      <c r="K147">
+        <v>2</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <v>3</v>
+      </c>
+      <c r="N147">
+        <v>4</v>
+      </c>
+      <c r="O147" t="s">
+        <v>103</v>
+      </c>
+      <c r="P147" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q147">
+        <v>2.95</v>
+      </c>
+      <c r="R147">
+        <v>1.79</v>
+      </c>
+      <c r="S147">
+        <v>4.56</v>
+      </c>
+      <c r="T147">
+        <v>1.55</v>
+      </c>
+      <c r="U147">
+        <v>2.25</v>
+      </c>
+      <c r="V147">
+        <v>3.55</v>
+      </c>
+      <c r="W147">
+        <v>1.24</v>
+      </c>
+      <c r="X147">
+        <v>9</v>
+      </c>
+      <c r="Y147">
+        <v>1.05</v>
+      </c>
+      <c r="Z147">
+        <v>2.3</v>
+      </c>
+      <c r="AA147">
+        <v>2.8</v>
+      </c>
+      <c r="AB147">
+        <v>3.4</v>
+      </c>
+      <c r="AC147">
+        <v>1.06</v>
+      </c>
+      <c r="AD147">
+        <v>6</v>
+      </c>
+      <c r="AE147">
+        <v>1.61</v>
+      </c>
+      <c r="AF147">
+        <v>2.36</v>
+      </c>
+      <c r="AG147">
+        <v>2.55</v>
+      </c>
+      <c r="AH147">
+        <v>1.45</v>
+      </c>
+      <c r="AI147">
+        <v>2.21</v>
+      </c>
+      <c r="AJ147">
+        <v>1.62</v>
+      </c>
+      <c r="AK147">
+        <v>1.4</v>
+      </c>
+      <c r="AL147">
+        <v>1.41</v>
+      </c>
+      <c r="AM147">
+        <v>1.57</v>
+      </c>
+      <c r="AN147">
+        <v>2</v>
+      </c>
+      <c r="AO147">
+        <v>0.57</v>
+      </c>
+      <c r="AP147">
+        <v>1.71</v>
+      </c>
+      <c r="AQ147">
+        <v>0.88</v>
+      </c>
+      <c r="AR147">
+        <v>1.83</v>
+      </c>
+      <c r="AS147">
+        <v>1.24</v>
+      </c>
+      <c r="AT147">
+        <v>3.07</v>
+      </c>
+      <c r="AU147">
+        <v>4</v>
+      </c>
+      <c r="AV147">
+        <v>10</v>
+      </c>
+      <c r="AW147">
+        <v>8</v>
+      </c>
+      <c r="AX147">
+        <v>4</v>
+      </c>
+      <c r="AY147">
+        <v>12</v>
+      </c>
+      <c r="AZ147">
+        <v>14</v>
+      </c>
+      <c r="BA147">
+        <v>7</v>
+      </c>
+      <c r="BB147">
+        <v>8</v>
+      </c>
+      <c r="BC147">
+        <v>15</v>
+      </c>
+      <c r="BD147">
+        <v>1.71</v>
+      </c>
+      <c r="BE147">
+        <v>6.75</v>
+      </c>
+      <c r="BF147">
+        <v>2.33</v>
+      </c>
+      <c r="BG147">
+        <v>1.2</v>
+      </c>
+      <c r="BH147">
+        <v>3.95</v>
+      </c>
+      <c r="BI147">
+        <v>1.36</v>
+      </c>
+      <c r="BJ147">
+        <v>2.78</v>
+      </c>
+      <c r="BK147">
+        <v>1.82</v>
+      </c>
+      <c r="BL147">
+        <v>2.1</v>
+      </c>
+      <c r="BM147">
+        <v>2.04</v>
+      </c>
+      <c r="BN147">
+        <v>1.69</v>
+      </c>
+      <c r="BO147">
+        <v>2.65</v>
+      </c>
+      <c r="BP147">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7841181</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45844.77083333334</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148" t="s">
+        <v>89</v>
+      </c>
+      <c r="H148" t="s">
+        <v>85</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148" t="s">
+        <v>97</v>
+      </c>
+      <c r="P148" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q148">
+        <v>4.3</v>
+      </c>
+      <c r="R148">
+        <v>1.72</v>
+      </c>
+      <c r="S148">
+        <v>3.27</v>
+      </c>
+      <c r="T148">
+        <v>1.74</v>
+      </c>
+      <c r="U148">
+        <v>2.13</v>
+      </c>
+      <c r="V148">
+        <v>3.8</v>
+      </c>
+      <c r="W148">
+        <v>1.2</v>
+      </c>
+      <c r="X148">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y148">
+        <v>1</v>
+      </c>
+      <c r="Z148">
+        <v>3.45</v>
+      </c>
+      <c r="AA148">
+        <v>2.78</v>
+      </c>
+      <c r="AB148">
+        <v>2.32</v>
+      </c>
+      <c r="AC148">
+        <v>1.11</v>
+      </c>
+      <c r="AD148">
+        <v>5.19</v>
+      </c>
+      <c r="AE148">
+        <v>1.75</v>
+      </c>
+      <c r="AF148">
+        <v>2.1</v>
+      </c>
+      <c r="AG148">
+        <v>3.5</v>
+      </c>
+      <c r="AH148">
+        <v>1.28</v>
+      </c>
+      <c r="AI148">
+        <v>2.45</v>
+      </c>
+      <c r="AJ148">
+        <v>1.48</v>
+      </c>
+      <c r="AK148">
+        <v>1.45</v>
+      </c>
+      <c r="AL148">
+        <v>1.4</v>
+      </c>
+      <c r="AM148">
+        <v>1.3</v>
+      </c>
+      <c r="AN148">
+        <v>1.29</v>
+      </c>
+      <c r="AO148">
+        <v>1.33</v>
+      </c>
+      <c r="AP148">
+        <v>1.25</v>
+      </c>
+      <c r="AQ148">
+        <v>1.29</v>
+      </c>
+      <c r="AR148">
+        <v>1.37</v>
+      </c>
+      <c r="AS148">
+        <v>1.21</v>
+      </c>
+      <c r="AT148">
+        <v>2.58</v>
+      </c>
+      <c r="AU148">
+        <v>7</v>
+      </c>
+      <c r="AV148">
+        <v>3</v>
+      </c>
+      <c r="AW148">
+        <v>6</v>
+      </c>
+      <c r="AX148">
+        <v>1</v>
+      </c>
+      <c r="AY148">
+        <v>13</v>
+      </c>
+      <c r="AZ148">
+        <v>4</v>
+      </c>
+      <c r="BA148">
+        <v>8</v>
+      </c>
+      <c r="BB148">
+        <v>2</v>
+      </c>
+      <c r="BC148">
+        <v>10</v>
+      </c>
+      <c r="BD148">
+        <v>2.15</v>
+      </c>
+      <c r="BE148">
+        <v>7.25</v>
+      </c>
+      <c r="BF148">
+        <v>2.04</v>
+      </c>
+      <c r="BG148">
+        <v>1.18</v>
+      </c>
+      <c r="BH148">
+        <v>3.8</v>
+      </c>
+      <c r="BI148">
+        <v>1.35</v>
+      </c>
+      <c r="BJ148">
+        <v>2.6</v>
+      </c>
+      <c r="BK148">
+        <v>1.68</v>
+      </c>
+      <c r="BL148">
+        <v>2.1</v>
+      </c>
+      <c r="BM148">
+        <v>2.1</v>
+      </c>
+      <c r="BN148">
+        <v>1.67</v>
+      </c>
+      <c r="BO148">
+        <v>2.78</v>
+      </c>
+      <c r="BP148">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -30696,19 +30696,19 @@
         <v>6</v>
       </c>
       <c r="AV144">
+        <v>5</v>
+      </c>
+      <c r="AW144">
+        <v>5</v>
+      </c>
+      <c r="AX144">
         <v>4</v>
       </c>
-      <c r="AW144">
-        <v>3</v>
-      </c>
-      <c r="AX144">
-        <v>3</v>
-      </c>
       <c r="AY144">
+        <v>11</v>
+      </c>
+      <c r="AZ144">
         <v>9</v>
-      </c>
-      <c r="AZ144">
-        <v>7</v>
       </c>
       <c r="BA144">
         <v>7</v>
@@ -30899,7 +30899,7 @@
         <v>3.09</v>
       </c>
       <c r="AU145">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AV145">
         <v>2</v>
@@ -30908,13 +30908,13 @@
         <v>9</v>
       </c>
       <c r="AX145">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY145">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ145">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA145">
         <v>2</v>
@@ -31108,19 +31108,19 @@
         <v>2</v>
       </c>
       <c r="AV146">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW146">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX146">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY146">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ146">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BA146">
         <v>3</v>
@@ -31311,22 +31311,22 @@
         <v>3.07</v>
       </c>
       <c r="AU147">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV147">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW147">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX147">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY147">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ147">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA147">
         <v>7</v>
@@ -31523,16 +31523,16 @@
         <v>3</v>
       </c>
       <c r="AW148">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AX148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY148">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ148">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA148">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="241">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -732,6 +732,12 @@
   <si>
     <t>['3', '61', '90+9']</t>
   </si>
+  <si>
+    <t>['67', '90+9']</t>
+  </si>
+  <si>
+    <t>['17']</t>
+  </si>
 </sst>
 </file>
 
@@ -1092,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2253,7 +2259,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ6">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2456,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -3283,7 +3289,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ11">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4722,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ18">
         <v>1.86</v>
@@ -5755,7 +5761,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ23">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR23">
         <v>1.37</v>
@@ -6579,7 +6585,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ27">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR27">
         <v>1.99</v>
@@ -7400,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31">
         <v>0.29</v>
@@ -7606,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ32">
         <v>0.75</v>
@@ -8021,7 +8027,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ34">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR34">
         <v>2.24</v>
@@ -8430,7 +8436,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ36">
         <v>1.86</v>
@@ -10081,7 +10087,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ44">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR44">
         <v>1.73</v>
@@ -12962,7 +12968,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ58">
         <v>0.86</v>
@@ -13789,7 +13795,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ62">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -15025,7 +15031,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ68">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -15640,7 +15646,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ71">
         <v>0.75</v>
@@ -16258,7 +16264,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -18115,7 +18121,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ83">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR83">
         <v>1.64</v>
@@ -18527,7 +18533,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ85">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR85">
         <v>1.73</v>
@@ -19760,7 +19766,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ91">
         <v>0.86</v>
@@ -20996,7 +21002,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ97">
         <v>1.43</v>
@@ -22235,7 +22241,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ103">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR103">
         <v>2.14</v>
@@ -22644,7 +22650,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ105">
         <v>0.75</v>
@@ -23883,7 +23889,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -26149,7 +26155,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ122">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AR122">
         <v>1.2</v>
@@ -26352,7 +26358,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AQ123">
         <v>0.83</v>
@@ -27794,7 +27800,7 @@
         <v>1.6</v>
       </c>
       <c r="AP130">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AQ130">
         <v>1.29</v>
@@ -28003,7 +28009,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ131">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR131">
         <v>1.55</v>
@@ -31581,6 +31587,418 @@
       </c>
       <c r="BP148">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7841177</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45845.79166666666</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149" t="s">
+        <v>86</v>
+      </c>
+      <c r="H149" t="s">
+        <v>82</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+      <c r="L149">
+        <v>1</v>
+      </c>
+      <c r="M149">
+        <v>2</v>
+      </c>
+      <c r="N149">
+        <v>3</v>
+      </c>
+      <c r="O149" t="s">
+        <v>111</v>
+      </c>
+      <c r="P149" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q149">
+        <v>2.45</v>
+      </c>
+      <c r="R149">
+        <v>1.95</v>
+      </c>
+      <c r="S149">
+        <v>6.72</v>
+      </c>
+      <c r="T149">
+        <v>1.64</v>
+      </c>
+      <c r="U149">
+        <v>2.25</v>
+      </c>
+      <c r="V149">
+        <v>3.9</v>
+      </c>
+      <c r="W149">
+        <v>1.23</v>
+      </c>
+      <c r="X149">
+        <v>13</v>
+      </c>
+      <c r="Y149">
+        <v>1.01</v>
+      </c>
+      <c r="Z149">
+        <v>1.74</v>
+      </c>
+      <c r="AA149">
+        <v>3</v>
+      </c>
+      <c r="AB149">
+        <v>4.85</v>
+      </c>
+      <c r="AC149">
+        <v>1.13</v>
+      </c>
+      <c r="AD149">
+        <v>5.85</v>
+      </c>
+      <c r="AE149">
+        <v>1.57</v>
+      </c>
+      <c r="AF149">
+        <v>2.32</v>
+      </c>
+      <c r="AG149">
+        <v>2.88</v>
+      </c>
+      <c r="AH149">
+        <v>1.38</v>
+      </c>
+      <c r="AI149">
+        <v>2.7</v>
+      </c>
+      <c r="AJ149">
+        <v>1.44</v>
+      </c>
+      <c r="AK149">
+        <v>1.34</v>
+      </c>
+      <c r="AL149">
+        <v>1.33</v>
+      </c>
+      <c r="AM149">
+        <v>2</v>
+      </c>
+      <c r="AN149">
+        <v>1.83</v>
+      </c>
+      <c r="AO149">
+        <v>0.57</v>
+      </c>
+      <c r="AP149">
+        <v>1.57</v>
+      </c>
+      <c r="AQ149">
+        <v>0.88</v>
+      </c>
+      <c r="AR149">
+        <v>1.71</v>
+      </c>
+      <c r="AS149">
+        <v>1.44</v>
+      </c>
+      <c r="AT149">
+        <v>3.15</v>
+      </c>
+      <c r="AU149">
+        <v>7</v>
+      </c>
+      <c r="AV149">
+        <v>7</v>
+      </c>
+      <c r="AW149">
+        <v>12</v>
+      </c>
+      <c r="AX149">
+        <v>6</v>
+      </c>
+      <c r="AY149">
+        <v>19</v>
+      </c>
+      <c r="AZ149">
+        <v>13</v>
+      </c>
+      <c r="BA149">
+        <v>1</v>
+      </c>
+      <c r="BB149">
+        <v>2</v>
+      </c>
+      <c r="BC149">
+        <v>3</v>
+      </c>
+      <c r="BD149">
+        <v>1.4</v>
+      </c>
+      <c r="BE149">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF149">
+        <v>3.12</v>
+      </c>
+      <c r="BG149">
+        <v>1.29</v>
+      </c>
+      <c r="BH149">
+        <v>3.3</v>
+      </c>
+      <c r="BI149">
+        <v>1.39</v>
+      </c>
+      <c r="BJ149">
+        <v>2.59</v>
+      </c>
+      <c r="BK149">
+        <v>1.83</v>
+      </c>
+      <c r="BL149">
+        <v>2.05</v>
+      </c>
+      <c r="BM149">
+        <v>2.05</v>
+      </c>
+      <c r="BN149">
+        <v>1.57</v>
+      </c>
+      <c r="BO149">
+        <v>2.88</v>
+      </c>
+      <c r="BP149">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7841179</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45845.875</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150" t="s">
+        <v>75</v>
+      </c>
+      <c r="H150" t="s">
+        <v>87</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>1</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>1</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150" t="s">
+        <v>97</v>
+      </c>
+      <c r="P150" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q150">
+        <v>2.56</v>
+      </c>
+      <c r="R150">
+        <v>1.89</v>
+      </c>
+      <c r="S150">
+        <v>5.5</v>
+      </c>
+      <c r="T150">
+        <v>1.45</v>
+      </c>
+      <c r="U150">
+        <v>2.45</v>
+      </c>
+      <c r="V150">
+        <v>3.2</v>
+      </c>
+      <c r="W150">
+        <v>1.3</v>
+      </c>
+      <c r="X150">
+        <v>8.5</v>
+      </c>
+      <c r="Y150">
+        <v>1.06</v>
+      </c>
+      <c r="Z150">
+        <v>1.82</v>
+      </c>
+      <c r="AA150">
+        <v>3.5</v>
+      </c>
+      <c r="AB150">
+        <v>4.85</v>
+      </c>
+      <c r="AC150">
+        <v>1.06</v>
+      </c>
+      <c r="AD150">
+        <v>7.2</v>
+      </c>
+      <c r="AE150">
+        <v>1.39</v>
+      </c>
+      <c r="AF150">
+        <v>2.6</v>
+      </c>
+      <c r="AG150">
+        <v>2.4</v>
+      </c>
+      <c r="AH150">
+        <v>1.5</v>
+      </c>
+      <c r="AI150">
+        <v>1.97</v>
+      </c>
+      <c r="AJ150">
+        <v>1.67</v>
+      </c>
+      <c r="AK150">
+        <v>1.25</v>
+      </c>
+      <c r="AL150">
+        <v>1.27</v>
+      </c>
+      <c r="AM150">
+        <v>1.97</v>
+      </c>
+      <c r="AN150">
+        <v>2</v>
+      </c>
+      <c r="AO150">
+        <v>0.86</v>
+      </c>
+      <c r="AP150">
+        <v>1.75</v>
+      </c>
+      <c r="AQ150">
+        <v>1.13</v>
+      </c>
+      <c r="AR150">
+        <v>1.79</v>
+      </c>
+      <c r="AS150">
+        <v>1.31</v>
+      </c>
+      <c r="AT150">
+        <v>3.1</v>
+      </c>
+      <c r="AU150">
+        <v>3</v>
+      </c>
+      <c r="AV150">
+        <v>7</v>
+      </c>
+      <c r="AW150">
+        <v>17</v>
+      </c>
+      <c r="AX150">
+        <v>7</v>
+      </c>
+      <c r="AY150">
+        <v>20</v>
+      </c>
+      <c r="AZ150">
+        <v>14</v>
+      </c>
+      <c r="BA150">
+        <v>8</v>
+      </c>
+      <c r="BB150">
+        <v>9</v>
+      </c>
+      <c r="BC150">
+        <v>17</v>
+      </c>
+      <c r="BD150">
+        <v>1.61</v>
+      </c>
+      <c r="BE150">
+        <v>7</v>
+      </c>
+      <c r="BF150">
+        <v>2.75</v>
+      </c>
+      <c r="BG150">
+        <v>1.17</v>
+      </c>
+      <c r="BH150">
+        <v>4.35</v>
+      </c>
+      <c r="BI150">
+        <v>1.3</v>
+      </c>
+      <c r="BJ150">
+        <v>3.2</v>
+      </c>
+      <c r="BK150">
+        <v>1.5</v>
+      </c>
+      <c r="BL150">
+        <v>2.4</v>
+      </c>
+      <c r="BM150">
+        <v>1.77</v>
+      </c>
+      <c r="BN150">
+        <v>1.96</v>
+      </c>
+      <c r="BO150">
+        <v>2.35</v>
+      </c>
+      <c r="BP150">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="241">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -592,6 +592,9 @@
     <t>['18', '23']</t>
   </si>
   <si>
+    <t>['49']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -692,9 +695,6 @@
   </si>
   <si>
     <t>['-1']</t>
-  </si>
-  <si>
-    <t>['49']</t>
   </si>
   <si>
     <t>['90+4', '81', '60']</t>
@@ -1098,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ2">
         <v>0.29</v>
@@ -1560,7 +1560,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1766,7 +1766,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2590,7 +2590,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3208,7 +3208,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3414,7 +3414,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3495,7 +3495,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ12">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3826,7 +3826,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4650,7 +4650,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4856,7 +4856,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5680,7 +5680,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6298,7 +6298,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6376,7 +6376,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ26">
         <v>0.88</v>
@@ -6916,7 +6916,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7328,7 +7328,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8564,7 +8564,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8770,7 +8770,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -8851,7 +8851,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ38">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -9594,7 +9594,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10830,7 +10830,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11036,7 +11036,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11448,7 +11448,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11654,7 +11654,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12559,7 +12559,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ56">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR56">
         <v>1.78</v>
@@ -12684,7 +12684,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13096,7 +13096,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13174,7 +13174,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ59">
         <v>1.29</v>
@@ -13508,7 +13508,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14204,7 +14204,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ64">
         <v>1.38</v>
@@ -14538,7 +14538,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14744,7 +14744,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14950,7 +14950,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15156,7 +15156,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15568,7 +15568,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16598,7 +16598,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17091,7 +17091,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ78">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR78">
         <v>1.76</v>
@@ -17912,7 +17912,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ82">
         <v>0.75</v>
@@ -18452,7 +18452,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19070,7 +19070,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19688,7 +19688,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19894,7 +19894,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20100,7 +20100,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20512,7 +20512,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20718,7 +20718,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21829,7 +21829,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ101">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR101">
         <v>1.81</v>
@@ -22572,7 +22572,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23062,7 +23062,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ107">
         <v>0.25</v>
@@ -23190,7 +23190,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23396,7 +23396,7 @@
         <v>167</v>
       </c>
       <c r="P109" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="Q109">
         <v>3.19</v>
@@ -24838,7 +24838,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -26361,7 +26361,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ123">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR123">
         <v>1.83</v>
@@ -28006,7 +28006,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="AQ131">
         <v>1.13</v>
@@ -28752,7 +28752,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -31999,6 +31999,212 @@
       </c>
       <c r="BP150">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7841173</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45846.8125</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151" t="s">
+        <v>70</v>
+      </c>
+      <c r="H151" t="s">
+        <v>72</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>2</v>
+      </c>
+      <c r="O151" t="s">
+        <v>192</v>
+      </c>
+      <c r="P151" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q151">
+        <v>2.56</v>
+      </c>
+      <c r="R151">
+        <v>1.9</v>
+      </c>
+      <c r="S151">
+        <v>5.7</v>
+      </c>
+      <c r="T151">
+        <v>1.55</v>
+      </c>
+      <c r="U151">
+        <v>2.3</v>
+      </c>
+      <c r="V151">
+        <v>3.4</v>
+      </c>
+      <c r="W151">
+        <v>1.26</v>
+      </c>
+      <c r="X151">
+        <v>9</v>
+      </c>
+      <c r="Y151">
+        <v>1.01</v>
+      </c>
+      <c r="Z151">
+        <v>1.82</v>
+      </c>
+      <c r="AA151">
+        <v>3.1</v>
+      </c>
+      <c r="AB151">
+        <v>5</v>
+      </c>
+      <c r="AC151">
+        <v>1.07</v>
+      </c>
+      <c r="AD151">
+        <v>6.5</v>
+      </c>
+      <c r="AE151">
+        <v>1.56</v>
+      </c>
+      <c r="AF151">
+        <v>2.47</v>
+      </c>
+      <c r="AG151">
+        <v>2.6</v>
+      </c>
+      <c r="AH151">
+        <v>1.45</v>
+      </c>
+      <c r="AI151">
+        <v>2.25</v>
+      </c>
+      <c r="AJ151">
+        <v>1.6</v>
+      </c>
+      <c r="AK151">
+        <v>1.33</v>
+      </c>
+      <c r="AL151">
+        <v>1.32</v>
+      </c>
+      <c r="AM151">
+        <v>1.91</v>
+      </c>
+      <c r="AN151">
+        <v>2.29</v>
+      </c>
+      <c r="AO151">
+        <v>0.83</v>
+      </c>
+      <c r="AP151">
+        <v>2.13</v>
+      </c>
+      <c r="AQ151">
+        <v>0.86</v>
+      </c>
+      <c r="AR151">
+        <v>1.53</v>
+      </c>
+      <c r="AS151">
+        <v>1.27</v>
+      </c>
+      <c r="AT151">
+        <v>2.8</v>
+      </c>
+      <c r="AU151">
+        <v>3</v>
+      </c>
+      <c r="AV151">
+        <v>3</v>
+      </c>
+      <c r="AW151">
+        <v>8</v>
+      </c>
+      <c r="AX151">
+        <v>13</v>
+      </c>
+      <c r="AY151">
+        <v>11</v>
+      </c>
+      <c r="AZ151">
+        <v>16</v>
+      </c>
+      <c r="BA151">
+        <v>8</v>
+      </c>
+      <c r="BB151">
+        <v>6</v>
+      </c>
+      <c r="BC151">
+        <v>14</v>
+      </c>
+      <c r="BD151">
+        <v>1.62</v>
+      </c>
+      <c r="BE151">
+        <v>6.75</v>
+      </c>
+      <c r="BF151">
+        <v>2.95</v>
+      </c>
+      <c r="BG151">
+        <v>1.2</v>
+      </c>
+      <c r="BH151">
+        <v>4</v>
+      </c>
+      <c r="BI151">
+        <v>1.36</v>
+      </c>
+      <c r="BJ151">
+        <v>3.05</v>
+      </c>
+      <c r="BK151">
+        <v>1.47</v>
+      </c>
+      <c r="BL151">
+        <v>2.4</v>
+      </c>
+      <c r="BM151">
+        <v>1.97</v>
+      </c>
+      <c r="BN151">
+        <v>1.76</v>
+      </c>
+      <c r="BO151">
+        <v>2.48</v>
+      </c>
+      <c r="BP151">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="241">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1098,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>0.88</v>
@@ -3907,7 +3907,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ14">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -6788,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>0.25</v>
@@ -9057,7 +9057,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ39">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR39">
         <v>1.19</v>
@@ -11735,7 +11735,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ52">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR52">
         <v>2.26</v>
@@ -13380,7 +13380,7 @@
         <v>2</v>
       </c>
       <c r="AP60">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>1.13</v>
@@ -14207,7 +14207,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ64">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR64">
         <v>1.84</v>
@@ -17088,7 +17088,7 @@
         <v>0.33</v>
       </c>
       <c r="AP78">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
         <v>0.86</v>
@@ -19151,7 +19151,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ88">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR88">
         <v>2.01</v>
@@ -21208,7 +21208,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ98">
         <v>1</v>
@@ -22035,7 +22035,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ102">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -24504,7 +24504,7 @@
         <v>2</v>
       </c>
       <c r="AP114">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
         <v>1.86</v>
@@ -25125,7 +25125,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ117">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR117">
         <v>1.9</v>
@@ -28212,7 +28212,7 @@
         <v>0.5</v>
       </c>
       <c r="AP132">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ132">
         <v>0.86</v>
@@ -28833,7 +28833,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ135">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR135">
         <v>1.89</v>
@@ -32205,6 +32205,212 @@
       </c>
       <c r="BP151">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7841188</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45848.89930555555</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152" t="s">
+        <v>74</v>
+      </c>
+      <c r="H152" t="s">
+        <v>73</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>1</v>
+      </c>
+      <c r="O152" t="s">
+        <v>97</v>
+      </c>
+      <c r="P152" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q152">
+        <v>2.85</v>
+      </c>
+      <c r="R152">
+        <v>1.83</v>
+      </c>
+      <c r="S152">
+        <v>4.5</v>
+      </c>
+      <c r="T152">
+        <v>1.6</v>
+      </c>
+      <c r="U152">
+        <v>2.35</v>
+      </c>
+      <c r="V152">
+        <v>3.66</v>
+      </c>
+      <c r="W152">
+        <v>1.27</v>
+      </c>
+      <c r="X152">
+        <v>9</v>
+      </c>
+      <c r="Y152">
+        <v>1.01</v>
+      </c>
+      <c r="Z152">
+        <v>2.3</v>
+      </c>
+      <c r="AA152">
+        <v>2.8</v>
+      </c>
+      <c r="AB152">
+        <v>3.4</v>
+      </c>
+      <c r="AC152">
+        <v>1.11</v>
+      </c>
+      <c r="AD152">
+        <v>5.75</v>
+      </c>
+      <c r="AE152">
+        <v>1.54</v>
+      </c>
+      <c r="AF152">
+        <v>2.51</v>
+      </c>
+      <c r="AG152">
+        <v>2.6</v>
+      </c>
+      <c r="AH152">
+        <v>1.47</v>
+      </c>
+      <c r="AI152">
+        <v>2.2</v>
+      </c>
+      <c r="AJ152">
+        <v>1.62</v>
+      </c>
+      <c r="AK152">
+        <v>1.25</v>
+      </c>
+      <c r="AL152">
+        <v>1.35</v>
+      </c>
+      <c r="AM152">
+        <v>1.64</v>
+      </c>
+      <c r="AN152">
+        <v>2.29</v>
+      </c>
+      <c r="AO152">
+        <v>1.38</v>
+      </c>
+      <c r="AP152">
+        <v>2</v>
+      </c>
+      <c r="AQ152">
+        <v>1.56</v>
+      </c>
+      <c r="AR152">
+        <v>1.82</v>
+      </c>
+      <c r="AS152">
+        <v>1.18</v>
+      </c>
+      <c r="AT152">
+        <v>3</v>
+      </c>
+      <c r="AU152">
+        <v>12</v>
+      </c>
+      <c r="AV152">
+        <v>4</v>
+      </c>
+      <c r="AW152">
+        <v>20</v>
+      </c>
+      <c r="AX152">
+        <v>2</v>
+      </c>
+      <c r="AY152">
+        <v>32</v>
+      </c>
+      <c r="AZ152">
+        <v>6</v>
+      </c>
+      <c r="BA152">
+        <v>10</v>
+      </c>
+      <c r="BB152">
+        <v>2</v>
+      </c>
+      <c r="BC152">
+        <v>12</v>
+      </c>
+      <c r="BD152">
+        <v>1.68</v>
+      </c>
+      <c r="BE152">
+        <v>6.75</v>
+      </c>
+      <c r="BF152">
+        <v>3.1</v>
+      </c>
+      <c r="BG152">
+        <v>1.17</v>
+      </c>
+      <c r="BH152">
+        <v>3.8</v>
+      </c>
+      <c r="BI152">
+        <v>1.53</v>
+      </c>
+      <c r="BJ152">
+        <v>2.25</v>
+      </c>
+      <c r="BK152">
+        <v>1.93</v>
+      </c>
+      <c r="BL152">
+        <v>2.11</v>
+      </c>
+      <c r="BM152">
+        <v>2.04</v>
+      </c>
+      <c r="BN152">
+        <v>1.66</v>
+      </c>
+      <c r="BO152">
+        <v>2.5</v>
+      </c>
+      <c r="BP152">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="241">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1098,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP152"/>
+  <dimension ref="A1:BP153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1847,7 +1847,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ4">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>0.75</v>
@@ -5967,7 +5967,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ24">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR24">
         <v>1.38</v>
@@ -7818,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -10084,7 +10084,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>0.88</v>
@@ -10293,7 +10293,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ45">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR45">
         <v>1.46</v>
@@ -14619,7 +14619,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ66">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR66">
         <v>1.58</v>
@@ -16470,7 +16470,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>1.43</v>
@@ -18945,7 +18945,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ87">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR87">
         <v>1.81</v>
@@ -20178,7 +20178,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ93">
         <v>1.29</v>
@@ -23477,7 +23477,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ109">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR109">
         <v>1.3</v>
@@ -24092,7 +24092,7 @@
         <v>0</v>
       </c>
       <c r="AP112">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ112">
         <v>0.86</v>
@@ -24919,7 +24919,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ116">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR116">
         <v>1.63</v>
@@ -28624,7 +28624,7 @@
         <v>1</v>
       </c>
       <c r="AP134">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>0.86</v>
@@ -29039,7 +29039,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ136">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR136">
         <v>2.25</v>
@@ -32411,6 +32411,212 @@
       </c>
       <c r="BP152">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7841183</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45849.79166666666</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153" t="s">
+        <v>83</v>
+      </c>
+      <c r="H153" t="s">
+        <v>86</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153" t="s">
+        <v>97</v>
+      </c>
+      <c r="P153" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q153">
+        <v>2.64</v>
+      </c>
+      <c r="R153">
+        <v>1.82</v>
+      </c>
+      <c r="S153">
+        <v>4.75</v>
+      </c>
+      <c r="T153">
+        <v>1.6</v>
+      </c>
+      <c r="U153">
+        <v>2.2</v>
+      </c>
+      <c r="V153">
+        <v>3.96</v>
+      </c>
+      <c r="W153">
+        <v>1.22</v>
+      </c>
+      <c r="X153">
+        <v>11.5</v>
+      </c>
+      <c r="Y153">
+        <v>1.04</v>
+      </c>
+      <c r="Z153">
+        <v>1.94</v>
+      </c>
+      <c r="AA153">
+        <v>2.87</v>
+      </c>
+      <c r="AB153">
+        <v>3.3</v>
+      </c>
+      <c r="AC153">
+        <v>1.13</v>
+      </c>
+      <c r="AD153">
+        <v>5.5</v>
+      </c>
+      <c r="AE153">
+        <v>1.6</v>
+      </c>
+      <c r="AF153">
+        <v>2.15</v>
+      </c>
+      <c r="AG153">
+        <v>2.88</v>
+      </c>
+      <c r="AH153">
+        <v>1.42</v>
+      </c>
+      <c r="AI153">
+        <v>2.3</v>
+      </c>
+      <c r="AJ153">
+        <v>1.57</v>
+      </c>
+      <c r="AK153">
+        <v>1.33</v>
+      </c>
+      <c r="AL153">
+        <v>1.36</v>
+      </c>
+      <c r="AM153">
+        <v>1.85</v>
+      </c>
+      <c r="AN153">
+        <v>2.14</v>
+      </c>
+      <c r="AO153">
+        <v>0.75</v>
+      </c>
+      <c r="AP153">
+        <v>2</v>
+      </c>
+      <c r="AQ153">
+        <v>0.78</v>
+      </c>
+      <c r="AR153">
+        <v>1.55</v>
+      </c>
+      <c r="AS153">
+        <v>1.34</v>
+      </c>
+      <c r="AT153">
+        <v>2.89</v>
+      </c>
+      <c r="AU153">
+        <v>6</v>
+      </c>
+      <c r="AV153">
+        <v>4</v>
+      </c>
+      <c r="AW153">
+        <v>5</v>
+      </c>
+      <c r="AX153">
+        <v>3</v>
+      </c>
+      <c r="AY153">
+        <v>11</v>
+      </c>
+      <c r="AZ153">
+        <v>7</v>
+      </c>
+      <c r="BA153">
+        <v>5</v>
+      </c>
+      <c r="BB153">
+        <v>0</v>
+      </c>
+      <c r="BC153">
+        <v>5</v>
+      </c>
+      <c r="BD153">
+        <v>1.57</v>
+      </c>
+      <c r="BE153">
+        <v>6.75</v>
+      </c>
+      <c r="BF153">
+        <v>2.9</v>
+      </c>
+      <c r="BG153">
+        <v>1.19</v>
+      </c>
+      <c r="BH153">
+        <v>3.4</v>
+      </c>
+      <c r="BI153">
+        <v>1.41</v>
+      </c>
+      <c r="BJ153">
+        <v>2.6</v>
+      </c>
+      <c r="BK153">
+        <v>1.78</v>
+      </c>
+      <c r="BL153">
+        <v>2</v>
+      </c>
+      <c r="BM153">
+        <v>2.16</v>
+      </c>
+      <c r="BN153">
+        <v>1.63</v>
+      </c>
+      <c r="BO153">
+        <v>2.82</v>
+      </c>
+      <c r="BP153">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="244">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,6 +595,12 @@
     <t>['49']</t>
   </si>
   <si>
+    <t>['45', '90+2', '71']</t>
+  </si>
+  <si>
+    <t>['41', '47']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -737,6 +743,9 @@
   </si>
   <si>
     <t>['17']</t>
+  </si>
+  <si>
+    <t>['45+11', '27']</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1560,7 +1569,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1638,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ3">
         <v>1.43</v>
@@ -1766,7 +1775,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2590,7 +2599,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3208,7 +3217,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3414,7 +3423,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3620,7 +3629,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3826,7 +3835,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4522,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17">
         <v>0.25</v>
@@ -4650,7 +4659,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4856,7 +4865,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5143,7 +5152,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ20">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5349,7 +5358,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ21">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5680,7 +5689,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5758,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ23">
         <v>0.88</v>
@@ -6298,7 +6307,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6916,7 +6925,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7203,7 +7212,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ30">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR30">
         <v>2.86</v>
@@ -7328,7 +7337,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8564,7 +8573,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8770,7 +8779,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -8848,7 +8857,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ38">
         <v>0.86</v>
@@ -9594,7 +9603,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9672,7 +9681,7 @@
         <v>1.5</v>
       </c>
       <c r="AP42">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ42">
         <v>1.43</v>
@@ -10499,7 +10508,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ46">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR46">
         <v>1.53</v>
@@ -10830,7 +10839,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10911,7 +10920,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ48">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR48">
         <v>2.04</v>
@@ -11036,7 +11045,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11114,7 +11123,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ49">
         <v>0.63</v>
@@ -11448,7 +11457,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11654,7 +11663,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12684,7 +12693,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12971,7 +12980,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ58">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR58">
         <v>1.48</v>
@@ -13096,7 +13105,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13508,7 +13517,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14001,7 +14010,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ63">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14538,7 +14547,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14744,7 +14753,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14822,7 +14831,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ67">
         <v>0.75</v>
@@ -14950,7 +14959,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15156,7 +15165,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15568,7 +15577,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16598,7 +16607,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17294,7 +17303,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ79">
         <v>1.86</v>
@@ -17709,7 +17718,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ81">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR81">
         <v>1.39</v>
@@ -18452,7 +18461,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18736,7 +18745,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ86">
         <v>0.75</v>
@@ -19070,7 +19079,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19688,7 +19697,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19769,7 +19778,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ91">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR91">
         <v>1.96</v>
@@ -19894,7 +19903,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20100,7 +20109,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20512,7 +20521,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20718,7 +20727,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21417,7 +21426,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ99">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR99">
         <v>2.28</v>
@@ -21826,7 +21835,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ101">
         <v>0.86</v>
@@ -22238,7 +22247,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ103">
         <v>0.88</v>
@@ -22572,7 +22581,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23190,7 +23199,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23271,7 +23280,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ108">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR108">
         <v>1.63</v>
@@ -24014,7 +24023,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24095,7 +24104,7 @@
         <v>2</v>
       </c>
       <c r="AQ112">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR112">
         <v>1.8</v>
@@ -24298,7 +24307,7 @@
         <v>0.8</v>
       </c>
       <c r="AP113">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ113">
         <v>1</v>
@@ -24632,7 +24641,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24838,7 +24847,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25328,7 +25337,7 @@
         <v>1.6</v>
       </c>
       <c r="AP118">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ118">
         <v>1.13</v>
@@ -25456,7 +25465,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25868,7 +25877,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26486,7 +26495,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26692,7 +26701,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27928,7 +27937,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28134,7 +28143,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28215,7 +28224,7 @@
         <v>2</v>
       </c>
       <c r="AQ132">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR132">
         <v>1.69</v>
@@ -28340,7 +28349,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28627,7 +28636,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR134">
         <v>1.64</v>
@@ -28752,7 +28761,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29164,7 +29173,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29370,7 +29379,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -29654,7 +29663,7 @@
         <v>0.17</v>
       </c>
       <c r="AP139">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ139">
         <v>0.29</v>
@@ -29860,7 +29869,7 @@
         <v>0.86</v>
       </c>
       <c r="AP140">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ140">
         <v>0.75</v>
@@ -31224,7 +31233,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31636,7 +31645,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31842,7 +31851,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32559,16 +32568,16 @@
         <v>4</v>
       </c>
       <c r="AW153">
+        <v>3</v>
+      </c>
+      <c r="AX153">
+        <v>1</v>
+      </c>
+      <c r="AY153">
+        <v>9</v>
+      </c>
+      <c r="AZ153">
         <v>5</v>
-      </c>
-      <c r="AX153">
-        <v>3</v>
-      </c>
-      <c r="AY153">
-        <v>11</v>
-      </c>
-      <c r="AZ153">
-        <v>7</v>
       </c>
       <c r="BA153">
         <v>5</v>
@@ -32617,6 +32626,418 @@
       </c>
       <c r="BP153">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7841190</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45850.66666666666</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154" t="s">
+        <v>85</v>
+      </c>
+      <c r="H154" t="s">
+        <v>75</v>
+      </c>
+      <c r="I154">
+        <v>1</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154">
+        <v>3</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>4</v>
+      </c>
+      <c r="O154" t="s">
+        <v>193</v>
+      </c>
+      <c r="P154" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q154">
+        <v>2.9</v>
+      </c>
+      <c r="R154">
+        <v>1.91</v>
+      </c>
+      <c r="S154">
+        <v>4.87</v>
+      </c>
+      <c r="T154">
+        <v>1.57</v>
+      </c>
+      <c r="U154">
+        <v>2.25</v>
+      </c>
+      <c r="V154">
+        <v>4.1</v>
+      </c>
+      <c r="W154">
+        <v>1.21</v>
+      </c>
+      <c r="X154">
+        <v>7.5</v>
+      </c>
+      <c r="Y154">
+        <v>1.03</v>
+      </c>
+      <c r="Z154">
+        <v>2.13</v>
+      </c>
+      <c r="AA154">
+        <v>3.05</v>
+      </c>
+      <c r="AB154">
+        <v>3.79</v>
+      </c>
+      <c r="AC154">
+        <v>1.09</v>
+      </c>
+      <c r="AD154">
+        <v>6.2</v>
+      </c>
+      <c r="AE154">
+        <v>1.57</v>
+      </c>
+      <c r="AF154">
+        <v>2.24</v>
+      </c>
+      <c r="AG154">
+        <v>2.8</v>
+      </c>
+      <c r="AH154">
+        <v>1.42</v>
+      </c>
+      <c r="AI154">
+        <v>2.2</v>
+      </c>
+      <c r="AJ154">
+        <v>1.62</v>
+      </c>
+      <c r="AK154">
+        <v>1.4</v>
+      </c>
+      <c r="AL154">
+        <v>1.35</v>
+      </c>
+      <c r="AM154">
+        <v>1.7</v>
+      </c>
+      <c r="AN154">
+        <v>2.25</v>
+      </c>
+      <c r="AO154">
+        <v>0.86</v>
+      </c>
+      <c r="AP154">
+        <v>2.33</v>
+      </c>
+      <c r="AQ154">
+        <v>0.75</v>
+      </c>
+      <c r="AR154">
+        <v>1.84</v>
+      </c>
+      <c r="AS154">
+        <v>1.62</v>
+      </c>
+      <c r="AT154">
+        <v>3.46</v>
+      </c>
+      <c r="AU154">
+        <v>6</v>
+      </c>
+      <c r="AV154">
+        <v>8</v>
+      </c>
+      <c r="AW154">
+        <v>7</v>
+      </c>
+      <c r="AX154">
+        <v>7</v>
+      </c>
+      <c r="AY154">
+        <v>13</v>
+      </c>
+      <c r="AZ154">
+        <v>15</v>
+      </c>
+      <c r="BA154">
+        <v>2</v>
+      </c>
+      <c r="BB154">
+        <v>3</v>
+      </c>
+      <c r="BC154">
+        <v>5</v>
+      </c>
+      <c r="BD154">
+        <v>1.36</v>
+      </c>
+      <c r="BE154">
+        <v>7.75</v>
+      </c>
+      <c r="BF154">
+        <v>3.8</v>
+      </c>
+      <c r="BG154">
+        <v>1.14</v>
+      </c>
+      <c r="BH154">
+        <v>4.43</v>
+      </c>
+      <c r="BI154">
+        <v>1.27</v>
+      </c>
+      <c r="BJ154">
+        <v>2.98</v>
+      </c>
+      <c r="BK154">
+        <v>1.76</v>
+      </c>
+      <c r="BL154">
+        <v>2.28</v>
+      </c>
+      <c r="BM154">
+        <v>1.99</v>
+      </c>
+      <c r="BN154">
+        <v>1.8</v>
+      </c>
+      <c r="BO154">
+        <v>2.52</v>
+      </c>
+      <c r="BP154">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7841185</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45850.77083333334</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155" t="s">
+        <v>71</v>
+      </c>
+      <c r="H155" t="s">
+        <v>79</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>2</v>
+      </c>
+      <c r="K155">
+        <v>3</v>
+      </c>
+      <c r="L155">
+        <v>2</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>4</v>
+      </c>
+      <c r="O155" t="s">
+        <v>194</v>
+      </c>
+      <c r="P155" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q155">
+        <v>3.5</v>
+      </c>
+      <c r="R155">
+        <v>1.75</v>
+      </c>
+      <c r="S155">
+        <v>3.9</v>
+      </c>
+      <c r="T155">
+        <v>1.62</v>
+      </c>
+      <c r="U155">
+        <v>2.15</v>
+      </c>
+      <c r="V155">
+        <v>3.75</v>
+      </c>
+      <c r="W155">
+        <v>1.21</v>
+      </c>
+      <c r="X155">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y155">
+        <v>1</v>
+      </c>
+      <c r="Z155">
+        <v>2.76</v>
+      </c>
+      <c r="AA155">
+        <v>2.78</v>
+      </c>
+      <c r="AB155">
+        <v>2.9</v>
+      </c>
+      <c r="AC155">
+        <v>1.09</v>
+      </c>
+      <c r="AD155">
+        <v>5.5</v>
+      </c>
+      <c r="AE155">
+        <v>1.62</v>
+      </c>
+      <c r="AF155">
+        <v>2.2</v>
+      </c>
+      <c r="AG155">
+        <v>2.75</v>
+      </c>
+      <c r="AH155">
+        <v>1.36</v>
+      </c>
+      <c r="AI155">
+        <v>2.05</v>
+      </c>
+      <c r="AJ155">
+        <v>1.62</v>
+      </c>
+      <c r="AK155">
+        <v>1.4</v>
+      </c>
+      <c r="AL155">
+        <v>1.39</v>
+      </c>
+      <c r="AM155">
+        <v>1.44</v>
+      </c>
+      <c r="AN155">
+        <v>1.14</v>
+      </c>
+      <c r="AO155">
+        <v>0.86</v>
+      </c>
+      <c r="AP155">
+        <v>1.13</v>
+      </c>
+      <c r="AQ155">
+        <v>0.88</v>
+      </c>
+      <c r="AR155">
+        <v>1.86</v>
+      </c>
+      <c r="AS155">
+        <v>1.49</v>
+      </c>
+      <c r="AT155">
+        <v>3.35</v>
+      </c>
+      <c r="AU155">
+        <v>7</v>
+      </c>
+      <c r="AV155">
+        <v>9</v>
+      </c>
+      <c r="AW155">
+        <v>4</v>
+      </c>
+      <c r="AX155">
+        <v>5</v>
+      </c>
+      <c r="AY155">
+        <v>11</v>
+      </c>
+      <c r="AZ155">
+        <v>14</v>
+      </c>
+      <c r="BA155">
+        <v>11</v>
+      </c>
+      <c r="BB155">
+        <v>6</v>
+      </c>
+      <c r="BC155">
+        <v>17</v>
+      </c>
+      <c r="BD155">
+        <v>1.73</v>
+      </c>
+      <c r="BE155">
+        <v>6.75</v>
+      </c>
+      <c r="BF155">
+        <v>2.45</v>
+      </c>
+      <c r="BG155">
+        <v>1.18</v>
+      </c>
+      <c r="BH155">
+        <v>4.78</v>
+      </c>
+      <c r="BI155">
+        <v>1.28</v>
+      </c>
+      <c r="BJ155">
+        <v>3.25</v>
+      </c>
+      <c r="BK155">
+        <v>1.52</v>
+      </c>
+      <c r="BL155">
+        <v>2.3</v>
+      </c>
+      <c r="BM155">
+        <v>1.85</v>
+      </c>
+      <c r="BN155">
+        <v>1.85</v>
+      </c>
+      <c r="BO155">
+        <v>2.34</v>
+      </c>
+      <c r="BP155">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="244">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1107,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ12">
         <v>0.86</v>
@@ -4740,7 +4740,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ18">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -8239,7 +8239,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ35">
         <v>0.63</v>
@@ -8448,7 +8448,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ36">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>1.95</v>
@@ -11538,7 +11538,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ51">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR51">
         <v>1.16</v>
@@ -12771,7 +12771,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ57">
         <v>1</v>
@@ -13801,7 +13801,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ62">
         <v>0.88</v>
@@ -17306,7 +17306,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ79">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR79">
         <v>1.67</v>
@@ -18127,7 +18127,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ83">
         <v>1.13</v>
@@ -20602,7 +20602,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ95">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR95">
         <v>1.93</v>
@@ -23277,7 +23277,7 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ108">
         <v>0.88</v>
@@ -24516,7 +24516,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR114">
         <v>1.72</v>
@@ -24719,7 +24719,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -28839,7 +28839,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AQ135">
         <v>1.56</v>
@@ -29460,7 +29460,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ138">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AR138">
         <v>1.57</v>
@@ -32568,16 +32568,16 @@
         <v>4</v>
       </c>
       <c r="AW153">
+        <v>5</v>
+      </c>
+      <c r="AX153">
         <v>3</v>
       </c>
-      <c r="AX153">
-        <v>1</v>
-      </c>
       <c r="AY153">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ153">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA153">
         <v>5</v>
@@ -32768,22 +32768,22 @@
         <v>3.46</v>
       </c>
       <c r="AU154">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV154">
         <v>8</v>
       </c>
       <c r="AW154">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX154">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY154">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ154">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA154">
         <v>2</v>
@@ -32977,28 +32977,28 @@
         <v>7</v>
       </c>
       <c r="AV155">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW155">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX155">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY155">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ155">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA155">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB155">
         <v>6</v>
       </c>
       <c r="BC155">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD155">
         <v>1.73</v>
@@ -33038,6 +33038,212 @@
       </c>
       <c r="BP155">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7841182</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45850.85416666666</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156" t="s">
+        <v>80</v>
+      </c>
+      <c r="H156" t="s">
+        <v>70</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="O156" t="s">
+        <v>97</v>
+      </c>
+      <c r="P156" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q156">
+        <v>2.5</v>
+      </c>
+      <c r="R156">
+        <v>1.93</v>
+      </c>
+      <c r="S156">
+        <v>5</v>
+      </c>
+      <c r="T156">
+        <v>1.51</v>
+      </c>
+      <c r="U156">
+        <v>2.39</v>
+      </c>
+      <c r="V156">
+        <v>3.4</v>
+      </c>
+      <c r="W156">
+        <v>1.29</v>
+      </c>
+      <c r="X156">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y156">
+        <v>1.05</v>
+      </c>
+      <c r="Z156">
+        <v>1.84</v>
+      </c>
+      <c r="AA156">
+        <v>3</v>
+      </c>
+      <c r="AB156">
+        <v>4.8</v>
+      </c>
+      <c r="AC156">
+        <v>1.06</v>
+      </c>
+      <c r="AD156">
+        <v>7</v>
+      </c>
+      <c r="AE156">
+        <v>1.5</v>
+      </c>
+      <c r="AF156">
+        <v>2.62</v>
+      </c>
+      <c r="AG156">
+        <v>2.45</v>
+      </c>
+      <c r="AH156">
+        <v>1.44</v>
+      </c>
+      <c r="AI156">
+        <v>2.25</v>
+      </c>
+      <c r="AJ156">
+        <v>1.57</v>
+      </c>
+      <c r="AK156">
+        <v>1.32</v>
+      </c>
+      <c r="AL156">
+        <v>1.31</v>
+      </c>
+      <c r="AM156">
+        <v>1.95</v>
+      </c>
+      <c r="AN156">
+        <v>1.63</v>
+      </c>
+      <c r="AO156">
+        <v>1.86</v>
+      </c>
+      <c r="AP156">
+        <v>1.44</v>
+      </c>
+      <c r="AQ156">
+        <v>2</v>
+      </c>
+      <c r="AR156">
+        <v>1.9</v>
+      </c>
+      <c r="AS156">
+        <v>1.47</v>
+      </c>
+      <c r="AT156">
+        <v>3.37</v>
+      </c>
+      <c r="AU156">
+        <v>4</v>
+      </c>
+      <c r="AV156">
+        <v>4</v>
+      </c>
+      <c r="AW156">
+        <v>18</v>
+      </c>
+      <c r="AX156">
+        <v>2</v>
+      </c>
+      <c r="AY156">
+        <v>22</v>
+      </c>
+      <c r="AZ156">
+        <v>6</v>
+      </c>
+      <c r="BA156">
+        <v>8</v>
+      </c>
+      <c r="BB156">
+        <v>2</v>
+      </c>
+      <c r="BC156">
+        <v>10</v>
+      </c>
+      <c r="BD156">
+        <v>1.44</v>
+      </c>
+      <c r="BE156">
+        <v>9.4</v>
+      </c>
+      <c r="BF156">
+        <v>3.26</v>
+      </c>
+      <c r="BG156">
+        <v>1.17</v>
+      </c>
+      <c r="BH156">
+        <v>4.5</v>
+      </c>
+      <c r="BI156">
+        <v>1.3</v>
+      </c>
+      <c r="BJ156">
+        <v>3.5</v>
+      </c>
+      <c r="BK156">
+        <v>1.44</v>
+      </c>
+      <c r="BL156">
+        <v>2.4</v>
+      </c>
+      <c r="BM156">
+        <v>1.8</v>
+      </c>
+      <c r="BN156">
+        <v>1.91</v>
+      </c>
+      <c r="BO156">
+        <v>2.25</v>
+      </c>
+      <c r="BP156">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -32768,22 +32768,22 @@
         <v>3.46</v>
       </c>
       <c r="AU154">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV154">
         <v>8</v>
       </c>
       <c r="AW154">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX154">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AY154">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ154">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA154">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="246">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -601,6 +601,12 @@
     <t>['41', '47']</t>
   </si>
   <si>
+    <t>['43', '77']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1107,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP156"/>
+  <dimension ref="A1:BP158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1569,7 +1575,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1775,7 +1781,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -1853,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ4">
         <v>0.78</v>
@@ -2599,7 +2605,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3217,7 +3223,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3423,7 +3429,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3629,7 +3635,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3835,7 +3841,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -3913,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>1.56</v>
@@ -4328,7 +4334,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ16">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4659,7 +4665,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4865,7 +4871,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5689,7 +5695,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6307,7 +6313,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6591,7 +6597,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ27">
         <v>1.13</v>
@@ -6925,7 +6931,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7337,7 +7343,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8033,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ34">
         <v>1.13</v>
@@ -8573,7 +8579,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8779,7 +8785,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9478,7 +9484,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ41">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR41">
         <v>1.74</v>
@@ -9603,7 +9609,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9887,7 +9893,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -10839,7 +10845,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11045,7 +11051,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11332,7 +11338,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ50">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR50">
         <v>1.55</v>
@@ -11457,7 +11463,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11663,7 +11669,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12565,7 +12571,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>0.86</v>
@@ -12693,7 +12699,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13105,7 +13111,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13517,7 +13523,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14419,7 +14425,7 @@
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ65">
         <v>0.25</v>
@@ -14547,7 +14553,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14753,7 +14759,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14834,7 +14840,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ67">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR67">
         <v>2.23</v>
@@ -14959,7 +14965,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15165,7 +15171,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15577,7 +15583,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16067,7 +16073,7 @@
         <v>1.67</v>
       </c>
       <c r="AP73">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
         <v>1.13</v>
@@ -16607,7 +16613,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17924,7 +17930,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ82">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR82">
         <v>1.86</v>
@@ -18461,7 +18467,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19079,7 +19085,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19157,7 +19163,7 @@
         <v>0.75</v>
       </c>
       <c r="AP88">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ88">
         <v>1.56</v>
@@ -19697,7 +19703,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19903,7 +19909,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20109,7 +20115,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20521,7 +20527,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20727,7 +20733,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21629,7 +21635,7 @@
         <v>0.25</v>
       </c>
       <c r="AP100">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>0.29</v>
@@ -22581,7 +22587,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22662,7 +22668,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ105">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR105">
         <v>1.85</v>
@@ -23199,7 +23205,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23689,7 +23695,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ110">
         <v>0.88</v>
@@ -24023,7 +24029,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24641,7 +24647,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24847,7 +24853,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25465,7 +25471,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25543,7 +25549,7 @@
         <v>0.2</v>
       </c>
       <c r="AP119">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ119">
         <v>0.29</v>
@@ -25749,10 +25755,10 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ120">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR120">
         <v>1.66</v>
@@ -25877,7 +25883,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26495,7 +26501,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26701,7 +26707,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27937,7 +27943,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28143,7 +28149,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28349,7 +28355,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28427,7 +28433,7 @@
         <v>1</v>
       </c>
       <c r="AP133">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ133">
         <v>1.29</v>
@@ -28761,7 +28767,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29173,7 +29179,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29379,7 +29385,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -29457,7 +29463,7 @@
         <v>1.67</v>
       </c>
       <c r="AP138">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ138">
         <v>2</v>
@@ -29872,7 +29878,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ140">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR140">
         <v>1.87</v>
@@ -31233,7 +31239,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31645,7 +31651,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31851,7 +31857,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32881,7 +32887,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -32977,28 +32983,28 @@
         <v>7</v>
       </c>
       <c r="AV155">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW155">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX155">
+        <v>5</v>
+      </c>
+      <c r="AY155">
         <v>11</v>
       </c>
-      <c r="AY155">
-        <v>15</v>
-      </c>
       <c r="AZ155">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="BA155">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB155">
         <v>6</v>
       </c>
       <c r="BC155">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD155">
         <v>1.73</v>
@@ -33180,22 +33186,22 @@
         <v>3.37</v>
       </c>
       <c r="AU156">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW156">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AX156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY156">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AZ156">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA156">
         <v>8</v>
@@ -33244,6 +33250,418 @@
       </c>
       <c r="BP156">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7841187</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45851.66666666666</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157" t="s">
+        <v>72</v>
+      </c>
+      <c r="H157" t="s">
+        <v>76</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>2</v>
+      </c>
+      <c r="L157">
+        <v>2</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>3</v>
+      </c>
+      <c r="O157" t="s">
+        <v>195</v>
+      </c>
+      <c r="P157" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q157">
+        <v>2.15</v>
+      </c>
+      <c r="R157">
+        <v>1.95</v>
+      </c>
+      <c r="S157">
+        <v>5</v>
+      </c>
+      <c r="T157">
+        <v>1.53</v>
+      </c>
+      <c r="U157">
+        <v>2.54</v>
+      </c>
+      <c r="V157">
+        <v>3.4</v>
+      </c>
+      <c r="W157">
+        <v>1.28</v>
+      </c>
+      <c r="X157">
+        <v>10</v>
+      </c>
+      <c r="Y157">
+        <v>1.05</v>
+      </c>
+      <c r="Z157">
+        <v>1.88</v>
+      </c>
+      <c r="AA157">
+        <v>3.05</v>
+      </c>
+      <c r="AB157">
+        <v>4.6</v>
+      </c>
+      <c r="AC157">
+        <v>1.1</v>
+      </c>
+      <c r="AD157">
+        <v>6.5</v>
+      </c>
+      <c r="AE157">
+        <v>1.44</v>
+      </c>
+      <c r="AF157">
+        <v>2.47</v>
+      </c>
+      <c r="AG157">
+        <v>2.55</v>
+      </c>
+      <c r="AH157">
+        <v>1.54</v>
+      </c>
+      <c r="AI157">
+        <v>2.2</v>
+      </c>
+      <c r="AJ157">
+        <v>1.58</v>
+      </c>
+      <c r="AK157">
+        <v>1.33</v>
+      </c>
+      <c r="AL157">
+        <v>1.31</v>
+      </c>
+      <c r="AM157">
+        <v>1.85</v>
+      </c>
+      <c r="AN157">
+        <v>1.38</v>
+      </c>
+      <c r="AO157">
+        <v>0.75</v>
+      </c>
+      <c r="AP157">
+        <v>1.56</v>
+      </c>
+      <c r="AQ157">
+        <v>0.67</v>
+      </c>
+      <c r="AR157">
+        <v>2.02</v>
+      </c>
+      <c r="AS157">
+        <v>1.49</v>
+      </c>
+      <c r="AT157">
+        <v>3.51</v>
+      </c>
+      <c r="AU157">
+        <v>9</v>
+      </c>
+      <c r="AV157">
+        <v>4</v>
+      </c>
+      <c r="AW157">
+        <v>1</v>
+      </c>
+      <c r="AX157">
+        <v>3</v>
+      </c>
+      <c r="AY157">
+        <v>10</v>
+      </c>
+      <c r="AZ157">
+        <v>7</v>
+      </c>
+      <c r="BA157">
+        <v>12</v>
+      </c>
+      <c r="BB157">
+        <v>2</v>
+      </c>
+      <c r="BC157">
+        <v>14</v>
+      </c>
+      <c r="BD157">
+        <v>1.35</v>
+      </c>
+      <c r="BE157">
+        <v>9.75</v>
+      </c>
+      <c r="BF157">
+        <v>5.11</v>
+      </c>
+      <c r="BG157">
+        <v>1.2</v>
+      </c>
+      <c r="BH157">
+        <v>4</v>
+      </c>
+      <c r="BI157">
+        <v>1.34</v>
+      </c>
+      <c r="BJ157">
+        <v>3.14</v>
+      </c>
+      <c r="BK157">
+        <v>1.54</v>
+      </c>
+      <c r="BL157">
+        <v>2.23</v>
+      </c>
+      <c r="BM157">
+        <v>1.91</v>
+      </c>
+      <c r="BN157">
+        <v>1.8</v>
+      </c>
+      <c r="BO157">
+        <v>2.38</v>
+      </c>
+      <c r="BP157">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7841186</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45851.77083333334</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158" t="s">
+        <v>82</v>
+      </c>
+      <c r="H158" t="s">
+        <v>88</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>1</v>
+      </c>
+      <c r="M158">
+        <v>1</v>
+      </c>
+      <c r="N158">
+        <v>2</v>
+      </c>
+      <c r="O158" t="s">
+        <v>196</v>
+      </c>
+      <c r="P158" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q158">
+        <v>2.45</v>
+      </c>
+      <c r="R158">
+        <v>1.93</v>
+      </c>
+      <c r="S158">
+        <v>3.85</v>
+      </c>
+      <c r="T158">
+        <v>1.44</v>
+      </c>
+      <c r="U158">
+        <v>2.6</v>
+      </c>
+      <c r="V158">
+        <v>3.25</v>
+      </c>
+      <c r="W158">
+        <v>1.3</v>
+      </c>
+      <c r="X158">
+        <v>10</v>
+      </c>
+      <c r="Y158">
+        <v>1.06</v>
+      </c>
+      <c r="Z158">
+        <v>2.15</v>
+      </c>
+      <c r="AA158">
+        <v>3</v>
+      </c>
+      <c r="AB158">
+        <v>3.35</v>
+      </c>
+      <c r="AC158">
+        <v>1.05</v>
+      </c>
+      <c r="AD158">
+        <v>7</v>
+      </c>
+      <c r="AE158">
+        <v>1.37</v>
+      </c>
+      <c r="AF158">
+        <v>2.63</v>
+      </c>
+      <c r="AG158">
+        <v>2.28</v>
+      </c>
+      <c r="AH158">
+        <v>1.57</v>
+      </c>
+      <c r="AI158">
+        <v>1.96</v>
+      </c>
+      <c r="AJ158">
+        <v>1.8</v>
+      </c>
+      <c r="AK158">
+        <v>1.36</v>
+      </c>
+      <c r="AL158">
+        <v>1.33</v>
+      </c>
+      <c r="AM158">
+        <v>1.65</v>
+      </c>
+      <c r="AN158">
+        <v>2.14</v>
+      </c>
+      <c r="AO158">
+        <v>1</v>
+      </c>
+      <c r="AP158">
+        <v>2</v>
+      </c>
+      <c r="AQ158">
+        <v>1</v>
+      </c>
+      <c r="AR158">
+        <v>1.47</v>
+      </c>
+      <c r="AS158">
+        <v>1.32</v>
+      </c>
+      <c r="AT158">
+        <v>2.79</v>
+      </c>
+      <c r="AU158">
+        <v>9</v>
+      </c>
+      <c r="AV158">
+        <v>4</v>
+      </c>
+      <c r="AW158">
+        <v>5</v>
+      </c>
+      <c r="AX158">
+        <v>3</v>
+      </c>
+      <c r="AY158">
+        <v>14</v>
+      </c>
+      <c r="AZ158">
+        <v>7</v>
+      </c>
+      <c r="BA158">
+        <v>6</v>
+      </c>
+      <c r="BB158">
+        <v>4</v>
+      </c>
+      <c r="BC158">
+        <v>10</v>
+      </c>
+      <c r="BD158">
+        <v>1.44</v>
+      </c>
+      <c r="BE158">
+        <v>7</v>
+      </c>
+      <c r="BF158">
+        <v>2.55</v>
+      </c>
+      <c r="BG158">
+        <v>1.12</v>
+      </c>
+      <c r="BH158">
+        <v>4</v>
+      </c>
+      <c r="BI158">
+        <v>1.31</v>
+      </c>
+      <c r="BJ158">
+        <v>2.88</v>
+      </c>
+      <c r="BK158">
+        <v>1.76</v>
+      </c>
+      <c r="BL158">
+        <v>2.24</v>
+      </c>
+      <c r="BM158">
+        <v>1.94</v>
+      </c>
+      <c r="BN158">
+        <v>1.8</v>
+      </c>
+      <c r="BO158">
+        <v>2.4</v>
+      </c>
+      <c r="BP158">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -32774,22 +32774,22 @@
         <v>3.46</v>
       </c>
       <c r="AU154">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV154">
         <v>8</v>
       </c>
       <c r="AW154">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX154">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY154">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ154">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA154">
         <v>2</v>
@@ -32983,28 +32983,28 @@
         <v>7</v>
       </c>
       <c r="AV155">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW155">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX155">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AY155">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ155">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BA155">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB155">
         <v>6</v>
       </c>
       <c r="BC155">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD155">
         <v>1.73</v>
@@ -33186,22 +33186,22 @@
         <v>3.37</v>
       </c>
       <c r="AU156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV156">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW156">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AX156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY156">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AZ156">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA156">
         <v>8</v>
@@ -33392,22 +33392,22 @@
         <v>3.51</v>
       </c>
       <c r="AU157">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV157">
         <v>4</v>
       </c>
       <c r="AW157">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AX157">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AY157">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AZ157">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA157">
         <v>12</v>
@@ -33604,16 +33604,16 @@
         <v>4</v>
       </c>
       <c r="AW158">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX158">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY158">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ158">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA158">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="247">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -607,6 +607,9 @@
     <t>['46']</t>
   </si>
   <si>
+    <t>['20', '9', '57', '84']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1113,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP158"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1575,7 +1578,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1781,7 +1784,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2605,7 +2608,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3223,7 +3226,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3429,7 +3432,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3635,7 +3638,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3716,7 +3719,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ13">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3841,7 +3844,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4665,7 +4668,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4871,7 +4874,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -4949,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ19">
         <v>0.63</v>
@@ -5695,7 +5698,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6313,7 +6316,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6931,7 +6934,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7343,7 +7346,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8579,7 +8582,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8660,7 +8663,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ37">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR37">
         <v>2.41</v>
@@ -8785,7 +8788,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9609,7 +9612,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10717,7 +10720,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ47">
         <v>0.25</v>
@@ -10845,7 +10848,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11051,7 +11054,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11463,7 +11466,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11669,7 +11672,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -12699,7 +12702,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13111,7 +13114,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13192,7 +13195,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ59">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR59">
         <v>1.57</v>
@@ -13523,7 +13526,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13601,7 +13604,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ61">
         <v>0.88</v>
@@ -14553,7 +14556,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14759,7 +14762,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14965,7 +14968,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15171,7 +15174,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15583,7 +15586,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15870,7 +15873,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ72">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR72">
         <v>2.1</v>
@@ -16613,7 +16616,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16691,7 +16694,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ76">
         <v>1.29</v>
@@ -18467,7 +18470,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19085,7 +19088,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19703,7 +19706,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19909,7 +19912,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20115,7 +20118,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20402,7 +20405,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ94">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR94">
         <v>1.37</v>
@@ -20527,7 +20530,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20733,7 +20736,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20811,7 +20814,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ96">
         <v>1.13</v>
@@ -22587,7 +22590,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23205,7 +23208,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -24029,7 +24032,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24647,7 +24650,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24853,7 +24856,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -24931,7 +24934,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ116">
         <v>0.78</v>
@@ -25471,7 +25474,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25883,7 +25886,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -25964,7 +25967,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ121">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR121">
         <v>2.18</v>
@@ -26501,7 +26504,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26707,7 +26710,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27943,7 +27946,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28149,7 +28152,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28355,7 +28358,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28436,7 +28439,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ133">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR133">
         <v>2.05</v>
@@ -28767,7 +28770,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29179,7 +29182,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29257,7 +29260,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AQ137">
         <v>1</v>
@@ -29385,7 +29388,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -31239,7 +31242,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31651,7 +31654,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31857,7 +31860,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32887,7 +32890,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -33392,22 +33395,22 @@
         <v>3.51</v>
       </c>
       <c r="AU157">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV157">
         <v>4</v>
       </c>
       <c r="AW157">
+        <v>1</v>
+      </c>
+      <c r="AX157">
+        <v>3</v>
+      </c>
+      <c r="AY157">
         <v>10</v>
       </c>
-      <c r="AX157">
-        <v>9</v>
-      </c>
-      <c r="AY157">
-        <v>21</v>
-      </c>
       <c r="AZ157">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA157">
         <v>12</v>
@@ -33604,16 +33607,16 @@
         <v>4</v>
       </c>
       <c r="AW158">
+        <v>5</v>
+      </c>
+      <c r="AX158">
+        <v>3</v>
+      </c>
+      <c r="AY158">
+        <v>14</v>
+      </c>
+      <c r="AZ158">
         <v>7</v>
-      </c>
-      <c r="AX158">
-        <v>8</v>
-      </c>
-      <c r="AY158">
-        <v>16</v>
-      </c>
-      <c r="AZ158">
-        <v>12</v>
       </c>
       <c r="BA158">
         <v>6</v>
@@ -33662,6 +33665,212 @@
       </c>
       <c r="BP158">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7841189</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45852.79166666666</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+      <c r="G159" t="s">
+        <v>87</v>
+      </c>
+      <c r="H159" t="s">
+        <v>78</v>
+      </c>
+      <c r="I159">
+        <v>2</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>2</v>
+      </c>
+      <c r="L159">
+        <v>4</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>4</v>
+      </c>
+      <c r="O159" t="s">
+        <v>197</v>
+      </c>
+      <c r="P159" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q159">
+        <v>3</v>
+      </c>
+      <c r="R159">
+        <v>1.9</v>
+      </c>
+      <c r="S159">
+        <v>4</v>
+      </c>
+      <c r="T159">
+        <v>1.5</v>
+      </c>
+      <c r="U159">
+        <v>2.45</v>
+      </c>
+      <c r="V159">
+        <v>3.3</v>
+      </c>
+      <c r="W159">
+        <v>1.27</v>
+      </c>
+      <c r="X159">
+        <v>10</v>
+      </c>
+      <c r="Y159">
+        <v>1.04</v>
+      </c>
+      <c r="Z159">
+        <v>2.42</v>
+      </c>
+      <c r="AA159">
+        <v>2.88</v>
+      </c>
+      <c r="AB159">
+        <v>3.15</v>
+      </c>
+      <c r="AC159">
+        <v>1.09</v>
+      </c>
+      <c r="AD159">
+        <v>7</v>
+      </c>
+      <c r="AE159">
+        <v>1.44</v>
+      </c>
+      <c r="AF159">
+        <v>2.55</v>
+      </c>
+      <c r="AG159">
+        <v>2.25</v>
+      </c>
+      <c r="AH159">
+        <v>1.5</v>
+      </c>
+      <c r="AI159">
+        <v>2</v>
+      </c>
+      <c r="AJ159">
+        <v>1.8</v>
+      </c>
+      <c r="AK159">
+        <v>1.34</v>
+      </c>
+      <c r="AL159">
+        <v>1.37</v>
+      </c>
+      <c r="AM159">
+        <v>1.66</v>
+      </c>
+      <c r="AN159">
+        <v>0.86</v>
+      </c>
+      <c r="AO159">
+        <v>1.29</v>
+      </c>
+      <c r="AP159">
+        <v>1.13</v>
+      </c>
+      <c r="AQ159">
+        <v>1.13</v>
+      </c>
+      <c r="AR159">
+        <v>1.73</v>
+      </c>
+      <c r="AS159">
+        <v>1.3</v>
+      </c>
+      <c r="AT159">
+        <v>3.03</v>
+      </c>
+      <c r="AU159">
+        <v>8</v>
+      </c>
+      <c r="AV159">
+        <v>0</v>
+      </c>
+      <c r="AW159">
+        <v>2</v>
+      </c>
+      <c r="AX159">
+        <v>5</v>
+      </c>
+      <c r="AY159">
+        <v>10</v>
+      </c>
+      <c r="AZ159">
+        <v>5</v>
+      </c>
+      <c r="BA159">
+        <v>5</v>
+      </c>
+      <c r="BB159">
+        <v>8</v>
+      </c>
+      <c r="BC159">
+        <v>13</v>
+      </c>
+      <c r="BD159">
+        <v>1.57</v>
+      </c>
+      <c r="BE159">
+        <v>7</v>
+      </c>
+      <c r="BF159">
+        <v>3</v>
+      </c>
+      <c r="BG159">
+        <v>1.09</v>
+      </c>
+      <c r="BH159">
+        <v>4</v>
+      </c>
+      <c r="BI159">
+        <v>1.25</v>
+      </c>
+      <c r="BJ159">
+        <v>3.28</v>
+      </c>
+      <c r="BK159">
+        <v>1.46</v>
+      </c>
+      <c r="BL159">
+        <v>2.43</v>
+      </c>
+      <c r="BM159">
+        <v>1.85</v>
+      </c>
+      <c r="BN159">
+        <v>1.85</v>
+      </c>
+      <c r="BO159">
+        <v>2.34</v>
+      </c>
+      <c r="BP159">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="247">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1116,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4543,7 +4543,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ17">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ21">
         <v>0.88</v>
@@ -6809,7 +6809,7 @@
         <v>2</v>
       </c>
       <c r="AQ28">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR28">
         <v>1.84</v>
@@ -7012,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -10723,7 +10723,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ47">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR47">
         <v>2.22</v>
@@ -11544,7 +11544,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ51">
         <v>2</v>
@@ -14431,7 +14431,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ65">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR65">
         <v>2.13</v>
@@ -15046,7 +15046,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ68">
         <v>1.13</v>
@@ -18345,7 +18345,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ84">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR84">
         <v>1.23</v>
@@ -19372,7 +19372,7 @@
         <v>1.25</v>
       </c>
       <c r="AP89">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ89">
         <v>0.63</v>
@@ -22050,7 +22050,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ102">
         <v>1.56</v>
@@ -23083,7 +23083,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ107">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR107">
         <v>1.73</v>
@@ -26170,7 +26170,7 @@
         <v>0.67</v>
       </c>
       <c r="AP122">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ122">
         <v>0.88</v>
@@ -27409,7 +27409,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ128">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR128">
         <v>1.85</v>
@@ -30499,7 +30499,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ143">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AR143">
         <v>1.44</v>
@@ -31526,7 +31526,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ148">
         <v>1.29</v>
@@ -33395,22 +33395,22 @@
         <v>3.51</v>
       </c>
       <c r="AU157">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV157">
         <v>4</v>
       </c>
       <c r="AW157">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AX157">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AY157">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AZ157">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BA157">
         <v>12</v>
@@ -33607,16 +33607,16 @@
         <v>4</v>
       </c>
       <c r="AW158">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX158">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY158">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ158">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BA158">
         <v>6</v>
@@ -33810,19 +33810,19 @@
         <v>8</v>
       </c>
       <c r="AV159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX159">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY159">
+        <v>9</v>
+      </c>
+      <c r="AZ159">
         <v>10</v>
-      </c>
-      <c r="AZ159">
-        <v>5</v>
       </c>
       <c r="BA159">
         <v>5</v>
@@ -33871,6 +33871,212 @@
       </c>
       <c r="BP159">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7841191</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45852.89583333334</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160" t="s">
+        <v>89</v>
+      </c>
+      <c r="H160" t="s">
+        <v>77</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160" t="s">
+        <v>97</v>
+      </c>
+      <c r="P160" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q160">
+        <v>3.25</v>
+      </c>
+      <c r="R160">
+        <v>1.7</v>
+      </c>
+      <c r="S160">
+        <v>4.1</v>
+      </c>
+      <c r="T160">
+        <v>1.69</v>
+      </c>
+      <c r="U160">
+        <v>2.13</v>
+      </c>
+      <c r="V160">
+        <v>3.9</v>
+      </c>
+      <c r="W160">
+        <v>1.22</v>
+      </c>
+      <c r="X160">
+        <v>11</v>
+      </c>
+      <c r="Y160">
+        <v>1.04</v>
+      </c>
+      <c r="Z160">
+        <v>2.14</v>
+      </c>
+      <c r="AA160">
+        <v>2.8</v>
+      </c>
+      <c r="AB160">
+        <v>3.5</v>
+      </c>
+      <c r="AC160">
+        <v>1.13</v>
+      </c>
+      <c r="AD160">
+        <v>5.3</v>
+      </c>
+      <c r="AE160">
+        <v>1.73</v>
+      </c>
+      <c r="AF160">
+        <v>2.05</v>
+      </c>
+      <c r="AG160">
+        <v>3</v>
+      </c>
+      <c r="AH160">
+        <v>1.35</v>
+      </c>
+      <c r="AI160">
+        <v>2.45</v>
+      </c>
+      <c r="AJ160">
+        <v>1.5</v>
+      </c>
+      <c r="AK160">
+        <v>1.4</v>
+      </c>
+      <c r="AL160">
+        <v>1.37</v>
+      </c>
+      <c r="AM160">
+        <v>1.55</v>
+      </c>
+      <c r="AN160">
+        <v>1.25</v>
+      </c>
+      <c r="AO160">
+        <v>0.25</v>
+      </c>
+      <c r="AP160">
+        <v>1.22</v>
+      </c>
+      <c r="AQ160">
+        <v>0.33</v>
+      </c>
+      <c r="AR160">
+        <v>1.44</v>
+      </c>
+      <c r="AS160">
+        <v>1.32</v>
+      </c>
+      <c r="AT160">
+        <v>2.76</v>
+      </c>
+      <c r="AU160">
+        <v>3</v>
+      </c>
+      <c r="AV160">
+        <v>4</v>
+      </c>
+      <c r="AW160">
+        <v>10</v>
+      </c>
+      <c r="AX160">
+        <v>12</v>
+      </c>
+      <c r="AY160">
+        <v>13</v>
+      </c>
+      <c r="AZ160">
+        <v>16</v>
+      </c>
+      <c r="BA160">
+        <v>6</v>
+      </c>
+      <c r="BB160">
+        <v>6</v>
+      </c>
+      <c r="BC160">
+        <v>12</v>
+      </c>
+      <c r="BD160">
+        <v>1.74</v>
+      </c>
+      <c r="BE160">
+        <v>6.5</v>
+      </c>
+      <c r="BF160">
+        <v>2.2</v>
+      </c>
+      <c r="BG160">
+        <v>1.15</v>
+      </c>
+      <c r="BH160">
+        <v>4.12</v>
+      </c>
+      <c r="BI160">
+        <v>1.32</v>
+      </c>
+      <c r="BJ160">
+        <v>2.8</v>
+      </c>
+      <c r="BK160">
+        <v>1.6</v>
+      </c>
+      <c r="BL160">
+        <v>2.11</v>
+      </c>
+      <c r="BM160">
+        <v>1.91</v>
+      </c>
+      <c r="BN160">
+        <v>1.83</v>
+      </c>
+      <c r="BO160">
+        <v>2.6</v>
+      </c>
+      <c r="BP160">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="248">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -610,6 +610,9 @@
     <t>['20', '9', '57', '84']</t>
   </si>
   <si>
+    <t>['74', '29', '35']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -1116,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1453,7 +1456,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ2">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1578,7 +1581,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1784,7 +1787,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2608,7 +2611,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3226,7 +3229,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3432,7 +3435,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3638,7 +3641,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3716,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>1.13</v>
@@ -3844,7 +3847,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4668,7 +4671,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4874,7 +4877,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5570,7 +5573,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>1.43</v>
@@ -5698,7 +5701,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6316,7 +6319,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6934,7 +6937,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7346,7 +7349,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7427,7 +7430,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ31">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR31">
         <v>2.07</v>
@@ -8582,7 +8585,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8788,7 +8791,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9612,7 +9615,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10848,7 +10851,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11054,7 +11057,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11338,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ50">
         <v>0.67</v>
@@ -11466,7 +11469,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11672,7 +11675,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11959,7 +11962,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ53">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR53">
         <v>1.06</v>
@@ -12702,7 +12705,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13114,7 +13117,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13526,7 +13529,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14556,7 +14559,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14634,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="AP66">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>0.78</v>
@@ -14762,7 +14765,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14968,7 +14971,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15174,7 +15177,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15586,7 +15589,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16616,7 +16619,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17521,7 +17524,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ80">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR80">
         <v>1.86</v>
@@ -18470,7 +18473,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19088,7 +19091,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19578,7 +19581,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ90">
         <v>0.88</v>
@@ -19706,7 +19709,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19912,7 +19915,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20118,7 +20121,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20530,7 +20533,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20736,7 +20739,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21641,7 +21644,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR100">
         <v>1.63</v>
@@ -22462,7 +22465,7 @@
         <v>0.4</v>
       </c>
       <c r="AP104">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ104">
         <v>0.75</v>
@@ -22590,7 +22593,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23208,7 +23211,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -24032,7 +24035,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24650,7 +24653,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24856,7 +24859,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25474,7 +25477,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25555,7 +25558,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ119">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR119">
         <v>1.99</v>
@@ -25886,7 +25889,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26504,7 +26507,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26710,7 +26713,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -27946,7 +27949,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28152,7 +28155,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28358,7 +28361,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28770,7 +28773,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29182,7 +29185,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29388,7 +29391,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -29675,7 +29678,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ139">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AR139">
         <v>1.83</v>
@@ -30084,7 +30087,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ141">
         <v>1</v>
@@ -31242,7 +31245,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31654,7 +31657,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31860,7 +31863,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32890,7 +32893,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -33810,28 +33813,28 @@
         <v>8</v>
       </c>
       <c r="AV159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX159">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY159">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ159">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA159">
         <v>5</v>
       </c>
       <c r="BB159">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC159">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD159">
         <v>1.57</v>
@@ -34077,6 +34080,212 @@
       </c>
       <c r="BP160">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7841184</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45853.8125</v>
+      </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
+      <c r="G161" t="s">
+        <v>81</v>
+      </c>
+      <c r="H161" t="s">
+        <v>84</v>
+      </c>
+      <c r="I161">
+        <v>2</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>3</v>
+      </c>
+      <c r="L161">
+        <v>3</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>4</v>
+      </c>
+      <c r="O161" t="s">
+        <v>198</v>
+      </c>
+      <c r="P161" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q161">
+        <v>2.31</v>
+      </c>
+      <c r="R161">
+        <v>1.92</v>
+      </c>
+      <c r="S161">
+        <v>6.2</v>
+      </c>
+      <c r="T161">
+        <v>1.57</v>
+      </c>
+      <c r="U161">
+        <v>2.25</v>
+      </c>
+      <c r="V161">
+        <v>3.66</v>
+      </c>
+      <c r="W161">
+        <v>1.24</v>
+      </c>
+      <c r="X161">
+        <v>12</v>
+      </c>
+      <c r="Y161">
+        <v>1.03</v>
+      </c>
+      <c r="Z161">
+        <v>1.6</v>
+      </c>
+      <c r="AA161">
+        <v>3.4</v>
+      </c>
+      <c r="AB161">
+        <v>6.5</v>
+      </c>
+      <c r="AC161">
+        <v>1.12</v>
+      </c>
+      <c r="AD161">
+        <v>6.46</v>
+      </c>
+      <c r="AE161">
+        <v>1.6</v>
+      </c>
+      <c r="AF161">
+        <v>2.24</v>
+      </c>
+      <c r="AG161">
+        <v>2.7</v>
+      </c>
+      <c r="AH161">
+        <v>1.49</v>
+      </c>
+      <c r="AI161">
+        <v>2.5</v>
+      </c>
+      <c r="AJ161">
+        <v>1.5</v>
+      </c>
+      <c r="AK161">
+        <v>1.33</v>
+      </c>
+      <c r="AL161">
+        <v>1.3</v>
+      </c>
+      <c r="AM161">
+        <v>2.1</v>
+      </c>
+      <c r="AN161">
+        <v>1.86</v>
+      </c>
+      <c r="AO161">
+        <v>0.29</v>
+      </c>
+      <c r="AP161">
+        <v>2</v>
+      </c>
+      <c r="AQ161">
+        <v>0.25</v>
+      </c>
+      <c r="AR161">
+        <v>1.76</v>
+      </c>
+      <c r="AS161">
+        <v>1.17</v>
+      </c>
+      <c r="AT161">
+        <v>2.93</v>
+      </c>
+      <c r="AU161">
+        <v>5</v>
+      </c>
+      <c r="AV161">
+        <v>6</v>
+      </c>
+      <c r="AW161">
+        <v>2</v>
+      </c>
+      <c r="AX161">
+        <v>6</v>
+      </c>
+      <c r="AY161">
+        <v>7</v>
+      </c>
+      <c r="AZ161">
+        <v>12</v>
+      </c>
+      <c r="BA161">
+        <v>1</v>
+      </c>
+      <c r="BB161">
+        <v>7</v>
+      </c>
+      <c r="BC161">
+        <v>8</v>
+      </c>
+      <c r="BD161">
+        <v>1.33</v>
+      </c>
+      <c r="BE161">
+        <v>9.9</v>
+      </c>
+      <c r="BF161">
+        <v>5.66</v>
+      </c>
+      <c r="BG161">
+        <v>1.21</v>
+      </c>
+      <c r="BH161">
+        <v>3.45</v>
+      </c>
+      <c r="BI161">
+        <v>1.43</v>
+      </c>
+      <c r="BJ161">
+        <v>2.54</v>
+      </c>
+      <c r="BK161">
+        <v>1.76</v>
+      </c>
+      <c r="BL161">
+        <v>1.95</v>
+      </c>
+      <c r="BM161">
+        <v>2.23</v>
+      </c>
+      <c r="BN161">
+        <v>1.55</v>
+      </c>
+      <c r="BO161">
+        <v>2.92</v>
+      </c>
+      <c r="BP161">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -33813,28 +33813,28 @@
         <v>8</v>
       </c>
       <c r="AV159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX159">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY159">
+        <v>9</v>
+      </c>
+      <c r="AZ159">
         <v>10</v>
-      </c>
-      <c r="AZ159">
-        <v>5</v>
       </c>
       <c r="BA159">
         <v>5</v>
       </c>
       <c r="BB159">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC159">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD159">
         <v>1.57</v>
@@ -34225,19 +34225,19 @@
         <v>5</v>
       </c>
       <c r="AV161">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW161">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX161">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY161">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ161">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA161">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="249">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -613,6 +613,9 @@
     <t>['74', '29', '35']</t>
   </si>
   <si>
+    <t>['18']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -653,9 +656,6 @@
   </si>
   <si>
     <t>['7', '45+4']</t>
-  </si>
-  <si>
-    <t>['18']</t>
   </si>
   <si>
     <t>['64']</t>
@@ -758,6 +758,9 @@
   </si>
   <si>
     <t>['45+11', '27']</t>
+  </si>
+  <si>
+    <t>['2']</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP161"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1581,7 +1584,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1787,7 +1790,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2611,7 +2614,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3104,7 +3107,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ10">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3229,7 +3232,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3435,7 +3438,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3641,7 +3644,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3847,7 +3850,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4671,7 +4674,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4749,7 +4752,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -4877,7 +4880,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -4958,7 +4961,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ19">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5161,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ20">
         <v>0.75</v>
@@ -5701,7 +5704,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6194,7 +6197,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ25">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR25">
         <v>1.41</v>
@@ -6319,7 +6322,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6937,7 +6940,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7349,7 +7352,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7633,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ32">
         <v>0.75</v>
@@ -8254,7 +8257,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ35">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR35">
         <v>1.66</v>
@@ -8585,7 +8588,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8791,7 +8794,7 @@
         <v>119</v>
       </c>
       <c r="P38" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="Q38">
         <v>2.58</v>
@@ -9075,7 +9078,7 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
         <v>1.56</v>
@@ -11138,7 +11141,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ49">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR49">
         <v>1.47</v>
@@ -11675,7 +11678,7 @@
         <v>129</v>
       </c>
       <c r="P52" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="Q52">
         <v>3.5</v>
@@ -11959,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
         <v>0.25</v>
@@ -12374,7 +12377,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ55">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR55">
         <v>1.76</v>
@@ -12989,7 +12992,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ58">
         <v>0.75</v>
@@ -15258,7 +15261,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ69">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR69">
         <v>1.87</v>
@@ -15461,7 +15464,7 @@
         <v>1.33</v>
       </c>
       <c r="AP70">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>0.88</v>
@@ -16285,7 +16288,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ74">
         <v>1</v>
@@ -16700,7 +16703,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ76">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR76">
         <v>1.64</v>
@@ -18345,7 +18348,7 @@
         <v>0.25</v>
       </c>
       <c r="AP84">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>0.33</v>
@@ -19378,7 +19381,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ89">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR89">
         <v>1.31</v>
@@ -19709,7 +19712,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -20202,7 +20205,7 @@
         <v>2</v>
       </c>
       <c r="AQ93">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR93">
         <v>1.7</v>
@@ -21023,7 +21026,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ97">
         <v>1.43</v>
@@ -22880,7 +22883,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ106">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR106">
         <v>1.79</v>
@@ -23495,7 +23498,7 @@
         <v>1.2</v>
       </c>
       <c r="AP109">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
         <v>0.78</v>
@@ -24859,7 +24862,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -26791,7 +26794,7 @@
         <v>0.33</v>
       </c>
       <c r="AP125">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>0.75</v>
@@ -27000,7 +27003,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ126">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR126">
         <v>1.99</v>
@@ -27821,10 +27824,10 @@
         <v>1.6</v>
       </c>
       <c r="AP130">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ130">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR130">
         <v>1.68</v>
@@ -30296,7 +30299,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ142">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AR142">
         <v>1.94</v>
@@ -30705,7 +30708,7 @@
         <v>1.14</v>
       </c>
       <c r="AP144">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ144">
         <v>1.13</v>
@@ -31532,7 +31535,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ148">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AR148">
         <v>1.37</v>
@@ -31735,7 +31738,7 @@
         <v>0.57</v>
       </c>
       <c r="AP149">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ149">
         <v>0.88</v>
@@ -34286,6 +34289,418 @@
       </c>
       <c r="BP161">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7841197</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45855.8125</v>
+      </c>
+      <c r="F162">
+        <v>0</v>
+      </c>
+      <c r="G162" t="s">
+        <v>86</v>
+      </c>
+      <c r="H162" t="s">
+        <v>74</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>2</v>
+      </c>
+      <c r="L162">
+        <v>1</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>2</v>
+      </c>
+      <c r="O162" t="s">
+        <v>199</v>
+      </c>
+      <c r="P162" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q162">
+        <v>2.7</v>
+      </c>
+      <c r="R162">
+        <v>1.9</v>
+      </c>
+      <c r="S162">
+        <v>5</v>
+      </c>
+      <c r="T162">
+        <v>1.58</v>
+      </c>
+      <c r="U162">
+        <v>2.5</v>
+      </c>
+      <c r="V162">
+        <v>3.42</v>
+      </c>
+      <c r="W162">
+        <v>1.25</v>
+      </c>
+      <c r="X162">
+        <v>10</v>
+      </c>
+      <c r="Y162">
+        <v>1.05</v>
+      </c>
+      <c r="Z162">
+        <v>2.2</v>
+      </c>
+      <c r="AA162">
+        <v>2.97</v>
+      </c>
+      <c r="AB162">
+        <v>4.55</v>
+      </c>
+      <c r="AC162">
+        <v>1.1</v>
+      </c>
+      <c r="AD162">
+        <v>6.5</v>
+      </c>
+      <c r="AE162">
+        <v>1.47</v>
+      </c>
+      <c r="AF162">
+        <v>2.4</v>
+      </c>
+      <c r="AG162">
+        <v>2.5</v>
+      </c>
+      <c r="AH162">
+        <v>1.53</v>
+      </c>
+      <c r="AI162">
+        <v>2.15</v>
+      </c>
+      <c r="AJ162">
+        <v>1.7</v>
+      </c>
+      <c r="AK162">
+        <v>1.2</v>
+      </c>
+      <c r="AL162">
+        <v>1.3</v>
+      </c>
+      <c r="AM162">
+        <v>1.81</v>
+      </c>
+      <c r="AN162">
+        <v>1.57</v>
+      </c>
+      <c r="AO162">
+        <v>0.63</v>
+      </c>
+      <c r="AP162">
+        <v>1.5</v>
+      </c>
+      <c r="AQ162">
+        <v>0.67</v>
+      </c>
+      <c r="AR162">
+        <v>1.74</v>
+      </c>
+      <c r="AS162">
+        <v>1.86</v>
+      </c>
+      <c r="AT162">
+        <v>3.6</v>
+      </c>
+      <c r="AU162">
+        <v>4</v>
+      </c>
+      <c r="AV162">
+        <v>3</v>
+      </c>
+      <c r="AW162">
+        <v>12</v>
+      </c>
+      <c r="AX162">
+        <v>5</v>
+      </c>
+      <c r="AY162">
+        <v>16</v>
+      </c>
+      <c r="AZ162">
+        <v>8</v>
+      </c>
+      <c r="BA162">
+        <v>5</v>
+      </c>
+      <c r="BB162">
+        <v>5</v>
+      </c>
+      <c r="BC162">
+        <v>10</v>
+      </c>
+      <c r="BD162">
+        <v>1.58</v>
+      </c>
+      <c r="BE162">
+        <v>6.75</v>
+      </c>
+      <c r="BF162">
+        <v>2.87</v>
+      </c>
+      <c r="BG162">
+        <v>1.19</v>
+      </c>
+      <c r="BH162">
+        <v>3.4</v>
+      </c>
+      <c r="BI162">
+        <v>1.47</v>
+      </c>
+      <c r="BJ162">
+        <v>2.5</v>
+      </c>
+      <c r="BK162">
+        <v>1.95</v>
+      </c>
+      <c r="BL162">
+        <v>1.99</v>
+      </c>
+      <c r="BM162">
+        <v>2.2</v>
+      </c>
+      <c r="BN162">
+        <v>1.6</v>
+      </c>
+      <c r="BO162">
+        <v>2.75</v>
+      </c>
+      <c r="BP162">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7841195</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45855.89930555555</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163" t="s">
+        <v>88</v>
+      </c>
+      <c r="H163" t="s">
+        <v>85</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>2</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>2</v>
+      </c>
+      <c r="O163" t="s">
+        <v>94</v>
+      </c>
+      <c r="P163" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q163">
+        <v>3</v>
+      </c>
+      <c r="R163">
+        <v>1.83</v>
+      </c>
+      <c r="S163">
+        <v>3.5</v>
+      </c>
+      <c r="T163">
+        <v>1.53</v>
+      </c>
+      <c r="U163">
+        <v>2.14</v>
+      </c>
+      <c r="V163">
+        <v>3.75</v>
+      </c>
+      <c r="W163">
+        <v>1.19</v>
+      </c>
+      <c r="X163">
+        <v>12</v>
+      </c>
+      <c r="Y163">
+        <v>1.02</v>
+      </c>
+      <c r="Z163">
+        <v>2.83</v>
+      </c>
+      <c r="AA163">
+        <v>2.82</v>
+      </c>
+      <c r="AB163">
+        <v>3.06</v>
+      </c>
+      <c r="AC163">
+        <v>1.09</v>
+      </c>
+      <c r="AD163">
+        <v>5.72</v>
+      </c>
+      <c r="AE163">
+        <v>1.58</v>
+      </c>
+      <c r="AF163">
+        <v>2.23</v>
+      </c>
+      <c r="AG163">
+        <v>2.75</v>
+      </c>
+      <c r="AH163">
+        <v>1.42</v>
+      </c>
+      <c r="AI163">
+        <v>2.25</v>
+      </c>
+      <c r="AJ163">
+        <v>1.52</v>
+      </c>
+      <c r="AK163">
+        <v>1.39</v>
+      </c>
+      <c r="AL163">
+        <v>1.38</v>
+      </c>
+      <c r="AM163">
+        <v>1.48</v>
+      </c>
+      <c r="AN163">
+        <v>2.13</v>
+      </c>
+      <c r="AO163">
+        <v>1.29</v>
+      </c>
+      <c r="AP163">
+        <v>2</v>
+      </c>
+      <c r="AQ163">
+        <v>1.25</v>
+      </c>
+      <c r="AR163">
+        <v>1.33</v>
+      </c>
+      <c r="AS163">
+        <v>1.14</v>
+      </c>
+      <c r="AT163">
+        <v>2.47</v>
+      </c>
+      <c r="AU163">
+        <v>3</v>
+      </c>
+      <c r="AV163">
+        <v>5</v>
+      </c>
+      <c r="AW163">
+        <v>6</v>
+      </c>
+      <c r="AX163">
+        <v>8</v>
+      </c>
+      <c r="AY163">
+        <v>9</v>
+      </c>
+      <c r="AZ163">
+        <v>13</v>
+      </c>
+      <c r="BA163">
+        <v>5</v>
+      </c>
+      <c r="BB163">
+        <v>7</v>
+      </c>
+      <c r="BC163">
+        <v>12</v>
+      </c>
+      <c r="BD163">
+        <v>1.85</v>
+      </c>
+      <c r="BE163">
+        <v>7</v>
+      </c>
+      <c r="BF163">
+        <v>2.25</v>
+      </c>
+      <c r="BG163">
+        <v>1.18</v>
+      </c>
+      <c r="BH163">
+        <v>4.33</v>
+      </c>
+      <c r="BI163">
+        <v>1.3</v>
+      </c>
+      <c r="BJ163">
+        <v>3.1</v>
+      </c>
+      <c r="BK163">
+        <v>1.79</v>
+      </c>
+      <c r="BL163">
+        <v>2.15</v>
+      </c>
+      <c r="BM163">
+        <v>2</v>
+      </c>
+      <c r="BN163">
+        <v>1.66</v>
+      </c>
+      <c r="BO163">
+        <v>2.25</v>
+      </c>
+      <c r="BP163">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -34431,22 +34431,22 @@
         <v>3.6</v>
       </c>
       <c r="AU162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV162">
         <v>3</v>
       </c>
       <c r="AW162">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY162">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ162">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA162">
         <v>5</v>
@@ -34643,16 +34643,16 @@
         <v>5</v>
       </c>
       <c r="AW163">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX163">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AY163">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ163">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BA163">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="249">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1122,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ11">
         <v>1.13</v>
@@ -3519,7 +3519,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ12">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ38">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR38">
         <v>1.97</v>
@@ -9284,7 +9284,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ40">
         <v>1.13</v>
@@ -12374,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ55">
         <v>1.25</v>
@@ -12583,7 +12583,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR56">
         <v>1.78</v>
@@ -16906,7 +16906,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17115,7 +17115,7 @@
         <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR78">
         <v>1.76</v>
@@ -20614,7 +20614,7 @@
         <v>1.75</v>
       </c>
       <c r="AP95">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ95">
         <v>2</v>
@@ -21853,7 +21853,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ101">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR101">
         <v>1.81</v>
@@ -25146,7 +25146,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ117">
         <v>1.56</v>
@@ -26385,7 +26385,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ123">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR123">
         <v>1.83</v>
@@ -27412,7 +27412,7 @@
         <v>0.33</v>
       </c>
       <c r="AP128">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ128">
         <v>0.33</v>
@@ -30296,7 +30296,7 @@
         <v>0.71</v>
       </c>
       <c r="AP142">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ142">
         <v>0.67</v>
@@ -32153,7 +32153,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ151">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR151">
         <v>1.53</v>
@@ -34431,22 +34431,22 @@
         <v>3.6</v>
       </c>
       <c r="AU162">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV162">
         <v>3</v>
       </c>
       <c r="AW162">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AX162">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY162">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ162">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA162">
         <v>5</v>
@@ -34643,16 +34643,16 @@
         <v>5</v>
       </c>
       <c r="AW163">
+        <v>6</v>
+      </c>
+      <c r="AX163">
         <v>8</v>
       </c>
-      <c r="AX163">
-        <v>15</v>
-      </c>
       <c r="AY163">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ163">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BA163">
         <v>5</v>
@@ -34700,6 +34700,212 @@
         <v>2.25</v>
       </c>
       <c r="BP163">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7841194</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45856.79166666666</v>
+      </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
+      <c r="G164" t="s">
+        <v>79</v>
+      </c>
+      <c r="H164" t="s">
+        <v>72</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164" t="s">
+        <v>97</v>
+      </c>
+      <c r="P164" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q164">
+        <v>2.62</v>
+      </c>
+      <c r="R164">
+        <v>1.95</v>
+      </c>
+      <c r="S164">
+        <v>5.2</v>
+      </c>
+      <c r="T164">
+        <v>1.53</v>
+      </c>
+      <c r="U164">
+        <v>2.38</v>
+      </c>
+      <c r="V164">
+        <v>3.5</v>
+      </c>
+      <c r="W164">
+        <v>1.29</v>
+      </c>
+      <c r="X164">
+        <v>9.5</v>
+      </c>
+      <c r="Y164">
+        <v>1.02</v>
+      </c>
+      <c r="Z164">
+        <v>1.76</v>
+      </c>
+      <c r="AA164">
+        <v>3.06</v>
+      </c>
+      <c r="AB164">
+        <v>4.4</v>
+      </c>
+      <c r="AC164">
+        <v>1.06</v>
+      </c>
+      <c r="AD164">
+        <v>6.5</v>
+      </c>
+      <c r="AE164">
+        <v>1.5</v>
+      </c>
+      <c r="AF164">
+        <v>2.4</v>
+      </c>
+      <c r="AG164">
+        <v>2.15</v>
+      </c>
+      <c r="AH164">
+        <v>1.57</v>
+      </c>
+      <c r="AI164">
+        <v>2.29</v>
+      </c>
+      <c r="AJ164">
+        <v>1.65</v>
+      </c>
+      <c r="AK164">
+        <v>1.36</v>
+      </c>
+      <c r="AL164">
+        <v>1.31</v>
+      </c>
+      <c r="AM164">
+        <v>1.75</v>
+      </c>
+      <c r="AN164">
+        <v>1.88</v>
+      </c>
+      <c r="AO164">
+        <v>0.86</v>
+      </c>
+      <c r="AP164">
+        <v>1.67</v>
+      </c>
+      <c r="AQ164">
+        <v>1.13</v>
+      </c>
+      <c r="AR164">
+        <v>1.95</v>
+      </c>
+      <c r="AS164">
+        <v>1.29</v>
+      </c>
+      <c r="AT164">
+        <v>3.24</v>
+      </c>
+      <c r="AU164">
+        <v>3</v>
+      </c>
+      <c r="AV164">
+        <v>3</v>
+      </c>
+      <c r="AW164">
+        <v>5</v>
+      </c>
+      <c r="AX164">
+        <v>4</v>
+      </c>
+      <c r="AY164">
+        <v>8</v>
+      </c>
+      <c r="AZ164">
+        <v>7</v>
+      </c>
+      <c r="BA164">
+        <v>4</v>
+      </c>
+      <c r="BB164">
+        <v>2</v>
+      </c>
+      <c r="BC164">
+        <v>6</v>
+      </c>
+      <c r="BD164">
+        <v>1.64</v>
+      </c>
+      <c r="BE164">
+        <v>7</v>
+      </c>
+      <c r="BF164">
+        <v>2.43</v>
+      </c>
+      <c r="BG164">
+        <v>1.17</v>
+      </c>
+      <c r="BH164">
+        <v>4.1</v>
+      </c>
+      <c r="BI164">
+        <v>1.3</v>
+      </c>
+      <c r="BJ164">
+        <v>3.2</v>
+      </c>
+      <c r="BK164">
+        <v>1.5</v>
+      </c>
+      <c r="BL164">
+        <v>2.4</v>
+      </c>
+      <c r="BM164">
+        <v>1.8</v>
+      </c>
+      <c r="BN164">
+        <v>1.91</v>
+      </c>
+      <c r="BO164">
+        <v>2.33</v>
+      </c>
+      <c r="BP164">
         <v>1.57</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="250">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -762,6 +762,9 @@
   <si>
     <t>['2']</t>
   </si>
+  <si>
+    <t>['45+8', '58']</t>
+  </si>
 </sst>
 </file>
 
@@ -1122,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP164"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2692,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -3313,7 +3316,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ11">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -6609,7 +6612,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ27">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR27">
         <v>1.99</v>
@@ -7224,7 +7227,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ30">
         <v>0.88</v>
@@ -8051,7 +8054,7 @@
         <v>2</v>
       </c>
       <c r="AQ34">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>2.24</v>
@@ -11756,7 +11759,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ52">
         <v>1.56</v>
@@ -15055,7 +15058,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ68">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR68">
         <v>1.28</v>
@@ -15876,7 +15879,7 @@
         <v>1.33</v>
       </c>
       <c r="AP72">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
         <v>1.13</v>
@@ -18145,7 +18148,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ83">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.64</v>
@@ -19996,7 +19999,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -23913,7 +23916,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR111">
         <v>1.71</v>
@@ -27000,7 +27003,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ126">
         <v>0.67</v>
@@ -28033,7 +28036,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ131">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR131">
         <v>1.55</v>
@@ -31326,7 +31329,7 @@
         <v>0.57</v>
       </c>
       <c r="AP147">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ147">
         <v>0.88</v>
@@ -31947,7 +31950,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ150">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR150">
         <v>1.79</v>
@@ -34431,22 +34434,22 @@
         <v>3.6</v>
       </c>
       <c r="AU162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV162">
         <v>3</v>
       </c>
       <c r="AW162">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY162">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ162">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA162">
         <v>5</v>
@@ -34643,16 +34646,16 @@
         <v>5</v>
       </c>
       <c r="AW163">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX163">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AY163">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ163">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BA163">
         <v>5</v>
@@ -34849,16 +34852,16 @@
         <v>3</v>
       </c>
       <c r="AW164">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX164">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY164">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ164">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA164">
         <v>4</v>
@@ -34907,6 +34910,212 @@
       </c>
       <c r="BP164">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7841200</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45856.89583333334</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+      <c r="G165" t="s">
+        <v>76</v>
+      </c>
+      <c r="H165" t="s">
+        <v>87</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="K165">
+        <v>2</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>2</v>
+      </c>
+      <c r="N165">
+        <v>3</v>
+      </c>
+      <c r="O165" t="s">
+        <v>94</v>
+      </c>
+      <c r="P165" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q165">
+        <v>3</v>
+      </c>
+      <c r="R165">
+        <v>1.9</v>
+      </c>
+      <c r="S165">
+        <v>3.8</v>
+      </c>
+      <c r="T165">
+        <v>1.56</v>
+      </c>
+      <c r="U165">
+        <v>2.3</v>
+      </c>
+      <c r="V165">
+        <v>3.4</v>
+      </c>
+      <c r="W165">
+        <v>1.25</v>
+      </c>
+      <c r="X165">
+        <v>10.25</v>
+      </c>
+      <c r="Y165">
+        <v>1</v>
+      </c>
+      <c r="Z165">
+        <v>1.79</v>
+      </c>
+      <c r="AA165">
+        <v>3.23</v>
+      </c>
+      <c r="AB165">
+        <v>3.97</v>
+      </c>
+      <c r="AC165">
+        <v>1.07</v>
+      </c>
+      <c r="AD165">
+        <v>6.5</v>
+      </c>
+      <c r="AE165">
+        <v>1.5</v>
+      </c>
+      <c r="AF165">
+        <v>2.44</v>
+      </c>
+      <c r="AG165">
+        <v>2.2</v>
+      </c>
+      <c r="AH165">
+        <v>1.55</v>
+      </c>
+      <c r="AI165">
+        <v>2.05</v>
+      </c>
+      <c r="AJ165">
+        <v>1.74</v>
+      </c>
+      <c r="AK165">
+        <v>1.34</v>
+      </c>
+      <c r="AL165">
+        <v>1.35</v>
+      </c>
+      <c r="AM165">
+        <v>1.52</v>
+      </c>
+      <c r="AN165">
+        <v>1.71</v>
+      </c>
+      <c r="AO165">
+        <v>1.13</v>
+      </c>
+      <c r="AP165">
+        <v>1.5</v>
+      </c>
+      <c r="AQ165">
+        <v>1.33</v>
+      </c>
+      <c r="AR165">
+        <v>1.86</v>
+      </c>
+      <c r="AS165">
+        <v>1.36</v>
+      </c>
+      <c r="AT165">
+        <v>3.22</v>
+      </c>
+      <c r="AU165">
+        <v>6</v>
+      </c>
+      <c r="AV165">
+        <v>3</v>
+      </c>
+      <c r="AW165">
+        <v>4</v>
+      </c>
+      <c r="AX165">
+        <v>2</v>
+      </c>
+      <c r="AY165">
+        <v>10</v>
+      </c>
+      <c r="AZ165">
+        <v>5</v>
+      </c>
+      <c r="BA165">
+        <v>2</v>
+      </c>
+      <c r="BB165">
+        <v>2</v>
+      </c>
+      <c r="BC165">
+        <v>4</v>
+      </c>
+      <c r="BD165">
+        <v>1.78</v>
+      </c>
+      <c r="BE165">
+        <v>6.75</v>
+      </c>
+      <c r="BF165">
+        <v>2.15</v>
+      </c>
+      <c r="BG165">
+        <v>1.2</v>
+      </c>
+      <c r="BH165">
+        <v>4</v>
+      </c>
+      <c r="BI165">
+        <v>1.34</v>
+      </c>
+      <c r="BJ165">
+        <v>2.9</v>
+      </c>
+      <c r="BK165">
+        <v>1.55</v>
+      </c>
+      <c r="BL165">
+        <v>2.25</v>
+      </c>
+      <c r="BM165">
+        <v>1.85</v>
+      </c>
+      <c r="BN165">
+        <v>1.85</v>
+      </c>
+      <c r="BO165">
+        <v>2.4</v>
+      </c>
+      <c r="BP165">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="255">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -616,6 +616,15 @@
     <t>['18']</t>
   </si>
   <si>
+    <t>['17', '78', '90+5']</t>
+  </si>
+  <si>
+    <t>['26', '57']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -730,9 +739,6 @@
     <t>['26', '76']</t>
   </si>
   <si>
-    <t>['72']</t>
-  </si>
-  <si>
     <t>['40', '90+5']</t>
   </si>
   <si>
@@ -764,6 +770,15 @@
   </si>
   <si>
     <t>['45+8', '58']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['44', '28', '31', '69', '87']</t>
+  </si>
+  <si>
+    <t>['87']</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1459,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ2">
         <v>0.25</v>
@@ -1587,7 +1602,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1793,7 +1808,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2077,10 +2092,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ5">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2617,7 +2632,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2904,7 +2919,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ9">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3107,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ10">
         <v>1.25</v>
@@ -3235,7 +3250,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3441,7 +3456,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3647,7 +3662,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3853,7 +3868,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4140,7 +4155,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4677,7 +4692,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4883,7 +4898,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5707,7 +5722,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5991,7 +6006,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ24">
         <v>0.78</v>
@@ -6197,7 +6212,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ25">
         <v>1.25</v>
@@ -6325,7 +6340,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6403,10 +6418,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ26">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6943,7 +6958,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7355,7 +7370,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7642,7 +7657,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ32">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.17</v>
@@ -8591,7 +8606,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -9290,7 +9305,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ40">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.82</v>
@@ -9621,7 +9636,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10317,7 +10332,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ45">
         <v>0.78</v>
@@ -10523,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="AP46">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ46">
         <v>0.75</v>
@@ -10857,7 +10872,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11063,7 +11078,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11475,7 +11490,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -12174,7 +12189,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ54">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>1.72</v>
@@ -12711,7 +12726,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13123,7 +13138,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13201,7 +13216,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ59">
         <v>1.13</v>
@@ -13410,7 +13425,7 @@
         <v>2</v>
       </c>
       <c r="AQ60">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.78</v>
@@ -13535,7 +13550,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13616,7 +13631,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ61">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR61">
         <v>1.76</v>
@@ -14025,7 +14040,7 @@
         <v>0.67</v>
       </c>
       <c r="AP63">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ63">
         <v>0.88</v>
@@ -14231,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ64">
         <v>1.56</v>
@@ -14565,7 +14580,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14771,7 +14786,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14977,7 +14992,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15183,7 +15198,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15470,7 +15485,7 @@
         <v>2</v>
       </c>
       <c r="AQ70">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR70">
         <v>1.26</v>
@@ -15595,7 +15610,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15676,7 +15691,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ71">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>2.01</v>
@@ -16088,7 +16103,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1.75</v>
@@ -16625,7 +16640,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17733,7 +17748,7 @@
         <v>0</v>
       </c>
       <c r="AP81">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ81">
         <v>0.75</v>
@@ -17939,7 +17954,7 @@
         <v>0.75</v>
       </c>
       <c r="AP82">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ82">
         <v>0.67</v>
@@ -18479,7 +18494,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18557,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ85">
         <v>0.88</v>
@@ -18766,7 +18781,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ86">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>2.07</v>
@@ -19097,7 +19112,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19590,7 +19605,7 @@
         <v>2</v>
       </c>
       <c r="AQ90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR90">
         <v>1.68</v>
@@ -19715,7 +19730,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19921,7 +19936,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20127,7 +20142,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20411,7 +20426,7 @@
         <v>1.25</v>
       </c>
       <c r="AP94">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ94">
         <v>1.13</v>
@@ -20539,7 +20554,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20745,7 +20760,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20826,7 +20841,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ96">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.76</v>
@@ -22474,7 +22489,7 @@
         <v>2</v>
       </c>
       <c r="AQ104">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.67</v>
@@ -22599,7 +22614,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22883,7 +22898,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ106">
         <v>0.67</v>
@@ -23089,7 +23104,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ107">
         <v>0.33</v>
@@ -23217,7 +23232,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23710,7 +23725,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ110">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR110">
         <v>2.01</v>
@@ -24041,7 +24056,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24659,7 +24674,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24865,7 +24880,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25358,7 +25373,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ118">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR118">
         <v>2</v>
@@ -25483,7 +25498,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25895,7 +25910,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26513,7 +26528,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26591,7 +26606,7 @@
         <v>0.8</v>
       </c>
       <c r="AP124">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ124">
         <v>1.43</v>
@@ -26719,7 +26734,7 @@
         <v>97</v>
       </c>
       <c r="P125" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="Q125">
         <v>2.8</v>
@@ -26800,7 +26815,7 @@
         <v>2</v>
       </c>
       <c r="AQ125">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR125">
         <v>1.3</v>
@@ -27209,10 +27224,10 @@
         <v>1.33</v>
       </c>
       <c r="AP127">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ127">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR127">
         <v>1.46</v>
@@ -27624,7 +27639,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ129">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR129">
         <v>1.61</v>
@@ -27955,7 +27970,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28033,7 +28048,7 @@
         <v>0.5</v>
       </c>
       <c r="AP131">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ131">
         <v>1.33</v>
@@ -28161,7 +28176,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28367,7 +28382,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28779,7 +28794,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29191,7 +29206,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29397,7 +29412,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -30505,7 +30520,7 @@
         <v>0.29</v>
       </c>
       <c r="AP143">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ143">
         <v>0.33</v>
@@ -30714,7 +30729,7 @@
         <v>2</v>
       </c>
       <c r="AQ144">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR144">
         <v>1.33</v>
@@ -30917,10 +30932,10 @@
         <v>0.71</v>
       </c>
       <c r="AP145">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ145">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AR145">
         <v>1.83</v>
@@ -31251,7 +31266,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31332,7 +31347,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ147">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR147">
         <v>1.83</v>
@@ -31663,7 +31678,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31869,7 +31884,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32153,7 +32168,7 @@
         <v>0.83</v>
       </c>
       <c r="AP151">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ151">
         <v>1.13</v>
@@ -32899,7 +32914,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -34341,7 +34356,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q162">
         <v>2.7</v>
@@ -34547,7 +34562,7 @@
         <v>94</v>
       </c>
       <c r="P163" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34753,7 +34768,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -34852,16 +34867,16 @@
         <v>3</v>
       </c>
       <c r="AW164">
+        <v>5</v>
+      </c>
+      <c r="AX164">
+        <v>4</v>
+      </c>
+      <c r="AY164">
+        <v>8</v>
+      </c>
+      <c r="AZ164">
         <v>7</v>
-      </c>
-      <c r="AX164">
-        <v>7</v>
-      </c>
-      <c r="AY164">
-        <v>10</v>
-      </c>
-      <c r="AZ164">
-        <v>10</v>
       </c>
       <c r="BA164">
         <v>4</v>
@@ -34959,7 +34974,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35058,16 +35073,16 @@
         <v>3</v>
       </c>
       <c r="AW165">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY165">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ165">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA165">
         <v>2</v>
@@ -35116,6 +35131,624 @@
       </c>
       <c r="BP165">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7841193</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45857.66666666666</v>
+      </c>
+      <c r="F166">
+        <v>0</v>
+      </c>
+      <c r="G166" t="s">
+        <v>70</v>
+      </c>
+      <c r="H166" t="s">
+        <v>81</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166">
+        <v>3</v>
+      </c>
+      <c r="M166">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>4</v>
+      </c>
+      <c r="O166" t="s">
+        <v>200</v>
+      </c>
+      <c r="P166" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q166">
+        <v>2.72</v>
+      </c>
+      <c r="R166">
+        <v>1.92</v>
+      </c>
+      <c r="S166">
+        <v>4.8</v>
+      </c>
+      <c r="T166">
+        <v>1.5</v>
+      </c>
+      <c r="U166">
+        <v>2.45</v>
+      </c>
+      <c r="V166">
+        <v>3.5</v>
+      </c>
+      <c r="W166">
+        <v>1.29</v>
+      </c>
+      <c r="X166">
+        <v>11</v>
+      </c>
+      <c r="Y166">
+        <v>1.04</v>
+      </c>
+      <c r="Z166">
+        <v>1.85</v>
+      </c>
+      <c r="AA166">
+        <v>3.1</v>
+      </c>
+      <c r="AB166">
+        <v>3.9</v>
+      </c>
+      <c r="AC166">
+        <v>1.08</v>
+      </c>
+      <c r="AD166">
+        <v>6.2</v>
+      </c>
+      <c r="AE166">
+        <v>1.47</v>
+      </c>
+      <c r="AF166">
+        <v>2.45</v>
+      </c>
+      <c r="AG166">
+        <v>2.5</v>
+      </c>
+      <c r="AH166">
+        <v>1.44</v>
+      </c>
+      <c r="AI166">
+        <v>2.27</v>
+      </c>
+      <c r="AJ166">
+        <v>1.6</v>
+      </c>
+      <c r="AK166">
+        <v>1.2</v>
+      </c>
+      <c r="AL166">
+        <v>1.35</v>
+      </c>
+      <c r="AM166">
+        <v>1.8</v>
+      </c>
+      <c r="AN166">
+        <v>2.13</v>
+      </c>
+      <c r="AO166">
+        <v>1.13</v>
+      </c>
+      <c r="AP166">
+        <v>2.22</v>
+      </c>
+      <c r="AQ166">
+        <v>1</v>
+      </c>
+      <c r="AR166">
+        <v>1.5</v>
+      </c>
+      <c r="AS166">
+        <v>1.55</v>
+      </c>
+      <c r="AT166">
+        <v>3.05</v>
+      </c>
+      <c r="AU166">
+        <v>5</v>
+      </c>
+      <c r="AV166">
+        <v>4</v>
+      </c>
+      <c r="AW166">
+        <v>6</v>
+      </c>
+      <c r="AX166">
+        <v>4</v>
+      </c>
+      <c r="AY166">
+        <v>11</v>
+      </c>
+      <c r="AZ166">
+        <v>8</v>
+      </c>
+      <c r="BA166">
+        <v>2</v>
+      </c>
+      <c r="BB166">
+        <v>5</v>
+      </c>
+      <c r="BC166">
+        <v>7</v>
+      </c>
+      <c r="BD166">
+        <v>1.56</v>
+      </c>
+      <c r="BE166">
+        <v>6.75</v>
+      </c>
+      <c r="BF166">
+        <v>2.84</v>
+      </c>
+      <c r="BG166">
+        <v>1.14</v>
+      </c>
+      <c r="BH166">
+        <v>3.9</v>
+      </c>
+      <c r="BI166">
+        <v>1.38</v>
+      </c>
+      <c r="BJ166">
+        <v>2.8</v>
+      </c>
+      <c r="BK166">
+        <v>1.67</v>
+      </c>
+      <c r="BL166">
+        <v>2.16</v>
+      </c>
+      <c r="BM166">
+        <v>2.03</v>
+      </c>
+      <c r="BN166">
+        <v>1.71</v>
+      </c>
+      <c r="BO166">
+        <v>2.6</v>
+      </c>
+      <c r="BP166">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7841192</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45857.77083333334</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+      <c r="G167" t="s">
+        <v>73</v>
+      </c>
+      <c r="H167" t="s">
+        <v>71</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>3</v>
+      </c>
+      <c r="K167">
+        <v>4</v>
+      </c>
+      <c r="L167">
+        <v>2</v>
+      </c>
+      <c r="M167">
+        <v>5</v>
+      </c>
+      <c r="N167">
+        <v>7</v>
+      </c>
+      <c r="O167" t="s">
+        <v>201</v>
+      </c>
+      <c r="P167" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q167">
+        <v>2.3</v>
+      </c>
+      <c r="R167">
+        <v>2.03</v>
+      </c>
+      <c r="S167">
+        <v>7</v>
+      </c>
+      <c r="T167">
+        <v>1.49</v>
+      </c>
+      <c r="U167">
+        <v>2.54</v>
+      </c>
+      <c r="V167">
+        <v>3.3</v>
+      </c>
+      <c r="W167">
+        <v>1.27</v>
+      </c>
+      <c r="X167">
+        <v>9</v>
+      </c>
+      <c r="Y167">
+        <v>1.03</v>
+      </c>
+      <c r="Z167">
+        <v>1.59</v>
+      </c>
+      <c r="AA167">
+        <v>3.7</v>
+      </c>
+      <c r="AB167">
+        <v>6.6</v>
+      </c>
+      <c r="AC167">
+        <v>1.08</v>
+      </c>
+      <c r="AD167">
+        <v>6.5</v>
+      </c>
+      <c r="AE167">
+        <v>1.48</v>
+      </c>
+      <c r="AF167">
+        <v>2.65</v>
+      </c>
+      <c r="AG167">
+        <v>2.4</v>
+      </c>
+      <c r="AH167">
+        <v>1.53</v>
+      </c>
+      <c r="AI167">
+        <v>2.44</v>
+      </c>
+      <c r="AJ167">
+        <v>1.53</v>
+      </c>
+      <c r="AK167">
+        <v>1.02</v>
+      </c>
+      <c r="AL167">
+        <v>1.28</v>
+      </c>
+      <c r="AM167">
+        <v>2.25</v>
+      </c>
+      <c r="AN167">
+        <v>2.71</v>
+      </c>
+      <c r="AO167">
+        <v>0.75</v>
+      </c>
+      <c r="AP167">
+        <v>2.38</v>
+      </c>
+      <c r="AQ167">
+        <v>1</v>
+      </c>
+      <c r="AR167">
+        <v>1.37</v>
+      </c>
+      <c r="AS167">
+        <v>1.18</v>
+      </c>
+      <c r="AT167">
+        <v>2.55</v>
+      </c>
+      <c r="AU167">
+        <v>4</v>
+      </c>
+      <c r="AV167">
+        <v>7</v>
+      </c>
+      <c r="AW167">
+        <v>9</v>
+      </c>
+      <c r="AX167">
+        <v>5</v>
+      </c>
+      <c r="AY167">
+        <v>13</v>
+      </c>
+      <c r="AZ167">
+        <v>12</v>
+      </c>
+      <c r="BA167">
+        <v>10</v>
+      </c>
+      <c r="BB167">
+        <v>2</v>
+      </c>
+      <c r="BC167">
+        <v>12</v>
+      </c>
+      <c r="BD167">
+        <v>1.44</v>
+      </c>
+      <c r="BE167">
+        <v>7.25</v>
+      </c>
+      <c r="BF167">
+        <v>3.56</v>
+      </c>
+      <c r="BG167">
+        <v>1.18</v>
+      </c>
+      <c r="BH167">
+        <v>4.3</v>
+      </c>
+      <c r="BI167">
+        <v>1.33</v>
+      </c>
+      <c r="BJ167">
+        <v>3.22</v>
+      </c>
+      <c r="BK167">
+        <v>1.47</v>
+      </c>
+      <c r="BL167">
+        <v>2.25</v>
+      </c>
+      <c r="BM167">
+        <v>1.8</v>
+      </c>
+      <c r="BN167">
+        <v>1.91</v>
+      </c>
+      <c r="BO167">
+        <v>2.39</v>
+      </c>
+      <c r="BP167">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7841196</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45857.77083333334</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+      <c r="G168" t="s">
+        <v>78</v>
+      </c>
+      <c r="H168" t="s">
+        <v>83</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>1</v>
+      </c>
+      <c r="M168">
+        <v>1</v>
+      </c>
+      <c r="N168">
+        <v>2</v>
+      </c>
+      <c r="O168" t="s">
+        <v>202</v>
+      </c>
+      <c r="P168" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q168">
+        <v>3</v>
+      </c>
+      <c r="R168">
+        <v>1.86</v>
+      </c>
+      <c r="S168">
+        <v>4.35</v>
+      </c>
+      <c r="T168">
+        <v>1.55</v>
+      </c>
+      <c r="U168">
+        <v>2.2</v>
+      </c>
+      <c r="V168">
+        <v>4.05</v>
+      </c>
+      <c r="W168">
+        <v>1.25</v>
+      </c>
+      <c r="X168">
+        <v>11</v>
+      </c>
+      <c r="Y168">
+        <v>1.04</v>
+      </c>
+      <c r="Z168">
+        <v>2.28</v>
+      </c>
+      <c r="AA168">
+        <v>2.9</v>
+      </c>
+      <c r="AB168">
+        <v>3.6</v>
+      </c>
+      <c r="AC168">
+        <v>1.09</v>
+      </c>
+      <c r="AD168">
+        <v>5.8</v>
+      </c>
+      <c r="AE168">
+        <v>1.5</v>
+      </c>
+      <c r="AF168">
+        <v>2.23</v>
+      </c>
+      <c r="AG168">
+        <v>3</v>
+      </c>
+      <c r="AH168">
+        <v>1.37</v>
+      </c>
+      <c r="AI168">
+        <v>2.3</v>
+      </c>
+      <c r="AJ168">
+        <v>1.57</v>
+      </c>
+      <c r="AK168">
+        <v>1.4</v>
+      </c>
+      <c r="AL168">
+        <v>1.38</v>
+      </c>
+      <c r="AM168">
+        <v>1.65</v>
+      </c>
+      <c r="AN168">
+        <v>1.88</v>
+      </c>
+      <c r="AO168">
+        <v>0.88</v>
+      </c>
+      <c r="AP168">
+        <v>1.78</v>
+      </c>
+      <c r="AQ168">
+        <v>0.89</v>
+      </c>
+      <c r="AR168">
+        <v>1.94</v>
+      </c>
+      <c r="AS168">
+        <v>1.32</v>
+      </c>
+      <c r="AT168">
+        <v>3.26</v>
+      </c>
+      <c r="AU168">
+        <v>7</v>
+      </c>
+      <c r="AV168">
+        <v>6</v>
+      </c>
+      <c r="AW168">
+        <v>10</v>
+      </c>
+      <c r="AX168">
+        <v>4</v>
+      </c>
+      <c r="AY168">
+        <v>17</v>
+      </c>
+      <c r="AZ168">
+        <v>10</v>
+      </c>
+      <c r="BA168">
+        <v>10</v>
+      </c>
+      <c r="BB168">
+        <v>6</v>
+      </c>
+      <c r="BC168">
+        <v>16</v>
+      </c>
+      <c r="BD168">
+        <v>1.61</v>
+      </c>
+      <c r="BE168">
+        <v>7.1</v>
+      </c>
+      <c r="BF168">
+        <v>3</v>
+      </c>
+      <c r="BG168">
+        <v>1.1</v>
+      </c>
+      <c r="BH168">
+        <v>4.74</v>
+      </c>
+      <c r="BI168">
+        <v>1.36</v>
+      </c>
+      <c r="BJ168">
+        <v>3.08</v>
+      </c>
+      <c r="BK168">
+        <v>1.59</v>
+      </c>
+      <c r="BL168">
+        <v>2.31</v>
+      </c>
+      <c r="BM168">
+        <v>1.85</v>
+      </c>
+      <c r="BN168">
+        <v>1.85</v>
+      </c>
+      <c r="BO168">
+        <v>2.47</v>
+      </c>
+      <c r="BP168">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="257">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -625,6 +625,9 @@
     <t>['72']</t>
   </si>
   <si>
+    <t>['81', '55', '67']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -779,6 +782,9 @@
   </si>
   <si>
     <t>['87']</t>
+  </si>
+  <si>
+    <t>['24', '39']</t>
   </si>
 </sst>
 </file>
@@ -1140,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP168"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1602,7 +1608,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1683,7 +1689,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ3">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1808,7 +1814,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2632,7 +2638,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -2916,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -3250,7 +3256,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3456,7 +3462,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3662,7 +3668,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3868,7 +3874,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4692,7 +4698,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4898,7 +4904,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5597,7 +5603,7 @@
         <v>2</v>
       </c>
       <c r="AQ22">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR22">
         <v>1.69</v>
@@ -5722,7 +5728,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6340,7 +6346,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6958,7 +6964,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7370,7 +7376,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -8606,7 +8612,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -9508,7 +9514,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ41">
         <v>0.67</v>
@@ -9636,7 +9642,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -9717,7 +9723,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ42">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR42">
         <v>2.49</v>
@@ -10872,7 +10878,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -11078,7 +11084,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11490,7 +11496,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -12186,7 +12192,7 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12726,7 +12732,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -13138,7 +13144,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13550,7 +13556,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -14580,7 +14586,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14786,7 +14792,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14992,7 +14998,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15198,7 +15204,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15610,7 +15616,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16515,7 +16521,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR75">
         <v>1.88</v>
@@ -16640,7 +16646,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -17542,7 +17548,7 @@
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ80">
         <v>0.25</v>
@@ -18494,7 +18500,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19112,7 +19118,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19730,7 +19736,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19936,7 +19942,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20142,7 +20148,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20554,7 +20560,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20760,7 +20766,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21047,7 +21053,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ97">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR97">
         <v>1.76</v>
@@ -21456,7 +21462,7 @@
         <v>0</v>
       </c>
       <c r="AP99">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ99">
         <v>0.75</v>
@@ -22614,7 +22620,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -23232,7 +23238,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -24056,7 +24062,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24674,7 +24680,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24880,7 +24886,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25498,7 +25504,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25910,7 +25916,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -25988,7 +25994,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ121">
         <v>1.13</v>
@@ -26528,7 +26534,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -26609,7 +26615,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ124">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR124">
         <v>1.84</v>
@@ -27970,7 +27976,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28176,7 +28182,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28382,7 +28388,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28794,7 +28800,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29078,7 +29084,7 @@
         <v>0.86</v>
       </c>
       <c r="AP136">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ136">
         <v>0.78</v>
@@ -29206,7 +29212,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29412,7 +29418,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -31141,7 +31147,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ146">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR146">
         <v>1.55</v>
@@ -31266,7 +31272,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31678,7 +31684,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31884,7 +31890,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32914,7 +32920,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -34356,7 +34362,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q162">
         <v>2.7</v>
@@ -34562,7 +34568,7 @@
         <v>94</v>
       </c>
       <c r="P163" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34768,7 +34774,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -34867,16 +34873,16 @@
         <v>3</v>
       </c>
       <c r="AW164">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX164">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY164">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ164">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA164">
         <v>4</v>
@@ -34974,7 +34980,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35073,16 +35079,16 @@
         <v>3</v>
       </c>
       <c r="AW165">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY165">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ165">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA165">
         <v>2</v>
@@ -35180,7 +35186,7 @@
         <v>200</v>
       </c>
       <c r="P166" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q166">
         <v>2.72</v>
@@ -35276,19 +35282,19 @@
         <v>5</v>
       </c>
       <c r="AV166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW166">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX166">
         <v>4</v>
       </c>
       <c r="AY166">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ166">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA166">
         <v>2</v>
@@ -35386,7 +35392,7 @@
         <v>201</v>
       </c>
       <c r="P167" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -35479,22 +35485,22 @@
         <v>2.55</v>
       </c>
       <c r="AU167">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV167">
         <v>7</v>
       </c>
       <c r="AW167">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AX167">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY167">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AZ167">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA167">
         <v>10</v>
@@ -35592,7 +35598,7 @@
         <v>202</v>
       </c>
       <c r="P168" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -35685,7 +35691,7 @@
         <v>3.26</v>
       </c>
       <c r="AU168">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV168">
         <v>6</v>
@@ -35694,13 +35700,13 @@
         <v>10</v>
       </c>
       <c r="AX168">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY168">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ168">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA168">
         <v>10</v>
@@ -35749,6 +35755,212 @@
       </c>
       <c r="BP168">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7841201</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45857.85416666666</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169" t="s">
+        <v>77</v>
+      </c>
+      <c r="H169" t="s">
+        <v>80</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>2</v>
+      </c>
+      <c r="K169">
+        <v>2</v>
+      </c>
+      <c r="L169">
+        <v>3</v>
+      </c>
+      <c r="M169">
+        <v>2</v>
+      </c>
+      <c r="N169">
+        <v>5</v>
+      </c>
+      <c r="O169" t="s">
+        <v>203</v>
+      </c>
+      <c r="P169" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q169">
+        <v>3.8</v>
+      </c>
+      <c r="R169">
+        <v>1.65</v>
+      </c>
+      <c r="S169">
+        <v>3.4</v>
+      </c>
+      <c r="T169">
+        <v>1.65</v>
+      </c>
+      <c r="U169">
+        <v>2.2</v>
+      </c>
+      <c r="V169">
+        <v>3.7</v>
+      </c>
+      <c r="W169">
+        <v>1.25</v>
+      </c>
+      <c r="X169">
+        <v>11</v>
+      </c>
+      <c r="Y169">
+        <v>1.02</v>
+      </c>
+      <c r="Z169">
+        <v>2.97</v>
+      </c>
+      <c r="AA169">
+        <v>3.11</v>
+      </c>
+      <c r="AB169">
+        <v>2.17</v>
+      </c>
+      <c r="AC169">
+        <v>1.12</v>
+      </c>
+      <c r="AD169">
+        <v>6.5</v>
+      </c>
+      <c r="AE169">
+        <v>1.48</v>
+      </c>
+      <c r="AF169">
+        <v>2.37</v>
+      </c>
+      <c r="AG169">
+        <v>2.52</v>
+      </c>
+      <c r="AH169">
+        <v>1.5</v>
+      </c>
+      <c r="AI169">
+        <v>2.2</v>
+      </c>
+      <c r="AJ169">
+        <v>1.62</v>
+      </c>
+      <c r="AK169">
+        <v>1.4</v>
+      </c>
+      <c r="AL169">
+        <v>1.38</v>
+      </c>
+      <c r="AM169">
+        <v>1.36</v>
+      </c>
+      <c r="AN169">
+        <v>1.71</v>
+      </c>
+      <c r="AO169">
+        <v>1.43</v>
+      </c>
+      <c r="AP169">
+        <v>1.88</v>
+      </c>
+      <c r="AQ169">
+        <v>1.25</v>
+      </c>
+      <c r="AR169">
+        <v>2.17</v>
+      </c>
+      <c r="AS169">
+        <v>1.38</v>
+      </c>
+      <c r="AT169">
+        <v>3.55</v>
+      </c>
+      <c r="AU169">
+        <v>7</v>
+      </c>
+      <c r="AV169">
+        <v>5</v>
+      </c>
+      <c r="AW169">
+        <v>8</v>
+      </c>
+      <c r="AX169">
+        <v>9</v>
+      </c>
+      <c r="AY169">
+        <v>15</v>
+      </c>
+      <c r="AZ169">
+        <v>14</v>
+      </c>
+      <c r="BA169">
+        <v>3</v>
+      </c>
+      <c r="BB169">
+        <v>4</v>
+      </c>
+      <c r="BC169">
+        <v>7</v>
+      </c>
+      <c r="BD169">
+        <v>1.87</v>
+      </c>
+      <c r="BE169">
+        <v>6.75</v>
+      </c>
+      <c r="BF169">
+        <v>2.47</v>
+      </c>
+      <c r="BG169">
+        <v>1.2</v>
+      </c>
+      <c r="BH169">
+        <v>3.9</v>
+      </c>
+      <c r="BI169">
+        <v>1.39</v>
+      </c>
+      <c r="BJ169">
+        <v>2.62</v>
+      </c>
+      <c r="BK169">
+        <v>1.73</v>
+      </c>
+      <c r="BL169">
+        <v>2</v>
+      </c>
+      <c r="BM169">
+        <v>2.07</v>
+      </c>
+      <c r="BN169">
+        <v>1.55</v>
+      </c>
+      <c r="BO169">
+        <v>2.55</v>
+      </c>
+      <c r="BP169">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -35282,19 +35282,19 @@
         <v>5</v>
       </c>
       <c r="AV166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW166">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX166">
         <v>4</v>
       </c>
       <c r="AY166">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ166">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA166">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="259">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,9 @@
     <t>['81', '55', '67']</t>
   </si>
   <si>
+    <t>['3', '52', '60']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -785,6 +788,9 @@
   </si>
   <si>
     <t>['24', '39']</t>
+  </si>
+  <si>
+    <t>['5']</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1608,7 +1614,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1814,7 +1820,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2307,7 +2313,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2510,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2638,7 +2644,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3256,7 +3262,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3462,7 +3468,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3668,7 +3674,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3874,7 +3880,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -4364,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ16">
         <v>0.67</v>
@@ -4698,7 +4704,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4904,7 +4910,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -5728,7 +5734,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -5809,7 +5815,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ23">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR23">
         <v>1.37</v>
@@ -6346,7 +6352,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6964,7 +6970,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7376,7 +7382,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7454,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ31">
         <v>0.25</v>
@@ -7869,7 +7875,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR33">
         <v>1.59</v>
@@ -8484,7 +8490,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ36">
         <v>2</v>
@@ -8612,7 +8618,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -8690,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
         <v>1.13</v>
@@ -9642,7 +9648,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10135,7 +10141,7 @@
         <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR44">
         <v>1.73</v>
@@ -10878,7 +10884,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10956,7 +10962,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ48">
         <v>0.88</v>
@@ -11084,7 +11090,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11496,7 +11502,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -12732,7 +12738,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12813,7 +12819,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -13144,7 +13150,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13556,7 +13562,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13843,7 +13849,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ62">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR62">
         <v>1.4</v>
@@ -14586,7 +14592,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14792,7 +14798,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14998,7 +15004,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15204,7 +15210,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15282,7 +15288,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ69">
         <v>0.67</v>
@@ -15616,7 +15622,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -15694,7 +15700,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -16315,7 +16321,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ74">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR74">
         <v>1.6</v>
@@ -16646,7 +16652,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -18500,7 +18506,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -18581,7 +18587,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ85">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR85">
         <v>1.73</v>
@@ -18990,7 +18996,7 @@
         <v>1.5</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ87">
         <v>0.78</v>
@@ -19118,7 +19124,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19736,7 +19742,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19814,7 +19820,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ91">
         <v>0.88</v>
@@ -19942,7 +19948,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20023,7 +20029,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR92">
         <v>2.06</v>
@@ -20148,7 +20154,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20560,7 +20566,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20766,7 +20772,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -22289,7 +22295,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ103">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR103">
         <v>2.14</v>
@@ -22620,7 +22626,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22698,7 +22704,7 @@
         <v>0.6</v>
       </c>
       <c r="AP105">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ105">
         <v>0.67</v>
@@ -23238,7 +23244,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23934,7 +23940,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ111">
         <v>1.33</v>
@@ -24062,7 +24068,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24349,7 +24355,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ113">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR113">
         <v>1.9</v>
@@ -24680,7 +24686,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24886,7 +24892,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -25504,7 +25510,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25916,7 +25922,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26203,7 +26209,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ122">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR122">
         <v>1.2</v>
@@ -26406,7 +26412,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ123">
         <v>1.13</v>
@@ -26534,7 +26540,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -27642,7 +27648,7 @@
         <v>0.67</v>
       </c>
       <c r="AP129">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ129">
         <v>0.89</v>
@@ -27976,7 +27982,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28182,7 +28188,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28388,7 +28394,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28800,7 +28806,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -29212,7 +29218,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29418,7 +29424,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -30117,7 +30123,7 @@
         <v>2</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR141">
         <v>1.78</v>
@@ -31144,7 +31150,7 @@
         <v>1.17</v>
       </c>
       <c r="AP146">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ146">
         <v>1.25</v>
@@ -31272,7 +31278,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31684,7 +31690,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31765,7 +31771,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ149">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR149">
         <v>1.71</v>
@@ -31890,7 +31896,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -31968,7 +31974,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ150">
         <v>1.33</v>
@@ -32920,7 +32926,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -34362,7 +34368,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q162">
         <v>2.7</v>
@@ -34568,7 +34574,7 @@
         <v>94</v>
       </c>
       <c r="P163" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34774,7 +34780,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -34980,7 +34986,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35186,7 +35192,7 @@
         <v>200</v>
       </c>
       <c r="P166" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q166">
         <v>2.72</v>
@@ -35392,7 +35398,7 @@
         <v>201</v>
       </c>
       <c r="P167" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -35485,31 +35491,31 @@
         <v>2.55</v>
       </c>
       <c r="AU167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV167">
         <v>7</v>
       </c>
       <c r="AW167">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AX167">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY167">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AZ167">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA167">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB167">
         <v>2</v>
       </c>
       <c r="BC167">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD167">
         <v>1.44</v>
@@ -35598,7 +35604,7 @@
         <v>202</v>
       </c>
       <c r="P168" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -35691,7 +35697,7 @@
         <v>3.26</v>
       </c>
       <c r="AU168">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV168">
         <v>6</v>
@@ -35700,13 +35706,13 @@
         <v>10</v>
       </c>
       <c r="AX168">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY168">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ168">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA168">
         <v>10</v>
@@ -35804,7 +35810,7 @@
         <v>203</v>
       </c>
       <c r="P169" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q169">
         <v>3.8</v>
@@ -35903,13 +35909,13 @@
         <v>5</v>
       </c>
       <c r="AW169">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX169">
         <v>9</v>
       </c>
       <c r="AY169">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ169">
         <v>14</v>
@@ -35961,6 +35967,418 @@
       </c>
       <c r="BP169">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7841198</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45858.66666666666</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+      <c r="G170" t="s">
+        <v>84</v>
+      </c>
+      <c r="H170" t="s">
+        <v>89</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>3</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>3</v>
+      </c>
+      <c r="O170" t="s">
+        <v>204</v>
+      </c>
+      <c r="P170" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q170">
+        <v>3.2</v>
+      </c>
+      <c r="R170">
+        <v>1.85</v>
+      </c>
+      <c r="S170">
+        <v>4</v>
+      </c>
+      <c r="T170">
+        <v>1.63</v>
+      </c>
+      <c r="U170">
+        <v>2.2</v>
+      </c>
+      <c r="V170">
+        <v>3.8</v>
+      </c>
+      <c r="W170">
+        <v>1.22</v>
+      </c>
+      <c r="X170">
+        <v>10</v>
+      </c>
+      <c r="Y170">
+        <v>1.04</v>
+      </c>
+      <c r="Z170">
+        <v>2.31</v>
+      </c>
+      <c r="AA170">
+        <v>2.75</v>
+      </c>
+      <c r="AB170">
+        <v>3.55</v>
+      </c>
+      <c r="AC170">
+        <v>1.13</v>
+      </c>
+      <c r="AD170">
+        <v>5.5</v>
+      </c>
+      <c r="AE170">
+        <v>1.55</v>
+      </c>
+      <c r="AF170">
+        <v>2.2</v>
+      </c>
+      <c r="AG170">
+        <v>2.91</v>
+      </c>
+      <c r="AH170">
+        <v>1.4</v>
+      </c>
+      <c r="AI170">
+        <v>2.2</v>
+      </c>
+      <c r="AJ170">
+        <v>1.55</v>
+      </c>
+      <c r="AK170">
+        <v>1.3</v>
+      </c>
+      <c r="AL170">
+        <v>1.37</v>
+      </c>
+      <c r="AM170">
+        <v>1.54</v>
+      </c>
+      <c r="AN170">
+        <v>1.5</v>
+      </c>
+      <c r="AO170">
+        <v>1</v>
+      </c>
+      <c r="AP170">
+        <v>1.67</v>
+      </c>
+      <c r="AQ170">
+        <v>0.88</v>
+      </c>
+      <c r="AR170">
+        <v>1.48</v>
+      </c>
+      <c r="AS170">
+        <v>1.23</v>
+      </c>
+      <c r="AT170">
+        <v>2.71</v>
+      </c>
+      <c r="AU170">
+        <v>4</v>
+      </c>
+      <c r="AV170">
+        <v>4</v>
+      </c>
+      <c r="AW170">
+        <v>5</v>
+      </c>
+      <c r="AX170">
+        <v>6</v>
+      </c>
+      <c r="AY170">
+        <v>9</v>
+      </c>
+      <c r="AZ170">
+        <v>10</v>
+      </c>
+      <c r="BA170">
+        <v>1</v>
+      </c>
+      <c r="BB170">
+        <v>6</v>
+      </c>
+      <c r="BC170">
+        <v>7</v>
+      </c>
+      <c r="BD170">
+        <v>1.69</v>
+      </c>
+      <c r="BE170">
+        <v>6.75</v>
+      </c>
+      <c r="BF170">
+        <v>2.83</v>
+      </c>
+      <c r="BG170">
+        <v>1.22</v>
+      </c>
+      <c r="BH170">
+        <v>3.8</v>
+      </c>
+      <c r="BI170">
+        <v>1.38</v>
+      </c>
+      <c r="BJ170">
+        <v>2.9</v>
+      </c>
+      <c r="BK170">
+        <v>1.58</v>
+      </c>
+      <c r="BL170">
+        <v>2.2</v>
+      </c>
+      <c r="BM170">
+        <v>2</v>
+      </c>
+      <c r="BN170">
+        <v>1.73</v>
+      </c>
+      <c r="BO170">
+        <v>2.4</v>
+      </c>
+      <c r="BP170">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7841199</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45858.77083333334</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171" t="s">
+        <v>75</v>
+      </c>
+      <c r="H171" t="s">
+        <v>82</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171" t="s">
+        <v>97</v>
+      </c>
+      <c r="P171" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q171">
+        <v>2.4</v>
+      </c>
+      <c r="R171">
+        <v>2.16</v>
+      </c>
+      <c r="S171">
+        <v>5.5</v>
+      </c>
+      <c r="T171">
+        <v>1.49</v>
+      </c>
+      <c r="U171">
+        <v>2.5</v>
+      </c>
+      <c r="V171">
+        <v>3.2</v>
+      </c>
+      <c r="W171">
+        <v>1.3</v>
+      </c>
+      <c r="X171">
+        <v>8.4</v>
+      </c>
+      <c r="Y171">
+        <v>1.01</v>
+      </c>
+      <c r="Z171">
+        <v>1.74</v>
+      </c>
+      <c r="AA171">
+        <v>3.3</v>
+      </c>
+      <c r="AB171">
+        <v>4.5</v>
+      </c>
+      <c r="AC171">
+        <v>1.08</v>
+      </c>
+      <c r="AD171">
+        <v>8</v>
+      </c>
+      <c r="AE171">
+        <v>1.45</v>
+      </c>
+      <c r="AF171">
+        <v>2.7</v>
+      </c>
+      <c r="AG171">
+        <v>2.3</v>
+      </c>
+      <c r="AH171">
+        <v>1.59</v>
+      </c>
+      <c r="AI171">
+        <v>2.2</v>
+      </c>
+      <c r="AJ171">
+        <v>1.62</v>
+      </c>
+      <c r="AK171">
+        <v>1.29</v>
+      </c>
+      <c r="AL171">
+        <v>1.3</v>
+      </c>
+      <c r="AM171">
+        <v>2.15</v>
+      </c>
+      <c r="AN171">
+        <v>1.75</v>
+      </c>
+      <c r="AO171">
+        <v>0.88</v>
+      </c>
+      <c r="AP171">
+        <v>1.56</v>
+      </c>
+      <c r="AQ171">
+        <v>1.11</v>
+      </c>
+      <c r="AR171">
+        <v>1.79</v>
+      </c>
+      <c r="AS171">
+        <v>1.47</v>
+      </c>
+      <c r="AT171">
+        <v>3.26</v>
+      </c>
+      <c r="AU171">
+        <v>8</v>
+      </c>
+      <c r="AV171">
+        <v>5</v>
+      </c>
+      <c r="AW171">
+        <v>7</v>
+      </c>
+      <c r="AX171">
+        <v>4</v>
+      </c>
+      <c r="AY171">
+        <v>15</v>
+      </c>
+      <c r="AZ171">
+        <v>9</v>
+      </c>
+      <c r="BA171">
+        <v>7</v>
+      </c>
+      <c r="BB171">
+        <v>3</v>
+      </c>
+      <c r="BC171">
+        <v>10</v>
+      </c>
+      <c r="BD171">
+        <v>1.34</v>
+      </c>
+      <c r="BE171">
+        <v>9.25</v>
+      </c>
+      <c r="BF171">
+        <v>3.4</v>
+      </c>
+      <c r="BG171">
+        <v>1.18</v>
+      </c>
+      <c r="BH171">
+        <v>3.9</v>
+      </c>
+      <c r="BI171">
+        <v>1.37</v>
+      </c>
+      <c r="BJ171">
+        <v>2.8</v>
+      </c>
+      <c r="BK171">
+        <v>1.6</v>
+      </c>
+      <c r="BL171">
+        <v>2.17</v>
+      </c>
+      <c r="BM171">
+        <v>1.95</v>
+      </c>
+      <c r="BN171">
+        <v>1.85</v>
+      </c>
+      <c r="BO171">
+        <v>2.4</v>
+      </c>
+      <c r="BP171">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -35288,19 +35288,19 @@
         <v>5</v>
       </c>
       <c r="AV166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW166">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX166">
         <v>4</v>
       </c>
       <c r="AY166">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ166">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA166">
         <v>2</v>
@@ -35491,31 +35491,31 @@
         <v>2.55</v>
       </c>
       <c r="AU167">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV167">
         <v>7</v>
       </c>
       <c r="AW167">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AX167">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY167">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AZ167">
+        <v>14</v>
+      </c>
+      <c r="BA167">
+        <v>10</v>
+      </c>
+      <c r="BB167">
+        <v>2</v>
+      </c>
+      <c r="BC167">
         <v>12</v>
-      </c>
-      <c r="BA167">
-        <v>9</v>
-      </c>
-      <c r="BB167">
-        <v>2</v>
-      </c>
-      <c r="BC167">
-        <v>11</v>
       </c>
       <c r="BD167">
         <v>1.44</v>
@@ -35697,7 +35697,7 @@
         <v>3.26</v>
       </c>
       <c r="AU168">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV168">
         <v>6</v>
@@ -35706,13 +35706,13 @@
         <v>10</v>
       </c>
       <c r="AX168">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY168">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ168">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA168">
         <v>10</v>
@@ -35909,13 +35909,13 @@
         <v>5</v>
       </c>
       <c r="AW169">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX169">
         <v>9</v>
       </c>
       <c r="AY169">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ169">
         <v>14</v>
@@ -36112,28 +36112,28 @@
         <v>4</v>
       </c>
       <c r="AV170">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW170">
+        <v>9</v>
+      </c>
+      <c r="AX170">
         <v>5</v>
       </c>
-      <c r="AX170">
-        <v>6</v>
-      </c>
       <c r="AY170">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ170">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA170">
         <v>1</v>
       </c>
       <c r="BB170">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC170">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD170">
         <v>1.69</v>
@@ -36315,22 +36315,22 @@
         <v>3.26</v>
       </c>
       <c r="AU171">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV171">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW171">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AX171">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY171">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AZ171">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA171">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -35986,7 +35986,7 @@
         <v>45858.66666666666</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G170" t="s">
         <v>84</v>
@@ -36192,7 +36192,7 @@
         <v>45858.77083333334</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G171" t="s">
         <v>75</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie B_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="262">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,12 @@
     <t>['3', '52', '60']</t>
   </si>
   <si>
+    <t>['87', '90+11', '67']</t>
+  </si>
+  <si>
+    <t>['19', '47']</t>
+  </si>
+  <si>
     <t>['33', '72']</t>
   </si>
   <si>
@@ -791,6 +797,9 @@
   </si>
   <si>
     <t>['5']</t>
+  </si>
+  <si>
+    <t>['37']</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1614,7 +1623,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -1820,7 +1829,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q4">
         <v>2.5</v>
@@ -2644,7 +2653,7 @@
         <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -3262,7 +3271,7 @@
         <v>99</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q11">
         <v>2.38</v>
@@ -3468,7 +3477,7 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q12">
         <v>2.51</v>
@@ -3546,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ12">
         <v>1.13</v>
@@ -3674,7 +3683,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q13">
         <v>2.8</v>
@@ -3880,7 +3889,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q14">
         <v>3.3</v>
@@ -3961,7 +3970,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4164,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4373,7 +4382,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ16">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4704,7 +4713,7 @@
         <v>105</v>
       </c>
       <c r="P18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q18">
         <v>3.22</v>
@@ -4782,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -4910,7 +4919,7 @@
         <v>106</v>
       </c>
       <c r="P19" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q19">
         <v>2.55</v>
@@ -4988,10 +4997,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ19">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5403,7 +5412,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ21">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5734,7 +5743,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q23">
         <v>2.33</v>
@@ -6352,7 +6361,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6970,7 +6979,7 @@
         <v>112</v>
       </c>
       <c r="P29" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q29">
         <v>3.1</v>
@@ -7257,7 +7266,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR30">
         <v>2.86</v>
@@ -7382,7 +7391,7 @@
         <v>114</v>
       </c>
       <c r="P31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q31">
         <v>2.2</v>
@@ -7666,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -7872,7 +7881,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ33">
         <v>0.88</v>
@@ -8284,10 +8293,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ35">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR35">
         <v>1.66</v>
@@ -8618,7 +8627,7 @@
         <v>97</v>
       </c>
       <c r="P37" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>3.6</v>
@@ -9111,7 +9120,7 @@
         <v>2</v>
       </c>
       <c r="AQ39">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR39">
         <v>1.19</v>
@@ -9523,7 +9532,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ41">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR41">
         <v>1.74</v>
@@ -9648,7 +9657,7 @@
         <v>122</v>
       </c>
       <c r="P42" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
@@ -10138,7 +10147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP44">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ44">
         <v>1.11</v>
@@ -10756,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ47">
         <v>0.33</v>
@@ -10884,7 +10893,7 @@
         <v>95</v>
       </c>
       <c r="P48" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q48">
         <v>3.08</v>
@@ -10965,7 +10974,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ48">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR48">
         <v>2.04</v>
@@ -11090,7 +11099,7 @@
         <v>127</v>
       </c>
       <c r="P49" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q49">
         <v>2.75</v>
@@ -11171,7 +11180,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ49">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR49">
         <v>1.47</v>
@@ -11377,7 +11386,7 @@
         <v>2</v>
       </c>
       <c r="AQ50">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR50">
         <v>1.55</v>
@@ -11502,7 +11511,7 @@
         <v>97</v>
       </c>
       <c r="P51" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q51">
         <v>4.2</v>
@@ -11789,7 +11798,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ52">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR52">
         <v>2.26</v>
@@ -12738,7 +12747,7 @@
         <v>133</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q57">
         <v>1.97</v>
@@ -12816,7 +12825,7 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ57">
         <v>0.88</v>
@@ -13022,7 +13031,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ58">
         <v>0.75</v>
@@ -13150,7 +13159,7 @@
         <v>135</v>
       </c>
       <c r="P59" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q59">
         <v>2.88</v>
@@ -13562,7 +13571,7 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q61">
         <v>2.85</v>
@@ -13640,7 +13649,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ61">
         <v>0.89</v>
@@ -13846,7 +13855,7 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ62">
         <v>1.11</v>
@@ -14055,7 +14064,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ63">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14261,7 +14270,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ64">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR64">
         <v>1.84</v>
@@ -14592,7 +14601,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q66">
         <v>2.6</v>
@@ -14798,7 +14807,7 @@
         <v>140</v>
       </c>
       <c r="P67" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q67">
         <v>2.35</v>
@@ -14879,7 +14888,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ67">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR67">
         <v>2.23</v>
@@ -15004,7 +15013,7 @@
         <v>97</v>
       </c>
       <c r="P68" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q68">
         <v>2.8</v>
@@ -15210,7 +15219,7 @@
         <v>141</v>
       </c>
       <c r="P69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q69">
         <v>3</v>
@@ -15291,7 +15300,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR69">
         <v>1.87</v>
@@ -15622,7 +15631,7 @@
         <v>143</v>
       </c>
       <c r="P71" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q71">
         <v>2.13</v>
@@ -16318,7 +16327,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74">
         <v>0.88</v>
@@ -16524,7 +16533,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ75">
         <v>1.25</v>
@@ -16652,7 +16661,7 @@
         <v>97</v>
       </c>
       <c r="P76" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q76">
         <v>3.64</v>
@@ -16730,7 +16739,7 @@
         <v>0.67</v>
       </c>
       <c r="AP76">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ76">
         <v>1.25</v>
@@ -17969,7 +17978,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ82">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR82">
         <v>1.86</v>
@@ -18172,7 +18181,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ83">
         <v>1.33</v>
@@ -18506,7 +18515,7 @@
         <v>154</v>
       </c>
       <c r="P85" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q85">
         <v>2.4</v>
@@ -19124,7 +19133,7 @@
         <v>97</v>
       </c>
       <c r="P88" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q88">
         <v>2.85</v>
@@ -19205,7 +19214,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ88">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR88">
         <v>2.01</v>
@@ -19411,7 +19420,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ89">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR89">
         <v>1.31</v>
@@ -19742,7 +19751,7 @@
         <v>158</v>
       </c>
       <c r="P91" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -19823,7 +19832,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ91">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR91">
         <v>1.96</v>
@@ -19948,7 +19957,7 @@
         <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q92">
         <v>2.78</v>
@@ -20154,7 +20163,7 @@
         <v>97</v>
       </c>
       <c r="P93" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q93">
         <v>3.12</v>
@@ -20232,7 +20241,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ93">
         <v>1.25</v>
@@ -20566,7 +20575,7 @@
         <v>94</v>
       </c>
       <c r="P95" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q95">
         <v>2.9</v>
@@ -20772,7 +20781,7 @@
         <v>97</v>
       </c>
       <c r="P96" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -20850,7 +20859,7 @@
         <v>1.25</v>
       </c>
       <c r="AP96">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21056,7 +21065,7 @@
         <v>0.75</v>
       </c>
       <c r="AP97">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ97">
         <v>1.25</v>
@@ -22089,7 +22098,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ102">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
         <v>1.3</v>
@@ -22626,7 +22635,7 @@
         <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q105">
         <v>2.19</v>
@@ -22707,7 +22716,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ105">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR105">
         <v>1.85</v>
@@ -22913,7 +22922,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ106">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR106">
         <v>1.79</v>
@@ -23244,7 +23253,7 @@
         <v>97</v>
       </c>
       <c r="P108" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q108">
         <v>2.47</v>
@@ -23322,10 +23331,10 @@
         <v>0.6</v>
       </c>
       <c r="AP108">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ108">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR108">
         <v>1.63</v>
@@ -24068,7 +24077,7 @@
         <v>97</v>
       </c>
       <c r="P112" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>2.62</v>
@@ -24146,7 +24155,7 @@
         <v>0</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ112">
         <v>0.75</v>
@@ -24686,7 +24695,7 @@
         <v>172</v>
       </c>
       <c r="P115" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q115">
         <v>2.2</v>
@@ -24764,7 +24773,7 @@
         <v>0.8</v>
       </c>
       <c r="AP115">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115">
         <v>1</v>
@@ -24892,7 +24901,7 @@
         <v>173</v>
       </c>
       <c r="P116" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q116">
         <v>3.15</v>
@@ -24970,7 +24979,7 @@
         <v>1</v>
       </c>
       <c r="AP116">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ116">
         <v>0.78</v>
@@ -25179,7 +25188,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ117">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR117">
         <v>1.9</v>
@@ -25510,7 +25519,7 @@
         <v>175</v>
       </c>
       <c r="P119" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -25797,7 +25806,7 @@
         <v>2</v>
       </c>
       <c r="AQ120">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR120">
         <v>1.66</v>
@@ -25922,7 +25931,7 @@
         <v>177</v>
       </c>
       <c r="P121" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q121">
         <v>3.22</v>
@@ -26540,7 +26549,7 @@
         <v>102</v>
       </c>
       <c r="P124" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q124">
         <v>3.6</v>
@@ -27033,7 +27042,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ126">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR126">
         <v>1.99</v>
@@ -27854,7 +27863,7 @@
         <v>1.6</v>
       </c>
       <c r="AP130">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ130">
         <v>1.25</v>
@@ -27982,7 +27991,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q131">
         <v>2.38</v>
@@ -28188,7 +28197,7 @@
         <v>134</v>
       </c>
       <c r="P132" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28394,7 +28403,7 @@
         <v>184</v>
       </c>
       <c r="P133" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q133">
         <v>3.01</v>
@@ -28678,10 +28687,10 @@
         <v>1</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ134">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR134">
         <v>1.64</v>
@@ -28806,7 +28815,7 @@
         <v>97</v>
       </c>
       <c r="P135" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q135">
         <v>3.1</v>
@@ -28884,10 +28893,10 @@
         <v>1.14</v>
       </c>
       <c r="AP135">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ135">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR135">
         <v>1.89</v>
@@ -29218,7 +29227,7 @@
         <v>187</v>
       </c>
       <c r="P137" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q137">
         <v>2.62</v>
@@ -29296,7 +29305,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ137">
         <v>1</v>
@@ -29424,7 +29433,7 @@
         <v>188</v>
       </c>
       <c r="P138" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q138">
         <v>3.02</v>
@@ -29917,7 +29926,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ140">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR140">
         <v>1.87</v>
@@ -30329,7 +30338,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ142">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR142">
         <v>1.94</v>
@@ -31278,7 +31287,7 @@
         <v>103</v>
       </c>
       <c r="P147" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q147">
         <v>2.95</v>
@@ -31690,7 +31699,7 @@
         <v>111</v>
       </c>
       <c r="P149" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q149">
         <v>2.45</v>
@@ -31768,7 +31777,7 @@
         <v>0.57</v>
       </c>
       <c r="AP149">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ149">
         <v>1.11</v>
@@ -31896,7 +31905,7 @@
         <v>97</v>
       </c>
       <c r="P150" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q150">
         <v>2.56</v>
@@ -32389,7 +32398,7 @@
         <v>2</v>
       </c>
       <c r="AQ152">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR152">
         <v>1.82</v>
@@ -32592,7 +32601,7 @@
         <v>0.75</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ153">
         <v>0.78</v>
@@ -32926,7 +32935,7 @@
         <v>194</v>
       </c>
       <c r="P155" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q155">
         <v>3.5</v>
@@ -33007,7 +33016,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ155">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR155">
         <v>1.86</v>
@@ -33210,7 +33219,7 @@
         <v>1.86</v>
       </c>
       <c r="AP156">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ156">
         <v>2</v>
@@ -33419,7 +33428,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ157">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR157">
         <v>2.02</v>
@@ -33828,7 +33837,7 @@
         <v>1.29</v>
       </c>
       <c r="AP159">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ159">
         <v>1.13</v>
@@ -34368,7 +34377,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q162">
         <v>2.7</v>
@@ -34446,10 +34455,10 @@
         <v>0.63</v>
       </c>
       <c r="AP162">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ162">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR162">
         <v>1.74</v>
@@ -34574,7 +34583,7 @@
         <v>94</v>
       </c>
       <c r="P163" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q163">
         <v>3</v>
@@ -34780,7 +34789,7 @@
         <v>97</v>
       </c>
       <c r="P164" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q164">
         <v>2.62</v>
@@ -34986,7 +34995,7 @@
         <v>94</v>
       </c>
       <c r="P165" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q165">
         <v>3</v>
@@ -35192,7 +35201,7 @@
         <v>200</v>
       </c>
       <c r="P166" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q166">
         <v>2.72</v>
@@ -35398,7 +35407,7 @@
         <v>201</v>
       </c>
       <c r="P167" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
@@ -35604,7 +35613,7 @@
         <v>202</v>
       </c>
       <c r="P168" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q168">
         <v>3</v>
@@ -35810,7 +35819,7 @@
         <v>203</v>
       </c>
       <c r="P169" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q169">
         <v>3.8</v>
@@ -36222,7 +36231,7 @@
         <v>97</v>
       </c>
       <c r="P171" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q171">
         <v>2.4</v>
@@ -36379,6 +36388,830 @@
       </c>
       <c r="BP171">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7841207</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45860.79166666666</v>
+      </c>
+      <c r="F172">
+        <v>18</v>
+      </c>
+      <c r="G172" t="s">
+        <v>86</v>
+      </c>
+      <c r="H172" t="s">
+        <v>79</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>3</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>3</v>
+      </c>
+      <c r="O172" t="s">
+        <v>205</v>
+      </c>
+      <c r="P172" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q172">
+        <v>3.3</v>
+      </c>
+      <c r="R172">
+        <v>1.86</v>
+      </c>
+      <c r="S172">
+        <v>4.1</v>
+      </c>
+      <c r="T172">
+        <v>1.58</v>
+      </c>
+      <c r="U172">
+        <v>2.18</v>
+      </c>
+      <c r="V172">
+        <v>3.8</v>
+      </c>
+      <c r="W172">
+        <v>1.21</v>
+      </c>
+      <c r="X172">
+        <v>11.5</v>
+      </c>
+      <c r="Y172">
+        <v>1</v>
+      </c>
+      <c r="Z172">
+        <v>2.4</v>
+      </c>
+      <c r="AA172">
+        <v>2.9</v>
+      </c>
+      <c r="AB172">
+        <v>3.4</v>
+      </c>
+      <c r="AC172">
+        <v>1.09</v>
+      </c>
+      <c r="AD172">
+        <v>6.4</v>
+      </c>
+      <c r="AE172">
+        <v>1.58</v>
+      </c>
+      <c r="AF172">
+        <v>2.42</v>
+      </c>
+      <c r="AG172">
+        <v>2.85</v>
+      </c>
+      <c r="AH172">
+        <v>1.4</v>
+      </c>
+      <c r="AI172">
+        <v>2.2</v>
+      </c>
+      <c r="AJ172">
+        <v>1.62</v>
+      </c>
+      <c r="AK172">
+        <v>1.4</v>
+      </c>
+      <c r="AL172">
+        <v>1.39</v>
+      </c>
+      <c r="AM172">
+        <v>1.5</v>
+      </c>
+      <c r="AN172">
+        <v>1.5</v>
+      </c>
+      <c r="AO172">
+        <v>0.88</v>
+      </c>
+      <c r="AP172">
+        <v>1.67</v>
+      </c>
+      <c r="AQ172">
+        <v>0.78</v>
+      </c>
+      <c r="AR172">
+        <v>1.75</v>
+      </c>
+      <c r="AS172">
+        <v>1.61</v>
+      </c>
+      <c r="AT172">
+        <v>3.36</v>
+      </c>
+      <c r="AU172">
+        <v>6</v>
+      </c>
+      <c r="AV172">
+        <v>4</v>
+      </c>
+      <c r="AW172">
+        <v>6</v>
+      </c>
+      <c r="AX172">
+        <v>1</v>
+      </c>
+      <c r="AY172">
+        <v>12</v>
+      </c>
+      <c r="AZ172">
+        <v>5</v>
+      </c>
+      <c r="BA172">
+        <v>3</v>
+      </c>
+      <c r="BB172">
+        <v>2</v>
+      </c>
+      <c r="BC172">
+        <v>5</v>
+      </c>
+      <c r="BD172">
+        <v>1.7</v>
+      </c>
+      <c r="BE172">
+        <v>6.5</v>
+      </c>
+      <c r="BF172">
+        <v>2.1</v>
+      </c>
+      <c r="BG172">
+        <v>1.29</v>
+      </c>
+      <c r="BH172">
+        <v>3.06</v>
+      </c>
+      <c r="BI172">
+        <v>1.57</v>
+      </c>
+      <c r="BJ172">
+        <v>2.22</v>
+      </c>
+      <c r="BK172">
+        <v>1.99</v>
+      </c>
+      <c r="BL172">
+        <v>1.75</v>
+      </c>
+      <c r="BM172">
+        <v>2.52</v>
+      </c>
+      <c r="BN172">
+        <v>1.51</v>
+      </c>
+      <c r="BO172">
+        <v>3.46</v>
+      </c>
+      <c r="BP172">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7841202</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45860.83333333334</v>
+      </c>
+      <c r="F173">
+        <v>18</v>
+      </c>
+      <c r="G173" t="s">
+        <v>80</v>
+      </c>
+      <c r="H173" t="s">
+        <v>76</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>2</v>
+      </c>
+      <c r="O173" t="s">
+        <v>169</v>
+      </c>
+      <c r="P173" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q173">
+        <v>2.11</v>
+      </c>
+      <c r="R173">
+        <v>1.98</v>
+      </c>
+      <c r="S173">
+        <v>7.42</v>
+      </c>
+      <c r="T173">
+        <v>1.54</v>
+      </c>
+      <c r="U173">
+        <v>2.4</v>
+      </c>
+      <c r="V173">
+        <v>3.4</v>
+      </c>
+      <c r="W173">
+        <v>1.32</v>
+      </c>
+      <c r="X173">
+        <v>9.75</v>
+      </c>
+      <c r="Y173">
+        <v>1</v>
+      </c>
+      <c r="Z173">
+        <v>1.45</v>
+      </c>
+      <c r="AA173">
+        <v>3.6</v>
+      </c>
+      <c r="AB173">
+        <v>6.6</v>
+      </c>
+      <c r="AC173">
+        <v>1.1</v>
+      </c>
+      <c r="AD173">
+        <v>6</v>
+      </c>
+      <c r="AE173">
+        <v>1.45</v>
+      </c>
+      <c r="AF173">
+        <v>2.44</v>
+      </c>
+      <c r="AG173">
+        <v>1.95</v>
+      </c>
+      <c r="AH173">
+        <v>1.75</v>
+      </c>
+      <c r="AI173">
+        <v>2.3</v>
+      </c>
+      <c r="AJ173">
+        <v>1.57</v>
+      </c>
+      <c r="AK173">
+        <v>1.12</v>
+      </c>
+      <c r="AL173">
+        <v>1.22</v>
+      </c>
+      <c r="AM173">
+        <v>2.2</v>
+      </c>
+      <c r="AN173">
+        <v>1.44</v>
+      </c>
+      <c r="AO173">
+        <v>0.67</v>
+      </c>
+      <c r="AP173">
+        <v>1.4</v>
+      </c>
+      <c r="AQ173">
+        <v>0.7</v>
+      </c>
+      <c r="AR173">
+        <v>1.9</v>
+      </c>
+      <c r="AS173">
+        <v>1.47</v>
+      </c>
+      <c r="AT173">
+        <v>3.37</v>
+      </c>
+      <c r="AU173">
+        <v>9</v>
+      </c>
+      <c r="AV173">
+        <v>4</v>
+      </c>
+      <c r="AW173">
+        <v>19</v>
+      </c>
+      <c r="AX173">
+        <v>5</v>
+      </c>
+      <c r="AY173">
+        <v>28</v>
+      </c>
+      <c r="AZ173">
+        <v>9</v>
+      </c>
+      <c r="BA173">
+        <v>11</v>
+      </c>
+      <c r="BB173">
+        <v>1</v>
+      </c>
+      <c r="BC173">
+        <v>12</v>
+      </c>
+      <c r="BD173">
+        <v>1.22</v>
+      </c>
+      <c r="BE173">
+        <v>11</v>
+      </c>
+      <c r="BF173">
+        <v>5.25</v>
+      </c>
+      <c r="BG173">
+        <v>1.19</v>
+      </c>
+      <c r="BH173">
+        <v>4.1</v>
+      </c>
+      <c r="BI173">
+        <v>1.41</v>
+      </c>
+      <c r="BJ173">
+        <v>2.65</v>
+      </c>
+      <c r="BK173">
+        <v>1.62</v>
+      </c>
+      <c r="BL173">
+        <v>2.1</v>
+      </c>
+      <c r="BM173">
+        <v>2</v>
+      </c>
+      <c r="BN173">
+        <v>1.76</v>
+      </c>
+      <c r="BO173">
+        <v>2.5</v>
+      </c>
+      <c r="BP173">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7841209</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45860.89583333334</v>
+      </c>
+      <c r="F174">
+        <v>18</v>
+      </c>
+      <c r="G174" t="s">
+        <v>87</v>
+      </c>
+      <c r="H174" t="s">
+        <v>73</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>2</v>
+      </c>
+      <c r="L174">
+        <v>1</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>2</v>
+      </c>
+      <c r="O174" t="s">
+        <v>199</v>
+      </c>
+      <c r="P174" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q174">
+        <v>3.25</v>
+      </c>
+      <c r="R174">
+        <v>1.76</v>
+      </c>
+      <c r="S174">
+        <v>3.8</v>
+      </c>
+      <c r="T174">
+        <v>1.64</v>
+      </c>
+      <c r="U174">
+        <v>2.4</v>
+      </c>
+      <c r="V174">
+        <v>3.75</v>
+      </c>
+      <c r="W174">
+        <v>1.22</v>
+      </c>
+      <c r="X174">
+        <v>10.5</v>
+      </c>
+      <c r="Y174">
+        <v>1.05</v>
+      </c>
+      <c r="Z174">
+        <v>2.13</v>
+      </c>
+      <c r="AA174">
+        <v>2.87</v>
+      </c>
+      <c r="AB174">
+        <v>3.33</v>
+      </c>
+      <c r="AC174">
+        <v>1.12</v>
+      </c>
+      <c r="AD174">
+        <v>5.5</v>
+      </c>
+      <c r="AE174">
+        <v>1.48</v>
+      </c>
+      <c r="AF174">
+        <v>2.4</v>
+      </c>
+      <c r="AG174">
+        <v>2.65</v>
+      </c>
+      <c r="AH174">
+        <v>1.42</v>
+      </c>
+      <c r="AI174">
+        <v>2.24</v>
+      </c>
+      <c r="AJ174">
+        <v>1.63</v>
+      </c>
+      <c r="AK174">
+        <v>1.35</v>
+      </c>
+      <c r="AL174">
+        <v>1.36</v>
+      </c>
+      <c r="AM174">
+        <v>1.53</v>
+      </c>
+      <c r="AN174">
+        <v>1.13</v>
+      </c>
+      <c r="AO174">
+        <v>1.56</v>
+      </c>
+      <c r="AP174">
+        <v>1.11</v>
+      </c>
+      <c r="AQ174">
+        <v>1.5</v>
+      </c>
+      <c r="AR174">
+        <v>1.7</v>
+      </c>
+      <c r="AS174">
+        <v>1.15</v>
+      </c>
+      <c r="AT174">
+        <v>2.85</v>
+      </c>
+      <c r="AU174">
+        <v>6</v>
+      </c>
+      <c r="AV174">
+        <v>7</v>
+      </c>
+      <c r="AW174">
+        <v>3</v>
+      </c>
+      <c r="AX174">
+        <v>1</v>
+      </c>
+      <c r="AY174">
+        <v>9</v>
+      </c>
+      <c r="AZ174">
+        <v>8</v>
+      </c>
+      <c r="BA174">
+        <v>5</v>
+      </c>
+      <c r="BB174">
+        <v>3</v>
+      </c>
+      <c r="BC174">
+        <v>8</v>
+      </c>
+      <c r="BD174">
+        <v>1.65</v>
+      </c>
+      <c r="BE174">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF174">
+        <v>2.94</v>
+      </c>
+      <c r="BG174">
+        <v>1.12</v>
+      </c>
+      <c r="BH174">
+        <v>3.7</v>
+      </c>
+      <c r="BI174">
+        <v>1.38</v>
+      </c>
+      <c r="BJ174">
+        <v>2.7</v>
+      </c>
+      <c r="BK174">
+        <v>1.74</v>
+      </c>
+      <c r="BL174">
+        <v>2.21</v>
+      </c>
+      <c r="BM174">
+        <v>1.92</v>
+      </c>
+      <c r="BN174">
+        <v>1.8</v>
+      </c>
+      <c r="BO174">
+        <v>2.55</v>
+      </c>
+      <c r="BP174">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7841203</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45860.89930555555</v>
+      </c>
+      <c r="F175">
+        <v>18</v>
+      </c>
+      <c r="G175" t="s">
+        <v>83</v>
+      </c>
+      <c r="H175" t="s">
+        <v>74</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>2</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>2</v>
+      </c>
+      <c r="O175" t="s">
+        <v>206</v>
+      </c>
+      <c r="P175" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q175">
+        <v>2.63</v>
+      </c>
+      <c r="R175">
+        <v>1.93</v>
+      </c>
+      <c r="S175">
+        <v>4</v>
+      </c>
+      <c r="T175">
+        <v>1.53</v>
+      </c>
+      <c r="U175">
+        <v>2.36</v>
+      </c>
+      <c r="V175">
+        <v>3.5</v>
+      </c>
+      <c r="W175">
+        <v>1.29</v>
+      </c>
+      <c r="X175">
+        <v>10</v>
+      </c>
+      <c r="Y175">
+        <v>1.05</v>
+      </c>
+      <c r="Z175">
+        <v>2.02</v>
+      </c>
+      <c r="AA175">
+        <v>2.83</v>
+      </c>
+      <c r="AB175">
+        <v>3.69</v>
+      </c>
+      <c r="AC175">
+        <v>1.05</v>
+      </c>
+      <c r="AD175">
+        <v>6.5</v>
+      </c>
+      <c r="AE175">
+        <v>1.5</v>
+      </c>
+      <c r="AF175">
+        <v>2.4</v>
+      </c>
+      <c r="AG175">
+        <v>2.3</v>
+      </c>
+      <c r="AH175">
+        <v>1.5</v>
+      </c>
+      <c r="AI175">
+        <v>2.37</v>
+      </c>
+      <c r="AJ175">
+        <v>1.66</v>
+      </c>
+      <c r="AK175">
+        <v>1.36</v>
+      </c>
+      <c r="AL175">
+        <v>1.34</v>
+      </c>
+      <c r="AM175">
+        <v>1.61</v>
+      </c>
+      <c r="AN175">
+        <v>2</v>
+      </c>
+      <c r="AO175">
+        <v>0.67</v>
+      </c>
+      <c r="AP175">
+        <v>2.11</v>
+      </c>
+      <c r="AQ175">
+        <v>0.6</v>
+      </c>
+      <c r="AR175">
+        <v>1.55</v>
+      </c>
+      <c r="AS175">
+        <v>1.76</v>
+      </c>
+      <c r="AT175">
+        <v>3.31</v>
+      </c>
+      <c r="AU175">
+        <v>7</v>
+      </c>
+      <c r="AV175">
+        <v>5</v>
+      </c>
+      <c r="AW175">
+        <v>7</v>
+      </c>
+      <c r="AX175">
+        <v>19</v>
+      </c>
+      <c r="AY175">
+        <v>14</v>
+      </c>
+      <c r="AZ175">
+        <v>24</v>
+      </c>
+      <c r="BA175">
+        <v>5</v>
+      </c>
+      <c r="BB175">
+        <v>7</v>
+      </c>
+      <c r="BC175">
+        <v>12</v>
+      </c>
+      <c r="BD175">
+        <v>1.84</v>
+      </c>
+      <c r="BE175">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF175">
+        <v>2.44</v>
+      </c>
+      <c r="BG175">
+        <v>1.2</v>
+      </c>
+      <c r="BH175">
+        <v>3.9</v>
+      </c>
+      <c r="BI175">
+        <v>1.27</v>
+      </c>
+      <c r="BJ175">
+        <v>3.14</v>
+      </c>
+      <c r="BK175">
+        <v>1.55</v>
+      </c>
+      <c r="BL175">
+        <v>2.18</v>
+      </c>
+      <c r="BM175">
+        <v>1.9</v>
+      </c>
+      <c r="BN175">
+        <v>1.77</v>
+      </c>
+      <c r="BO175">
+        <v>2.4</v>
+      </c>
+      <c r="BP175">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
